--- a/DND05S.xlsx
+++ b/DND05S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="658">
   <si>
     <t/>
   </si>
@@ -61,109 +61,451 @@
     <t>PT,(E-1B)</t>
   </si>
   <si>
+    <t>20099414</t>
+  </si>
+  <si>
+    <t>SOKLIN SOFT PRPL1.44</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20123338</t>
+  </si>
+  <si>
+    <t>RNSO+ML LIQ RS1.45KG</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20109454</t>
+  </si>
+  <si>
+    <t>SOKLIN CAIR SCRLT1.6</t>
+  </si>
+  <si>
+    <t>20099420</t>
+  </si>
+  <si>
+    <t>SOKLIN CAIR VIO 1.6L</t>
+  </si>
+  <si>
+    <t>20067585</t>
+  </si>
+  <si>
+    <t>SOKLN LIQ RED SB 700</t>
+  </si>
+  <si>
+    <t>20054747</t>
+  </si>
+  <si>
+    <t>SO KLIN VL/BLSOM 700</t>
+  </si>
+  <si>
+    <t>20046548</t>
+  </si>
+  <si>
+    <t>SOKLIN SOFT CAIR 700</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20137791</t>
+  </si>
+  <si>
+    <t>SO KLIN LIQ HJB 700</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20129837</t>
+  </si>
+  <si>
+    <t>LARIST SPR.GRD 750ML</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20037446</t>
+  </si>
+  <si>
+    <t>RNSO+ML LIQ ROSE 700</t>
+  </si>
+  <si>
+    <t>20138867</t>
+  </si>
+  <si>
+    <t>RNSO JAP PEACH 700G</t>
+  </si>
+  <si>
+    <t>PT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20141203</t>
+  </si>
+  <si>
+    <t>RINSO RYL GOLD 700G</t>
+  </si>
+  <si>
+    <t>20140001</t>
+  </si>
+  <si>
+    <t>RINSO PURE LIQ 510G</t>
+  </si>
+  <si>
+    <t>20133212</t>
+  </si>
+  <si>
+    <t>BOOM DET.CAIR RSE510</t>
+  </si>
+  <si>
+    <t>20133213</t>
+  </si>
+  <si>
+    <t>BOOM DET.CAIR LAV510</t>
+  </si>
+  <si>
+    <t>20134103</t>
+  </si>
+  <si>
+    <t>ATTACK GEL S.CNTA515</t>
+  </si>
+  <si>
+    <t>20138111</t>
+  </si>
+  <si>
+    <t>JAZ 1 ROSE BERY 515G</t>
+  </si>
+  <si>
+    <t>20131373</t>
+  </si>
+  <si>
+    <t>GENTLE GEN FR.PE 360</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20054750</t>
+  </si>
+  <si>
+    <t>RNSO+ML LIQ PRFM 510</t>
+  </si>
+  <si>
+    <t>20093188</t>
+  </si>
+  <si>
+    <t>RINSO MLTO GLD LQ510</t>
+  </si>
+  <si>
+    <t>20122879</t>
+  </si>
+  <si>
+    <t>RNSO MLTO KRN STR510</t>
+  </si>
+  <si>
+    <t>20104950</t>
+  </si>
+  <si>
+    <t>RINSO MLTO JP/PCH510</t>
+  </si>
+  <si>
+    <t>20137793</t>
+  </si>
+  <si>
+    <t>RINSO ROSE FRESH 510</t>
+  </si>
+  <si>
+    <t>20093627</t>
+  </si>
+  <si>
+    <t>SOKLN LIQ SAKURA 510</t>
+  </si>
+  <si>
+    <t>20123818</t>
+  </si>
+  <si>
+    <t>SOKLN LIQ LVNDR 510</t>
+  </si>
+  <si>
+    <t>20091870</t>
+  </si>
+  <si>
+    <t>SO KLN LIQ WH&amp;BR 510</t>
+  </si>
+  <si>
+    <t>20114428</t>
+  </si>
+  <si>
+    <t>SOKLN LIQ KOREAN 510</t>
+  </si>
+  <si>
+    <t>20141373</t>
+  </si>
+  <si>
+    <t>RINSO PW.CLN BTL 650</t>
+  </si>
+  <si>
+    <t>20141369</t>
+  </si>
+  <si>
+    <t>RINSO P.BRZE BTL 650</t>
+  </si>
+  <si>
+    <t>20131730</t>
+  </si>
+  <si>
+    <t>SYANG LIQ R/ROSE 700</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20132442</t>
+  </si>
+  <si>
+    <t>SYANG LIQ ORIGNAL700</t>
+  </si>
+  <si>
+    <t>20135849</t>
+  </si>
+  <si>
+    <t>LARIST SMR.BRZ 700ML</t>
+  </si>
+  <si>
+    <t>20139955</t>
+  </si>
+  <si>
+    <t>BU KRM JNHAE CB700ML</t>
+  </si>
+  <si>
+    <t>20113809</t>
+  </si>
+  <si>
+    <t>OXYKLIN DTRG LIQ 700</t>
+  </si>
+  <si>
+    <t>20123019</t>
+  </si>
+  <si>
+    <t>SAYANG LIQ ROSE 510</t>
+  </si>
+  <si>
+    <t>20120180</t>
+  </si>
+  <si>
+    <t>SO SOFT RS&amp;WTRLY 700</t>
+  </si>
+  <si>
+    <t>20121364</t>
+  </si>
+  <si>
+    <t>SO SOFT SKR BLSM 700</t>
+  </si>
+  <si>
+    <t>20135246</t>
+  </si>
+  <si>
+    <t>SO SOFT SWT PEONY700</t>
+  </si>
+  <si>
+    <t>20128720</t>
+  </si>
+  <si>
+    <t>SO SOFT FLO BRS 700</t>
+  </si>
+  <si>
+    <t>20140325</t>
+  </si>
+  <si>
+    <t>SO SOFT FLO LILY 700</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20141371</t>
+  </si>
+  <si>
+    <t>GNTLE GEN CMLLIA 700</t>
+  </si>
+  <si>
+    <t>20141372</t>
+  </si>
+  <si>
+    <t>GENTLE GEN LILAC 700</t>
+  </si>
+  <si>
+    <t>20135245</t>
+  </si>
+  <si>
+    <t>SO KLIN LIQ FRNCH700</t>
+  </si>
+  <si>
+    <t>20133798</t>
+  </si>
+  <si>
+    <t>SO KLIN LIQ EN.RS700</t>
+  </si>
+  <si>
+    <t>20139729</t>
+  </si>
+  <si>
+    <t>SOKLN GR.TEA&amp;JSM 700</t>
+  </si>
+  <si>
+    <t>20113567</t>
+  </si>
+  <si>
+    <t>GENTLE GEN MR.BRZ700</t>
+  </si>
+  <si>
+    <t>20115959</t>
+  </si>
+  <si>
+    <t>GENTLE GEN FR.PE 700</t>
+  </si>
+  <si>
+    <t>20115958</t>
+  </si>
+  <si>
+    <t>GENTLE GEN PRS.G 700</t>
+  </si>
+  <si>
+    <t>20133333</t>
+  </si>
+  <si>
+    <t>GENTLE GEN A/KRGT700</t>
+  </si>
+  <si>
     <t>20073805</t>
   </si>
   <si>
     <t>SOKLN RED/MG&amp;B1.44KG</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20123338</t>
-  </si>
-  <si>
-    <t>RNSO+ML LIQ RS1.45KG</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20109454</t>
-  </si>
-  <si>
-    <t>SOKLIN CAIR SCRLT1.6</t>
-  </si>
-  <si>
-    <t>20099420</t>
-  </si>
-  <si>
-    <t>SOKLIN CAIR VIO 1.6L</t>
-  </si>
-  <si>
-    <t>20067585</t>
-  </si>
-  <si>
-    <t>SOKLN LIQ RED SB 700</t>
-  </si>
-  <si>
-    <t>20054747</t>
-  </si>
-  <si>
-    <t>SO KLIN VL/BLSOM 700</t>
-  </si>
-  <si>
-    <t>20046548</t>
-  </si>
-  <si>
-    <t>SOKLIN SOFT CAIR 700</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20137791</t>
-  </si>
-  <si>
-    <t>SO KLIN LIQ HJB 700</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20131373</t>
-  </si>
-  <si>
-    <t>GENTLE GEN FR.PE 360</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20113809</t>
-  </si>
-  <si>
-    <t>OXYKLIN DTRG LIQ 700</t>
-  </si>
-  <si>
-    <t>20133212</t>
-  </si>
-  <si>
-    <t>BOOM DET.CAIR RSE510</t>
-  </si>
-  <si>
-    <t>20133213</t>
-  </si>
-  <si>
-    <t>BOOM DET.CAIR LAV510</t>
-  </si>
-  <si>
-    <t>20123019</t>
-  </si>
-  <si>
-    <t>SAYANG LIQ ROSE 510</t>
-  </si>
-  <si>
-    <t>20134103</t>
-  </si>
-  <si>
-    <t>ATTACK GEL S.CNTA515</t>
-  </si>
-  <si>
-    <t>20138111</t>
-  </si>
-  <si>
-    <t>JAZ 1 ROSE BERY 515G</t>
+    <t>20041483</t>
+  </si>
+  <si>
+    <t>SO/KLN SOFT P/RS1.44</t>
+  </si>
+  <si>
+    <t>20140806</t>
+  </si>
+  <si>
+    <t>SO KLN EDP D.LS 144</t>
+  </si>
+  <si>
+    <t>20140804</t>
+  </si>
+  <si>
+    <t>SO KLN EDP BLNC 1.44</t>
+  </si>
+  <si>
+    <t>20091352</t>
+  </si>
+  <si>
+    <t>DAIA+SOFT VIOLET 1.5</t>
+  </si>
+  <si>
+    <t>20052321</t>
+  </si>
+  <si>
+    <t>DAIA+SOFT PINK 1.5KG</t>
+  </si>
+  <si>
+    <t>20030446</t>
+  </si>
+  <si>
+    <t>DAIA PUTIH 1.5KG</t>
+  </si>
+  <si>
+    <t>20121050</t>
+  </si>
+  <si>
+    <t>DAIA HIJAB C&amp;F 1.5G</t>
+  </si>
+  <si>
+    <t>10014547</t>
+  </si>
+  <si>
+    <t>DAIA DTRG.BBK BGA1.5</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20053796</t>
+  </si>
+  <si>
+    <t>SOKLN SOFTG PRPL 720</t>
+  </si>
+  <si>
+    <t>20073499</t>
+  </si>
+  <si>
+    <t>SO KLN MGNL&amp;BRY 720G</t>
+  </si>
+  <si>
+    <t>20012188</t>
+  </si>
+  <si>
+    <t>SOKLN SOFTR ROSY 720</t>
+  </si>
+  <si>
+    <t>20119238</t>
+  </si>
+  <si>
+    <t>TOTAL DET.PERFUME750</t>
+  </si>
+  <si>
+    <t>20061748</t>
+  </si>
+  <si>
+    <t>DAIA DET+SFT VLT 800</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20036047</t>
+  </si>
+  <si>
+    <t>DAIA DET+SOFT  800G</t>
+  </si>
+  <si>
+    <t>20012007</t>
+  </si>
+  <si>
+    <t>DAIA DET.BBK PTH 800</t>
+  </si>
+  <si>
+    <t>10005245</t>
+  </si>
+  <si>
+    <t>DAIA BBK FLORAL 800G</t>
+  </si>
+  <si>
+    <t>20074992</t>
+  </si>
+  <si>
+    <t>BUKRIM OXY/K VIOL700</t>
+  </si>
+  <si>
+    <t>20090425</t>
+  </si>
+  <si>
+    <t>IDM SOFT DET BTK 450</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
   </si>
   <si>
     <t>20097739</t>
@@ -172,354 +514,12 @@
     <t>IDM DET.CAIR PCH 700</t>
   </si>
   <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20129837</t>
-  </si>
-  <si>
-    <t>LARIST SPR.GRD 750ML</t>
-  </si>
-  <si>
-    <t>20090425</t>
-  </si>
-  <si>
-    <t>IDM SOFT DET BTK 450</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20054750</t>
-  </si>
-  <si>
-    <t>RNSO+ML LIQ PRFM 510</t>
-  </si>
-  <si>
-    <t>20093188</t>
-  </si>
-  <si>
-    <t>RINSO MLTO GLD LQ510</t>
-  </si>
-  <si>
-    <t>20122879</t>
-  </si>
-  <si>
-    <t>RNSO MLTO KRN STR510</t>
-  </si>
-  <si>
-    <t>20104950</t>
-  </si>
-  <si>
-    <t>RINSO MLTO JP/PCH510</t>
-  </si>
-  <si>
-    <t>20137793</t>
-  </si>
-  <si>
-    <t>RINSO ROSE FRESH 510</t>
-  </si>
-  <si>
-    <t>20093627</t>
-  </si>
-  <si>
-    <t>SOKLN LIQ SAKURA 510</t>
-  </si>
-  <si>
-    <t>20123818</t>
-  </si>
-  <si>
-    <t>SOKLN LIQ LVNDR 510</t>
-  </si>
-  <si>
-    <t>20091870</t>
-  </si>
-  <si>
-    <t>SO KLN LIQ WH&amp;BR 510</t>
-  </si>
-  <si>
-    <t>20114428</t>
-  </si>
-  <si>
-    <t>SOKLN LIQ KOREAN 510</t>
-  </si>
-  <si>
-    <t>20131730</t>
-  </si>
-  <si>
-    <t>SYANG LIQ R/ROSE 700</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20132442</t>
-  </si>
-  <si>
-    <t>SYANG LIQ ORIGNAL700</t>
-  </si>
-  <si>
-    <t>20135849</t>
-  </si>
-  <si>
-    <t>LARIST SMR.BRZ 700ML</t>
-  </si>
-  <si>
-    <t>20139955</t>
-  </si>
-  <si>
-    <t>BU KRM JNHAE CB700ML</t>
-  </si>
-  <si>
-    <t>20037446</t>
-  </si>
-  <si>
-    <t>RNSO+ML LIQ ROSE 700</t>
-  </si>
-  <si>
-    <t>20138867</t>
-  </si>
-  <si>
-    <t>RNSO JAP PEACH 700G</t>
-  </si>
-  <si>
-    <t>PT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20141203</t>
-  </si>
-  <si>
-    <t>RINSO RYL GOLD 700G</t>
-  </si>
-  <si>
-    <t>20140001</t>
-  </si>
-  <si>
-    <t>RINSO PURE LIQ 510G</t>
-  </si>
-  <si>
-    <t>20120180</t>
-  </si>
-  <si>
-    <t>SO SOFT RS&amp;WTRLY 700</t>
-  </si>
-  <si>
-    <t>20121364</t>
-  </si>
-  <si>
-    <t>SO SOFT SKR BLSM 700</t>
-  </si>
-  <si>
-    <t>20135246</t>
-  </si>
-  <si>
-    <t>SO SOFT SWT PEONY700</t>
-  </si>
-  <si>
-    <t>20128720</t>
-  </si>
-  <si>
-    <t>SO SOFT FLO BRS 700</t>
-  </si>
-  <si>
-    <t>20140325</t>
-  </si>
-  <si>
-    <t>SO SOFT FLO LILY 700</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20141373</t>
-  </si>
-  <si>
-    <t>RINSO PW.CLN BTL 650</t>
-  </si>
-  <si>
-    <t>20141369</t>
-  </si>
-  <si>
-    <t>RINSO P.BRZE BTL 650</t>
-  </si>
-  <si>
-    <t>20141372</t>
-  </si>
-  <si>
-    <t>GENTLE GEN LILAC 700</t>
-  </si>
-  <si>
-    <t>20135245</t>
-  </si>
-  <si>
-    <t>SO KLIN LIQ FRNCH700</t>
-  </si>
-  <si>
-    <t>20133798</t>
-  </si>
-  <si>
-    <t>SO KLIN LIQ EN.RS700</t>
-  </si>
-  <si>
-    <t>20139729</t>
-  </si>
-  <si>
-    <t>SOKLN GR.TEA&amp;JSM 700</t>
-  </si>
-  <si>
-    <t>20113567</t>
-  </si>
-  <si>
-    <t>GENTLE GEN MR.BRZ700</t>
-  </si>
-  <si>
-    <t>20115959</t>
-  </si>
-  <si>
-    <t>GENTLE GEN FR.PE 700</t>
-  </si>
-  <si>
-    <t>20115958</t>
-  </si>
-  <si>
-    <t>GENTLE GEN PRS.G 700</t>
-  </si>
-  <si>
-    <t>20133333</t>
-  </si>
-  <si>
-    <t>GENTLE GEN A/KRGT700</t>
-  </si>
-  <si>
-    <t>20141371</t>
-  </si>
-  <si>
-    <t>GNTLE GEN CMLLIA 700</t>
-  </si>
-  <si>
-    <t>20099414</t>
-  </si>
-  <si>
-    <t>SOKLIN SOFT PRPL1.44</t>
-  </si>
-  <si>
-    <t>20041483</t>
-  </si>
-  <si>
-    <t>SO/KLN SOFT P/RS1.44</t>
-  </si>
-  <si>
-    <t>20140806</t>
-  </si>
-  <si>
-    <t>SO KLN EDP D.LS 144</t>
-  </si>
-  <si>
-    <t>20140804</t>
-  </si>
-  <si>
-    <t>SO KLN EDP BLNC 1.44</t>
-  </si>
-  <si>
-    <t>20052321</t>
-  </si>
-  <si>
-    <t>DAIA+SOFT PINK 1.5KG</t>
-  </si>
-  <si>
-    <t>20091352</t>
-  </si>
-  <si>
-    <t>DAIA+SOFT VIOLET 1.5</t>
-  </si>
-  <si>
-    <t>20030446</t>
-  </si>
-  <si>
-    <t>DAIA PUTIH 1.5KG</t>
-  </si>
-  <si>
-    <t>20121050</t>
-  </si>
-  <si>
-    <t>DAIA HIJAB C&amp;F 1.5G</t>
-  </si>
-  <si>
-    <t>10014547</t>
-  </si>
-  <si>
-    <t>DAIA DTRG.BBK BGA1.5</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20053796</t>
-  </si>
-  <si>
-    <t>SOKLN SOFTG PRPL 720</t>
-  </si>
-  <si>
-    <t>20073499</t>
-  </si>
-  <si>
-    <t>SO KLN MGNL&amp;BRY 720G</t>
-  </si>
-  <si>
-    <t>20012188</t>
-  </si>
-  <si>
-    <t>SOKLN SOFTR ROSY 720</t>
-  </si>
-  <si>
-    <t>20119238</t>
-  </si>
-  <si>
-    <t>TOTAL DET.PERFUME750</t>
-  </si>
-  <si>
-    <t>20061748</t>
-  </si>
-  <si>
-    <t>DAIA DET+SFT VLT 800</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20036047</t>
-  </si>
-  <si>
-    <t>DAIA DET+SOFT  800G</t>
-  </si>
-  <si>
-    <t>20012007</t>
-  </si>
-  <si>
-    <t>DAIA DET.BBK PTH 800</t>
-  </si>
-  <si>
-    <t>10005245</t>
-  </si>
-  <si>
-    <t>DAIA BBK FLORAL 800G</t>
-  </si>
-  <si>
-    <t>20074992</t>
-  </si>
-  <si>
-    <t>BUKRIM OXY/K VIOL700</t>
-  </si>
-  <si>
     <t>20067586</t>
   </si>
   <si>
     <t>SOKLIN LIQ.BM TOP700</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>20054610</t>
   </si>
   <si>
@@ -544,202 +544,1432 @@
     <t>SAYANG PWDR ROSE 770</t>
   </si>
   <si>
+    <t>20081448</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT H.SM 650</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20081449</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT P.DW 650</t>
+  </si>
+  <si>
+    <t>20104951</t>
+  </si>
+  <si>
+    <t>ROYALE HJB BLCK.V650</t>
+  </si>
+  <si>
+    <t>20091457</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT BS 650</t>
+  </si>
+  <si>
+    <t>20098312</t>
+  </si>
+  <si>
+    <t>ROYALE PINK STN 650</t>
+  </si>
+  <si>
+    <t>20113101</t>
+  </si>
+  <si>
+    <t>ROYALE SWT FLORL 680</t>
+  </si>
+  <si>
+    <t>20128706</t>
+  </si>
+  <si>
+    <t>ROYALE LNVDR VNL 680</t>
+  </si>
+  <si>
+    <t>20113093</t>
+  </si>
+  <si>
+    <t>ROYALE SUNNY DAY 680</t>
+  </si>
+  <si>
+    <t>20126740</t>
+  </si>
+  <si>
+    <t>MOLTO FRSH.CSBLCA650</t>
+  </si>
+  <si>
+    <t>20094735</t>
+  </si>
+  <si>
+    <t>DOWNY SUNRISE 950</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>PT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20094733</t>
+  </si>
+  <si>
+    <t>DOWNY MYSTIQUE 850</t>
+  </si>
+  <si>
+    <t>20140221</t>
+  </si>
+  <si>
+    <t>DOWNY PASSION 950ML</t>
+  </si>
+  <si>
+    <t>20074226</t>
+  </si>
+  <si>
+    <t>DOWNY SUN.FRSH 600</t>
+  </si>
+  <si>
+    <t>20080360</t>
+  </si>
+  <si>
+    <t>DOWNY MYSTIQUE 600ML</t>
+  </si>
+  <si>
+    <t>20080361</t>
+  </si>
+  <si>
+    <t>DOWNY PASSION 600ML</t>
+  </si>
+  <si>
+    <t>20139145</t>
+  </si>
+  <si>
+    <t>DOWNY MLKY TOUCH 500</t>
+  </si>
+  <si>
+    <t>20141324</t>
+  </si>
+  <si>
+    <t>DOWNY SUNSHINE 500ML</t>
+  </si>
+  <si>
+    <t>20141323</t>
+  </si>
+  <si>
+    <t>DOWNY MIDNIGHT 500ML</t>
+  </si>
+  <si>
+    <t>20140003</t>
+  </si>
+  <si>
+    <t>RNSO PWD ROSE.F 1.44</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20093521</t>
+  </si>
+  <si>
+    <t>RINSO+MOLTO ESC1440G</t>
+  </si>
+  <si>
+    <t>20139609</t>
+  </si>
+  <si>
+    <t>RNSO JPN PEAC 1440G</t>
+  </si>
+  <si>
+    <t>20140002</t>
+  </si>
+  <si>
+    <t>RINSO PWD PURE 1440G</t>
+  </si>
+  <si>
+    <t>20064413</t>
+  </si>
+  <si>
+    <t>ATCK JAZ1 S/CNTA 1.5</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20064414</t>
+  </si>
+  <si>
+    <t>ATTACK JAZ1 P/SGR1.5</t>
+  </si>
+  <si>
+    <t>20130527</t>
+  </si>
+  <si>
+    <t>ATTACK DET+SF RB 1.4</t>
+  </si>
+  <si>
+    <t>20138108</t>
+  </si>
+  <si>
+    <t>JAZ 1 PRPL BLS 1.4KG</t>
+  </si>
+  <si>
+    <t>20071827</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD ROSE 700</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20085113</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD PRFM 700</t>
+  </si>
+  <si>
+    <t>20123256</t>
+  </si>
+  <si>
+    <t>RINSO+MLT KRN STW700</t>
+  </si>
+  <si>
+    <t>20105968</t>
+  </si>
+  <si>
+    <t>RNSO PWD JPN PC 700G</t>
+  </si>
+  <si>
     <t>20131516</t>
   </si>
   <si>
     <t>LARIST DET.FRS BT450</t>
   </si>
   <si>
-    <t>20081448</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT H.SM 650</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20081449</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT P.DW 650</t>
-  </si>
-  <si>
-    <t>20104951</t>
-  </si>
-  <si>
-    <t>ROYALE HJB BLCK.V650</t>
-  </si>
-  <si>
-    <t>20091457</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT BS 650</t>
-  </si>
-  <si>
-    <t>20098312</t>
-  </si>
-  <si>
-    <t>ROYALE PINK STN 650</t>
-  </si>
-  <si>
-    <t>20113101</t>
-  </si>
-  <si>
-    <t>ROYALE SWT FLORL 680</t>
-  </si>
-  <si>
-    <t>20128706</t>
-  </si>
-  <si>
-    <t>ROYALE LNVDR VNL 680</t>
-  </si>
-  <si>
-    <t>20113093</t>
-  </si>
-  <si>
-    <t>ROYALE SUNNY DAY 680</t>
-  </si>
-  <si>
-    <t>20126740</t>
-  </si>
-  <si>
-    <t>MOLTO FRSH.CSBLCA650</t>
-  </si>
-  <si>
-    <t>20094735</t>
-  </si>
-  <si>
-    <t>DOWNY SUNRISE 950</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>PT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20094733</t>
-  </si>
-  <si>
-    <t>DOWNY MYSTIQUE 850</t>
-  </si>
-  <si>
-    <t>20140221</t>
-  </si>
-  <si>
-    <t>DOWNY PASSION 950ML</t>
-  </si>
-  <si>
-    <t>20074226</t>
-  </si>
-  <si>
-    <t>DOWNY SUN.FRSH 600</t>
-  </si>
-  <si>
-    <t>20080360</t>
-  </si>
-  <si>
-    <t>DOWNY MYSTIQUE 600ML</t>
-  </si>
-  <si>
-    <t>20080361</t>
-  </si>
-  <si>
-    <t>DOWNY PASSION 600ML</t>
-  </si>
-  <si>
-    <t>20139145</t>
-  </si>
-  <si>
-    <t>DOWNY MLKY TOUCH 500</t>
-  </si>
-  <si>
-    <t>20141324</t>
-  </si>
-  <si>
-    <t>DOWNY SUNSHINE 500ML</t>
-  </si>
-  <si>
-    <t>20141323</t>
-  </si>
-  <si>
-    <t>DOWNY MIDNIGHT 500ML</t>
-  </si>
-  <si>
-    <t>20140003</t>
-  </si>
-  <si>
-    <t>RNSO PWD ROSE.F 1.44</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20093521</t>
-  </si>
-  <si>
-    <t>RINSO+MOLTO ESC1440G</t>
-  </si>
-  <si>
-    <t>20139609</t>
-  </si>
-  <si>
-    <t>RNSO JPN PEAC 1440G</t>
-  </si>
-  <si>
-    <t>20140002</t>
-  </si>
-  <si>
-    <t>RINSO PWD PURE 1440G</t>
-  </si>
-  <si>
-    <t>20064413</t>
-  </si>
-  <si>
-    <t>ATCK JAZ1 S/CNTA 1.5</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20064414</t>
-  </si>
-  <si>
-    <t>ATTACK JAZ1 P/SGR1.5</t>
-  </si>
-  <si>
-    <t>20130527</t>
-  </si>
-  <si>
-    <t>ATTACK DET+SF RB 1.4</t>
-  </si>
-  <si>
-    <t>20138108</t>
-  </si>
-  <si>
-    <t>JAZ 1 PRPL BLS 1.4KG</t>
-  </si>
-  <si>
-    <t>20071827</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD ROSE 700</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20085113</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD PRFM 700</t>
-  </si>
-  <si>
-    <t>20123256</t>
-  </si>
-  <si>
-    <t>RINSO+MLT KRN STW700</t>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20113183</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD ROSE 380</t>
+  </si>
+  <si>
+    <t>20121372</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD PRFM 380</t>
+  </si>
+  <si>
+    <t>20128719</t>
+  </si>
+  <si>
+    <t>SOKLIN LVD&amp;LILY 425G</t>
+  </si>
+  <si>
+    <t>20042466</t>
+  </si>
+  <si>
+    <t>DAIA DET+SOFT 470G</t>
+  </si>
+  <si>
+    <t>20139595</t>
+  </si>
+  <si>
+    <t>MOLTO TRKA BDD 3X300</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20133398</t>
+  </si>
+  <si>
+    <t>TRKA PURE 300ML</t>
+  </si>
+  <si>
+    <t>10011440</t>
+  </si>
+  <si>
+    <t>RAPIKA LVDR SPLAS300</t>
+  </si>
+  <si>
+    <t>20084780</t>
+  </si>
+  <si>
+    <t>RAPIKA GOLD 250ML</t>
+  </si>
+  <si>
+    <t>20093193</t>
+  </si>
+  <si>
+    <t>RAPIKA PINK SKR 300</t>
+  </si>
+  <si>
+    <t>20138071</t>
+  </si>
+  <si>
+    <t>KISPRAY KASTURI 280</t>
+  </si>
+  <si>
+    <t>20074721</t>
+  </si>
+  <si>
+    <t>KISPRAY GLM.GOLD 280</t>
+  </si>
+  <si>
+    <t>20116685</t>
+  </si>
+  <si>
+    <t>KISPRAY ELG.SAPH 200</t>
+  </si>
+  <si>
+    <t>20032250</t>
+  </si>
+  <si>
+    <t>KISPRAY VIOLET PC280</t>
+  </si>
+  <si>
+    <t>20000980</t>
+  </si>
+  <si>
+    <t>KISPRAY VIOLET 318ML</t>
+  </si>
+  <si>
+    <t>20138470</t>
+  </si>
+  <si>
+    <t>SO KLN PWNG RED 1.7L</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>10005803</t>
+  </si>
+  <si>
+    <t>SOKLIN PWNGI RED 780</t>
+  </si>
+  <si>
+    <t>10007389</t>
+  </si>
+  <si>
+    <t>SOKLIN PWNGI PINK780</t>
+  </si>
+  <si>
+    <t>10008104</t>
+  </si>
+  <si>
+    <t>SO KLIN PWG BLUE 780</t>
+  </si>
+  <si>
+    <t>20108418</t>
+  </si>
+  <si>
+    <t>SOKLIN PWG HJB GR780</t>
+  </si>
+  <si>
+    <t>10005802</t>
+  </si>
+  <si>
+    <t>SOKLIN PEWANGI VL780</t>
+  </si>
+  <si>
+    <t>20134526</t>
+  </si>
+  <si>
+    <t>SOKLIN PWG COT.FN780</t>
+  </si>
+  <si>
+    <t>20125391</t>
+  </si>
+  <si>
+    <t>SOKLIN PWG AC/SPT780</t>
+  </si>
+  <si>
+    <t>20129370</t>
+  </si>
+  <si>
+    <t>MOLTO MORNING FRS550</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20129160</t>
+  </si>
+  <si>
+    <t>MOLTO LUXURY PRF 650</t>
+  </si>
+  <si>
+    <t>20128919</t>
+  </si>
+  <si>
+    <t>MOLTO SFTNR PURE 550</t>
+  </si>
+  <si>
+    <t>20087464</t>
+  </si>
+  <si>
+    <t>IDM PWNG PINK.PAS720</t>
+  </si>
+  <si>
+    <t>20137582</t>
+  </si>
+  <si>
+    <t>IDM PWNG ROM.AURA720</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20137581</t>
+  </si>
+  <si>
+    <t>IDM PWNG EXO.BLUE720</t>
+  </si>
+  <si>
+    <t>20020245</t>
+  </si>
+  <si>
+    <t>MOLTO PWNGI BLUE 765</t>
+  </si>
+  <si>
+    <t>20020226</t>
+  </si>
+  <si>
+    <t>MOLTO PWNGI PINK 765</t>
+  </si>
+  <si>
+    <t>20106821</t>
+  </si>
+  <si>
+    <t>MOLTO PURPLE 765ML</t>
+  </si>
+  <si>
+    <t>20135847</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT SUMMR600</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20135846</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT SPRNG600</t>
+  </si>
+  <si>
+    <t>20014403</t>
+  </si>
+  <si>
+    <t>BAYCLIN REGLR 1000ML</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>20082581</t>
+  </si>
+  <si>
+    <t>VANISH CAIR WHT 425</t>
+  </si>
+  <si>
+    <t>20052662</t>
+  </si>
+  <si>
+    <t>VANISH CAIR PCH 425</t>
+  </si>
+  <si>
+    <t>20089665</t>
+  </si>
+  <si>
+    <t>IDM PHLANG NODA 450</t>
+  </si>
+  <si>
+    <t>20079788</t>
+  </si>
+  <si>
+    <t>PROCLIN PCH 400ML</t>
+  </si>
+  <si>
+    <t>10025646</t>
+  </si>
+  <si>
+    <t>YURI TAF LMN&amp;LIME500</t>
+  </si>
+  <si>
+    <t>10014263</t>
+  </si>
+  <si>
+    <t>WIPOL KARBOL CMR 720</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>20001645</t>
+  </si>
+  <si>
+    <t>WIPOL KARBOL LMN 720</t>
+  </si>
+  <si>
+    <t>20090066</t>
+  </si>
+  <si>
+    <t>WIPOL SRH + JRK 720</t>
+  </si>
+  <si>
+    <t>20122478</t>
+  </si>
+  <si>
+    <t>WIPOL CITRUS FRS 390</t>
+  </si>
+  <si>
+    <t>20023111</t>
+  </si>
+  <si>
+    <t>SOS KARBOL CLS PN725</t>
+  </si>
+  <si>
+    <t>10013107</t>
+  </si>
+  <si>
+    <t>SUPERSOL PINE 750ML</t>
+  </si>
+  <si>
+    <t>20104030</t>
+  </si>
+  <si>
+    <t>SUPER SOL SEREH 750</t>
+  </si>
+  <si>
+    <t>20132664</t>
+  </si>
+  <si>
+    <t>VIXAL KUAT SEGAR 600</t>
+  </si>
+  <si>
+    <t>10004612</t>
+  </si>
+  <si>
+    <t>SOS P.LNT ORANGE 700</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10004610</t>
+  </si>
+  <si>
+    <t>SOS P/LT APLL REF700</t>
+  </si>
+  <si>
+    <t>10010480</t>
+  </si>
+  <si>
+    <t>SPR PELL FRS.APEL760</t>
+  </si>
+  <si>
+    <t>20121373</t>
+  </si>
+  <si>
+    <t>SPR PELL AB CTRS 500</t>
+  </si>
+  <si>
+    <t>20137408</t>
+  </si>
+  <si>
+    <t>SPR PELL SAKURA 740</t>
+  </si>
+  <si>
+    <t>20001407</t>
+  </si>
+  <si>
+    <t>IDM P'LANTAI LAV 800</t>
+  </si>
+  <si>
+    <t>20001402</t>
+  </si>
+  <si>
+    <t>IDM P'LANTAI APL 800</t>
+  </si>
+  <si>
+    <t>20028779</t>
+  </si>
+  <si>
+    <t>IDM KRBOL WNG650(BR)</t>
+  </si>
+  <si>
+    <t>20089486</t>
+  </si>
+  <si>
+    <t>IDM KRBL SRH CTR 650</t>
+  </si>
+  <si>
+    <t>20128125</t>
+  </si>
+  <si>
+    <t>IDM PURPOSE CLN 375</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>20027963</t>
+  </si>
+  <si>
+    <t>IDM PMBERSH KACA 400</t>
+  </si>
+  <si>
+    <t>10003706</t>
+  </si>
+  <si>
+    <t>MR.MUSCLE ORGNL 400</t>
+  </si>
+  <si>
+    <t>10012548</t>
+  </si>
+  <si>
+    <t>SOKLIN RLX/LAV RF770</t>
+  </si>
+  <si>
+    <t>10003646</t>
+  </si>
+  <si>
+    <t>SO KLIN P/L APPLE770</t>
+  </si>
+  <si>
+    <t>10003645</t>
+  </si>
+  <si>
+    <t>SO KLIN P/L LMN 780</t>
+  </si>
+  <si>
+    <t>20101095</t>
+  </si>
+  <si>
+    <t>SO KLN LNT SEREH 770</t>
+  </si>
+  <si>
+    <t>20131223</t>
+  </si>
+  <si>
+    <t>SO KLN LNT CT.GRD700</t>
+  </si>
+  <si>
+    <t>20131788</t>
+  </si>
+  <si>
+    <t>MAMA LMN JR.NPS 950</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>20136124</t>
+  </si>
+  <si>
+    <t>EKNOMI LIQ N&amp;JN 675G</t>
+  </si>
+  <si>
+    <t>20092331</t>
+  </si>
+  <si>
+    <t>EKONOMI LIQ JR.NP650</t>
+  </si>
+  <si>
+    <t>20123812</t>
+  </si>
+  <si>
+    <t>EKONOMI LQ.SEREH 650</t>
+  </si>
+  <si>
+    <t>20107240</t>
+  </si>
+  <si>
+    <t>EKONOMI LIQ.SW&amp;JR650</t>
+  </si>
+  <si>
+    <t>20129722</t>
+  </si>
+  <si>
+    <t>BUKRIM LIQ.JRK NP550</t>
+  </si>
+  <si>
+    <t>20138518</t>
+  </si>
+  <si>
+    <t>KILAU NIPIS 630ML</t>
+  </si>
+  <si>
+    <t>20034450</t>
+  </si>
+  <si>
+    <t>MAMA/L JERUK NPS 690</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>10004067</t>
+  </si>
+  <si>
+    <t>MAMA/L PCH LEMON 690</t>
+  </si>
+  <si>
+    <t>20099424</t>
+  </si>
+  <si>
+    <t>MAMA LIME CHARCO 690</t>
+  </si>
+  <si>
+    <t>20052031</t>
+  </si>
+  <si>
+    <t>MAMA LIME GRN TEA690</t>
+  </si>
+  <si>
+    <t>10004068</t>
+  </si>
+  <si>
+    <t>MAMA LIME POUCH 690</t>
+  </si>
+  <si>
+    <t>20134303</t>
+  </si>
+  <si>
+    <t>MAMA/L REF YUZU 690</t>
+  </si>
+  <si>
+    <t>20137792</t>
+  </si>
+  <si>
+    <t>MAMA LIME GREEN 690</t>
+  </si>
+  <si>
+    <t>20034449</t>
+  </si>
+  <si>
+    <t>MAMA/L JERUK NPS 430</t>
+  </si>
+  <si>
+    <t>20090067</t>
+  </si>
+  <si>
+    <t>SNLGHT MINT A.BAU600</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>20086172</t>
+  </si>
+  <si>
+    <t>SNLIGHT MND.ORGE 600</t>
+  </si>
+  <si>
+    <t>20112492</t>
+  </si>
+  <si>
+    <t>SUNLIGHT JRK NPS400G</t>
+  </si>
+  <si>
+    <t>20128374</t>
+  </si>
+  <si>
+    <t>LFEBUOY REF LIME 650</t>
+  </si>
+  <si>
+    <t>20134576</t>
+  </si>
+  <si>
+    <t>LFEBUOY REF LEMON650</t>
+  </si>
+  <si>
+    <t>20073425</t>
+  </si>
+  <si>
+    <t>IDM P.PRNG JRK.N 650</t>
+  </si>
+  <si>
+    <t>20141204</t>
+  </si>
+  <si>
+    <t>IDM P.PRG JR.NPS 950</t>
+  </si>
+  <si>
+    <t>20112491</t>
+  </si>
+  <si>
+    <t>SNLIGHT LIME PCH 910</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>20139728</t>
+  </si>
+  <si>
+    <t>SNLGHT BIO BLBR 870G</t>
+  </si>
+  <si>
+    <t>10005482</t>
+  </si>
+  <si>
+    <t>SNLIGHT LIME PCH 660</t>
+  </si>
+  <si>
+    <t>20135144</t>
+  </si>
+  <si>
+    <t>SNLGHT BIO NATURE600</t>
+  </si>
+  <si>
+    <t>10013205</t>
+  </si>
+  <si>
+    <t>SUNLIGHT J/NIPIS.750</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>20139947</t>
+  </si>
+  <si>
+    <t>SNLGHT BIO BLBR 675G</t>
+  </si>
+  <si>
+    <t>20139948</t>
+  </si>
+  <si>
+    <t>SNLGHT BERY&amp;LIME 675</t>
+  </si>
+  <si>
+    <t>20135845</t>
+  </si>
+  <si>
+    <t>EKNOMI LIQ JR&amp;LMN650</t>
+  </si>
+  <si>
+    <t>20093919</t>
+  </si>
+  <si>
+    <t>IDM PURPOSE CLN 400</t>
+  </si>
+  <si>
+    <t>10003498</t>
+  </si>
+  <si>
+    <t>CLEAR PUMP ORIGNL500</t>
+  </si>
+  <si>
+    <t>10034652</t>
+  </si>
+  <si>
+    <t>GLADE OCEAN ESCP 350</t>
+  </si>
+  <si>
+    <t>20105576</t>
+  </si>
+  <si>
+    <t>STELLA A/F SAKURA350</t>
+  </si>
+  <si>
+    <t>10029632</t>
+  </si>
+  <si>
+    <t>STELLA ALAT MATIC</t>
+  </si>
+  <si>
+    <t>10004032</t>
+  </si>
+  <si>
+    <t>VIXAL KUAT HARUM 720</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>10004034</t>
+  </si>
+  <si>
+    <t>VIXAL KMR MD KUAT720</t>
+  </si>
+  <si>
+    <t>10003359</t>
+  </si>
+  <si>
+    <t>WIPOL CEMARA BTL 730</t>
+  </si>
+  <si>
+    <t>10000955</t>
+  </si>
+  <si>
+    <t>PORSTEX N.PARFUM 1L</t>
+  </si>
+  <si>
+    <t>10018962</t>
+  </si>
+  <si>
+    <t>YURI PORSTEX OB.B700</t>
+  </si>
+  <si>
+    <t>10005246</t>
+  </si>
+  <si>
+    <t>WING PRCLN CLN BR750</t>
+  </si>
+  <si>
+    <t>20040315</t>
+  </si>
+  <si>
+    <t>IDM PORSELEN BTL 800</t>
+  </si>
+  <si>
+    <t>20015040</t>
+  </si>
+  <si>
+    <t>HARPIC TRIPLE ACT450</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20095746</t>
+  </si>
+  <si>
+    <t>HRPC PNG.KRK CTR 405</t>
+  </si>
+  <si>
+    <t>20042956</t>
+  </si>
+  <si>
+    <t>HARPIC PWR PLS CT450</t>
+  </si>
+  <si>
+    <t>10010232</t>
+  </si>
+  <si>
+    <t>KIWI LIQ.SHOE BLCK75</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>10007934</t>
+  </si>
+  <si>
+    <t>KIWI PASTE BLACK 45M</t>
+  </si>
+  <si>
+    <t>20012183</t>
+  </si>
+  <si>
+    <t>BAYGON BKR D.DRH 5'S</t>
+  </si>
+  <si>
+    <t>20014401</t>
+  </si>
+  <si>
+    <t>BYGON BKR JMB LVD 5S</t>
+  </si>
+  <si>
+    <t>20128711</t>
+  </si>
+  <si>
+    <t>AUTAN LOT.JRK&amp;LMN 50</t>
+  </si>
+  <si>
+    <t>20106983</t>
+  </si>
+  <si>
+    <t>AUTAN LOT.SAKURA 50</t>
+  </si>
+  <si>
+    <t>20054250</t>
+  </si>
+  <si>
+    <t>AUTAN REFRESH/S 100</t>
+  </si>
+  <si>
+    <t>20128713</t>
+  </si>
+  <si>
+    <t>SOFEL LOT.KRN/SMR 60</t>
+  </si>
+  <si>
+    <t>20078241</t>
+  </si>
+  <si>
+    <t>SOFFELL LOT.APEL 60G</t>
+  </si>
+  <si>
+    <t>10040202</t>
+  </si>
+  <si>
+    <t>SOFFELL A.NYMK K/J60</t>
+  </si>
+  <si>
+    <t>10037280</t>
+  </si>
+  <si>
+    <t>BAGUS KAPUR AJAIB</t>
+  </si>
+  <si>
+    <t>20109069</t>
+  </si>
+  <si>
+    <t>BAGUS LEM TIKUS PCS</t>
+  </si>
+  <si>
+    <t>10003479</t>
+  </si>
+  <si>
+    <t>GAJAH LEM TIKUS KT70</t>
+  </si>
+  <si>
+    <t>20139525</t>
+  </si>
+  <si>
+    <t>VAPE DORA LEM TIKUS</t>
+  </si>
+  <si>
+    <t>10037275</t>
+  </si>
+  <si>
+    <t>SWALLOW KMPR BTR 300</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>20027997</t>
+  </si>
+  <si>
+    <t>IDM KAMPER NAPTLN150</t>
+  </si>
+  <si>
+    <t>20131886</t>
+  </si>
+  <si>
+    <t>IDM KMPR DEO SKRA 5S</t>
+  </si>
+  <si>
+    <t>20131885</t>
+  </si>
+  <si>
+    <t>IDM KMPR DEO CFFE 5S</t>
+  </si>
+  <si>
+    <t>20079794</t>
+  </si>
+  <si>
+    <t>IDM KAMPER TOILET 5S</t>
+  </si>
+  <si>
+    <t>20139963</t>
+  </si>
+  <si>
+    <t>LARISST CTRONELLA 5S</t>
+  </si>
+  <si>
+    <t>10000279</t>
+  </si>
+  <si>
+    <t>SWALLOW TLT.BALL 5'S</t>
+  </si>
+  <si>
+    <t>10000482</t>
+  </si>
+  <si>
+    <t>SWALLOW K/DEO BAL105</t>
+  </si>
+  <si>
+    <t>20017478</t>
+  </si>
+  <si>
+    <t>SWALLOW ORG S-160</t>
+  </si>
+  <si>
+    <t>20122471</t>
+  </si>
+  <si>
+    <t>STELLA LAV.GRD 42+13</t>
+  </si>
+  <si>
+    <t>20136409</t>
+  </si>
+  <si>
+    <t>STELLA BALI JAS42+13</t>
+  </si>
+  <si>
+    <t>20109616</t>
+  </si>
+  <si>
+    <t>STELLA CAFF.LATTE 42</t>
+  </si>
+  <si>
+    <t>20075791</t>
+  </si>
+  <si>
+    <t>STELLA POCKET ORG 10</t>
+  </si>
+  <si>
+    <t>20075798</t>
+  </si>
+  <si>
+    <t>STLLA POCKET PRPL 10</t>
+  </si>
+  <si>
+    <t>20091307</t>
+  </si>
+  <si>
+    <t>STELLA POCKET BLU 10</t>
+  </si>
+  <si>
+    <t>20138481</t>
+  </si>
+  <si>
+    <t>STELLA EXO.FRUIT 10G</t>
+  </si>
+  <si>
+    <t>20138482</t>
+  </si>
+  <si>
+    <t>STELLA LUX.FLOWR 10G</t>
+  </si>
+  <si>
+    <t>20105573</t>
+  </si>
+  <si>
+    <t>STELLA AF REF JPS160</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>20037058</t>
+  </si>
+  <si>
+    <t>STELLA AF REF FLW160</t>
+  </si>
+  <si>
+    <t>20036827</t>
+  </si>
+  <si>
+    <t>STELLA AF REF GRN160</t>
+  </si>
+  <si>
+    <t>20044100</t>
+  </si>
+  <si>
+    <t>STELLA AF REF APL160</t>
+  </si>
+  <si>
+    <t>20135485</t>
+  </si>
+  <si>
+    <t>STELLA AF REF BAL160</t>
+  </si>
+  <si>
+    <t>20046210</t>
+  </si>
+  <si>
+    <t>GLADE OCN ESCPE 146G</t>
+  </si>
+  <si>
+    <t>10023003</t>
+  </si>
+  <si>
+    <t>GLADE PNY&amp;BRY BLS 70</t>
+  </si>
+  <si>
+    <t>10023002</t>
+  </si>
+  <si>
+    <t>GLADE FRESH ONE EF70</t>
+  </si>
+  <si>
+    <t>20096642</t>
+  </si>
+  <si>
+    <t>IDM FRSHNS LEMON 50</t>
+  </si>
+  <si>
+    <t>20096641</t>
+  </si>
+  <si>
+    <t>IDM FRSHNS ORANGE 50</t>
+  </si>
+  <si>
+    <t>10005428</t>
+  </si>
+  <si>
+    <t>STELLA IN ONE ORG 42</t>
+  </si>
+  <si>
+    <t>10005427</t>
+  </si>
+  <si>
+    <t>STELLA IN ONE LMN 42</t>
+  </si>
+  <si>
+    <t>20134373</t>
+  </si>
+  <si>
+    <t>STELLA ALAT+REFILL25</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>20134374</t>
+  </si>
+  <si>
+    <t>STELLA ELCTRIC LAV25</t>
+  </si>
+  <si>
+    <t>20139144</t>
+  </si>
+  <si>
+    <t>HIT XPRES PINK BL.35</t>
+  </si>
+  <si>
+    <t>20131161</t>
+  </si>
+  <si>
+    <t>HIT REF XPRES APLE35</t>
+  </si>
+  <si>
+    <t>20095744</t>
+  </si>
+  <si>
+    <t>HIT REF EXPRT FRS 35</t>
+  </si>
+  <si>
+    <t>20039183</t>
+  </si>
+  <si>
+    <t>HIT ALAT+REF EXP APL</t>
+  </si>
+  <si>
+    <t>10034732</t>
+  </si>
+  <si>
+    <t>HIT MAT ELECTRK 48'S</t>
+  </si>
+  <si>
+    <t>10027329</t>
+  </si>
+  <si>
+    <t>HIT ALT NYAMUK ELC 5</t>
+  </si>
+  <si>
+    <t>20084568</t>
+  </si>
+  <si>
+    <t>VAPE LIQ.SKR BLOSM45</t>
+  </si>
+  <si>
+    <t>20008748</t>
+  </si>
+  <si>
+    <t>VAPE LIQUID REF 45ML</t>
+  </si>
+  <si>
+    <t>20023870</t>
+  </si>
+  <si>
+    <t>VAPE LIQUID ELEKTRIK</t>
+  </si>
+  <si>
+    <t>20030445</t>
+  </si>
+  <si>
+    <t>VAPE SPRAY 1XSMP ORG</t>
+  </si>
+  <si>
+    <t>20073974</t>
+  </si>
+  <si>
+    <t>VAPE SPRAY 1XSMP SKR</t>
+  </si>
+  <si>
+    <t>20135247</t>
+  </si>
+  <si>
+    <t>BAYGON FLRL.FNTSY500</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>20135248</t>
+  </si>
+  <si>
+    <t>BAYGON CHRRY BRRY500</t>
+  </si>
+  <si>
+    <t>10015526</t>
+  </si>
+  <si>
+    <t>BAYGON SPRY LVND 750</t>
+  </si>
+  <si>
+    <t>20124346</t>
+  </si>
+  <si>
+    <t>BAYGON JPNSE&amp;PCH 600</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>20098605</t>
+  </si>
+  <si>
+    <t>BYGON SPRY CHR.BL600</t>
+  </si>
+  <si>
+    <t>10003272</t>
+  </si>
+  <si>
+    <t>BAYGON SPRY CITRS675</t>
+  </si>
+  <si>
+    <t>20071775</t>
+  </si>
+  <si>
+    <t>BAYGON FLO.GRDN 675</t>
+  </si>
+  <si>
+    <t>20139154</t>
+  </si>
+  <si>
+    <t>HIT COTTON PWD 600ML</t>
+  </si>
+  <si>
+    <t>20054151</t>
+  </si>
+  <si>
+    <t>HIT INS.SPRY LILY600</t>
+  </si>
+  <si>
+    <t>10005198</t>
+  </si>
+  <si>
+    <t>HIT INS.SPRAY ORG600</t>
+  </si>
+  <si>
+    <t>20109613</t>
+  </si>
+  <si>
+    <t>HIT SPRY.P/BLOSM 600</t>
+  </si>
+  <si>
+    <t>20080868</t>
+  </si>
+  <si>
+    <t>HIT FRESH CITRUS 600</t>
+  </si>
+  <si>
+    <t>20131365</t>
+  </si>
+  <si>
+    <t>HIT SPRY JPN.SKR 600</t>
+  </si>
+  <si>
+    <t>20076987</t>
+  </si>
+  <si>
+    <t>BAYGON FLOW.GRDN 200</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>20022902</t>
+  </si>
+  <si>
+    <t>HIT SPRAY ORG 180</t>
+  </si>
+  <si>
+    <t>20064216</t>
+  </si>
+  <si>
+    <t>HIT INS.SPRY LILY180</t>
+  </si>
+  <si>
+    <t>20124418</t>
+  </si>
+  <si>
+    <t>VAPE SWEET PWDR 200</t>
+  </si>
+  <si>
+    <t>20139446</t>
+  </si>
+  <si>
+    <t>BAYGON CTRS FRSH 400</t>
+  </si>
+  <si>
+    <t>20128132</t>
+  </si>
+  <si>
+    <t>BAYGON FLO.GRDN 400</t>
+  </si>
+  <si>
+    <t>20088715</t>
+  </si>
+  <si>
+    <t>HIT SPRAY LILY 400ML</t>
+  </si>
+  <si>
+    <t>20022498</t>
+  </si>
+  <si>
+    <t>HIT SPRAY ORG 400ML</t>
+  </si>
+  <si>
+    <t>20134237</t>
+  </si>
+  <si>
+    <t>HIT SPRY.P/BLOSM 400</t>
+  </si>
+  <si>
+    <t>20136130</t>
+  </si>
+  <si>
+    <t>VAPE FLO.BUBBLE 600</t>
+  </si>
+  <si>
+    <t>20124850</t>
+  </si>
+  <si>
+    <t>VAPE SPRY SWET PD600</t>
+  </si>
+  <si>
+    <t>20136134</t>
+  </si>
+  <si>
+    <t>VAPE CANDY FLO 600</t>
+  </si>
+  <si>
+    <t>10006651</t>
+  </si>
+  <si>
+    <t>VAPE FMK ORANGE 600</t>
   </si>
   <si>
     <t>20053058</t>
@@ -748,1240 +1978,13 @@
     <t>ATTACK JAZ1 P/SGR800</t>
   </si>
   <si>
+    <t>999</t>
+  </si>
+  <si>
     <t>20053059</t>
   </si>
   <si>
     <t>ATTACK JAZ1 S/CNT800</t>
-  </si>
-  <si>
-    <t>20105968</t>
-  </si>
-  <si>
-    <t>RNSO PWD JPN PC 700G</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20113183</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD ROSE 380</t>
-  </si>
-  <si>
-    <t>20121372</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD PRFM 380</t>
-  </si>
-  <si>
-    <t>20128719</t>
-  </si>
-  <si>
-    <t>SOKLIN LVD&amp;LILY 425G</t>
-  </si>
-  <si>
-    <t>20042466</t>
-  </si>
-  <si>
-    <t>DAIA DET+SOFT 470G</t>
-  </si>
-  <si>
-    <t>20139595</t>
-  </si>
-  <si>
-    <t>MOLTO TRKA BDD 3X300</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20133398</t>
-  </si>
-  <si>
-    <t>TRKA PURE 300ML</t>
-  </si>
-  <si>
-    <t>10011440</t>
-  </si>
-  <si>
-    <t>RAPIKA LVDR SPLAS300</t>
-  </si>
-  <si>
-    <t>20084780</t>
-  </si>
-  <si>
-    <t>RAPIKA GOLD 250ML</t>
-  </si>
-  <si>
-    <t>20093193</t>
-  </si>
-  <si>
-    <t>RAPIKA PINK SKR 300</t>
-  </si>
-  <si>
-    <t>20138071</t>
-  </si>
-  <si>
-    <t>KISPRAY KASTURI 280</t>
-  </si>
-  <si>
-    <t>20074721</t>
-  </si>
-  <si>
-    <t>KISPRAY GLM.GOLD 280</t>
-  </si>
-  <si>
-    <t>20116685</t>
-  </si>
-  <si>
-    <t>KISPRAY ELG.SAPH 200</t>
-  </si>
-  <si>
-    <t>20032250</t>
-  </si>
-  <si>
-    <t>KISPRAY VIOLET PC280</t>
-  </si>
-  <si>
-    <t>20000980</t>
-  </si>
-  <si>
-    <t>KISPRAY VIOLET 318ML</t>
-  </si>
-  <si>
-    <t>20138470</t>
-  </si>
-  <si>
-    <t>SO KLN PWNG RED 1.7L</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>10005803</t>
-  </si>
-  <si>
-    <t>SOKLIN PWNGI RED 780</t>
-  </si>
-  <si>
-    <t>10007389</t>
-  </si>
-  <si>
-    <t>SOKLIN PWNGI PINK780</t>
-  </si>
-  <si>
-    <t>10008104</t>
-  </si>
-  <si>
-    <t>SO KLIN PWG BLUE 780</t>
-  </si>
-  <si>
-    <t>20108418</t>
-  </si>
-  <si>
-    <t>SOKLIN PWG HJB GR780</t>
-  </si>
-  <si>
-    <t>10005802</t>
-  </si>
-  <si>
-    <t>SOKLIN PEWANGI VL780</t>
-  </si>
-  <si>
-    <t>20134526</t>
-  </si>
-  <si>
-    <t>SOKLIN PWG COT.FN780</t>
-  </si>
-  <si>
-    <t>20125391</t>
-  </si>
-  <si>
-    <t>SOKLIN PWG AC/SPT780</t>
-  </si>
-  <si>
-    <t>20129370</t>
-  </si>
-  <si>
-    <t>MOLTO MORNING FRS550</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20129160</t>
-  </si>
-  <si>
-    <t>MOLTO LUXURY PRF 650</t>
-  </si>
-  <si>
-    <t>20128919</t>
-  </si>
-  <si>
-    <t>MOLTO SFTNR PURE 550</t>
-  </si>
-  <si>
-    <t>20087464</t>
-  </si>
-  <si>
-    <t>IDM PWNG PINK.PAS720</t>
-  </si>
-  <si>
-    <t>20137582</t>
-  </si>
-  <si>
-    <t>IDM PWNG ROM.AURA720</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20137581</t>
-  </si>
-  <si>
-    <t>IDM PWNG EXO.BLUE720</t>
-  </si>
-  <si>
-    <t>20020245</t>
-  </si>
-  <si>
-    <t>MOLTO PWNGI BLUE 765</t>
-  </si>
-  <si>
-    <t>20020226</t>
-  </si>
-  <si>
-    <t>MOLTO PWNGI PINK 765</t>
-  </si>
-  <si>
-    <t>20106821</t>
-  </si>
-  <si>
-    <t>MOLTO PURPLE 765ML</t>
-  </si>
-  <si>
-    <t>20135847</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT SUMMR600</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>20135846</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT SPRNG600</t>
-  </si>
-  <si>
-    <t>20014403</t>
-  </si>
-  <si>
-    <t>BAYCLIN REGLR 1000ML</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>20082581</t>
-  </si>
-  <si>
-    <t>VANISH CAIR WHT 425</t>
-  </si>
-  <si>
-    <t>20052662</t>
-  </si>
-  <si>
-    <t>VANISH CAIR PCH 425</t>
-  </si>
-  <si>
-    <t>20089665</t>
-  </si>
-  <si>
-    <t>IDM PHLANG NODA 450</t>
-  </si>
-  <si>
-    <t>20079788</t>
-  </si>
-  <si>
-    <t>PROCLIN PCH 400ML</t>
-  </si>
-  <si>
-    <t>10025646</t>
-  </si>
-  <si>
-    <t>YURI TAF LMN&amp;LIME500</t>
-  </si>
-  <si>
-    <t>10014263</t>
-  </si>
-  <si>
-    <t>WIPOL KARBOL CMR 720</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>20001645</t>
-  </si>
-  <si>
-    <t>WIPOL KARBOL LMN 720</t>
-  </si>
-  <si>
-    <t>20090066</t>
-  </si>
-  <si>
-    <t>WIPOL SRH + JRK 720</t>
-  </si>
-  <si>
-    <t>20122478</t>
-  </si>
-  <si>
-    <t>WIPOL CITRUS FRS 390</t>
-  </si>
-  <si>
-    <t>20023111</t>
-  </si>
-  <si>
-    <t>SOS KARBOL CLS PN725</t>
-  </si>
-  <si>
-    <t>10013107</t>
-  </si>
-  <si>
-    <t>SUPERSOL PINE 750ML</t>
-  </si>
-  <si>
-    <t>20104030</t>
-  </si>
-  <si>
-    <t>SUPER SOL SEREH 750</t>
-  </si>
-  <si>
-    <t>20132664</t>
-  </si>
-  <si>
-    <t>VIXAL KUAT SEGAR 600</t>
-  </si>
-  <si>
-    <t>10004612</t>
-  </si>
-  <si>
-    <t>SOS P.LNT ORANGE 700</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10004610</t>
-  </si>
-  <si>
-    <t>SOS P/LT APLL REF700</t>
-  </si>
-  <si>
-    <t>10010480</t>
-  </si>
-  <si>
-    <t>SPR PELL FRS.APEL760</t>
-  </si>
-  <si>
-    <t>20121373</t>
-  </si>
-  <si>
-    <t>SPR PELL AB CTRS 500</t>
-  </si>
-  <si>
-    <t>20137408</t>
-  </si>
-  <si>
-    <t>SPR PELL SAKURA 740</t>
-  </si>
-  <si>
-    <t>20001407</t>
-  </si>
-  <si>
-    <t>IDM P'LANTAI LAV 800</t>
-  </si>
-  <si>
-    <t>20001402</t>
-  </si>
-  <si>
-    <t>IDM P'LANTAI APL 800</t>
-  </si>
-  <si>
-    <t>20028779</t>
-  </si>
-  <si>
-    <t>IDM KRBOL WNG650(BR)</t>
-  </si>
-  <si>
-    <t>20089486</t>
-  </si>
-  <si>
-    <t>IDM KRBL SRH CTR 650</t>
-  </si>
-  <si>
-    <t>20128125</t>
-  </si>
-  <si>
-    <t>IDM PURPOSE CLN 375</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>20027963</t>
-  </si>
-  <si>
-    <t>IDM PMBERSH KACA 400</t>
-  </si>
-  <si>
-    <t>10003706</t>
-  </si>
-  <si>
-    <t>MR.MUSCLE ORGNL 400</t>
-  </si>
-  <si>
-    <t>10012548</t>
-  </si>
-  <si>
-    <t>SOKLIN RLX/LAV RF770</t>
-  </si>
-  <si>
-    <t>10003646</t>
-  </si>
-  <si>
-    <t>SO KLIN P/L APPLE770</t>
-  </si>
-  <si>
-    <t>10003645</t>
-  </si>
-  <si>
-    <t>SO KLIN P/L LMN 780</t>
-  </si>
-  <si>
-    <t>20101095</t>
-  </si>
-  <si>
-    <t>SO KLN LNT SEREH 770</t>
-  </si>
-  <si>
-    <t>20131223</t>
-  </si>
-  <si>
-    <t>SO KLN LNT CT.GRD700</t>
-  </si>
-  <si>
-    <t>20131788</t>
-  </si>
-  <si>
-    <t>MAMA LMN JR.NPS 950</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>20092331</t>
-  </si>
-  <si>
-    <t>EKONOMI LIQ JR.NP650</t>
-  </si>
-  <si>
-    <t>20123812</t>
-  </si>
-  <si>
-    <t>EKONOMI LQ.SEREH 650</t>
-  </si>
-  <si>
-    <t>20107240</t>
-  </si>
-  <si>
-    <t>EKONOMI LIQ.SW&amp;JR650</t>
-  </si>
-  <si>
-    <t>20136124</t>
-  </si>
-  <si>
-    <t>EKNOMI LIQ N&amp;JN 675G</t>
-  </si>
-  <si>
-    <t>20129722</t>
-  </si>
-  <si>
-    <t>BUKRIM LIQ.JRK NP550</t>
-  </si>
-  <si>
-    <t>20138518</t>
-  </si>
-  <si>
-    <t>KILAU NIPIS 630ML</t>
-  </si>
-  <si>
-    <t>20034450</t>
-  </si>
-  <si>
-    <t>MAMA/L JERUK NPS 690</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>10004067</t>
-  </si>
-  <si>
-    <t>MAMA/L PCH LEMON 690</t>
-  </si>
-  <si>
-    <t>20099424</t>
-  </si>
-  <si>
-    <t>MAMA LIME CHARCO 690</t>
-  </si>
-  <si>
-    <t>20052031</t>
-  </si>
-  <si>
-    <t>MAMA LIME GRN TEA690</t>
-  </si>
-  <si>
-    <t>10004068</t>
-  </si>
-  <si>
-    <t>MAMA LIME POUCH 690</t>
-  </si>
-  <si>
-    <t>20134303</t>
-  </si>
-  <si>
-    <t>MAMA/L REF YUZU 690</t>
-  </si>
-  <si>
-    <t>20137792</t>
-  </si>
-  <si>
-    <t>MAMA LIME GREEN 690</t>
-  </si>
-  <si>
-    <t>20034449</t>
-  </si>
-  <si>
-    <t>MAMA/L JERUK NPS 430</t>
-  </si>
-  <si>
-    <t>20090067</t>
-  </si>
-  <si>
-    <t>SNLGHT MINT A.BAU600</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>20086172</t>
-  </si>
-  <si>
-    <t>SNLIGHT MND.ORGE 600</t>
-  </si>
-  <si>
-    <t>20112492</t>
-  </si>
-  <si>
-    <t>SUNLIGHT JRK NPS400G</t>
-  </si>
-  <si>
-    <t>20128374</t>
-  </si>
-  <si>
-    <t>LFEBUOY REF LIME 650</t>
-  </si>
-  <si>
-    <t>20134576</t>
-  </si>
-  <si>
-    <t>LFEBUOY REF LEMON650</t>
-  </si>
-  <si>
-    <t>20073425</t>
-  </si>
-  <si>
-    <t>IDM P.PRNG JRK.N 650</t>
-  </si>
-  <si>
-    <t>20141204</t>
-  </si>
-  <si>
-    <t>IDM P.PRG JR.NPS 950</t>
-  </si>
-  <si>
-    <t>20112491</t>
-  </si>
-  <si>
-    <t>SNLIGHT LIME PCH 910</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>20139728</t>
-  </si>
-  <si>
-    <t>SNLGHT BIO BLBR 870G</t>
-  </si>
-  <si>
-    <t>10005482</t>
-  </si>
-  <si>
-    <t>SNLIGHT LIME PCH 660</t>
-  </si>
-  <si>
-    <t>20135144</t>
-  </si>
-  <si>
-    <t>SNLGHT BIO NATURE600</t>
-  </si>
-  <si>
-    <t>10013205</t>
-  </si>
-  <si>
-    <t>SUNLIGHT J/NIPIS.750</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>20139947</t>
-  </si>
-  <si>
-    <t>SNLGHT BIO BLBR 675G</t>
-  </si>
-  <si>
-    <t>20139948</t>
-  </si>
-  <si>
-    <t>SNLGHT BERY&amp;LIME 675</t>
-  </si>
-  <si>
-    <t>20135845</t>
-  </si>
-  <si>
-    <t>EKNOMI LIQ JR&amp;LMN650</t>
-  </si>
-  <si>
-    <t>20093919</t>
-  </si>
-  <si>
-    <t>IDM PURPOSE CLN 400</t>
-  </si>
-  <si>
-    <t>10003498</t>
-  </si>
-  <si>
-    <t>CLEAR PUMP ORIGNL500</t>
-  </si>
-  <si>
-    <t>10034652</t>
-  </si>
-  <si>
-    <t>GLADE OCEAN ESCP 350</t>
-  </si>
-  <si>
-    <t>20105576</t>
-  </si>
-  <si>
-    <t>STELLA A/F SAKURA350</t>
-  </si>
-  <si>
-    <t>10029632</t>
-  </si>
-  <si>
-    <t>STELLA ALAT MATIC</t>
-  </si>
-  <si>
-    <t>10004032</t>
-  </si>
-  <si>
-    <t>VIXAL KUAT HARUM 720</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>10004034</t>
-  </si>
-  <si>
-    <t>VIXAL KMR MD KUAT720</t>
-  </si>
-  <si>
-    <t>10003359</t>
-  </si>
-  <si>
-    <t>WIPOL CEMARA BTL 730</t>
-  </si>
-  <si>
-    <t>10000955</t>
-  </si>
-  <si>
-    <t>PORSTEX N.PARFUM 1L</t>
-  </si>
-  <si>
-    <t>10018962</t>
-  </si>
-  <si>
-    <t>YURI PORSTEX OB.B700</t>
-  </si>
-  <si>
-    <t>10005246</t>
-  </si>
-  <si>
-    <t>WING PRCLN CLN BR750</t>
-  </si>
-  <si>
-    <t>20040315</t>
-  </si>
-  <si>
-    <t>IDM PORSELEN BTL 800</t>
-  </si>
-  <si>
-    <t>20015040</t>
-  </si>
-  <si>
-    <t>HARPIC TRIPLE ACT450</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20095746</t>
-  </si>
-  <si>
-    <t>HRPC PNG.KRK CTR 405</t>
-  </si>
-  <si>
-    <t>20042956</t>
-  </si>
-  <si>
-    <t>HARPIC PWR PLS CT450</t>
-  </si>
-  <si>
-    <t>10010232</t>
-  </si>
-  <si>
-    <t>KIWI LIQ.SHOE BLCK75</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>10007934</t>
-  </si>
-  <si>
-    <t>KIWI PASTE BLACK 45M</t>
-  </si>
-  <si>
-    <t>20012183</t>
-  </si>
-  <si>
-    <t>BAYGON BKR D.DRH 5'S</t>
-  </si>
-  <si>
-    <t>20014401</t>
-  </si>
-  <si>
-    <t>BYGON BKR JMB LVD 5S</t>
-  </si>
-  <si>
-    <t>20128711</t>
-  </si>
-  <si>
-    <t>AUTAN LOT.JRK&amp;LMN 50</t>
-  </si>
-  <si>
-    <t>20106983</t>
-  </si>
-  <si>
-    <t>AUTAN LOT.SAKURA 50</t>
-  </si>
-  <si>
-    <t>20054250</t>
-  </si>
-  <si>
-    <t>AUTAN REFRESH/S 100</t>
-  </si>
-  <si>
-    <t>20128713</t>
-  </si>
-  <si>
-    <t>SOFEL LOT.KRN/SMR 60</t>
-  </si>
-  <si>
-    <t>20078241</t>
-  </si>
-  <si>
-    <t>SOFFELL LOT.APEL 60G</t>
-  </si>
-  <si>
-    <t>10040202</t>
-  </si>
-  <si>
-    <t>SOFFELL A.NYMK K/J60</t>
-  </si>
-  <si>
-    <t>10037280</t>
-  </si>
-  <si>
-    <t>BAGUS KAPUR AJAIB</t>
-  </si>
-  <si>
-    <t>20109069</t>
-  </si>
-  <si>
-    <t>BAGUS LEM TIKUS PCS</t>
-  </si>
-  <si>
-    <t>10003479</t>
-  </si>
-  <si>
-    <t>GAJAH LEM TIKUS KT70</t>
-  </si>
-  <si>
-    <t>20139525</t>
-  </si>
-  <si>
-    <t>VAPE DORA LEM TIKUS</t>
-  </si>
-  <si>
-    <t>10037275</t>
-  </si>
-  <si>
-    <t>SWALLOW KMPR BTR 300</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>20027997</t>
-  </si>
-  <si>
-    <t>IDM KAMPER NAPTLN150</t>
-  </si>
-  <si>
-    <t>20131886</t>
-  </si>
-  <si>
-    <t>IDM KMPR DEO SKRA 5S</t>
-  </si>
-  <si>
-    <t>20131885</t>
-  </si>
-  <si>
-    <t>IDM KMPR DEO CFFE 5S</t>
-  </si>
-  <si>
-    <t>20079794</t>
-  </si>
-  <si>
-    <t>IDM KAMPER TOILET 5S</t>
-  </si>
-  <si>
-    <t>20139963</t>
-  </si>
-  <si>
-    <t>LARISST CTRONELLA 5S</t>
-  </si>
-  <si>
-    <t>10000279</t>
-  </si>
-  <si>
-    <t>SWALLOW TLT.BALL 5'S</t>
-  </si>
-  <si>
-    <t>10000482</t>
-  </si>
-  <si>
-    <t>SWALLOW K/DEO BAL105</t>
-  </si>
-  <si>
-    <t>20017478</t>
-  </si>
-  <si>
-    <t>SWALLOW ORG S-160</t>
-  </si>
-  <si>
-    <t>20122471</t>
-  </si>
-  <si>
-    <t>STELLA LAV.GRD 42+13</t>
-  </si>
-  <si>
-    <t>20136409</t>
-  </si>
-  <si>
-    <t>STELLA BALI JAS42+13</t>
-  </si>
-  <si>
-    <t>20109616</t>
-  </si>
-  <si>
-    <t>STELLA CAFF.LATTE 42</t>
-  </si>
-  <si>
-    <t>20075791</t>
-  </si>
-  <si>
-    <t>STELLA POCKET ORG 10</t>
-  </si>
-  <si>
-    <t>20075798</t>
-  </si>
-  <si>
-    <t>STLLA POCKET PRPL 10</t>
-  </si>
-  <si>
-    <t>20091307</t>
-  </si>
-  <si>
-    <t>STELLA POCKET BLU 10</t>
-  </si>
-  <si>
-    <t>20138481</t>
-  </si>
-  <si>
-    <t>STELLA EXO.FRUIT 10G</t>
-  </si>
-  <si>
-    <t>20138482</t>
-  </si>
-  <si>
-    <t>STELLA LUX.FLOWR 10G</t>
-  </si>
-  <si>
-    <t>20105573</t>
-  </si>
-  <si>
-    <t>STELLA AF REF JPS160</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>20037058</t>
-  </si>
-  <si>
-    <t>STELLA AF REF FLW160</t>
-  </si>
-  <si>
-    <t>20036827</t>
-  </si>
-  <si>
-    <t>STELLA AF REF GRN160</t>
-  </si>
-  <si>
-    <t>20044100</t>
-  </si>
-  <si>
-    <t>STELLA AF REF APL160</t>
-  </si>
-  <si>
-    <t>20135485</t>
-  </si>
-  <si>
-    <t>STELLA AF REF BAL160</t>
-  </si>
-  <si>
-    <t>20046210</t>
-  </si>
-  <si>
-    <t>GLADE OCN ESCPE 146G</t>
-  </si>
-  <si>
-    <t>10023003</t>
-  </si>
-  <si>
-    <t>GLADE PNY&amp;BRY BLS 70</t>
-  </si>
-  <si>
-    <t>10023002</t>
-  </si>
-  <si>
-    <t>GLADE FRESH ONE EF70</t>
-  </si>
-  <si>
-    <t>20096642</t>
-  </si>
-  <si>
-    <t>IDM FRSHNS LEMON 50</t>
-  </si>
-  <si>
-    <t>20096641</t>
-  </si>
-  <si>
-    <t>IDM FRSHNS ORANGE 50</t>
-  </si>
-  <si>
-    <t>10005428</t>
-  </si>
-  <si>
-    <t>STELLA IN ONE ORG 42</t>
-  </si>
-  <si>
-    <t>10005427</t>
-  </si>
-  <si>
-    <t>STELLA IN ONE LMN 42</t>
-  </si>
-  <si>
-    <t>20134373</t>
-  </si>
-  <si>
-    <t>STELLA ALAT+REFILL25</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>20134374</t>
-  </si>
-  <si>
-    <t>STELLA ELCTRIC LAV25</t>
-  </si>
-  <si>
-    <t>20139144</t>
-  </si>
-  <si>
-    <t>HIT XPRES PINK BL.35</t>
-  </si>
-  <si>
-    <t>20131161</t>
-  </si>
-  <si>
-    <t>HIT REF XPRES APLE35</t>
-  </si>
-  <si>
-    <t>20095744</t>
-  </si>
-  <si>
-    <t>HIT REF EXPRT FRS 35</t>
-  </si>
-  <si>
-    <t>20039183</t>
-  </si>
-  <si>
-    <t>HIT ALAT+REF EXP APL</t>
-  </si>
-  <si>
-    <t>10034732</t>
-  </si>
-  <si>
-    <t>HIT MAT ELECTRK 48'S</t>
-  </si>
-  <si>
-    <t>10027329</t>
-  </si>
-  <si>
-    <t>HIT ALT NYAMUK ELC 5</t>
-  </si>
-  <si>
-    <t>20084568</t>
-  </si>
-  <si>
-    <t>VAPE LIQ.SKR BLOSM45</t>
-  </si>
-  <si>
-    <t>20008748</t>
-  </si>
-  <si>
-    <t>VAPE LIQUID REF 45ML</t>
-  </si>
-  <si>
-    <t>20023870</t>
-  </si>
-  <si>
-    <t>VAPE LIQUID ELEKTRIK</t>
-  </si>
-  <si>
-    <t>20030445</t>
-  </si>
-  <si>
-    <t>VAPE SPRAY 1XSMP ORG</t>
-  </si>
-  <si>
-    <t>20073974</t>
-  </si>
-  <si>
-    <t>VAPE SPRAY 1XSMP SKR</t>
-  </si>
-  <si>
-    <t>20135247</t>
-  </si>
-  <si>
-    <t>BAYGON FLRL.FNTSY500</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>20135248</t>
-  </si>
-  <si>
-    <t>BAYGON CHRRY BRRY500</t>
-  </si>
-  <si>
-    <t>10015526</t>
-  </si>
-  <si>
-    <t>BAYGON SPRY LVND 750</t>
-  </si>
-  <si>
-    <t>20124346</t>
-  </si>
-  <si>
-    <t>BAYGON JPNSE&amp;PCH 600</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20098605</t>
-  </si>
-  <si>
-    <t>BYGON SPRY CHR.BL600</t>
-  </si>
-  <si>
-    <t>10003272</t>
-  </si>
-  <si>
-    <t>BAYGON SPRY CITRS675</t>
-  </si>
-  <si>
-    <t>20071775</t>
-  </si>
-  <si>
-    <t>BAYGON FLO.GRDN 675</t>
-  </si>
-  <si>
-    <t>20139154</t>
-  </si>
-  <si>
-    <t>HIT COTTON PWD 600ML</t>
-  </si>
-  <si>
-    <t>20054151</t>
-  </si>
-  <si>
-    <t>HIT INS.SPRY LILY600</t>
-  </si>
-  <si>
-    <t>10005198</t>
-  </si>
-  <si>
-    <t>HIT INS.SPRAY ORG600</t>
-  </si>
-  <si>
-    <t>20109613</t>
-  </si>
-  <si>
-    <t>HIT SPRY.P/BLOSM 600</t>
-  </si>
-  <si>
-    <t>20080868</t>
-  </si>
-  <si>
-    <t>HIT FRESH CITRUS 600</t>
-  </si>
-  <si>
-    <t>20131365</t>
-  </si>
-  <si>
-    <t>HIT SPRY JPN.SKR 600</t>
-  </si>
-  <si>
-    <t>20076987</t>
-  </si>
-  <si>
-    <t>BAYGON FLOW.GRDN 200</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>20022902</t>
-  </si>
-  <si>
-    <t>HIT SPRAY ORG 180</t>
-  </si>
-  <si>
-    <t>20064216</t>
-  </si>
-  <si>
-    <t>HIT INS.SPRY LILY180</t>
-  </si>
-  <si>
-    <t>20124418</t>
-  </si>
-  <si>
-    <t>VAPE SWEET PWDR 200</t>
-  </si>
-  <si>
-    <t>20139446</t>
-  </si>
-  <si>
-    <t>BAYGON CTRS FRSH 400</t>
-  </si>
-  <si>
-    <t>20128132</t>
-  </si>
-  <si>
-    <t>BAYGON FLO.GRDN 400</t>
-  </si>
-  <si>
-    <t>20088715</t>
-  </si>
-  <si>
-    <t>HIT SPRAY LILY 400ML</t>
-  </si>
-  <si>
-    <t>20022498</t>
-  </si>
-  <si>
-    <t>HIT SPRAY ORG 400ML</t>
-  </si>
-  <si>
-    <t>20134237</t>
-  </si>
-  <si>
-    <t>HIT SPRY.P/BLOSM 400</t>
-  </si>
-  <si>
-    <t>20136130</t>
-  </si>
-  <si>
-    <t>VAPE FLO.BUBBLE 600</t>
-  </si>
-  <si>
-    <t>20124850</t>
-  </si>
-  <si>
-    <t>VAPE SPRY SWET PD600</t>
-  </si>
-  <si>
-    <t>20136134</t>
-  </si>
-  <si>
-    <t>VAPE CANDY FLO 600</t>
-  </si>
-  <si>
-    <t>10006651</t>
-  </si>
-  <si>
-    <t>VAPE FMK ORANGE 600</t>
   </si>
 </sst>
 </file>
@@ -2380,7 +2383,8 @@
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="5" width="4" customWidth="1"/>
+    <col min="4" max="4" width="5" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2661,7 +2665,7 @@
         <v>38</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2681,7 +2685,7 @@
         <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2701,15 +2705,15 @@
         <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -2721,15 +2725,15 @@
         <v>11</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -2741,15 +2745,15 @@
         <v>14</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -2766,10 +2770,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -2786,10 +2790,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -2801,7 +2805,7 @@
         <v>35</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2821,7 +2825,7 @@
         <v>38</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2841,7 +2845,7 @@
         <v>58</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -3041,15 +3045,15 @@
         <v>4</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>79</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -3061,15 +3065,15 @@
         <v>8</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>79</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -3081,7 +3085,7 @@
         <v>11</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>15</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -3101,7 +3105,7 @@
         <v>14</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -3121,7 +3125,7 @@
         <v>18</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -3141,15 +3145,15 @@
         <v>32</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>90</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -3161,15 +3165,15 @@
         <v>35</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -3181,15 +3185,15 @@
         <v>38</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -3206,10 +3210,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -3226,10 +3230,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -3246,10 +3250,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -3266,10 +3270,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -3281,15 +3285,15 @@
         <v>18</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -3301,15 +3305,15 @@
         <v>32</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -3321,24 +3325,24 @@
         <v>35</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -3346,10 +3350,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -3358,7 +3362,7 @@
         <v>35</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -3366,10 +3370,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -3378,18 +3382,18 @@
         <v>35</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>5</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -3398,18 +3402,18 @@
         <v>35</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>105</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -3418,7 +3422,7 @@
         <v>35</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -3426,10 +3430,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -3438,7 +3442,7 @@
         <v>35</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -3446,10 +3450,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -3458,7 +3462,7 @@
         <v>35</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -3466,19 +3470,19 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -3486,19 +3490,19 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -3506,10 +3510,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>129</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -3518,18 +3522,18 @@
         <v>38</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>5</v>
+        <v>104</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -3538,58 +3542,58 @@
         <v>38</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>5</v>
+        <v>104</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>105</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>105</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -3598,7 +3602,7 @@
         <v>58</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -3606,10 +3610,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>139</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -3618,7 +3622,7 @@
         <v>58</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -3626,22 +3630,22 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="C63" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="E63" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>5</v>
+        <v>104</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -3655,10 +3659,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3675,30 +3679,30 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>105</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3706,39 +3710,39 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>5</v>
+        <v>104</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="C68" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="E68" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -3755,13 +3759,13 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>105</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -3775,10 +3779,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -3786,19 +3790,19 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -3806,19 +3810,19 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -3826,59 +3830,59 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="C73" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="E73" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>5</v>
+        <v>164</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F74" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -3895,10 +3899,10 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>21</v>
@@ -3915,13 +3919,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3935,10 +3939,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3955,10 +3959,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3975,30 +3979,30 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>181</v>
-      </c>
       <c r="E81" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -4015,10 +4019,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -4035,10 +4039,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -4055,10 +4059,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -4075,10 +4079,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -4095,10 +4099,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -4115,10 +4119,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -4135,13 +4139,13 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -4155,33 +4159,33 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>21</v>
+        <v>199</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="E90" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -4195,10 +4199,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>15</v>
@@ -4215,13 +4219,13 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>15</v>
+        <v>199</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -4235,13 +4239,13 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -4255,13 +4259,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -4275,13 +4279,13 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -4295,10 +4299,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>15</v>
@@ -4315,10 +4319,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>15</v>
@@ -4335,30 +4339,30 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="E99" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>21</v>
@@ -4375,10 +4379,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>21</v>
@@ -4395,10 +4399,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>21</v>
@@ -4415,33 +4419,33 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>21</v>
+        <v>104</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -4455,13 +4459,13 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -4475,13 +4479,13 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -4495,30 +4499,30 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>105</v>
+        <v>21</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="E107" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>21</v>
@@ -4535,10 +4539,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>21</v>
@@ -4555,10 +4559,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>21</v>
@@ -4575,50 +4579,50 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>105</v>
+        <v>15</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="E111" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>105</v>
+        <v>21</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>21</v>
@@ -4635,13 +4639,13 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -4655,13 +4659,13 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -4675,53 +4679,53 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>5</v>
+        <v>257</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="E116" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>261</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4735,13 +4739,13 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4755,10 +4759,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -4775,13 +4779,13 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>5</v>
+        <v>104</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4795,13 +4799,13 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>5</v>
+        <v>104</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4815,13 +4819,13 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4835,13 +4839,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4855,13 +4859,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>38</v>
+        <v>141</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4875,50 +4879,50 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>105</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D126" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="E126" s="1" t="s">
-        <v>146</v>
+        <v>8</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>105</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4935,10 +4939,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4955,10 +4959,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4975,10 +4979,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -4995,10 +4999,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -5015,10 +5019,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -5035,50 +5039,50 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>282</v>
-      </c>
       <c r="E134" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>21</v>
@@ -5095,13 +5099,13 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>21</v>
+        <v>164</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -5115,53 +5119,53 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>21</v>
+        <v>304</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F138" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F138" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>308</v>
+        <v>21</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -5175,13 +5179,13 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>308</v>
+        <v>21</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -5195,10 +5199,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>21</v>
@@ -5215,93 +5219,93 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="E143" s="1" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F145" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F145" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -5315,13 +5319,13 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>324</v>
+        <v>164</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -5335,13 +5339,13 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>324</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -5355,13 +5359,13 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -5375,50 +5379,50 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="E151" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>21</v>
@@ -5435,10 +5439,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>21</v>
@@ -5455,13 +5459,13 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -5475,13 +5479,13 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -5495,13 +5499,13 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>5</v>
+        <v>104</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -5515,13 +5519,13 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -5535,53 +5539,53 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>105</v>
+        <v>351</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="E159" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>21</v>
+        <v>304</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>355</v>
+        <v>21</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -5595,13 +5599,13 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>308</v>
+        <v>21</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -5615,13 +5619,13 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -5635,13 +5639,13 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>21</v>
+        <v>164</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -5655,13 +5659,13 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>15</v>
+        <v>164</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -5675,13 +5679,13 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>53</v>
+        <v>164</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -5695,13 +5699,13 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>53</v>
+        <v>164</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -5715,53 +5719,53 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>354</v>
+        <v>370</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>53</v>
+        <v>164</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D168" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>354</v>
-      </c>
       <c r="E168" s="1" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>53</v>
+        <v>164</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>53</v>
+        <v>104</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -5775,13 +5779,13 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5795,13 +5799,13 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>105</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5815,10 +5819,10 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5835,10 +5839,10 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5855,10 +5859,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5875,10 +5879,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5886,39 +5890,39 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D176" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>374</v>
-      </c>
       <c r="E176" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5935,10 +5939,10 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5955,10 +5959,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5975,10 +5979,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5995,13 +5999,13 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -6015,10 +6019,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -6026,39 +6030,39 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="B183" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>391</v>
-      </c>
       <c r="E183" s="1" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -6075,10 +6079,10 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -6095,10 +6099,10 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -6115,13 +6119,13 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -6135,13 +6139,13 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6155,13 +6159,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -6175,50 +6179,50 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>79</v>
+        <v>21</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D191" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B191" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="C191" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="E191" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>5</v>
+        <v>257</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>21</v>
@@ -6235,13 +6239,13 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>261</v>
+        <v>21</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -6255,10 +6259,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>21</v>
@@ -6275,13 +6279,13 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>21</v>
+        <v>164</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -6295,13 +6299,13 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>21</v>
+        <v>164</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -6315,50 +6319,50 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D198" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="B198" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="C198" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D198" s="1" t="s">
-        <v>423</v>
-      </c>
       <c r="E198" s="1" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>21</v>
@@ -6375,10 +6379,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>21</v>
@@ -6395,10 +6399,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>21</v>
@@ -6406,19 +6410,19 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D202" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="B202" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="C202" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="E202" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>21</v>
@@ -6426,19 +6430,19 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>21</v>
@@ -6455,13 +6459,13 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -6475,13 +6479,13 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>21</v>
+        <v>164</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -6495,13 +6499,13 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -6515,13 +6519,13 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>53</v>
+        <v>104</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -6535,13 +6539,13 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>105</v>
+        <v>351</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -6555,13 +6559,13 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>105</v>
+        <v>320</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -6575,50 +6579,50 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>355</v>
+        <v>21</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D211" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="B211" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="C211" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D211" s="1" t="s">
-        <v>447</v>
-      </c>
       <c r="E211" s="1" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>324</v>
+        <v>21</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>21</v>
@@ -6635,13 +6639,13 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -6655,13 +6659,13 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>21</v>
+        <v>304</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -6675,13 +6679,13 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -6695,13 +6699,13 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>308</v>
+        <v>164</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -6715,53 +6719,53 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>5</v>
+        <v>477</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>53</v>
+        <v>320</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>38</v>
+        <v>141</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -6775,53 +6779,53 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>466</v>
+        <v>484</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D221" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="B221" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="C221" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D221" s="1" t="s">
-        <v>466</v>
-      </c>
       <c r="E221" s="1" t="s">
-        <v>146</v>
+        <v>8</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>481</v>
+        <v>320</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -6835,13 +6839,13 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>324</v>
+        <v>351</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -6855,13 +6859,13 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>324</v>
+        <v>304</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -6875,13 +6879,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>355</v>
+        <v>320</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -6895,13 +6899,13 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -6915,13 +6919,13 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>324</v>
+        <v>351</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -6935,13 +6939,13 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -6955,13 +6959,13 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>38</v>
+        <v>141</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>355</v>
+        <v>320</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -6975,13 +6979,13 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>58</v>
+        <v>163</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>324</v>
+        <v>83</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -6995,13 +6999,13 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>324</v>
+        <v>104</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -7015,13 +7019,13 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>79</v>
+        <v>320</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -7035,13 +7039,13 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -7055,53 +7059,53 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>488</v>
+        <v>513</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>324</v>
+        <v>83</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D235" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="B235" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="C235" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D235" s="1" t="s">
-        <v>488</v>
-      </c>
       <c r="E235" s="1" t="s">
-        <v>220</v>
+        <v>8</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>105</v>
+        <v>304</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>79</v>
+        <v>304</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -7115,13 +7119,13 @@
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -7135,13 +7139,13 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -7155,13 +7159,13 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -7175,13 +7179,13 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>308</v>
+        <v>83</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -7195,13 +7199,13 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>308</v>
+        <v>83</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -7215,13 +7219,13 @@
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -7235,13 +7239,13 @@
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>38</v>
+        <v>141</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -7255,13 +7259,13 @@
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>58</v>
+        <v>152</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -7275,10 +7279,10 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>5</v>
@@ -7295,13 +7299,13 @@
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>5</v>
+        <v>304</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -7315,13 +7319,13 @@
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>5</v>
+        <v>304</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -7335,13 +7339,13 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -7355,13 +7359,13 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>308</v>
+        <v>83</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -7375,13 +7379,13 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>308</v>
+        <v>83</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -7395,53 +7399,53 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>517</v>
+        <v>548</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>181</v>
+        <v>4</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>79</v>
+        <v>351</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B252" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D252" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="B252" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="C252" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D252" s="1" t="s">
-        <v>517</v>
-      </c>
       <c r="E252" s="1" t="s">
-        <v>181</v>
+        <v>8</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>79</v>
+        <v>320</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>355</v>
+        <v>320</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -7455,13 +7459,13 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -7475,13 +7479,13 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>324</v>
+        <v>5</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -7495,13 +7499,13 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>324</v>
+        <v>104</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -7515,13 +7519,13 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>5</v>
+        <v>104</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -7535,13 +7539,13 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -7555,13 +7559,13 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>105</v>
+        <v>257</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -7575,13 +7579,13 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>38</v>
+        <v>141</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>105</v>
+        <v>257</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -7595,13 +7599,13 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>58</v>
+        <v>152</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -7615,13 +7619,13 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -7635,53 +7639,53 @@
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>552</v>
+        <v>573</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>157</v>
+        <v>4</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>324</v>
+        <v>5</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B264" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D264" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="B264" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="C264" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D264" s="1" t="s">
-        <v>552</v>
-      </c>
       <c r="E264" s="1" t="s">
-        <v>168</v>
+        <v>8</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>324</v>
+        <v>5</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -7695,13 +7699,13 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -7715,13 +7719,13 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -7735,13 +7739,13 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -7755,13 +7759,13 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -7775,13 +7779,13 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -7795,13 +7799,13 @@
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>324</v>
+        <v>5</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -7815,13 +7819,13 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>38</v>
+        <v>141</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>324</v>
+        <v>5</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -7835,10 +7839,10 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>58</v>
+        <v>152</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>5</v>
@@ -7855,13 +7859,13 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -7875,13 +7879,13 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -7895,53 +7899,53 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>577</v>
+        <v>600</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>168</v>
+        <v>4</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>79</v>
+        <v>320</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B277" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C277" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D277" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="B277" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="C277" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D277" s="1" t="s">
-        <v>577</v>
-      </c>
       <c r="E277" s="1" t="s">
-        <v>181</v>
+        <v>8</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>79</v>
+        <v>320</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -7955,53 +7959,53 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>324</v>
+        <v>607</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>611</v>
+        <v>320</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -8015,13 +8019,13 @@
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -8035,13 +8039,13 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>324</v>
+        <v>5</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -8055,13 +8059,13 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -8075,13 +8079,13 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>38</v>
+        <v>141</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -8095,13 +8099,13 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>58</v>
+        <v>152</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>324</v>
+        <v>5</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -8115,13 +8119,13 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>324</v>
+        <v>5</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -8135,13 +8139,13 @@
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -8155,53 +8159,53 @@
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>604</v>
+        <v>628</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>168</v>
+        <v>4</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="B290" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="C290" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D290" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="B290" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="C290" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D290" s="1" t="s">
-        <v>604</v>
-      </c>
       <c r="E290" s="1" t="s">
-        <v>181</v>
+        <v>8</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -8215,13 +8219,13 @@
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>324</v>
+        <v>5</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8235,13 +8239,13 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>324</v>
+        <v>351</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8255,13 +8259,13 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8275,13 +8279,13 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>355</v>
+        <v>320</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8295,13 +8299,13 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8315,13 +8319,13 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>324</v>
+        <v>5</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -8335,13 +8339,13 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>38</v>
+        <v>141</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>324</v>
+        <v>5</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -8355,10 +8359,10 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>58</v>
+        <v>152</v>
       </c>
       <c r="F299" s="1" t="s">
         <v>5</v>
@@ -8375,10 +8379,10 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>5</v>
@@ -8395,13 +8399,13 @@
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>5</v>
+        <v>104</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
@@ -8415,33 +8419,33 @@
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>632</v>
+        <v>655</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>168</v>
+        <v>4</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>5</v>
+        <v>104</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="B303" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="C303" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D303" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="B303" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="C303" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D303" s="1" t="s">
-        <v>632</v>
-      </c>
       <c r="E303" s="1" t="s">
-        <v>181</v>
+        <v>8</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/DND05S.xlsx
+++ b/DND05S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="655">
   <si>
     <t/>
   </si>
@@ -547,7 +547,7 @@
     <t>20081448</t>
   </si>
   <si>
-    <t>ROYALE SOFT H.SM 650</t>
+    <t>ROYALE SOFT H.SM 600</t>
   </si>
   <si>
     <t>13</t>
@@ -556,43 +556,43 @@
     <t>20081449</t>
   </si>
   <si>
-    <t>ROYALE SOFT P.DW 650</t>
+    <t>ROYALE SOFT P.DW 600</t>
   </si>
   <si>
     <t>20104951</t>
   </si>
   <si>
-    <t>ROYALE HJB BLCK.V650</t>
+    <t>ROYALE HJB BLCK.V600</t>
   </si>
   <si>
     <t>20091457</t>
   </si>
   <si>
-    <t>ROYALE SOFT BS 650</t>
+    <t>ROYALE SOFT BS 600</t>
   </si>
   <si>
     <t>20098312</t>
   </si>
   <si>
-    <t>ROYALE PINK STN 650</t>
+    <t>ROYALE PINK STN 600</t>
   </si>
   <si>
     <t>20113101</t>
   </si>
   <si>
-    <t>ROYALE SWT FLORL 680</t>
+    <t>ROYALE SWT FLORL 600</t>
   </si>
   <si>
     <t>20128706</t>
   </si>
   <si>
-    <t>ROYALE LNVDR VNL 680</t>
+    <t>ROYALE LNVDR VNL 600</t>
   </si>
   <si>
     <t>20113093</t>
   </si>
   <si>
-    <t>ROYALE SUNNY DAY 680</t>
+    <t>ROYALE SUNNY DAY 600</t>
   </si>
   <si>
     <t>20126740</t>
@@ -616,31 +616,31 @@
     <t>20094733</t>
   </si>
   <si>
-    <t>DOWNY MYSTIQUE 850</t>
+    <t>DOWNY MYSTIQUE 900</t>
   </si>
   <si>
     <t>20140221</t>
   </si>
   <si>
-    <t>DOWNY PASSION 950ML</t>
+    <t>DOWNY PASSION 875ML</t>
   </si>
   <si>
     <t>20074226</t>
   </si>
   <si>
-    <t>DOWNY SUN.FRSH 600</t>
+    <t>DOWNY SUN.FRSH 550</t>
   </si>
   <si>
     <t>20080360</t>
   </si>
   <si>
-    <t>DOWNY MYSTIQUE 600ML</t>
+    <t>DOWNY MYSTIQUE 550ML</t>
   </si>
   <si>
     <t>20080361</t>
   </si>
   <si>
-    <t>DOWNY PASSION 600ML</t>
+    <t>DOWNY PASSION 550ML</t>
   </si>
   <si>
     <t>20139145</t>
@@ -1042,13 +1042,13 @@
     <t>10013107</t>
   </si>
   <si>
-    <t>SUPERSOL PINE 750ML</t>
+    <t>SUPERSOL PINE 720G</t>
   </si>
   <si>
     <t>20104030</t>
   </si>
   <si>
-    <t>SUPER SOL SEREH 750</t>
+    <t>SUPER SOL SEREH720G</t>
   </si>
   <si>
     <t>20132664</t>
@@ -1297,6 +1297,12 @@
     <t>LFEBUOY REF LEMON650</t>
   </si>
   <si>
+    <t>20141345</t>
+  </si>
+  <si>
+    <t>LARISST S/PCC PRG650</t>
+  </si>
+  <si>
     <t>20073425</t>
   </si>
   <si>
@@ -1970,21 +1976,6 @@
   </si>
   <si>
     <t>VAPE FMK ORANGE 600</t>
-  </si>
-  <si>
-    <t>20053058</t>
-  </si>
-  <si>
-    <t>ATTACK JAZ1 P/SGR800</t>
-  </si>
-  <si>
-    <t>999</t>
-  </si>
-  <si>
-    <t>20053059</t>
-  </si>
-  <si>
-    <t>ATTACK JAZ1 S/CNT800</t>
   </si>
 </sst>
 </file>
@@ -2377,14 +2368,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F303"/>
+  <dimension ref="A1:F302"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="5" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
+    <col min="4" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6282,7 +6272,7 @@
         <v>419</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>164</v>
@@ -6302,7 +6292,7 @@
         <v>419</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>164</v>
@@ -6319,30 +6309,30 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>21</v>
+        <v>164</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="B198" s="1" t="s">
+      <c r="C198" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D198" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="C198" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D198" s="1" t="s">
-        <v>434</v>
-      </c>
       <c r="E198" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>21</v>
@@ -6359,10 +6349,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>21</v>
@@ -6379,10 +6369,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>21</v>
@@ -6399,10 +6389,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>21</v>
@@ -6410,19 +6400,19 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B202" s="1" t="s">
+      <c r="C202" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D202" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="C202" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>443</v>
-      </c>
       <c r="E202" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>21</v>
@@ -6439,10 +6429,10 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>21</v>
@@ -6459,13 +6449,13 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -6479,13 +6469,13 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>164</v>
+        <v>83</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -6499,13 +6489,13 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>104</v>
+        <v>164</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -6519,10 +6509,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>104</v>
@@ -6539,13 +6529,13 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>351</v>
+        <v>104</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -6559,13 +6549,13 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>320</v>
+        <v>351</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -6579,30 +6569,30 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>462</v>
+        <v>445</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>21</v>
+        <v>320</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B211" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B211" s="1" t="s">
+      <c r="C211" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D211" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="C211" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D211" s="1" t="s">
-        <v>462</v>
-      </c>
       <c r="E211" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>21</v>
@@ -6619,10 +6609,10 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>21</v>
@@ -6639,13 +6629,13 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -6659,13 +6649,13 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -6679,13 +6669,13 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>5</v>
+        <v>304</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -6699,13 +6689,13 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>164</v>
+        <v>5</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -6719,33 +6709,33 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>477</v>
+        <v>164</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="B218" s="1" t="s">
+      <c r="C218" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F218" s="1" t="s">
         <v>479</v>
-      </c>
-      <c r="C218" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D218" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E218" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F218" s="1" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -6759,13 +6749,13 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>477</v>
+        <v>320</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -6779,30 +6769,30 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>484</v>
+        <v>464</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>4</v>
+        <v>141</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>320</v>
+        <v>479</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B221" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="B221" s="1" t="s">
+      <c r="C221" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D221" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="C221" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D221" s="1" t="s">
-        <v>484</v>
-      </c>
       <c r="E221" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>320</v>
@@ -6819,10 +6809,10 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>320</v>
@@ -6839,13 +6829,13 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>351</v>
+        <v>320</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -6859,13 +6849,13 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>304</v>
+        <v>351</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -6879,13 +6869,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -6899,13 +6889,13 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -6919,13 +6909,13 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>351</v>
+        <v>304</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -6939,13 +6929,13 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>320</v>
+        <v>351</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -6959,10 +6949,10 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>320</v>
@@ -6979,13 +6969,13 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>83</v>
+        <v>320</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -6999,13 +6989,13 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -7019,13 +7009,13 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>320</v>
+        <v>104</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -7039,13 +7029,13 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>104</v>
+        <v>320</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -7059,33 +7049,33 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>513</v>
+        <v>486</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>4</v>
+        <v>218</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B235" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="B235" s="1" t="s">
+      <c r="C235" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D235" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="C235" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D235" s="1" t="s">
-        <v>513</v>
-      </c>
       <c r="E235" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -7099,10 +7089,10 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>304</v>
@@ -7119,10 +7109,10 @@
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>304</v>
@@ -7139,10 +7129,10 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F238" s="1" t="s">
         <v>304</v>
@@ -7159,10 +7149,10 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F239" s="1" t="s">
         <v>304</v>
@@ -7179,13 +7169,13 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>83</v>
+        <v>304</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -7199,10 +7189,10 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F241" s="1" t="s">
         <v>83</v>
@@ -7219,10 +7209,10 @@
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F242" s="1" t="s">
         <v>83</v>
@@ -7239,13 +7229,13 @@
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -7259,10 +7249,10 @@
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="F244" s="1" t="s">
         <v>5</v>
@@ -7279,10 +7269,10 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>5</v>
@@ -7299,13 +7289,13 @@
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>304</v>
+        <v>5</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -7319,7 +7309,7 @@
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E247" s="1" t="s">
         <v>179</v>
@@ -7339,7 +7329,7 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E248" s="1" t="s">
         <v>179</v>
@@ -7359,13 +7349,13 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E249" s="1" t="s">
         <v>179</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>83</v>
+        <v>304</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -7379,7 +7369,7 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>179</v>
@@ -7399,33 +7389,33 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>548</v>
+        <v>515</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>4</v>
+        <v>179</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>351</v>
+        <v>83</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B252" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="B252" s="1" t="s">
+      <c r="C252" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D252" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="C252" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D252" s="1" t="s">
-        <v>548</v>
-      </c>
       <c r="E252" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>320</v>
+        <v>351</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7439,10 +7429,10 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F253" s="1" t="s">
         <v>320</v>
@@ -7459,10 +7449,10 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>320</v>
@@ -7479,13 +7469,13 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -7499,13 +7489,13 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>104</v>
+        <v>5</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -7519,10 +7509,10 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>104</v>
@@ -7539,10 +7529,10 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>104</v>
@@ -7559,13 +7549,13 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>257</v>
+        <v>104</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -7579,10 +7569,10 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="F260" s="1" t="s">
         <v>257</v>
@@ -7599,13 +7589,13 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>320</v>
+        <v>257</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -7619,10 +7609,10 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="F262" s="1" t="s">
         <v>320</v>
@@ -7639,30 +7629,30 @@
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>573</v>
+        <v>550</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>4</v>
+        <v>163</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="B264" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="B264" s="1" t="s">
+      <c r="C264" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D264" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="C264" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D264" s="1" t="s">
-        <v>573</v>
-      </c>
       <c r="E264" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F264" s="1" t="s">
         <v>5</v>
@@ -7679,13 +7669,13 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>320</v>
+        <v>5</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -7699,10 +7689,10 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>320</v>
@@ -7719,10 +7709,10 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>320</v>
@@ -7739,10 +7729,10 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>320</v>
@@ -7759,10 +7749,10 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>320</v>
@@ -7779,10 +7769,10 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>320</v>
@@ -7799,13 +7789,13 @@
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -7819,10 +7809,10 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>5</v>
@@ -7839,10 +7829,10 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>5</v>
@@ -7859,13 +7849,13 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -7879,10 +7869,10 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>83</v>
@@ -7899,30 +7889,30 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>600</v>
+        <v>575</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>4</v>
+        <v>179</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>320</v>
+        <v>83</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B277" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="B277" s="1" t="s">
+      <c r="C277" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D277" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="C277" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D277" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="E277" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>320</v>
@@ -7939,10 +7929,10 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>320</v>
@@ -7959,33 +7949,33 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>607</v>
+        <v>320</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="B280" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="B280" s="1" t="s">
+      <c r="C280" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D280" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E280" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F280" s="1" t="s">
         <v>609</v>
-      </c>
-      <c r="C280" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D280" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="E280" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F280" s="1" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -7999,10 +7989,10 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>320</v>
@@ -8019,10 +8009,10 @@
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>320</v>
@@ -8039,13 +8029,13 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -8059,13 +8049,13 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>320</v>
+        <v>5</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -8079,10 +8069,10 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>320</v>
@@ -8099,13 +8089,13 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -8119,10 +8109,10 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>5</v>
@@ -8139,13 +8129,13 @@
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>320</v>
+        <v>5</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -8159,10 +8149,10 @@
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>628</v>
+        <v>602</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>4</v>
+        <v>179</v>
       </c>
       <c r="F289" s="1" t="s">
         <v>320</v>
@@ -8170,19 +8160,19 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B290" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="B290" s="1" t="s">
+      <c r="C290" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D290" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="C290" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D290" s="1" t="s">
-        <v>628</v>
-      </c>
       <c r="E290" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F290" s="1" t="s">
         <v>320</v>
@@ -8199,10 +8189,10 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F291" s="1" t="s">
         <v>320</v>
@@ -8219,13 +8209,13 @@
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8239,13 +8229,13 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>351</v>
+        <v>5</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8259,13 +8249,13 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>320</v>
+        <v>351</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8279,10 +8269,10 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F295" s="1" t="s">
         <v>320</v>
@@ -8299,10 +8289,10 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F296" s="1" t="s">
         <v>320</v>
@@ -8319,13 +8309,13 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -8339,10 +8329,10 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="F298" s="1" t="s">
         <v>5</v>
@@ -8359,10 +8349,10 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="F299" s="1" t="s">
         <v>5</v>
@@ -8379,10 +8369,10 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>5</v>
@@ -8399,13 +8389,13 @@
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>104</v>
+        <v>5</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
@@ -8419,32 +8409,12 @@
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>655</v>
+        <v>630</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>4</v>
+        <v>179</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A303" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="B303" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="C303" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D303" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="E303" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F303" s="1" t="s">
         <v>104</v>
       </c>
     </row>

--- a/DND05S.xlsx
+++ b/DND05S.xlsx
@@ -625,40 +625,40 @@
     <t>DOWNY PASSION 875ML</t>
   </si>
   <si>
+    <t>20141324</t>
+  </si>
+  <si>
+    <t>DOWNY SUNSHINE 500ML</t>
+  </si>
+  <si>
+    <t>20141323</t>
+  </si>
+  <si>
+    <t>DOWNY MIDNIGHT 500ML</t>
+  </si>
+  <si>
+    <t>20080360</t>
+  </si>
+  <si>
+    <t>DOWNY MYSTIQUE 550ML</t>
+  </si>
+  <si>
+    <t>20080361</t>
+  </si>
+  <si>
+    <t>DOWNY PASSION 550ML</t>
+  </si>
+  <si>
     <t>20074226</t>
   </si>
   <si>
     <t>DOWNY SUN.FRSH 550</t>
   </si>
   <si>
-    <t>20080360</t>
-  </si>
-  <si>
-    <t>DOWNY MYSTIQUE 550ML</t>
-  </si>
-  <si>
-    <t>20080361</t>
-  </si>
-  <si>
-    <t>DOWNY PASSION 550ML</t>
-  </si>
-  <si>
     <t>20139145</t>
   </si>
   <si>
     <t>DOWNY MLKY TOUCH 500</t>
-  </si>
-  <si>
-    <t>20141324</t>
-  </si>
-  <si>
-    <t>DOWNY SUNSHINE 500ML</t>
-  </si>
-  <si>
-    <t>20141323</t>
-  </si>
-  <si>
-    <t>DOWNY MIDNIGHT 500ML</t>
   </si>
   <si>
     <t>20140003</t>
@@ -4215,7 +4215,7 @@
         <v>14</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>199</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -4235,7 +4235,7 @@
         <v>18</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>199</v>
+        <v>15</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -4275,7 +4275,7 @@
         <v>35</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>15</v>
+        <v>199</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -4295,7 +4295,7 @@
         <v>38</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>15</v>
+        <v>199</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -5892,7 +5892,7 @@
         <v>387</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>83</v>
@@ -5912,7 +5912,7 @@
         <v>387</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5932,7 +5932,7 @@
         <v>387</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5952,7 +5952,7 @@
         <v>387</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5972,7 +5972,7 @@
         <v>387</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5992,7 +5992,7 @@
         <v>387</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>83</v>

--- a/DND05S.xlsx
+++ b/DND05S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1824" uniqueCount="660">
   <si>
     <t/>
   </si>
@@ -1177,6 +1177,15 @@
     <t>26</t>
   </si>
   <si>
+    <t>20141956</t>
+  </si>
+  <si>
+    <t>EKONOMI NANAS 920G</t>
+  </si>
+  <si>
+    <t>,(E-1B)</t>
+  </si>
+  <si>
     <t>20136124</t>
   </si>
   <si>
@@ -1465,15 +1474,27 @@
     <t>HARPIC PWR PLS CT450</t>
   </si>
   <si>
+    <t>20134373</t>
+  </si>
+  <si>
+    <t>STELLA ALAT+REFILL25</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>20134374</t>
+  </si>
+  <si>
+    <t>STELLA ELCTRIC LAV25</t>
+  </si>
+  <si>
     <t>10010232</t>
   </si>
   <si>
     <t>KIWI LIQ.SHOE BLCK75</t>
   </si>
   <si>
-    <t>32</t>
-  </si>
-  <si>
     <t>10007934</t>
   </si>
   <si>
@@ -1732,19 +1753,19 @@
     <t>STELLA IN ONE LMN 42</t>
   </si>
   <si>
-    <t>20134373</t>
-  </si>
-  <si>
-    <t>STELLA ALAT+REFILL25</t>
+    <t>20022902</t>
+  </si>
+  <si>
+    <t>HIT SPRAY ORG 180</t>
   </si>
   <si>
     <t>35</t>
   </si>
   <si>
-    <t>20134374</t>
-  </si>
-  <si>
-    <t>STELLA ELCTRIC LAV25</t>
+    <t>20064216</t>
+  </si>
+  <si>
+    <t>HIT INS.SPRY LILY180</t>
   </si>
   <si>
     <t>20139144</t>
@@ -1813,129 +1834,117 @@
     <t>VAPE SPRAY 1XSMP SKR</t>
   </si>
   <si>
+    <t>20124418</t>
+  </si>
+  <si>
+    <t>VAPE SWEET PWDR 200</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>20076987</t>
+  </si>
+  <si>
+    <t>BAYGON FLOW.GRDN 200</t>
+  </si>
+  <si>
+    <t>10015526</t>
+  </si>
+  <si>
+    <t>BAYGON SPRY LVND 750</t>
+  </si>
+  <si>
+    <t>20124346</t>
+  </si>
+  <si>
+    <t>BAYGON JPNSE&amp;PCH 600</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>20098605</t>
+  </si>
+  <si>
+    <t>BYGON SPRY CHR.BL600</t>
+  </si>
+  <si>
+    <t>10003272</t>
+  </si>
+  <si>
+    <t>BAYGON SPRY CITRS675</t>
+  </si>
+  <si>
+    <t>20071775</t>
+  </si>
+  <si>
+    <t>BAYGON FLO.GRDN 675</t>
+  </si>
+  <si>
+    <t>20139154</t>
+  </si>
+  <si>
+    <t>HIT COTTON PWD 600ML</t>
+  </si>
+  <si>
+    <t>20054151</t>
+  </si>
+  <si>
+    <t>HIT INS.SPRY LILY600</t>
+  </si>
+  <si>
+    <t>10005198</t>
+  </si>
+  <si>
+    <t>HIT INS.SPRAY ORG600</t>
+  </si>
+  <si>
+    <t>20109613</t>
+  </si>
+  <si>
+    <t>HIT SPRY.P/BLOSM 600</t>
+  </si>
+  <si>
+    <t>20080868</t>
+  </si>
+  <si>
+    <t>HIT FRESH CITRUS 600</t>
+  </si>
+  <si>
+    <t>20131365</t>
+  </si>
+  <si>
+    <t>HIT SPRY JPN.SKR 600</t>
+  </si>
+  <si>
+    <t>20139446</t>
+  </si>
+  <si>
+    <t>BAYGON CTRS FRSH 400</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>20128132</t>
+  </si>
+  <si>
+    <t>BAYGON FLO.GRDN 400</t>
+  </si>
+  <si>
     <t>20135247</t>
   </si>
   <si>
     <t>BAYGON FLRL.FNTSY500</t>
   </si>
   <si>
-    <t>36</t>
-  </si>
-  <si>
     <t>20135248</t>
   </si>
   <si>
     <t>BAYGON CHRRY BRRY500</t>
   </si>
   <si>
-    <t>10015526</t>
-  </si>
-  <si>
-    <t>BAYGON SPRY LVND 750</t>
-  </si>
-  <si>
-    <t>20124346</t>
-  </si>
-  <si>
-    <t>BAYGON JPNSE&amp;PCH 600</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20098605</t>
-  </si>
-  <si>
-    <t>BYGON SPRY CHR.BL600</t>
-  </si>
-  <si>
-    <t>10003272</t>
-  </si>
-  <si>
-    <t>BAYGON SPRY CITRS675</t>
-  </si>
-  <si>
-    <t>20071775</t>
-  </si>
-  <si>
-    <t>BAYGON FLO.GRDN 675</t>
-  </si>
-  <si>
-    <t>20139154</t>
-  </si>
-  <si>
-    <t>HIT COTTON PWD 600ML</t>
-  </si>
-  <si>
-    <t>20054151</t>
-  </si>
-  <si>
-    <t>HIT INS.SPRY LILY600</t>
-  </si>
-  <si>
-    <t>10005198</t>
-  </si>
-  <si>
-    <t>HIT INS.SPRAY ORG600</t>
-  </si>
-  <si>
-    <t>20109613</t>
-  </si>
-  <si>
-    <t>HIT SPRY.P/BLOSM 600</t>
-  </si>
-  <si>
-    <t>20080868</t>
-  </si>
-  <si>
-    <t>HIT FRESH CITRUS 600</t>
-  </si>
-  <si>
-    <t>20131365</t>
-  </si>
-  <si>
-    <t>HIT SPRY JPN.SKR 600</t>
-  </si>
-  <si>
-    <t>20076987</t>
-  </si>
-  <si>
-    <t>BAYGON FLOW.GRDN 200</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>20022902</t>
-  </si>
-  <si>
-    <t>HIT SPRAY ORG 180</t>
-  </si>
-  <si>
-    <t>20064216</t>
-  </si>
-  <si>
-    <t>HIT INS.SPRY LILY180</t>
-  </si>
-  <si>
-    <t>20124418</t>
-  </si>
-  <si>
-    <t>VAPE SWEET PWDR 200</t>
-  </si>
-  <si>
-    <t>20139446</t>
-  </si>
-  <si>
-    <t>BAYGON CTRS FRSH 400</t>
-  </si>
-  <si>
-    <t>20128132</t>
-  </si>
-  <si>
-    <t>BAYGON FLO.GRDN 400</t>
-  </si>
-  <si>
     <t>20088715</t>
   </si>
   <si>
@@ -1976,6 +1985,12 @@
   </si>
   <si>
     <t>VAPE FMK ORANGE 600</t>
+  </si>
+  <si>
+    <t>20142133</t>
+  </si>
+  <si>
+    <t>VAPE MILK TEA 600ML</t>
   </si>
 </sst>
 </file>
@@ -2368,7 +2383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F302"/>
+  <dimension ref="A1:F304"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -5892,18 +5907,18 @@
         <v>387</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>83</v>
+        <v>390</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
@@ -5912,18 +5927,18 @@
         <v>387</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
@@ -5932,7 +5947,7 @@
         <v>387</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5940,10 +5955,10 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
@@ -5952,7 +5967,7 @@
         <v>387</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5960,10 +5975,10 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
@@ -5972,7 +5987,7 @@
         <v>387</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5980,10 +5995,10 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
@@ -5992,30 +6007,30 @@
         <v>387</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -6029,10 +6044,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -6040,19 +6055,19 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D184" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B184" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>402</v>
-      </c>
       <c r="E184" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -6060,19 +6075,19 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -6080,19 +6095,19 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -6100,39 +6115,39 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>83</v>
@@ -6140,42 +6155,42 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>419</v>
+        <v>405</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -6189,50 +6204,50 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>257</v>
+        <v>21</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D192" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B192" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="E192" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>21</v>
+        <v>257</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>21</v>
@@ -6240,19 +6255,19 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>21</v>
@@ -6260,39 +6275,39 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>164</v>
+        <v>21</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>164</v>
@@ -6300,19 +6315,19 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>164</v>
@@ -6320,22 +6335,22 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>21</v>
+        <v>164</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -6349,10 +6364,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>21</v>
@@ -6360,19 +6375,19 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D200" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B200" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="C200" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="E200" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>21</v>
@@ -6380,19 +6395,19 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>21</v>
@@ -6400,19 +6415,19 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>21</v>
@@ -6429,10 +6444,10 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>21</v>
@@ -6440,19 +6455,19 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D204" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="B204" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D204" s="1" t="s">
-        <v>445</v>
-      </c>
       <c r="E204" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>21</v>
@@ -6460,79 +6475,79 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>164</v>
+        <v>83</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>104</v>
+        <v>164</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>104</v>
@@ -6540,62 +6555,62 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>351</v>
+        <v>104</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>320</v>
+        <v>351</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>21</v>
+        <v>320</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -6609,10 +6624,10 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>21</v>
@@ -6620,19 +6635,19 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D213" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="B213" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="C213" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D213" s="1" t="s">
-        <v>464</v>
-      </c>
       <c r="E213" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>21</v>
@@ -6640,102 +6655,102 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>5</v>
+        <v>304</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>164</v>
+        <v>5</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>479</v>
+        <v>164</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -6749,53 +6764,53 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>320</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>479</v>
+        <v>320</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>486</v>
+        <v>467</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>4</v>
+        <v>141</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>320</v>
+        <v>482</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -6809,90 +6824,90 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>320</v>
+        <v>5</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D223" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="B223" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="C223" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D223" s="1" t="s">
-        <v>486</v>
-      </c>
       <c r="E223" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>320</v>
+        <v>5</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>351</v>
+        <v>320</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F226" s="1" t="s">
         <v>320</v>
@@ -6900,59 +6915,59 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>304</v>
+        <v>351</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>351</v>
+        <v>304</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>320</v>
@@ -6960,79 +6975,79 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>83</v>
+        <v>351</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>179</v>
+        <v>152</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>104</v>
+        <v>320</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>198</v>
+        <v>163</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>320</v>
@@ -7040,42 +7055,42 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>218</v>
+        <v>179</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>515</v>
+        <v>489</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>4</v>
+        <v>198</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -7089,13 +7104,13 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>515</v>
+        <v>489</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -7109,13 +7124,13 @@
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>515</v>
+        <v>489</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>11</v>
+        <v>227</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>304</v>
+        <v>104</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -7129,30 +7144,30 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D239" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="B239" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="C239" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D239" s="1" t="s">
-        <v>515</v>
-      </c>
       <c r="E239" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F239" s="1" t="s">
         <v>304</v>
@@ -7160,19 +7175,19 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F240" s="1" t="s">
         <v>304</v>
@@ -7180,242 +7195,242 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>83</v>
+        <v>304</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>83</v>
+        <v>304</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>83</v>
+        <v>304</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>152</v>
+        <v>38</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>163</v>
+        <v>58</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>304</v>
+        <v>5</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>179</v>
+        <v>152</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>304</v>
+        <v>5</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>304</v>
+        <v>5</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>179</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>83</v>
+        <v>304</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="E251" s="1" t="s">
         <v>179</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>83</v>
+        <v>304</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>550</v>
+        <v>522</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>4</v>
+        <v>179</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>351</v>
+        <v>304</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7429,13 +7444,13 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>550</v>
+        <v>522</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>8</v>
+        <v>179</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>320</v>
+        <v>83</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -7449,13 +7464,13 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>550</v>
+        <v>522</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>11</v>
+        <v>179</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>320</v>
+        <v>83</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -7469,193 +7484,193 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>320</v>
+        <v>351</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="B256" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D256" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="B256" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="C256" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D256" s="1" t="s">
-        <v>550</v>
-      </c>
       <c r="E256" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>104</v>
+        <v>320</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>104</v>
+        <v>320</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>104</v>
+        <v>5</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>257</v>
+        <v>104</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>257</v>
+        <v>104</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>152</v>
+        <v>38</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>320</v>
+        <v>104</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>163</v>
+        <v>58</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>320</v>
+        <v>257</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>575</v>
+        <v>557</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>4</v>
+        <v>141</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>5</v>
+        <v>257</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -7669,13 +7684,13 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>575</v>
+        <v>557</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>8</v>
+        <v>152</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -7689,10 +7704,10 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>575</v>
+        <v>557</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>11</v>
+        <v>163</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>320</v>
@@ -7709,10 +7724,10 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>320</v>
@@ -7720,19 +7735,19 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="B268" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="C268" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D268" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="B268" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="C268" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D268" s="1" t="s">
-        <v>575</v>
-      </c>
       <c r="E268" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>320</v>
@@ -7740,19 +7755,19 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>320</v>
@@ -7760,19 +7775,19 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>320</v>
@@ -7780,19 +7795,19 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>320</v>
@@ -7800,122 +7815,122 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>152</v>
+        <v>38</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>163</v>
+        <v>58</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>602</v>
+        <v>582</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>4</v>
+        <v>152</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>320</v>
+        <v>5</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -7929,13 +7944,13 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>602</v>
+        <v>582</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>8</v>
+        <v>163</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>320</v>
+        <v>83</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -7949,13 +7964,13 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>602</v>
+        <v>582</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>11</v>
+        <v>179</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>320</v>
+        <v>83</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -7969,13 +7984,13 @@
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>609</v>
+        <v>5</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -7989,10 +8004,10 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>320</v>
@@ -8009,10 +8024,10 @@
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>320</v>
@@ -8029,50 +8044,50 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>320</v>
+        <v>616</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>320</v>
@@ -8080,19 +8095,19 @@
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>320</v>
@@ -8100,19 +8115,19 @@
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>152</v>
+        <v>38</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>5</v>
@@ -8120,39 +8135,39 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>163</v>
+        <v>58</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="F289" s="1" t="s">
         <v>320</v>
@@ -8160,22 +8175,22 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>630</v>
+        <v>609</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>4</v>
+        <v>152</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>320</v>
+        <v>5</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -8189,13 +8204,13 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>630</v>
+        <v>609</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>8</v>
+        <v>163</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>320</v>
+        <v>5</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -8209,10 +8224,10 @@
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>630</v>
+        <v>609</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>11</v>
+        <v>179</v>
       </c>
       <c r="F292" s="1" t="s">
         <v>320</v>
@@ -8229,50 +8244,50 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>5</v>
+        <v>351</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="B294" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="C294" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D294" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="B294" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="C294" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D294" s="1" t="s">
-        <v>630</v>
-      </c>
       <c r="E294" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>351</v>
+        <v>320</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F295" s="1" t="s">
         <v>320</v>
@@ -8280,19 +8295,19 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F296" s="1" t="s">
         <v>320</v>
@@ -8300,19 +8315,19 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="F297" s="1" t="s">
         <v>320</v>
@@ -8320,39 +8335,39 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="F299" s="1" t="s">
         <v>5</v>
@@ -8360,19 +8375,19 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>152</v>
+        <v>38</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>5</v>
@@ -8380,19 +8395,19 @@
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>163</v>
+        <v>58</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>5</v>
@@ -8400,22 +8415,62 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="F302" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A303" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="B303" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="C303" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D303" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="E303" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F303" s="1" t="s">
         <v>104</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A304" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B304" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C304" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D304" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="E304" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F304" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/DND05S.xlsx
+++ b/DND05S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1824" uniqueCount="660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1836" uniqueCount="665">
   <si>
     <t/>
   </si>
@@ -571,1426 +571,1441 @@
     <t>ROYALE SOFT BS 600</t>
   </si>
   <si>
+    <t>20113101</t>
+  </si>
+  <si>
+    <t>ROYALE SWT FLORL 600</t>
+  </si>
+  <si>
+    <t>20128706</t>
+  </si>
+  <si>
+    <t>ROYALE LNVDR VNL 600</t>
+  </si>
+  <si>
+    <t>20113093</t>
+  </si>
+  <si>
+    <t>ROYALE SUNNY DAY 600</t>
+  </si>
+  <si>
+    <t>20142010</t>
+  </si>
+  <si>
+    <t>ROYALE MTCHA BLS 600</t>
+  </si>
+  <si>
+    <t>20126740</t>
+  </si>
+  <si>
+    <t>MOLTO FRSH.CSBLCA650</t>
+  </si>
+  <si>
+    <t>20094735</t>
+  </si>
+  <si>
+    <t>DOWNY SUNRISE 950</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>PT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20094733</t>
+  </si>
+  <si>
+    <t>DOWNY MYSTIQUE 900</t>
+  </si>
+  <si>
+    <t>20140221</t>
+  </si>
+  <si>
+    <t>DOWNY PASSION 875ML</t>
+  </si>
+  <si>
+    <t>20141324</t>
+  </si>
+  <si>
+    <t>DOWNY SUNSHINE 500ML</t>
+  </si>
+  <si>
+    <t>20141323</t>
+  </si>
+  <si>
+    <t>DOWNY MIDNIGHT 500ML</t>
+  </si>
+  <si>
+    <t>20080360</t>
+  </si>
+  <si>
+    <t>DOWNY MYSTIQUE 550ML</t>
+  </si>
+  <si>
+    <t>20080361</t>
+  </si>
+  <si>
+    <t>DOWNY PASSION 550ML</t>
+  </si>
+  <si>
+    <t>20074226</t>
+  </si>
+  <si>
+    <t>DOWNY SUN.FRSH 550</t>
+  </si>
+  <si>
+    <t>20139145</t>
+  </si>
+  <si>
+    <t>DOWNY MLKY TOUCH 500</t>
+  </si>
+  <si>
+    <t>20140003</t>
+  </si>
+  <si>
+    <t>RNSO PWD ROSE.F 1.44</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20093521</t>
+  </si>
+  <si>
+    <t>RINSO+MOLTO ESC1440G</t>
+  </si>
+  <si>
+    <t>20139609</t>
+  </si>
+  <si>
+    <t>RNSO JPN PEAC 1440G</t>
+  </si>
+  <si>
+    <t>20140002</t>
+  </si>
+  <si>
+    <t>RINSO PWD PURE 1440G</t>
+  </si>
+  <si>
+    <t>20064413</t>
+  </si>
+  <si>
+    <t>ATCK JAZ1 S/CNTA 1.5</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20064414</t>
+  </si>
+  <si>
+    <t>ATTACK JAZ1 P/SGR1.5</t>
+  </si>
+  <si>
+    <t>20130527</t>
+  </si>
+  <si>
+    <t>ATTACK DET+SF RB 1.4</t>
+  </si>
+  <si>
+    <t>20138108</t>
+  </si>
+  <si>
+    <t>JAZ 1 PRPL BLS 1.4KG</t>
+  </si>
+  <si>
+    <t>20071827</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD ROSE 700</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20085113</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD PRFM 700</t>
+  </si>
+  <si>
+    <t>20123256</t>
+  </si>
+  <si>
+    <t>RINSO+MLT KRN STW700</t>
+  </si>
+  <si>
+    <t>20105968</t>
+  </si>
+  <si>
+    <t>RNSO PWD JPN PC 700G</t>
+  </si>
+  <si>
+    <t>20131516</t>
+  </si>
+  <si>
+    <t>LARIST DET.FRS BT450</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20113183</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD ROSE 380</t>
+  </si>
+  <si>
+    <t>20121372</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD PRFM 380</t>
+  </si>
+  <si>
+    <t>20128719</t>
+  </si>
+  <si>
+    <t>SOKLIN LVD&amp;LILY 425G</t>
+  </si>
+  <si>
+    <t>20042466</t>
+  </si>
+  <si>
+    <t>DAIA DET+SOFT 470G</t>
+  </si>
+  <si>
+    <t>20139595</t>
+  </si>
+  <si>
+    <t>MOLTO TRKA BDD 3X300</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20133398</t>
+  </si>
+  <si>
+    <t>TRKA PURE 300ML</t>
+  </si>
+  <si>
+    <t>10011440</t>
+  </si>
+  <si>
+    <t>RAPIKA LVDR SPLAS300</t>
+  </si>
+  <si>
+    <t>20084780</t>
+  </si>
+  <si>
+    <t>RAPIKA GOLD 250ML</t>
+  </si>
+  <si>
+    <t>20093193</t>
+  </si>
+  <si>
+    <t>RAPIKA PINK SKR 300</t>
+  </si>
+  <si>
+    <t>20138071</t>
+  </si>
+  <si>
+    <t>KISPRAY KASTURI 280</t>
+  </si>
+  <si>
+    <t>20074721</t>
+  </si>
+  <si>
+    <t>KISPRAY GLM.GOLD 280</t>
+  </si>
+  <si>
+    <t>20116685</t>
+  </si>
+  <si>
+    <t>KISPRAY ELG.SAPH 200</t>
+  </si>
+  <si>
+    <t>20032250</t>
+  </si>
+  <si>
+    <t>KISPRAY VIOLET PC280</t>
+  </si>
+  <si>
+    <t>20000980</t>
+  </si>
+  <si>
+    <t>KISPRAY VIOLET 318ML</t>
+  </si>
+  <si>
+    <t>20138470</t>
+  </si>
+  <si>
+    <t>SO KLN PWNG RED 1.7L</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>10005803</t>
+  </si>
+  <si>
+    <t>SOKLIN PWNGI RED 780</t>
+  </si>
+  <si>
+    <t>10007389</t>
+  </si>
+  <si>
+    <t>SOKLIN PWNGI PINK780</t>
+  </si>
+  <si>
+    <t>10008104</t>
+  </si>
+  <si>
+    <t>SO KLIN PWG BLUE 780</t>
+  </si>
+  <si>
+    <t>20108418</t>
+  </si>
+  <si>
+    <t>SOKLIN PWG HJB GR780</t>
+  </si>
+  <si>
+    <t>10005802</t>
+  </si>
+  <si>
+    <t>SOKLIN PEWANGI VL780</t>
+  </si>
+  <si>
+    <t>20141985</t>
+  </si>
+  <si>
+    <t>SO KLN TROP SUMR 780</t>
+  </si>
+  <si>
+    <t>20134526</t>
+  </si>
+  <si>
+    <t>SOKLIN PWG COT.FN780</t>
+  </si>
+  <si>
+    <t>20129370</t>
+  </si>
+  <si>
+    <t>MOLTO MORNING FRS550</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20129160</t>
+  </si>
+  <si>
+    <t>MOLTO LUXURY PRF 650</t>
+  </si>
+  <si>
+    <t>20128919</t>
+  </si>
+  <si>
+    <t>MOLTO SFTNR PURE 550</t>
+  </si>
+  <si>
+    <t>20087464</t>
+  </si>
+  <si>
+    <t>IDM PWNG PINK.PAS720</t>
+  </si>
+  <si>
+    <t>20137582</t>
+  </si>
+  <si>
+    <t>IDM PWNG ROM.AURA720</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20137581</t>
+  </si>
+  <si>
+    <t>IDM PWNG EXO.BLUE720</t>
+  </si>
+  <si>
+    <t>20020245</t>
+  </si>
+  <si>
+    <t>MOLTO PWNGI BLUE 765</t>
+  </si>
+  <si>
+    <t>20020226</t>
+  </si>
+  <si>
+    <t>MOLTO PWNGI PINK 765</t>
+  </si>
+  <si>
+    <t>20106821</t>
+  </si>
+  <si>
+    <t>MOLTO PURPLE 765ML</t>
+  </si>
+  <si>
+    <t>20135847</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT SUMMR600</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20135846</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT SPRNG600</t>
+  </si>
+  <si>
+    <t>20014403</t>
+  </si>
+  <si>
+    <t>BAYCLIN REGLR 1000ML</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>20082581</t>
+  </si>
+  <si>
+    <t>VANISH CAIR WHT 425</t>
+  </si>
+  <si>
+    <t>20052662</t>
+  </si>
+  <si>
+    <t>VANISH CAIR PCH 425</t>
+  </si>
+  <si>
+    <t>20089665</t>
+  </si>
+  <si>
+    <t>IDM PHLANG NODA 450</t>
+  </si>
+  <si>
+    <t>20079788</t>
+  </si>
+  <si>
+    <t>PROCLIN PCH 400ML</t>
+  </si>
+  <si>
+    <t>10025646</t>
+  </si>
+  <si>
+    <t>YURI TAF LMN&amp;LIME500</t>
+  </si>
+  <si>
+    <t>10014263</t>
+  </si>
+  <si>
+    <t>WIPOL KARBOL CMR 720</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>20001645</t>
+  </si>
+  <si>
+    <t>WIPOL KARBOL LMN 720</t>
+  </si>
+  <si>
+    <t>20090066</t>
+  </si>
+  <si>
+    <t>WIPOL SRH + JRK 720</t>
+  </si>
+  <si>
+    <t>20122478</t>
+  </si>
+  <si>
+    <t>WIPOL CITRUS FRS 390</t>
+  </si>
+  <si>
+    <t>20023111</t>
+  </si>
+  <si>
+    <t>SOS KARBOL CLS PN725</t>
+  </si>
+  <si>
+    <t>10013107</t>
+  </si>
+  <si>
+    <t>SUPERSOL PINE 720G</t>
+  </si>
+  <si>
+    <t>20104030</t>
+  </si>
+  <si>
+    <t>SUPER SOL SEREH720G</t>
+  </si>
+  <si>
+    <t>20132664</t>
+  </si>
+  <si>
+    <t>VIXAL KUAT SEGAR 600</t>
+  </si>
+  <si>
+    <t>10004612</t>
+  </si>
+  <si>
+    <t>SOS P.LNT ORANGE 700</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10004610</t>
+  </si>
+  <si>
+    <t>SOS P/LT APLL REF700</t>
+  </si>
+  <si>
+    <t>10010480</t>
+  </si>
+  <si>
+    <t>SPR PELL FRS.APEL760</t>
+  </si>
+  <si>
+    <t>20121373</t>
+  </si>
+  <si>
+    <t>SPR PELL AB CTRS 500</t>
+  </si>
+  <si>
+    <t>20137408</t>
+  </si>
+  <si>
+    <t>SPR PELL SAKURA 740</t>
+  </si>
+  <si>
+    <t>20001407</t>
+  </si>
+  <si>
+    <t>IDM P'LANTAI LAV 800</t>
+  </si>
+  <si>
+    <t>20001402</t>
+  </si>
+  <si>
+    <t>IDM P'LANTAI APL 800</t>
+  </si>
+  <si>
+    <t>20028779</t>
+  </si>
+  <si>
+    <t>IDM KRBOL WNG650(BR)</t>
+  </si>
+  <si>
+    <t>20089486</t>
+  </si>
+  <si>
+    <t>IDM KRBL SRH CTR 650</t>
+  </si>
+  <si>
+    <t>20128125</t>
+  </si>
+  <si>
+    <t>IDM PURPOSE CLN 375</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>20027963</t>
+  </si>
+  <si>
+    <t>IDM PMBERSH KACA 400</t>
+  </si>
+  <si>
+    <t>10003706</t>
+  </si>
+  <si>
+    <t>MR.MUSCLE ORGNL 400</t>
+  </si>
+  <si>
+    <t>10012548</t>
+  </si>
+  <si>
+    <t>SOKLIN RLX/LAV RF770</t>
+  </si>
+  <si>
+    <t>10003646</t>
+  </si>
+  <si>
+    <t>SO KLIN P/L APPLE770</t>
+  </si>
+  <si>
+    <t>10003645</t>
+  </si>
+  <si>
+    <t>SO KLIN P/L LMN 780</t>
+  </si>
+  <si>
+    <t>20101095</t>
+  </si>
+  <si>
+    <t>SO KLN LNT SEREH 770</t>
+  </si>
+  <si>
+    <t>20131223</t>
+  </si>
+  <si>
+    <t>SO KLN LNT CT.GRD700</t>
+  </si>
+  <si>
+    <t>20131788</t>
+  </si>
+  <si>
+    <t>MAMA LMN JR.NPS 950</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>20141956</t>
+  </si>
+  <si>
+    <t>EKONOMI NANAS 920G</t>
+  </si>
+  <si>
+    <t>,(E-1B)</t>
+  </si>
+  <si>
+    <t>20136124</t>
+  </si>
+  <si>
+    <t>EKNOMI LIQ N&amp;JN 675G</t>
+  </si>
+  <si>
+    <t>20092331</t>
+  </si>
+  <si>
+    <t>EKONOMI LIQ JR.NP650</t>
+  </si>
+  <si>
+    <t>20123812</t>
+  </si>
+  <si>
+    <t>EKONOMI LQ.SEREH 650</t>
+  </si>
+  <si>
+    <t>20107240</t>
+  </si>
+  <si>
+    <t>EKONOMI LIQ.SW&amp;JR650</t>
+  </si>
+  <si>
+    <t>20129722</t>
+  </si>
+  <si>
+    <t>BUKRIM LIQ.JRK NP550</t>
+  </si>
+  <si>
+    <t>20138518</t>
+  </si>
+  <si>
+    <t>KILAU NIPIS 630ML</t>
+  </si>
+  <si>
+    <t>20034450</t>
+  </si>
+  <si>
+    <t>MAMA/L JERUK NPS 690</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>10004067</t>
+  </si>
+  <si>
+    <t>MAMA/L PCH LEMON 690</t>
+  </si>
+  <si>
+    <t>20099424</t>
+  </si>
+  <si>
+    <t>MAMA LIME CHARCO 690</t>
+  </si>
+  <si>
+    <t>20052031</t>
+  </si>
+  <si>
+    <t>MAMA LIME GRN TEA690</t>
+  </si>
+  <si>
+    <t>10004068</t>
+  </si>
+  <si>
+    <t>MAMA LIME POUCH 690</t>
+  </si>
+  <si>
+    <t>20134303</t>
+  </si>
+  <si>
+    <t>MAMA/L REF YUZU 690</t>
+  </si>
+  <si>
+    <t>20137792</t>
+  </si>
+  <si>
+    <t>MAMA LIME GREEN 690</t>
+  </si>
+  <si>
+    <t>20034449</t>
+  </si>
+  <si>
+    <t>MAMA/L JERUK NPS 430</t>
+  </si>
+  <si>
+    <t>20090067</t>
+  </si>
+  <si>
+    <t>SNLGHT MINT A.BAU600</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>20086172</t>
+  </si>
+  <si>
+    <t>SNLIGHT MND.ORGE 600</t>
+  </si>
+  <si>
+    <t>20112492</t>
+  </si>
+  <si>
+    <t>SUNLIGHT JRK NPS400G</t>
+  </si>
+  <si>
+    <t>20128374</t>
+  </si>
+  <si>
+    <t>LFEBUOY REF LIME 650</t>
+  </si>
+  <si>
+    <t>20134576</t>
+  </si>
+  <si>
+    <t>LFEBUOY REF LEMON650</t>
+  </si>
+  <si>
+    <t>20141345</t>
+  </si>
+  <si>
+    <t>LARISST S/PCC PRG650</t>
+  </si>
+  <si>
+    <t>20073425</t>
+  </si>
+  <si>
+    <t>IDM P.PRNG JRK.N 650</t>
+  </si>
+  <si>
+    <t>20141204</t>
+  </si>
+  <si>
+    <t>IDM P.PRG JR.NPS 950</t>
+  </si>
+  <si>
+    <t>20112491</t>
+  </si>
+  <si>
+    <t>SNLIGHT LIME PCH 910</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>20139728</t>
+  </si>
+  <si>
+    <t>SNLGHT BIO BLBR 870G</t>
+  </si>
+  <si>
+    <t>10005482</t>
+  </si>
+  <si>
+    <t>SNLIGHT LIME PCH 660</t>
+  </si>
+  <si>
+    <t>20135144</t>
+  </si>
+  <si>
+    <t>SNLGHT BIO NATURE600</t>
+  </si>
+  <si>
+    <t>10013205</t>
+  </si>
+  <si>
+    <t>SUNLIGHT J/NIPIS.750</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>20139947</t>
+  </si>
+  <si>
+    <t>SNLGHT BIO BLBR 675G</t>
+  </si>
+  <si>
+    <t>20139948</t>
+  </si>
+  <si>
+    <t>SNLGHT BERY&amp;LIME 675</t>
+  </si>
+  <si>
+    <t>20135845</t>
+  </si>
+  <si>
+    <t>EKNOMI LIQ JR&amp;LMN650</t>
+  </si>
+  <si>
+    <t>20093919</t>
+  </si>
+  <si>
+    <t>IDM PURPOSE CLN 400</t>
+  </si>
+  <si>
+    <t>10003498</t>
+  </si>
+  <si>
+    <t>CLEAR PUMP ORIGNL500</t>
+  </si>
+  <si>
+    <t>10034652</t>
+  </si>
+  <si>
+    <t>GLADE OCEAN ESCP 350</t>
+  </si>
+  <si>
+    <t>20105576</t>
+  </si>
+  <si>
+    <t>STELLA A/F SAKURA350</t>
+  </si>
+  <si>
+    <t>10029632</t>
+  </si>
+  <si>
+    <t>STELLA ALAT MATIC</t>
+  </si>
+  <si>
+    <t>10004032</t>
+  </si>
+  <si>
+    <t>VIXAL KUAT HARUM 720</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>10004034</t>
+  </si>
+  <si>
+    <t>VIXAL KMR MD KUAT720</t>
+  </si>
+  <si>
+    <t>10003359</t>
+  </si>
+  <si>
+    <t>WIPOL CEMARA BTL 730</t>
+  </si>
+  <si>
+    <t>10000955</t>
+  </si>
+  <si>
+    <t>PORSTEX N.PARFUM 1L</t>
+  </si>
+  <si>
+    <t>10018962</t>
+  </si>
+  <si>
+    <t>YURI PORSTEX OB.B700</t>
+  </si>
+  <si>
+    <t>10005246</t>
+  </si>
+  <si>
+    <t>WING PRCLN CLN BR750</t>
+  </si>
+  <si>
+    <t>20040315</t>
+  </si>
+  <si>
+    <t>IDM PORSELEN BTL 800</t>
+  </si>
+  <si>
+    <t>20015040</t>
+  </si>
+  <si>
+    <t>HARPIC TRIPLE ACT450</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20095746</t>
+  </si>
+  <si>
+    <t>HRPC PNG.KRK CTR 405</t>
+  </si>
+  <si>
+    <t>20042956</t>
+  </si>
+  <si>
+    <t>HARPIC PWR PLS CT450</t>
+  </si>
+  <si>
+    <t>20134373</t>
+  </si>
+  <si>
+    <t>STELLA ALAT+REFILL25</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>20134374</t>
+  </si>
+  <si>
+    <t>STELLA ELCTRIC LAV25</t>
+  </si>
+  <si>
+    <t>10010232</t>
+  </si>
+  <si>
+    <t>KIWI LIQ.SHOE BLCK75</t>
+  </si>
+  <si>
+    <t>10007934</t>
+  </si>
+  <si>
+    <t>KIWI PASTE BLACK 45M</t>
+  </si>
+  <si>
+    <t>20012183</t>
+  </si>
+  <si>
+    <t>BAYGON BKR D.DRH 5'S</t>
+  </si>
+  <si>
+    <t>20014401</t>
+  </si>
+  <si>
+    <t>BYGON BKR JMB LVD 5S</t>
+  </si>
+  <si>
+    <t>20128711</t>
+  </si>
+  <si>
+    <t>AUTAN LOT.JRK&amp;LMN 50</t>
+  </si>
+  <si>
+    <t>20106983</t>
+  </si>
+  <si>
+    <t>AUTAN LOT.SAKURA 50</t>
+  </si>
+  <si>
+    <t>20054250</t>
+  </si>
+  <si>
+    <t>AUTAN REFRESH/S 100</t>
+  </si>
+  <si>
+    <t>20128713</t>
+  </si>
+  <si>
+    <t>SOFEL LOT.KRN/SMR 60</t>
+  </si>
+  <si>
+    <t>20078241</t>
+  </si>
+  <si>
+    <t>SOFFELL LOT.APEL 60G</t>
+  </si>
+  <si>
+    <t>10040202</t>
+  </si>
+  <si>
+    <t>SOFFELL A.NYMK K/J60</t>
+  </si>
+  <si>
+    <t>10037280</t>
+  </si>
+  <si>
+    <t>BAGUS KAPUR AJAIB</t>
+  </si>
+  <si>
+    <t>20109069</t>
+  </si>
+  <si>
+    <t>BAGUS LEM TIKUS PCS</t>
+  </si>
+  <si>
+    <t>10003479</t>
+  </si>
+  <si>
+    <t>GAJAH LEM TIKUS KT70</t>
+  </si>
+  <si>
+    <t>20139525</t>
+  </si>
+  <si>
+    <t>VAPE DORA LEM TIKUS</t>
+  </si>
+  <si>
+    <t>10037275</t>
+  </si>
+  <si>
+    <t>SWALLOW KMPR BTR 300</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>20027997</t>
+  </si>
+  <si>
+    <t>IDM KAMPER NAPTLN150</t>
+  </si>
+  <si>
+    <t>20131886</t>
+  </si>
+  <si>
+    <t>IDM KMPR DEO SKRA 5S</t>
+  </si>
+  <si>
+    <t>20131885</t>
+  </si>
+  <si>
+    <t>IDM KMPR DEO CFFE 5S</t>
+  </si>
+  <si>
+    <t>20079794</t>
+  </si>
+  <si>
+    <t>IDM KAMPER TOILET 5S</t>
+  </si>
+  <si>
+    <t>20139963</t>
+  </si>
+  <si>
+    <t>LARISST CTRONELLA 5S</t>
+  </si>
+  <si>
+    <t>10000279</t>
+  </si>
+  <si>
+    <t>SWALLOW TLT.BALL 5'S</t>
+  </si>
+  <si>
+    <t>10000482</t>
+  </si>
+  <si>
+    <t>SWALLOW K/DEO BAL105</t>
+  </si>
+  <si>
+    <t>20017478</t>
+  </si>
+  <si>
+    <t>SWALLOW ORG S-160</t>
+  </si>
+  <si>
+    <t>20122471</t>
+  </si>
+  <si>
+    <t>STELLA LAV.GRD 42+13</t>
+  </si>
+  <si>
+    <t>20136409</t>
+  </si>
+  <si>
+    <t>STELLA BALI JAS42+13</t>
+  </si>
+  <si>
+    <t>20109616</t>
+  </si>
+  <si>
+    <t>STELLA CAFF.LATTE 42</t>
+  </si>
+  <si>
+    <t>20075791</t>
+  </si>
+  <si>
+    <t>STELLA POCKET ORG 10</t>
+  </si>
+  <si>
+    <t>20075798</t>
+  </si>
+  <si>
+    <t>STLLA POCKET PRPL 10</t>
+  </si>
+  <si>
+    <t>20091307</t>
+  </si>
+  <si>
+    <t>STELLA POCKET BLU 10</t>
+  </si>
+  <si>
+    <t>20138481</t>
+  </si>
+  <si>
+    <t>STELLA EXO.FRUIT 10G</t>
+  </si>
+  <si>
+    <t>20138482</t>
+  </si>
+  <si>
+    <t>STELLA LUX.FLOWR 10G</t>
+  </si>
+  <si>
+    <t>20105573</t>
+  </si>
+  <si>
+    <t>STELLA AF REF JPS160</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>20037058</t>
+  </si>
+  <si>
+    <t>STELLA AF REF FLW160</t>
+  </si>
+  <si>
+    <t>20036827</t>
+  </si>
+  <si>
+    <t>STELLA AF REF GRN160</t>
+  </si>
+  <si>
+    <t>20044100</t>
+  </si>
+  <si>
+    <t>STELLA AF REF APL160</t>
+  </si>
+  <si>
+    <t>20135485</t>
+  </si>
+  <si>
+    <t>STELLA AF REF BAL160</t>
+  </si>
+  <si>
+    <t>20046210</t>
+  </si>
+  <si>
+    <t>GLADE OCN ESCPE 146G</t>
+  </si>
+  <si>
+    <t>10023003</t>
+  </si>
+  <si>
+    <t>GLADE PNY&amp;BRY BLS 70</t>
+  </si>
+  <si>
+    <t>10023002</t>
+  </si>
+  <si>
+    <t>GLADE FRESH ONE EF70</t>
+  </si>
+  <si>
+    <t>20096642</t>
+  </si>
+  <si>
+    <t>IDM FRSHNS LEMON 50</t>
+  </si>
+  <si>
+    <t>20096641</t>
+  </si>
+  <si>
+    <t>IDM FRSHNS ORANGE 50</t>
+  </si>
+  <si>
+    <t>10005428</t>
+  </si>
+  <si>
+    <t>STELLA IN ONE ORG 42</t>
+  </si>
+  <si>
+    <t>10005427</t>
+  </si>
+  <si>
+    <t>STELLA IN ONE LMN 42</t>
+  </si>
+  <si>
+    <t>20022902</t>
+  </si>
+  <si>
+    <t>HIT SPRAY ORG 180</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>20064216</t>
+  </si>
+  <si>
+    <t>HIT INS.SPRY LILY180</t>
+  </si>
+  <si>
+    <t>20139144</t>
+  </si>
+  <si>
+    <t>HIT XPRES PINK BL.35</t>
+  </si>
+  <si>
+    <t>20131161</t>
+  </si>
+  <si>
+    <t>HIT REF XPRES APLE35</t>
+  </si>
+  <si>
+    <t>20095744</t>
+  </si>
+  <si>
+    <t>HIT REF EXPRT FRS 35</t>
+  </si>
+  <si>
+    <t>20039183</t>
+  </si>
+  <si>
+    <t>HIT ALAT+REF EXP APL</t>
+  </si>
+  <si>
+    <t>10034732</t>
+  </si>
+  <si>
+    <t>HIT MAT ELECTRK 48'S</t>
+  </si>
+  <si>
+    <t>10027329</t>
+  </si>
+  <si>
+    <t>HIT ALT NYAMUK ELC 5</t>
+  </si>
+  <si>
+    <t>20084568</t>
+  </si>
+  <si>
+    <t>VAPE LIQ.SKR BLOSM45</t>
+  </si>
+  <si>
+    <t>20008748</t>
+  </si>
+  <si>
+    <t>VAPE LIQUID REF 45ML</t>
+  </si>
+  <si>
+    <t>20023870</t>
+  </si>
+  <si>
+    <t>VAPE LIQUID ELEKTRIK</t>
+  </si>
+  <si>
+    <t>20030445</t>
+  </si>
+  <si>
+    <t>VAPE SPRAY 1XSMP ORG</t>
+  </si>
+  <si>
+    <t>20073974</t>
+  </si>
+  <si>
+    <t>VAPE SPRAY 1XSMP SKR</t>
+  </si>
+  <si>
+    <t>20124418</t>
+  </si>
+  <si>
+    <t>VAPE SWEET PWDR 200</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>20076987</t>
+  </si>
+  <si>
+    <t>BAYGON FLOW.GRDN 200</t>
+  </si>
+  <si>
+    <t>10015526</t>
+  </si>
+  <si>
+    <t>BAYGON SPRY LVND 750</t>
+  </si>
+  <si>
+    <t>20124346</t>
+  </si>
+  <si>
+    <t>BAYGON JPNSE&amp;PCH 600</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>20098605</t>
+  </si>
+  <si>
+    <t>BYGON SPRY CHR.BL600</t>
+  </si>
+  <si>
+    <t>10003272</t>
+  </si>
+  <si>
+    <t>BAYGON SPRY CITRS675</t>
+  </si>
+  <si>
+    <t>20071775</t>
+  </si>
+  <si>
+    <t>BAYGON FLO.GRDN 675</t>
+  </si>
+  <si>
+    <t>20139154</t>
+  </si>
+  <si>
+    <t>HIT COTTON PWD 600ML</t>
+  </si>
+  <si>
+    <t>20054151</t>
+  </si>
+  <si>
+    <t>HIT INS.SPRY LILY600</t>
+  </si>
+  <si>
+    <t>10005198</t>
+  </si>
+  <si>
+    <t>HIT INS.SPRAY ORG600</t>
+  </si>
+  <si>
+    <t>20109613</t>
+  </si>
+  <si>
+    <t>HIT SPRY.P/BLOSM 600</t>
+  </si>
+  <si>
+    <t>20080868</t>
+  </si>
+  <si>
+    <t>HIT FRESH CITRUS 600</t>
+  </si>
+  <si>
+    <t>20131365</t>
+  </si>
+  <si>
+    <t>HIT SPRY JPN.SKR 600</t>
+  </si>
+  <si>
+    <t>20139446</t>
+  </si>
+  <si>
+    <t>BAYGON CTRS FRSH 400</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>20128132</t>
+  </si>
+  <si>
+    <t>BAYGON FLO.GRDN 400</t>
+  </si>
+  <si>
+    <t>20135247</t>
+  </si>
+  <si>
+    <t>BAYGON FLRL.FNTSY500</t>
+  </si>
+  <si>
+    <t>20135248</t>
+  </si>
+  <si>
+    <t>BAYGON CHRRY BRRY500</t>
+  </si>
+  <si>
+    <t>20088715</t>
+  </si>
+  <si>
+    <t>HIT SPRAY LILY 400ML</t>
+  </si>
+  <si>
+    <t>20022498</t>
+  </si>
+  <si>
+    <t>HIT SPRAY ORG 400ML</t>
+  </si>
+  <si>
+    <t>20134237</t>
+  </si>
+  <si>
+    <t>HIT SPRY.P/BLOSM 400</t>
+  </si>
+  <si>
+    <t>20136130</t>
+  </si>
+  <si>
+    <t>VAPE FLO.BUBBLE 600</t>
+  </si>
+  <si>
+    <t>20124850</t>
+  </si>
+  <si>
+    <t>VAPE SPRY SWET PD600</t>
+  </si>
+  <si>
+    <t>20136134</t>
+  </si>
+  <si>
+    <t>VAPE CANDY FLO 600</t>
+  </si>
+  <si>
+    <t>10006651</t>
+  </si>
+  <si>
+    <t>VAPE FMK ORANGE 600</t>
+  </si>
+  <si>
+    <t>20142133</t>
+  </si>
+  <si>
+    <t>VAPE MILK TEA 600ML</t>
+  </si>
+  <si>
+    <t>20125391</t>
+  </si>
+  <si>
+    <t>SOKLIN PWG AC/SPT780</t>
+  </si>
+  <si>
+    <t>999</t>
+  </si>
+  <si>
     <t>20098312</t>
   </si>
   <si>
     <t>ROYALE PINK STN 600</t>
-  </si>
-  <si>
-    <t>20113101</t>
-  </si>
-  <si>
-    <t>ROYALE SWT FLORL 600</t>
-  </si>
-  <si>
-    <t>20128706</t>
-  </si>
-  <si>
-    <t>ROYALE LNVDR VNL 600</t>
-  </si>
-  <si>
-    <t>20113093</t>
-  </si>
-  <si>
-    <t>ROYALE SUNNY DAY 600</t>
-  </si>
-  <si>
-    <t>20126740</t>
-  </si>
-  <si>
-    <t>MOLTO FRSH.CSBLCA650</t>
-  </si>
-  <si>
-    <t>20094735</t>
-  </si>
-  <si>
-    <t>DOWNY SUNRISE 950</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>PT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20094733</t>
-  </si>
-  <si>
-    <t>DOWNY MYSTIQUE 900</t>
-  </si>
-  <si>
-    <t>20140221</t>
-  </si>
-  <si>
-    <t>DOWNY PASSION 875ML</t>
-  </si>
-  <si>
-    <t>20141324</t>
-  </si>
-  <si>
-    <t>DOWNY SUNSHINE 500ML</t>
-  </si>
-  <si>
-    <t>20141323</t>
-  </si>
-  <si>
-    <t>DOWNY MIDNIGHT 500ML</t>
-  </si>
-  <si>
-    <t>20080360</t>
-  </si>
-  <si>
-    <t>DOWNY MYSTIQUE 550ML</t>
-  </si>
-  <si>
-    <t>20080361</t>
-  </si>
-  <si>
-    <t>DOWNY PASSION 550ML</t>
-  </si>
-  <si>
-    <t>20074226</t>
-  </si>
-  <si>
-    <t>DOWNY SUN.FRSH 550</t>
-  </si>
-  <si>
-    <t>20139145</t>
-  </si>
-  <si>
-    <t>DOWNY MLKY TOUCH 500</t>
-  </si>
-  <si>
-    <t>20140003</t>
-  </si>
-  <si>
-    <t>RNSO PWD ROSE.F 1.44</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20093521</t>
-  </si>
-  <si>
-    <t>RINSO+MOLTO ESC1440G</t>
-  </si>
-  <si>
-    <t>20139609</t>
-  </si>
-  <si>
-    <t>RNSO JPN PEAC 1440G</t>
-  </si>
-  <si>
-    <t>20140002</t>
-  </si>
-  <si>
-    <t>RINSO PWD PURE 1440G</t>
-  </si>
-  <si>
-    <t>20064413</t>
-  </si>
-  <si>
-    <t>ATCK JAZ1 S/CNTA 1.5</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20064414</t>
-  </si>
-  <si>
-    <t>ATTACK JAZ1 P/SGR1.5</t>
-  </si>
-  <si>
-    <t>20130527</t>
-  </si>
-  <si>
-    <t>ATTACK DET+SF RB 1.4</t>
-  </si>
-  <si>
-    <t>20138108</t>
-  </si>
-  <si>
-    <t>JAZ 1 PRPL BLS 1.4KG</t>
-  </si>
-  <si>
-    <t>20071827</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD ROSE 700</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20085113</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD PRFM 700</t>
-  </si>
-  <si>
-    <t>20123256</t>
-  </si>
-  <si>
-    <t>RINSO+MLT KRN STW700</t>
-  </si>
-  <si>
-    <t>20105968</t>
-  </si>
-  <si>
-    <t>RNSO PWD JPN PC 700G</t>
-  </si>
-  <si>
-    <t>20131516</t>
-  </si>
-  <si>
-    <t>LARIST DET.FRS BT450</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20113183</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD ROSE 380</t>
-  </si>
-  <si>
-    <t>20121372</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD PRFM 380</t>
-  </si>
-  <si>
-    <t>20128719</t>
-  </si>
-  <si>
-    <t>SOKLIN LVD&amp;LILY 425G</t>
-  </si>
-  <si>
-    <t>20042466</t>
-  </si>
-  <si>
-    <t>DAIA DET+SOFT 470G</t>
-  </si>
-  <si>
-    <t>20139595</t>
-  </si>
-  <si>
-    <t>MOLTO TRKA BDD 3X300</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20133398</t>
-  </si>
-  <si>
-    <t>TRKA PURE 300ML</t>
-  </si>
-  <si>
-    <t>10011440</t>
-  </si>
-  <si>
-    <t>RAPIKA LVDR SPLAS300</t>
-  </si>
-  <si>
-    <t>20084780</t>
-  </si>
-  <si>
-    <t>RAPIKA GOLD 250ML</t>
-  </si>
-  <si>
-    <t>20093193</t>
-  </si>
-  <si>
-    <t>RAPIKA PINK SKR 300</t>
-  </si>
-  <si>
-    <t>20138071</t>
-  </si>
-  <si>
-    <t>KISPRAY KASTURI 280</t>
-  </si>
-  <si>
-    <t>20074721</t>
-  </si>
-  <si>
-    <t>KISPRAY GLM.GOLD 280</t>
-  </si>
-  <si>
-    <t>20116685</t>
-  </si>
-  <si>
-    <t>KISPRAY ELG.SAPH 200</t>
-  </si>
-  <si>
-    <t>20032250</t>
-  </si>
-  <si>
-    <t>KISPRAY VIOLET PC280</t>
-  </si>
-  <si>
-    <t>20000980</t>
-  </si>
-  <si>
-    <t>KISPRAY VIOLET 318ML</t>
-  </si>
-  <si>
-    <t>20138470</t>
-  </si>
-  <si>
-    <t>SO KLN PWNG RED 1.7L</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>10005803</t>
-  </si>
-  <si>
-    <t>SOKLIN PWNGI RED 780</t>
-  </si>
-  <si>
-    <t>10007389</t>
-  </si>
-  <si>
-    <t>SOKLIN PWNGI PINK780</t>
-  </si>
-  <si>
-    <t>10008104</t>
-  </si>
-  <si>
-    <t>SO KLIN PWG BLUE 780</t>
-  </si>
-  <si>
-    <t>20108418</t>
-  </si>
-  <si>
-    <t>SOKLIN PWG HJB GR780</t>
-  </si>
-  <si>
-    <t>10005802</t>
-  </si>
-  <si>
-    <t>SOKLIN PEWANGI VL780</t>
-  </si>
-  <si>
-    <t>20134526</t>
-  </si>
-  <si>
-    <t>SOKLIN PWG COT.FN780</t>
-  </si>
-  <si>
-    <t>20125391</t>
-  </si>
-  <si>
-    <t>SOKLIN PWG AC/SPT780</t>
-  </si>
-  <si>
-    <t>20129370</t>
-  </si>
-  <si>
-    <t>MOLTO MORNING FRS550</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20129160</t>
-  </si>
-  <si>
-    <t>MOLTO LUXURY PRF 650</t>
-  </si>
-  <si>
-    <t>20128919</t>
-  </si>
-  <si>
-    <t>MOLTO SFTNR PURE 550</t>
-  </si>
-  <si>
-    <t>20087464</t>
-  </si>
-  <si>
-    <t>IDM PWNG PINK.PAS720</t>
-  </si>
-  <si>
-    <t>20137582</t>
-  </si>
-  <si>
-    <t>IDM PWNG ROM.AURA720</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20137581</t>
-  </si>
-  <si>
-    <t>IDM PWNG EXO.BLUE720</t>
-  </si>
-  <si>
-    <t>20020245</t>
-  </si>
-  <si>
-    <t>MOLTO PWNGI BLUE 765</t>
-  </si>
-  <si>
-    <t>20020226</t>
-  </si>
-  <si>
-    <t>MOLTO PWNGI PINK 765</t>
-  </si>
-  <si>
-    <t>20106821</t>
-  </si>
-  <si>
-    <t>MOLTO PURPLE 765ML</t>
-  </si>
-  <si>
-    <t>20135847</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT SUMMR600</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>20135846</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT SPRNG600</t>
-  </si>
-  <si>
-    <t>20014403</t>
-  </si>
-  <si>
-    <t>BAYCLIN REGLR 1000ML</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>20082581</t>
-  </si>
-  <si>
-    <t>VANISH CAIR WHT 425</t>
-  </si>
-  <si>
-    <t>20052662</t>
-  </si>
-  <si>
-    <t>VANISH CAIR PCH 425</t>
-  </si>
-  <si>
-    <t>20089665</t>
-  </si>
-  <si>
-    <t>IDM PHLANG NODA 450</t>
-  </si>
-  <si>
-    <t>20079788</t>
-  </si>
-  <si>
-    <t>PROCLIN PCH 400ML</t>
-  </si>
-  <si>
-    <t>10025646</t>
-  </si>
-  <si>
-    <t>YURI TAF LMN&amp;LIME500</t>
-  </si>
-  <si>
-    <t>10014263</t>
-  </si>
-  <si>
-    <t>WIPOL KARBOL CMR 720</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>20001645</t>
-  </si>
-  <si>
-    <t>WIPOL KARBOL LMN 720</t>
-  </si>
-  <si>
-    <t>20090066</t>
-  </si>
-  <si>
-    <t>WIPOL SRH + JRK 720</t>
-  </si>
-  <si>
-    <t>20122478</t>
-  </si>
-  <si>
-    <t>WIPOL CITRUS FRS 390</t>
-  </si>
-  <si>
-    <t>20023111</t>
-  </si>
-  <si>
-    <t>SOS KARBOL CLS PN725</t>
-  </si>
-  <si>
-    <t>10013107</t>
-  </si>
-  <si>
-    <t>SUPERSOL PINE 720G</t>
-  </si>
-  <si>
-    <t>20104030</t>
-  </si>
-  <si>
-    <t>SUPER SOL SEREH720G</t>
-  </si>
-  <si>
-    <t>20132664</t>
-  </si>
-  <si>
-    <t>VIXAL KUAT SEGAR 600</t>
-  </si>
-  <si>
-    <t>10004612</t>
-  </si>
-  <si>
-    <t>SOS P.LNT ORANGE 700</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10004610</t>
-  </si>
-  <si>
-    <t>SOS P/LT APLL REF700</t>
-  </si>
-  <si>
-    <t>10010480</t>
-  </si>
-  <si>
-    <t>SPR PELL FRS.APEL760</t>
-  </si>
-  <si>
-    <t>20121373</t>
-  </si>
-  <si>
-    <t>SPR PELL AB CTRS 500</t>
-  </si>
-  <si>
-    <t>20137408</t>
-  </si>
-  <si>
-    <t>SPR PELL SAKURA 740</t>
-  </si>
-  <si>
-    <t>20001407</t>
-  </si>
-  <si>
-    <t>IDM P'LANTAI LAV 800</t>
-  </si>
-  <si>
-    <t>20001402</t>
-  </si>
-  <si>
-    <t>IDM P'LANTAI APL 800</t>
-  </si>
-  <si>
-    <t>20028779</t>
-  </si>
-  <si>
-    <t>IDM KRBOL WNG650(BR)</t>
-  </si>
-  <si>
-    <t>20089486</t>
-  </si>
-  <si>
-    <t>IDM KRBL SRH CTR 650</t>
-  </si>
-  <si>
-    <t>20128125</t>
-  </si>
-  <si>
-    <t>IDM PURPOSE CLN 375</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>20027963</t>
-  </si>
-  <si>
-    <t>IDM PMBERSH KACA 400</t>
-  </si>
-  <si>
-    <t>10003706</t>
-  </si>
-  <si>
-    <t>MR.MUSCLE ORGNL 400</t>
-  </si>
-  <si>
-    <t>10012548</t>
-  </si>
-  <si>
-    <t>SOKLIN RLX/LAV RF770</t>
-  </si>
-  <si>
-    <t>10003646</t>
-  </si>
-  <si>
-    <t>SO KLIN P/L APPLE770</t>
-  </si>
-  <si>
-    <t>10003645</t>
-  </si>
-  <si>
-    <t>SO KLIN P/L LMN 780</t>
-  </si>
-  <si>
-    <t>20101095</t>
-  </si>
-  <si>
-    <t>SO KLN LNT SEREH 770</t>
-  </si>
-  <si>
-    <t>20131223</t>
-  </si>
-  <si>
-    <t>SO KLN LNT CT.GRD700</t>
-  </si>
-  <si>
-    <t>20131788</t>
-  </si>
-  <si>
-    <t>MAMA LMN JR.NPS 950</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>20141956</t>
-  </si>
-  <si>
-    <t>EKONOMI NANAS 920G</t>
-  </si>
-  <si>
-    <t>,(E-1B)</t>
-  </si>
-  <si>
-    <t>20136124</t>
-  </si>
-  <si>
-    <t>EKNOMI LIQ N&amp;JN 675G</t>
-  </si>
-  <si>
-    <t>20092331</t>
-  </si>
-  <si>
-    <t>EKONOMI LIQ JR.NP650</t>
-  </si>
-  <si>
-    <t>20123812</t>
-  </si>
-  <si>
-    <t>EKONOMI LQ.SEREH 650</t>
-  </si>
-  <si>
-    <t>20107240</t>
-  </si>
-  <si>
-    <t>EKONOMI LIQ.SW&amp;JR650</t>
-  </si>
-  <si>
-    <t>20129722</t>
-  </si>
-  <si>
-    <t>BUKRIM LIQ.JRK NP550</t>
-  </si>
-  <si>
-    <t>20138518</t>
-  </si>
-  <si>
-    <t>KILAU NIPIS 630ML</t>
-  </si>
-  <si>
-    <t>20034450</t>
-  </si>
-  <si>
-    <t>MAMA/L JERUK NPS 690</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>10004067</t>
-  </si>
-  <si>
-    <t>MAMA/L PCH LEMON 690</t>
-  </si>
-  <si>
-    <t>20099424</t>
-  </si>
-  <si>
-    <t>MAMA LIME CHARCO 690</t>
-  </si>
-  <si>
-    <t>20052031</t>
-  </si>
-  <si>
-    <t>MAMA LIME GRN TEA690</t>
-  </si>
-  <si>
-    <t>10004068</t>
-  </si>
-  <si>
-    <t>MAMA LIME POUCH 690</t>
-  </si>
-  <si>
-    <t>20134303</t>
-  </si>
-  <si>
-    <t>MAMA/L REF YUZU 690</t>
-  </si>
-  <si>
-    <t>20137792</t>
-  </si>
-  <si>
-    <t>MAMA LIME GREEN 690</t>
-  </si>
-  <si>
-    <t>20034449</t>
-  </si>
-  <si>
-    <t>MAMA/L JERUK NPS 430</t>
-  </si>
-  <si>
-    <t>20090067</t>
-  </si>
-  <si>
-    <t>SNLGHT MINT A.BAU600</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>20086172</t>
-  </si>
-  <si>
-    <t>SNLIGHT MND.ORGE 600</t>
-  </si>
-  <si>
-    <t>20112492</t>
-  </si>
-  <si>
-    <t>SUNLIGHT JRK NPS400G</t>
-  </si>
-  <si>
-    <t>20128374</t>
-  </si>
-  <si>
-    <t>LFEBUOY REF LIME 650</t>
-  </si>
-  <si>
-    <t>20134576</t>
-  </si>
-  <si>
-    <t>LFEBUOY REF LEMON650</t>
-  </si>
-  <si>
-    <t>20141345</t>
-  </si>
-  <si>
-    <t>LARISST S/PCC PRG650</t>
-  </si>
-  <si>
-    <t>20073425</t>
-  </si>
-  <si>
-    <t>IDM P.PRNG JRK.N 650</t>
-  </si>
-  <si>
-    <t>20141204</t>
-  </si>
-  <si>
-    <t>IDM P.PRG JR.NPS 950</t>
-  </si>
-  <si>
-    <t>20112491</t>
-  </si>
-  <si>
-    <t>SNLIGHT LIME PCH 910</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>20139728</t>
-  </si>
-  <si>
-    <t>SNLGHT BIO BLBR 870G</t>
-  </si>
-  <si>
-    <t>10005482</t>
-  </si>
-  <si>
-    <t>SNLIGHT LIME PCH 660</t>
-  </si>
-  <si>
-    <t>20135144</t>
-  </si>
-  <si>
-    <t>SNLGHT BIO NATURE600</t>
-  </si>
-  <si>
-    <t>10013205</t>
-  </si>
-  <si>
-    <t>SUNLIGHT J/NIPIS.750</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>20139947</t>
-  </si>
-  <si>
-    <t>SNLGHT BIO BLBR 675G</t>
-  </si>
-  <si>
-    <t>20139948</t>
-  </si>
-  <si>
-    <t>SNLGHT BERY&amp;LIME 675</t>
-  </si>
-  <si>
-    <t>20135845</t>
-  </si>
-  <si>
-    <t>EKNOMI LIQ JR&amp;LMN650</t>
-  </si>
-  <si>
-    <t>20093919</t>
-  </si>
-  <si>
-    <t>IDM PURPOSE CLN 400</t>
-  </si>
-  <si>
-    <t>10003498</t>
-  </si>
-  <si>
-    <t>CLEAR PUMP ORIGNL500</t>
-  </si>
-  <si>
-    <t>10034652</t>
-  </si>
-  <si>
-    <t>GLADE OCEAN ESCP 350</t>
-  </si>
-  <si>
-    <t>20105576</t>
-  </si>
-  <si>
-    <t>STELLA A/F SAKURA350</t>
-  </si>
-  <si>
-    <t>10029632</t>
-  </si>
-  <si>
-    <t>STELLA ALAT MATIC</t>
-  </si>
-  <si>
-    <t>10004032</t>
-  </si>
-  <si>
-    <t>VIXAL KUAT HARUM 720</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>10004034</t>
-  </si>
-  <si>
-    <t>VIXAL KMR MD KUAT720</t>
-  </si>
-  <si>
-    <t>10003359</t>
-  </si>
-  <si>
-    <t>WIPOL CEMARA BTL 730</t>
-  </si>
-  <si>
-    <t>10000955</t>
-  </si>
-  <si>
-    <t>PORSTEX N.PARFUM 1L</t>
-  </si>
-  <si>
-    <t>10018962</t>
-  </si>
-  <si>
-    <t>YURI PORSTEX OB.B700</t>
-  </si>
-  <si>
-    <t>10005246</t>
-  </si>
-  <si>
-    <t>WING PRCLN CLN BR750</t>
-  </si>
-  <si>
-    <t>20040315</t>
-  </si>
-  <si>
-    <t>IDM PORSELEN BTL 800</t>
-  </si>
-  <si>
-    <t>20015040</t>
-  </si>
-  <si>
-    <t>HARPIC TRIPLE ACT450</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20095746</t>
-  </si>
-  <si>
-    <t>HRPC PNG.KRK CTR 405</t>
-  </si>
-  <si>
-    <t>20042956</t>
-  </si>
-  <si>
-    <t>HARPIC PWR PLS CT450</t>
-  </si>
-  <si>
-    <t>20134373</t>
-  </si>
-  <si>
-    <t>STELLA ALAT+REFILL25</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>20134374</t>
-  </si>
-  <si>
-    <t>STELLA ELCTRIC LAV25</t>
-  </si>
-  <si>
-    <t>10010232</t>
-  </si>
-  <si>
-    <t>KIWI LIQ.SHOE BLCK75</t>
-  </si>
-  <si>
-    <t>10007934</t>
-  </si>
-  <si>
-    <t>KIWI PASTE BLACK 45M</t>
-  </si>
-  <si>
-    <t>20012183</t>
-  </si>
-  <si>
-    <t>BAYGON BKR D.DRH 5'S</t>
-  </si>
-  <si>
-    <t>20014401</t>
-  </si>
-  <si>
-    <t>BYGON BKR JMB LVD 5S</t>
-  </si>
-  <si>
-    <t>20128711</t>
-  </si>
-  <si>
-    <t>AUTAN LOT.JRK&amp;LMN 50</t>
-  </si>
-  <si>
-    <t>20106983</t>
-  </si>
-  <si>
-    <t>AUTAN LOT.SAKURA 50</t>
-  </si>
-  <si>
-    <t>20054250</t>
-  </si>
-  <si>
-    <t>AUTAN REFRESH/S 100</t>
-  </si>
-  <si>
-    <t>20128713</t>
-  </si>
-  <si>
-    <t>SOFEL LOT.KRN/SMR 60</t>
-  </si>
-  <si>
-    <t>20078241</t>
-  </si>
-  <si>
-    <t>SOFFELL LOT.APEL 60G</t>
-  </si>
-  <si>
-    <t>10040202</t>
-  </si>
-  <si>
-    <t>SOFFELL A.NYMK K/J60</t>
-  </si>
-  <si>
-    <t>10037280</t>
-  </si>
-  <si>
-    <t>BAGUS KAPUR AJAIB</t>
-  </si>
-  <si>
-    <t>20109069</t>
-  </si>
-  <si>
-    <t>BAGUS LEM TIKUS PCS</t>
-  </si>
-  <si>
-    <t>10003479</t>
-  </si>
-  <si>
-    <t>GAJAH LEM TIKUS KT70</t>
-  </si>
-  <si>
-    <t>20139525</t>
-  </si>
-  <si>
-    <t>VAPE DORA LEM TIKUS</t>
-  </si>
-  <si>
-    <t>10037275</t>
-  </si>
-  <si>
-    <t>SWALLOW KMPR BTR 300</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>20027997</t>
-  </si>
-  <si>
-    <t>IDM KAMPER NAPTLN150</t>
-  </si>
-  <si>
-    <t>20131886</t>
-  </si>
-  <si>
-    <t>IDM KMPR DEO SKRA 5S</t>
-  </si>
-  <si>
-    <t>20131885</t>
-  </si>
-  <si>
-    <t>IDM KMPR DEO CFFE 5S</t>
-  </si>
-  <si>
-    <t>20079794</t>
-  </si>
-  <si>
-    <t>IDM KAMPER TOILET 5S</t>
-  </si>
-  <si>
-    <t>20139963</t>
-  </si>
-  <si>
-    <t>LARISST CTRONELLA 5S</t>
-  </si>
-  <si>
-    <t>10000279</t>
-  </si>
-  <si>
-    <t>SWALLOW TLT.BALL 5'S</t>
-  </si>
-  <si>
-    <t>10000482</t>
-  </si>
-  <si>
-    <t>SWALLOW K/DEO BAL105</t>
-  </si>
-  <si>
-    <t>20017478</t>
-  </si>
-  <si>
-    <t>SWALLOW ORG S-160</t>
-  </si>
-  <si>
-    <t>20122471</t>
-  </si>
-  <si>
-    <t>STELLA LAV.GRD 42+13</t>
-  </si>
-  <si>
-    <t>20136409</t>
-  </si>
-  <si>
-    <t>STELLA BALI JAS42+13</t>
-  </si>
-  <si>
-    <t>20109616</t>
-  </si>
-  <si>
-    <t>STELLA CAFF.LATTE 42</t>
-  </si>
-  <si>
-    <t>20075791</t>
-  </si>
-  <si>
-    <t>STELLA POCKET ORG 10</t>
-  </si>
-  <si>
-    <t>20075798</t>
-  </si>
-  <si>
-    <t>STLLA POCKET PRPL 10</t>
-  </si>
-  <si>
-    <t>20091307</t>
-  </si>
-  <si>
-    <t>STELLA POCKET BLU 10</t>
-  </si>
-  <si>
-    <t>20138481</t>
-  </si>
-  <si>
-    <t>STELLA EXO.FRUIT 10G</t>
-  </si>
-  <si>
-    <t>20138482</t>
-  </si>
-  <si>
-    <t>STELLA LUX.FLOWR 10G</t>
-  </si>
-  <si>
-    <t>20105573</t>
-  </si>
-  <si>
-    <t>STELLA AF REF JPS160</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>20037058</t>
-  </si>
-  <si>
-    <t>STELLA AF REF FLW160</t>
-  </si>
-  <si>
-    <t>20036827</t>
-  </si>
-  <si>
-    <t>STELLA AF REF GRN160</t>
-  </si>
-  <si>
-    <t>20044100</t>
-  </si>
-  <si>
-    <t>STELLA AF REF APL160</t>
-  </si>
-  <si>
-    <t>20135485</t>
-  </si>
-  <si>
-    <t>STELLA AF REF BAL160</t>
-  </si>
-  <si>
-    <t>20046210</t>
-  </si>
-  <si>
-    <t>GLADE OCN ESCPE 146G</t>
-  </si>
-  <si>
-    <t>10023003</t>
-  </si>
-  <si>
-    <t>GLADE PNY&amp;BRY BLS 70</t>
-  </si>
-  <si>
-    <t>10023002</t>
-  </si>
-  <si>
-    <t>GLADE FRESH ONE EF70</t>
-  </si>
-  <si>
-    <t>20096642</t>
-  </si>
-  <si>
-    <t>IDM FRSHNS LEMON 50</t>
-  </si>
-  <si>
-    <t>20096641</t>
-  </si>
-  <si>
-    <t>IDM FRSHNS ORANGE 50</t>
-  </si>
-  <si>
-    <t>10005428</t>
-  </si>
-  <si>
-    <t>STELLA IN ONE ORG 42</t>
-  </si>
-  <si>
-    <t>10005427</t>
-  </si>
-  <si>
-    <t>STELLA IN ONE LMN 42</t>
-  </si>
-  <si>
-    <t>20022902</t>
-  </si>
-  <si>
-    <t>HIT SPRAY ORG 180</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>20064216</t>
-  </si>
-  <si>
-    <t>HIT INS.SPRY LILY180</t>
-  </si>
-  <si>
-    <t>20139144</t>
-  </si>
-  <si>
-    <t>HIT XPRES PINK BL.35</t>
-  </si>
-  <si>
-    <t>20131161</t>
-  </si>
-  <si>
-    <t>HIT REF XPRES APLE35</t>
-  </si>
-  <si>
-    <t>20095744</t>
-  </si>
-  <si>
-    <t>HIT REF EXPRT FRS 35</t>
-  </si>
-  <si>
-    <t>20039183</t>
-  </si>
-  <si>
-    <t>HIT ALAT+REF EXP APL</t>
-  </si>
-  <si>
-    <t>10034732</t>
-  </si>
-  <si>
-    <t>HIT MAT ELECTRK 48'S</t>
-  </si>
-  <si>
-    <t>10027329</t>
-  </si>
-  <si>
-    <t>HIT ALT NYAMUK ELC 5</t>
-  </si>
-  <si>
-    <t>20084568</t>
-  </si>
-  <si>
-    <t>VAPE LIQ.SKR BLOSM45</t>
-  </si>
-  <si>
-    <t>20008748</t>
-  </si>
-  <si>
-    <t>VAPE LIQUID REF 45ML</t>
-  </si>
-  <si>
-    <t>20023870</t>
-  </si>
-  <si>
-    <t>VAPE LIQUID ELEKTRIK</t>
-  </si>
-  <si>
-    <t>20030445</t>
-  </si>
-  <si>
-    <t>VAPE SPRAY 1XSMP ORG</t>
-  </si>
-  <si>
-    <t>20073974</t>
-  </si>
-  <si>
-    <t>VAPE SPRAY 1XSMP SKR</t>
-  </si>
-  <si>
-    <t>20124418</t>
-  </si>
-  <si>
-    <t>VAPE SWEET PWDR 200</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>20076987</t>
-  </si>
-  <si>
-    <t>BAYGON FLOW.GRDN 200</t>
-  </si>
-  <si>
-    <t>10015526</t>
-  </si>
-  <si>
-    <t>BAYGON SPRY LVND 750</t>
-  </si>
-  <si>
-    <t>20124346</t>
-  </si>
-  <si>
-    <t>BAYGON JPNSE&amp;PCH 600</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20098605</t>
-  </si>
-  <si>
-    <t>BYGON SPRY CHR.BL600</t>
-  </si>
-  <si>
-    <t>10003272</t>
-  </si>
-  <si>
-    <t>BAYGON SPRY CITRS675</t>
-  </si>
-  <si>
-    <t>20071775</t>
-  </si>
-  <si>
-    <t>BAYGON FLO.GRDN 675</t>
-  </si>
-  <si>
-    <t>20139154</t>
-  </si>
-  <si>
-    <t>HIT COTTON PWD 600ML</t>
-  </si>
-  <si>
-    <t>20054151</t>
-  </si>
-  <si>
-    <t>HIT INS.SPRY LILY600</t>
-  </si>
-  <si>
-    <t>10005198</t>
-  </si>
-  <si>
-    <t>HIT INS.SPRAY ORG600</t>
-  </si>
-  <si>
-    <t>20109613</t>
-  </si>
-  <si>
-    <t>HIT SPRY.P/BLOSM 600</t>
-  </si>
-  <si>
-    <t>20080868</t>
-  </si>
-  <si>
-    <t>HIT FRESH CITRUS 600</t>
-  </si>
-  <si>
-    <t>20131365</t>
-  </si>
-  <si>
-    <t>HIT SPRY JPN.SKR 600</t>
-  </si>
-  <si>
-    <t>20139446</t>
-  </si>
-  <si>
-    <t>BAYGON CTRS FRSH 400</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>20128132</t>
-  </si>
-  <si>
-    <t>BAYGON FLO.GRDN 400</t>
-  </si>
-  <si>
-    <t>20135247</t>
-  </si>
-  <si>
-    <t>BAYGON FLRL.FNTSY500</t>
-  </si>
-  <si>
-    <t>20135248</t>
-  </si>
-  <si>
-    <t>BAYGON CHRRY BRRY500</t>
-  </si>
-  <si>
-    <t>20088715</t>
-  </si>
-  <si>
-    <t>HIT SPRAY LILY 400ML</t>
-  </si>
-  <si>
-    <t>20022498</t>
-  </si>
-  <si>
-    <t>HIT SPRAY ORG 400ML</t>
-  </si>
-  <si>
-    <t>20134237</t>
-  </si>
-  <si>
-    <t>HIT SPRY.P/BLOSM 400</t>
-  </si>
-  <si>
-    <t>20136130</t>
-  </si>
-  <si>
-    <t>VAPE FLO.BUBBLE 600</t>
-  </si>
-  <si>
-    <t>20124850</t>
-  </si>
-  <si>
-    <t>VAPE SPRY SWET PD600</t>
-  </si>
-  <si>
-    <t>20136134</t>
-  </si>
-  <si>
-    <t>VAPE CANDY FLO 600</t>
-  </si>
-  <si>
-    <t>10006651</t>
-  </si>
-  <si>
-    <t>VAPE FMK ORANGE 600</t>
-  </si>
-  <si>
-    <t>20142133</t>
-  </si>
-  <si>
-    <t>VAPE MILK TEA 600ML</t>
   </si>
 </sst>
 </file>
@@ -2383,13 +2398,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F304"/>
+  <dimension ref="A1:F306"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="5" width="4" customWidth="1"/>
+    <col min="4" max="4" width="5" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8473,6 +8489,46 @@
         <v>5</v>
       </c>
     </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A305" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="B305" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="C305" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D305" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="E305" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F305" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A306" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="B306" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="C306" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D306" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="E306" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F306" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/DND05S.xlsx
+++ b/DND05S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1836" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="669">
   <si>
     <t/>
   </si>
@@ -79,6 +79,12 @@
     <t>PT</t>
   </si>
   <si>
+    <t>20099812</t>
+  </si>
+  <si>
+    <t>RNSO+ML LIQ PRF1.5L</t>
+  </si>
+  <si>
     <t>20109454</t>
   </si>
   <si>
@@ -103,13 +109,16 @@
     <t>SO KLIN VL/BLSOM 700</t>
   </si>
   <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>20046548</t>
   </si>
   <si>
     <t>SOKLIN SOFT CAIR 700</t>
   </si>
   <si>
-    <t>6</t>
+    <t>7</t>
   </si>
   <si>
     <t>20137791</t>
@@ -118,7 +127,370 @@
     <t>SO KLIN LIQ HJB 700</t>
   </si>
   <si>
-    <t>7</t>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20037446</t>
+  </si>
+  <si>
+    <t>RNSO+ML LIQ ROSE 700</t>
+  </si>
+  <si>
+    <t>20138867</t>
+  </si>
+  <si>
+    <t>RNSO JAP PEACH 700G</t>
+  </si>
+  <si>
+    <t>PT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20141203</t>
+  </si>
+  <si>
+    <t>RINSO RYL GOLD 700G</t>
+  </si>
+  <si>
+    <t>20140001</t>
+  </si>
+  <si>
+    <t>RINSO PURE LIQ 510G</t>
+  </si>
+  <si>
+    <t>20133212</t>
+  </si>
+  <si>
+    <t>BOOM DET.CAIR RSE510</t>
+  </si>
+  <si>
+    <t>20133213</t>
+  </si>
+  <si>
+    <t>BOOM DET.CAIR LAV510</t>
+  </si>
+  <si>
+    <t>20134103</t>
+  </si>
+  <si>
+    <t>ATTACK GEL S.CNTA515</t>
+  </si>
+  <si>
+    <t>20138111</t>
+  </si>
+  <si>
+    <t>JAZ 1 ROSE BERY 515G</t>
+  </si>
+  <si>
+    <t>20131373</t>
+  </si>
+  <si>
+    <t>GENTLE GEN FR.PE 360</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20137793</t>
+  </si>
+  <si>
+    <t>RINSO ROSE FRESH 510</t>
+  </si>
+  <si>
+    <t>20054750</t>
+  </si>
+  <si>
+    <t>RNSO+ML LIQ PRFM 510</t>
+  </si>
+  <si>
+    <t>20093188</t>
+  </si>
+  <si>
+    <t>RINSO MLTO GLD LQ510</t>
+  </si>
+  <si>
+    <t>20122879</t>
+  </si>
+  <si>
+    <t>RNSO MLTO KRN STR510</t>
+  </si>
+  <si>
+    <t>20104950</t>
+  </si>
+  <si>
+    <t>RINSO MLTO JP/PCH510</t>
+  </si>
+  <si>
+    <t>20093627</t>
+  </si>
+  <si>
+    <t>SOKLN LIQ SAKURA 510</t>
+  </si>
+  <si>
+    <t>20123818</t>
+  </si>
+  <si>
+    <t>SOKLN LIQ LVNDR 510</t>
+  </si>
+  <si>
+    <t>20091870</t>
+  </si>
+  <si>
+    <t>SO KLN LIQ WH&amp;BR 510</t>
+  </si>
+  <si>
+    <t>20114428</t>
+  </si>
+  <si>
+    <t>SOKLN LIQ KOREAN 510</t>
+  </si>
+  <si>
+    <t>20141373</t>
+  </si>
+  <si>
+    <t>RINSO PW.CLN BTL 650</t>
+  </si>
+  <si>
+    <t>20141369</t>
+  </si>
+  <si>
+    <t>RINSO P.BRZE BTL 650</t>
+  </si>
+  <si>
+    <t>20131730</t>
+  </si>
+  <si>
+    <t>SYANG LIQ R/ROSE 700</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20132442</t>
+  </si>
+  <si>
+    <t>SYANG LIQ ORIGNAL700</t>
+  </si>
+  <si>
+    <t>20135849</t>
+  </si>
+  <si>
+    <t>LARIST SMR.BRZ 700ML</t>
+  </si>
+  <si>
+    <t>20139955</t>
+  </si>
+  <si>
+    <t>BU KRM JNHAE CB700ML</t>
+  </si>
+  <si>
+    <t>20120180</t>
+  </si>
+  <si>
+    <t>SO SOFT RS&amp;WTRLY 700</t>
+  </si>
+  <si>
+    <t>20121364</t>
+  </si>
+  <si>
+    <t>SO SOFT SKR BLSM 700</t>
+  </si>
+  <si>
+    <t>20135246</t>
+  </si>
+  <si>
+    <t>SO SOFT SWT PEONY700</t>
+  </si>
+  <si>
+    <t>20128720</t>
+  </si>
+  <si>
+    <t>SO SOFT FLO BRS 700</t>
+  </si>
+  <si>
+    <t>20140325</t>
+  </si>
+  <si>
+    <t>SO SOFT FLO LILY 700</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20141371</t>
+  </si>
+  <si>
+    <t>GNTLE GEN CMLLIA 700</t>
+  </si>
+  <si>
+    <t>20141372</t>
+  </si>
+  <si>
+    <t>GENTLE GEN LILAC 700</t>
+  </si>
+  <si>
+    <t>20135245</t>
+  </si>
+  <si>
+    <t>SO KLIN LIQ FRNCH700</t>
+  </si>
+  <si>
+    <t>20133798</t>
+  </si>
+  <si>
+    <t>SO KLIN LIQ EN.RS700</t>
+  </si>
+  <si>
+    <t>20139729</t>
+  </si>
+  <si>
+    <t>SOKLN GR.TEA&amp;JSM 700</t>
+  </si>
+  <si>
+    <t>20113567</t>
+  </si>
+  <si>
+    <t>GENTLE GEN MR.BRZ700</t>
+  </si>
+  <si>
+    <t>20115959</t>
+  </si>
+  <si>
+    <t>GENTLE GEN FR.PE 700</t>
+  </si>
+  <si>
+    <t>20115958</t>
+  </si>
+  <si>
+    <t>GENTLE GEN PRS.G 700</t>
+  </si>
+  <si>
+    <t>20133333</t>
+  </si>
+  <si>
+    <t>GENTLE GEN A/KRGT700</t>
+  </si>
+  <si>
+    <t>20073805</t>
+  </si>
+  <si>
+    <t>SOKLN RED/MG&amp;B1.44KG</t>
+  </si>
+  <si>
+    <t>20041483</t>
+  </si>
+  <si>
+    <t>SO/KLN SOFT P/RS1.44</t>
+  </si>
+  <si>
+    <t>20140806</t>
+  </si>
+  <si>
+    <t>SO KLN EDP D.LS 144</t>
+  </si>
+  <si>
+    <t>20140804</t>
+  </si>
+  <si>
+    <t>SO KLN EDP BLNC 1.44</t>
+  </si>
+  <si>
+    <t>20091352</t>
+  </si>
+  <si>
+    <t>DAIA+SOFT VIOLET 1.5</t>
+  </si>
+  <si>
+    <t>20052321</t>
+  </si>
+  <si>
+    <t>DAIA+SOFT PINK 1.5KG</t>
+  </si>
+  <si>
+    <t>20030446</t>
+  </si>
+  <si>
+    <t>DAIA PUTIH 1.5KG</t>
+  </si>
+  <si>
+    <t>20121050</t>
+  </si>
+  <si>
+    <t>DAIA HIJAB C&amp;F 1.5G</t>
+  </si>
+  <si>
+    <t>10014547</t>
+  </si>
+  <si>
+    <t>DAIA DTRG.BBK BGA1.5</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20053796</t>
+  </si>
+  <si>
+    <t>SOKLN SOFTG PRPL 720</t>
+  </si>
+  <si>
+    <t>20073499</t>
+  </si>
+  <si>
+    <t>SO KLN MGNL&amp;BRY 720G</t>
+  </si>
+  <si>
+    <t>20012188</t>
+  </si>
+  <si>
+    <t>SOKLN SOFTR ROSY 720</t>
+  </si>
+  <si>
+    <t>20119238</t>
+  </si>
+  <si>
+    <t>TOTAL DET.PERFUME750</t>
+  </si>
+  <si>
+    <t>20061748</t>
+  </si>
+  <si>
+    <t>DAIA DET+SFT VLT 800</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20036047</t>
+  </si>
+  <si>
+    <t>DAIA DET+SOFT  800G</t>
+  </si>
+  <si>
+    <t>20012007</t>
+  </si>
+  <si>
+    <t>DAIA DET.BBK PTH 800</t>
+  </si>
+  <si>
+    <t>10005245</t>
+  </si>
+  <si>
+    <t>DAIA BBK FLORAL 800G</t>
+  </si>
+  <si>
+    <t>20074992</t>
+  </si>
+  <si>
+    <t>BUKRIM OXY/K VIOL700</t>
+  </si>
+  <si>
+    <t>20113809</t>
+  </si>
+  <si>
+    <t>OXYKLIN DTRG LIQ 700</t>
+  </si>
+  <si>
+    <t>12</t>
   </si>
   <si>
     <t>20129837</t>
@@ -127,384 +499,18 @@
     <t>LARIST SPR.GRD 750ML</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20037446</t>
-  </si>
-  <si>
-    <t>RNSO+ML LIQ ROSE 700</t>
-  </si>
-  <si>
-    <t>20138867</t>
-  </si>
-  <si>
-    <t>RNSO JAP PEACH 700G</t>
-  </si>
-  <si>
-    <t>PT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20141203</t>
-  </si>
-  <si>
-    <t>RINSO RYL GOLD 700G</t>
-  </si>
-  <si>
-    <t>20140001</t>
-  </si>
-  <si>
-    <t>RINSO PURE LIQ 510G</t>
-  </si>
-  <si>
-    <t>20133212</t>
-  </si>
-  <si>
-    <t>BOOM DET.CAIR RSE510</t>
-  </si>
-  <si>
-    <t>20133213</t>
-  </si>
-  <si>
-    <t>BOOM DET.CAIR LAV510</t>
-  </si>
-  <si>
-    <t>20134103</t>
-  </si>
-  <si>
-    <t>ATTACK GEL S.CNTA515</t>
-  </si>
-  <si>
-    <t>20138111</t>
-  </si>
-  <si>
-    <t>JAZ 1 ROSE BERY 515G</t>
-  </si>
-  <si>
-    <t>20131373</t>
-  </si>
-  <si>
-    <t>GENTLE GEN FR.PE 360</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20054750</t>
-  </si>
-  <si>
-    <t>RNSO+ML LIQ PRFM 510</t>
-  </si>
-  <si>
-    <t>20093188</t>
-  </si>
-  <si>
-    <t>RINSO MLTO GLD LQ510</t>
-  </si>
-  <si>
-    <t>20122879</t>
-  </si>
-  <si>
-    <t>RNSO MLTO KRN STR510</t>
-  </si>
-  <si>
-    <t>20104950</t>
-  </si>
-  <si>
-    <t>RINSO MLTO JP/PCH510</t>
-  </si>
-  <si>
-    <t>20137793</t>
-  </si>
-  <si>
-    <t>RINSO ROSE FRESH 510</t>
-  </si>
-  <si>
-    <t>20093627</t>
-  </si>
-  <si>
-    <t>SOKLN LIQ SAKURA 510</t>
-  </si>
-  <si>
-    <t>20123818</t>
-  </si>
-  <si>
-    <t>SOKLN LIQ LVNDR 510</t>
-  </si>
-  <si>
-    <t>20091870</t>
-  </si>
-  <si>
-    <t>SO KLN LIQ WH&amp;BR 510</t>
-  </si>
-  <si>
-    <t>20114428</t>
-  </si>
-  <si>
-    <t>SOKLN LIQ KOREAN 510</t>
-  </si>
-  <si>
-    <t>20141373</t>
-  </si>
-  <si>
-    <t>RINSO PW.CLN BTL 650</t>
-  </si>
-  <si>
-    <t>20141369</t>
-  </si>
-  <si>
-    <t>RINSO P.BRZE BTL 650</t>
-  </si>
-  <si>
-    <t>20131730</t>
-  </si>
-  <si>
-    <t>SYANG LIQ R/ROSE 700</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20132442</t>
-  </si>
-  <si>
-    <t>SYANG LIQ ORIGNAL700</t>
-  </si>
-  <si>
-    <t>20135849</t>
-  </si>
-  <si>
-    <t>LARIST SMR.BRZ 700ML</t>
-  </si>
-  <si>
-    <t>20139955</t>
-  </si>
-  <si>
-    <t>BU KRM JNHAE CB700ML</t>
-  </si>
-  <si>
-    <t>20113809</t>
-  </si>
-  <si>
-    <t>OXYKLIN DTRG LIQ 700</t>
-  </si>
-  <si>
     <t>20123019</t>
   </si>
   <si>
     <t>SAYANG LIQ ROSE 510</t>
   </si>
   <si>
-    <t>20120180</t>
-  </si>
-  <si>
-    <t>SO SOFT RS&amp;WTRLY 700</t>
-  </si>
-  <si>
-    <t>20121364</t>
-  </si>
-  <si>
-    <t>SO SOFT SKR BLSM 700</t>
-  </si>
-  <si>
-    <t>20135246</t>
-  </si>
-  <si>
-    <t>SO SOFT SWT PEONY700</t>
-  </si>
-  <si>
-    <t>20128720</t>
-  </si>
-  <si>
-    <t>SO SOFT FLO BRS 700</t>
-  </si>
-  <si>
-    <t>20140325</t>
-  </si>
-  <si>
-    <t>SO SOFT FLO LILY 700</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20141371</t>
-  </si>
-  <si>
-    <t>GNTLE GEN CMLLIA 700</t>
-  </si>
-  <si>
-    <t>20141372</t>
-  </si>
-  <si>
-    <t>GENTLE GEN LILAC 700</t>
-  </si>
-  <si>
-    <t>20135245</t>
-  </si>
-  <si>
-    <t>SO KLIN LIQ FRNCH700</t>
-  </si>
-  <si>
-    <t>20133798</t>
-  </si>
-  <si>
-    <t>SO KLIN LIQ EN.RS700</t>
-  </si>
-  <si>
-    <t>20139729</t>
-  </si>
-  <si>
-    <t>SOKLN GR.TEA&amp;JSM 700</t>
-  </si>
-  <si>
-    <t>20113567</t>
-  </si>
-  <si>
-    <t>GENTLE GEN MR.BRZ700</t>
-  </si>
-  <si>
-    <t>20115959</t>
-  </si>
-  <si>
-    <t>GENTLE GEN FR.PE 700</t>
-  </si>
-  <si>
-    <t>20115958</t>
-  </si>
-  <si>
-    <t>GENTLE GEN PRS.G 700</t>
-  </si>
-  <si>
-    <t>20133333</t>
-  </si>
-  <si>
-    <t>GENTLE GEN A/KRGT700</t>
-  </si>
-  <si>
-    <t>20073805</t>
-  </si>
-  <si>
-    <t>SOKLN RED/MG&amp;B1.44KG</t>
-  </si>
-  <si>
-    <t>20041483</t>
-  </si>
-  <si>
-    <t>SO/KLN SOFT P/RS1.44</t>
-  </si>
-  <si>
-    <t>20140806</t>
-  </si>
-  <si>
-    <t>SO KLN EDP D.LS 144</t>
-  </si>
-  <si>
-    <t>20140804</t>
-  </si>
-  <si>
-    <t>SO KLN EDP BLNC 1.44</t>
-  </si>
-  <si>
-    <t>20091352</t>
-  </si>
-  <si>
-    <t>DAIA+SOFT VIOLET 1.5</t>
-  </si>
-  <si>
-    <t>20052321</t>
-  </si>
-  <si>
-    <t>DAIA+SOFT PINK 1.5KG</t>
-  </si>
-  <si>
-    <t>20030446</t>
-  </si>
-  <si>
-    <t>DAIA PUTIH 1.5KG</t>
-  </si>
-  <si>
-    <t>20121050</t>
-  </si>
-  <si>
-    <t>DAIA HIJAB C&amp;F 1.5G</t>
-  </si>
-  <si>
-    <t>10014547</t>
-  </si>
-  <si>
-    <t>DAIA DTRG.BBK BGA1.5</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20053796</t>
-  </si>
-  <si>
-    <t>SOKLN SOFTG PRPL 720</t>
-  </si>
-  <si>
-    <t>20073499</t>
-  </si>
-  <si>
-    <t>SO KLN MGNL&amp;BRY 720G</t>
-  </si>
-  <si>
-    <t>20012188</t>
-  </si>
-  <si>
-    <t>SOKLN SOFTR ROSY 720</t>
-  </si>
-  <si>
-    <t>20119238</t>
-  </si>
-  <si>
-    <t>TOTAL DET.PERFUME750</t>
-  </si>
-  <si>
-    <t>20061748</t>
-  </si>
-  <si>
-    <t>DAIA DET+SFT VLT 800</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20036047</t>
-  </si>
-  <si>
-    <t>DAIA DET+SOFT  800G</t>
-  </si>
-  <si>
-    <t>20012007</t>
-  </si>
-  <si>
-    <t>DAIA DET.BBK PTH 800</t>
-  </si>
-  <si>
-    <t>10005245</t>
-  </si>
-  <si>
-    <t>DAIA BBK FLORAL 800G</t>
-  </si>
-  <si>
-    <t>20074992</t>
-  </si>
-  <si>
-    <t>BUKRIM OXY/K VIOL700</t>
-  </si>
-  <si>
     <t>20090425</t>
   </si>
   <si>
     <t>IDM SOFT DET BTK 450</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>PT,(E-2B)</t>
   </si>
   <si>
@@ -532,6 +538,198 @@
     <t>SOKLIN MTC F/LD 900G</t>
   </si>
   <si>
+    <t>20081448</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT H.SM 600</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20081449</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT P.DW 600</t>
+  </si>
+  <si>
+    <t>20104951</t>
+  </si>
+  <si>
+    <t>ROYALE HJB BLCK.V600</t>
+  </si>
+  <si>
+    <t>20091457</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT BS 600</t>
+  </si>
+  <si>
+    <t>20113101</t>
+  </si>
+  <si>
+    <t>ROYALE SWT FLORL 600</t>
+  </si>
+  <si>
+    <t>20128706</t>
+  </si>
+  <si>
+    <t>ROYALE LNVDR VNL 600</t>
+  </si>
+  <si>
+    <t>20113093</t>
+  </si>
+  <si>
+    <t>ROYALE SUNNY DAY 600</t>
+  </si>
+  <si>
+    <t>20142010</t>
+  </si>
+  <si>
+    <t>ROYALE MTCHA BLS 600</t>
+  </si>
+  <si>
+    <t>20128919</t>
+  </si>
+  <si>
+    <t>MOLTO SFTNR PURE 550</t>
+  </si>
+  <si>
+    <t>20094735</t>
+  </si>
+  <si>
+    <t>DOWNY SUNRISE 950</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>PT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20094733</t>
+  </si>
+  <si>
+    <t>DOWNY MYSTIQUE 900</t>
+  </si>
+  <si>
+    <t>20140221</t>
+  </si>
+  <si>
+    <t>DOWNY PASSION 875ML</t>
+  </si>
+  <si>
+    <t>20141324</t>
+  </si>
+  <si>
+    <t>DOWNY SUNSHINE 500ML</t>
+  </si>
+  <si>
+    <t>20141323</t>
+  </si>
+  <si>
+    <t>DOWNY MIDNIGHT 500ML</t>
+  </si>
+  <si>
+    <t>20080360</t>
+  </si>
+  <si>
+    <t>DOWNY MYSTIQUE 550ML</t>
+  </si>
+  <si>
+    <t>20080361</t>
+  </si>
+  <si>
+    <t>DOWNY PASSION 550ML</t>
+  </si>
+  <si>
+    <t>20074226</t>
+  </si>
+  <si>
+    <t>DOWNY SUN.FRSH 550</t>
+  </si>
+  <si>
+    <t>20139145</t>
+  </si>
+  <si>
+    <t>DOWNY MLKY TOUCH 500</t>
+  </si>
+  <si>
+    <t>20140003</t>
+  </si>
+  <si>
+    <t>RNSO PWD ROSE.F 1.44</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20093521</t>
+  </si>
+  <si>
+    <t>RINSO+MOLTO ESC1440G</t>
+  </si>
+  <si>
+    <t>20139609</t>
+  </si>
+  <si>
+    <t>RNSO JPN PEAC 1440G</t>
+  </si>
+  <si>
+    <t>20140002</t>
+  </si>
+  <si>
+    <t>RINSO PWD PURE 1440G</t>
+  </si>
+  <si>
+    <t>20064413</t>
+  </si>
+  <si>
+    <t>ATCK JAZ1 S/CNTA 1.5</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20064414</t>
+  </si>
+  <si>
+    <t>ATTACK JAZ1 P/SGR1.5</t>
+  </si>
+  <si>
+    <t>20130527</t>
+  </si>
+  <si>
+    <t>ATTACK DET+SF RB 1.4</t>
+  </si>
+  <si>
+    <t>20138108</t>
+  </si>
+  <si>
+    <t>JAZ 1 PRPL BLS 1.4KG</t>
+  </si>
+  <si>
+    <t>20071827</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD ROSE 700</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20085113</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD PRFM 700</t>
+  </si>
+  <si>
+    <t>20105968</t>
+  </si>
+  <si>
+    <t>RNSO PWD JPN PC 700G</t>
+  </si>
+  <si>
     <t>20131792</t>
   </si>
   <si>
@@ -544,55 +742,1261 @@
     <t>SAYANG PWDR ROSE 770</t>
   </si>
   <si>
-    <t>20081448</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT H.SM 600</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20081449</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT P.DW 600</t>
-  </si>
-  <si>
-    <t>20104951</t>
-  </si>
-  <si>
-    <t>ROYALE HJB BLCK.V600</t>
-  </si>
-  <si>
-    <t>20091457</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT BS 600</t>
-  </si>
-  <si>
-    <t>20113101</t>
-  </si>
-  <si>
-    <t>ROYALE SWT FLORL 600</t>
-  </si>
-  <si>
-    <t>20128706</t>
-  </si>
-  <si>
-    <t>ROYALE LNVDR VNL 600</t>
-  </si>
-  <si>
-    <t>20113093</t>
-  </si>
-  <si>
-    <t>ROYALE SUNNY DAY 600</t>
-  </si>
-  <si>
-    <t>20142010</t>
-  </si>
-  <si>
-    <t>ROYALE MTCHA BLS 600</t>
+    <t>20131516</t>
+  </si>
+  <si>
+    <t>LARIST DET.FRS BT450</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20113183</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD ROSE 380</t>
+  </si>
+  <si>
+    <t>20121372</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD PRFM 380</t>
+  </si>
+  <si>
+    <t>20128719</t>
+  </si>
+  <si>
+    <t>SOKLIN LVD&amp;LILY 425G</t>
+  </si>
+  <si>
+    <t>20042466</t>
+  </si>
+  <si>
+    <t>DAIA DET+SOFT 470G</t>
+  </si>
+  <si>
+    <t>20139595</t>
+  </si>
+  <si>
+    <t>MOLTO TRKA BDD 3X300</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20133398</t>
+  </si>
+  <si>
+    <t>TRKA PURE 300ML</t>
+  </si>
+  <si>
+    <t>10011440</t>
+  </si>
+  <si>
+    <t>RAPIKA LVDR SPLAS300</t>
+  </si>
+  <si>
+    <t>20084780</t>
+  </si>
+  <si>
+    <t>RAPIKA GOLD 250ML</t>
+  </si>
+  <si>
+    <t>20093193</t>
+  </si>
+  <si>
+    <t>RAPIKA PINK SKR 300</t>
+  </si>
+  <si>
+    <t>20138071</t>
+  </si>
+  <si>
+    <t>KISPRAY KASTURI 280</t>
+  </si>
+  <si>
+    <t>20074721</t>
+  </si>
+  <si>
+    <t>KISPRAY GLM.GOLD 280</t>
+  </si>
+  <si>
+    <t>20116685</t>
+  </si>
+  <si>
+    <t>KISPRAY ELG.SAPH 200</t>
+  </si>
+  <si>
+    <t>20032250</t>
+  </si>
+  <si>
+    <t>KISPRAY VIOLET PC280</t>
+  </si>
+  <si>
+    <t>20000980</t>
+  </si>
+  <si>
+    <t>KISPRAY VIOLET 318ML</t>
+  </si>
+  <si>
+    <t>20138470</t>
+  </si>
+  <si>
+    <t>SO KLN PWNG RED 1.7L</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>10005803</t>
+  </si>
+  <si>
+    <t>SOKLIN PWNGI RED 780</t>
+  </si>
+  <si>
+    <t>10007389</t>
+  </si>
+  <si>
+    <t>SOKLIN PWNGI PINK780</t>
+  </si>
+  <si>
+    <t>10008104</t>
+  </si>
+  <si>
+    <t>SO KLIN PWG BLUE 780</t>
+  </si>
+  <si>
+    <t>20108418</t>
+  </si>
+  <si>
+    <t>SOKLIN PWG HJB GR780</t>
+  </si>
+  <si>
+    <t>10005802</t>
+  </si>
+  <si>
+    <t>SOKLIN PEWANGI VL780</t>
+  </si>
+  <si>
+    <t>20141985</t>
+  </si>
+  <si>
+    <t>SO KLN TROP SUMR 780</t>
+  </si>
+  <si>
+    <t>20134526</t>
+  </si>
+  <si>
+    <t>SOKLIN PWG COT.FN780</t>
+  </si>
+  <si>
+    <t>20129370</t>
+  </si>
+  <si>
+    <t>MOLTO MORNING FRS550</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20129160</t>
+  </si>
+  <si>
+    <t>MOLTO LUXURY PRF 650</t>
+  </si>
+  <si>
+    <t>20087464</t>
+  </si>
+  <si>
+    <t>IDM PWNG PINK.PAS720</t>
+  </si>
+  <si>
+    <t>20137582</t>
+  </si>
+  <si>
+    <t>IDM PWNG ROM.AURA720</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20137581</t>
+  </si>
+  <si>
+    <t>IDM PWNG EXO.BLUE720</t>
+  </si>
+  <si>
+    <t>20020245</t>
+  </si>
+  <si>
+    <t>MOLTO PWNGI BLUE 765</t>
+  </si>
+  <si>
+    <t>20020226</t>
+  </si>
+  <si>
+    <t>MOLTO PWNGI PINK 765</t>
+  </si>
+  <si>
+    <t>20106821</t>
+  </si>
+  <si>
+    <t>MOLTO PURPLE 765ML</t>
+  </si>
+  <si>
+    <t>20142219</t>
+  </si>
+  <si>
+    <t>MLTO GNTL FRSH 765ML</t>
+  </si>
+  <si>
+    <t>,(E-1B)</t>
+  </si>
+  <si>
+    <t>20135847</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT SUMMR600</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20135846</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT SPRNG600</t>
+  </si>
+  <si>
+    <t>20014403</t>
+  </si>
+  <si>
+    <t>BAYCLIN REGLR 1000ML</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>20082581</t>
+  </si>
+  <si>
+    <t>VANISH CAIR WHT 425</t>
+  </si>
+  <si>
+    <t>20052662</t>
+  </si>
+  <si>
+    <t>VANISH CAIR PCH 425</t>
+  </si>
+  <si>
+    <t>20089665</t>
+  </si>
+  <si>
+    <t>IDM PHLANG NODA 450</t>
+  </si>
+  <si>
+    <t>20079788</t>
+  </si>
+  <si>
+    <t>PROCLIN PCH 400ML</t>
+  </si>
+  <si>
+    <t>10025646</t>
+  </si>
+  <si>
+    <t>YURI TAF LMN&amp;LIME500</t>
+  </si>
+  <si>
+    <t>20093919</t>
+  </si>
+  <si>
+    <t>IDM PURPOSE CLN 400</t>
+  </si>
+  <si>
+    <t>10014263</t>
+  </si>
+  <si>
+    <t>WIPOL KARBOL CMR 720</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>20001645</t>
+  </si>
+  <si>
+    <t>WIPOL KARBOL LMN 720</t>
+  </si>
+  <si>
+    <t>20090066</t>
+  </si>
+  <si>
+    <t>WIPOL SRH + JRK 720</t>
+  </si>
+  <si>
+    <t>20122478</t>
+  </si>
+  <si>
+    <t>WIPOL CITRUS FRS 390</t>
+  </si>
+  <si>
+    <t>20023111</t>
+  </si>
+  <si>
+    <t>SOS KARBOL CLS PN725</t>
+  </si>
+  <si>
+    <t>10013107</t>
+  </si>
+  <si>
+    <t>SUPERSOL PINE 720G</t>
+  </si>
+  <si>
+    <t>20104030</t>
+  </si>
+  <si>
+    <t>SUPER SOL SEREH720G</t>
+  </si>
+  <si>
+    <t>20132664</t>
+  </si>
+  <si>
+    <t>VIXAL KUAT SEGAR 600</t>
+  </si>
+  <si>
+    <t>10004612</t>
+  </si>
+  <si>
+    <t>SOS P.LNT ORANGE 700</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10004610</t>
+  </si>
+  <si>
+    <t>SOS P/LT APLL REF700</t>
+  </si>
+  <si>
+    <t>10010480</t>
+  </si>
+  <si>
+    <t>SPR PELL FRS.APEL760</t>
+  </si>
+  <si>
+    <t>20121373</t>
+  </si>
+  <si>
+    <t>SPR PELL AB CTRS 500</t>
+  </si>
+  <si>
+    <t>20137408</t>
+  </si>
+  <si>
+    <t>SPR PELL SAKURA 740</t>
+  </si>
+  <si>
+    <t>20001407</t>
+  </si>
+  <si>
+    <t>IDM P'LANTAI LAV 800</t>
+  </si>
+  <si>
+    <t>20001402</t>
+  </si>
+  <si>
+    <t>IDM P'LANTAI APL 800</t>
+  </si>
+  <si>
+    <t>20028779</t>
+  </si>
+  <si>
+    <t>IDM KRBOL WNG650(BR)</t>
+  </si>
+  <si>
+    <t>20089486</t>
+  </si>
+  <si>
+    <t>IDM KRBL SRH CTR 650</t>
+  </si>
+  <si>
+    <t>20128125</t>
+  </si>
+  <si>
+    <t>IDM PURPOSE CLN 375</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>20027963</t>
+  </si>
+  <si>
+    <t>IDM PMBERSH KACA 400</t>
+  </si>
+  <si>
+    <t>10003706</t>
+  </si>
+  <si>
+    <t>MR.MUSCLE ORGNL 400</t>
+  </si>
+  <si>
+    <t>10012548</t>
+  </si>
+  <si>
+    <t>SOKLIN RLX/LAV RF770</t>
+  </si>
+  <si>
+    <t>10003646</t>
+  </si>
+  <si>
+    <t>SO KLIN P/L APPLE770</t>
+  </si>
+  <si>
+    <t>10003645</t>
+  </si>
+  <si>
+    <t>SO KLIN P/L LMN 780</t>
+  </si>
+  <si>
+    <t>20101095</t>
+  </si>
+  <si>
+    <t>SO KLN LNT SEREH 770</t>
+  </si>
+  <si>
+    <t>20131223</t>
+  </si>
+  <si>
+    <t>SO KLN LNT CT.GRD700</t>
+  </si>
+  <si>
+    <t>20131788</t>
+  </si>
+  <si>
+    <t>MAMA LMN JR.NPS 950</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>20141956</t>
+  </si>
+  <si>
+    <t>EKONOMI NANAS 920G</t>
+  </si>
+  <si>
+    <t>20136124</t>
+  </si>
+  <si>
+    <t>EKNOMI LIQ N&amp;JN 675G</t>
+  </si>
+  <si>
+    <t>20092331</t>
+  </si>
+  <si>
+    <t>EKONOMI LIQ JR.NP650</t>
+  </si>
+  <si>
+    <t>20123812</t>
+  </si>
+  <si>
+    <t>EKONOMI LQ.SEREH 650</t>
+  </si>
+  <si>
+    <t>20107240</t>
+  </si>
+  <si>
+    <t>EKONOMI LIQ.SW&amp;JR650</t>
+  </si>
+  <si>
+    <t>20129722</t>
+  </si>
+  <si>
+    <t>BUKRIM LIQ.JRK NP550</t>
+  </si>
+  <si>
+    <t>20138518</t>
+  </si>
+  <si>
+    <t>KILAU NIPIS 630ML</t>
+  </si>
+  <si>
+    <t>20034450</t>
+  </si>
+  <si>
+    <t>MAMA/L JERUK NPS 690</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>10004067</t>
+  </si>
+  <si>
+    <t>MAMA/L PCH LEMON 690</t>
+  </si>
+  <si>
+    <t>20099424</t>
+  </si>
+  <si>
+    <t>MAMA LIME CHARCO 690</t>
+  </si>
+  <si>
+    <t>20052031</t>
+  </si>
+  <si>
+    <t>MAMA LIME GRN TEA690</t>
+  </si>
+  <si>
+    <t>10004068</t>
+  </si>
+  <si>
+    <t>MAMA LIME POUCH 690</t>
+  </si>
+  <si>
+    <t>20134303</t>
+  </si>
+  <si>
+    <t>MAMA/L REF YUZU 690</t>
+  </si>
+  <si>
+    <t>20034449</t>
+  </si>
+  <si>
+    <t>MAMA/L JERUK NPS 430</t>
+  </si>
+  <si>
+    <t>20090067</t>
+  </si>
+  <si>
+    <t>SNLGHT MINT A.BAU600</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>20086172</t>
+  </si>
+  <si>
+    <t>SNLIGHT MND.ORGE 600</t>
+  </si>
+  <si>
+    <t>20112492</t>
+  </si>
+  <si>
+    <t>SUNLIGHT JRK NPS400G</t>
+  </si>
+  <si>
+    <t>20128374</t>
+  </si>
+  <si>
+    <t>LFEBUOY REF LIME 650</t>
+  </si>
+  <si>
+    <t>20134576</t>
+  </si>
+  <si>
+    <t>LFEBUOY REF LEMON650</t>
+  </si>
+  <si>
+    <t>20141345</t>
+  </si>
+  <si>
+    <t>LARISST S/PCC PRG650</t>
+  </si>
+  <si>
+    <t>20073425</t>
+  </si>
+  <si>
+    <t>IDM P.PRNG JRK.N 650</t>
+  </si>
+  <si>
+    <t>20141204</t>
+  </si>
+  <si>
+    <t>IDM P.PRG JR.NPS 950</t>
+  </si>
+  <si>
+    <t>20112491</t>
+  </si>
+  <si>
+    <t>SNLIGHT LIME PCH 910</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>20139728</t>
+  </si>
+  <si>
+    <t>SNLGHT BIO BLBR 870G</t>
+  </si>
+  <si>
+    <t>10005482</t>
+  </si>
+  <si>
+    <t>SNLIGHT LIME PCH 660</t>
+  </si>
+  <si>
+    <t>20135144</t>
+  </si>
+  <si>
+    <t>SNLGHT BIO NATURE600</t>
+  </si>
+  <si>
+    <t>10003498</t>
+  </si>
+  <si>
+    <t>CLEAR PUMP ORIGNL500</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>10013205</t>
+  </si>
+  <si>
+    <t>SUNLIGHT J/NIPIS.750</t>
+  </si>
+  <si>
+    <t>20139947</t>
+  </si>
+  <si>
+    <t>SNLGHT BIO BLBR 675G</t>
+  </si>
+  <si>
+    <t>20139948</t>
+  </si>
+  <si>
+    <t>SNLGHT BERY&amp;LIME 675</t>
+  </si>
+  <si>
+    <t>20142277</t>
+  </si>
+  <si>
+    <t>MAMA LM GRN BTL 690</t>
+  </si>
+  <si>
+    <t>20135845</t>
+  </si>
+  <si>
+    <t>EKNOMI LIQ JR&amp;LMN650</t>
+  </si>
+  <si>
+    <t>10034652</t>
+  </si>
+  <si>
+    <t>GLADE OCEAN ESCP 350</t>
+  </si>
+  <si>
+    <t>20105576</t>
+  </si>
+  <si>
+    <t>STELLA A/F SAKURA350</t>
+  </si>
+  <si>
+    <t>10029632</t>
+  </si>
+  <si>
+    <t>STELLA ALAT MATIC</t>
+  </si>
+  <si>
+    <t>10004032</t>
+  </si>
+  <si>
+    <t>VIXAL KUAT HARUM 720</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>10004034</t>
+  </si>
+  <si>
+    <t>VIXAL KMR MD KUAT720</t>
+  </si>
+  <si>
+    <t>10003359</t>
+  </si>
+  <si>
+    <t>WIPOL CEMARA BTL 730</t>
+  </si>
+  <si>
+    <t>10000955</t>
+  </si>
+  <si>
+    <t>PORSTEX N.PARFUM 1L</t>
+  </si>
+  <si>
+    <t>10018962</t>
+  </si>
+  <si>
+    <t>YURI PORSTEX OB.B700</t>
+  </si>
+  <si>
+    <t>10005246</t>
+  </si>
+  <si>
+    <t>WING PRCLN CLN BR750</t>
+  </si>
+  <si>
+    <t>20040315</t>
+  </si>
+  <si>
+    <t>IDM PORSELEN BTL 800</t>
+  </si>
+  <si>
+    <t>20015040</t>
+  </si>
+  <si>
+    <t>HARPIC TRIPLE ACT450</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20095746</t>
+  </si>
+  <si>
+    <t>HRPC PNG.KRK CTR 405</t>
+  </si>
+  <si>
+    <t>20042956</t>
+  </si>
+  <si>
+    <t>HARPIC PWR PLS CT450</t>
+  </si>
+  <si>
+    <t>20134373</t>
+  </si>
+  <si>
+    <t>STELLA ALAT+REFILL25</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>20134374</t>
+  </si>
+  <si>
+    <t>STELLA ELCTRIC LAV25</t>
+  </si>
+  <si>
+    <t>10010232</t>
+  </si>
+  <si>
+    <t>KIWI LIQ.SHOE BLCK75</t>
+  </si>
+  <si>
+    <t>10007934</t>
+  </si>
+  <si>
+    <t>KIWI PASTE BLACK 45M</t>
+  </si>
+  <si>
+    <t>20012183</t>
+  </si>
+  <si>
+    <t>BAYGON BKR D.DRH 5'S</t>
+  </si>
+  <si>
+    <t>20014401</t>
+  </si>
+  <si>
+    <t>BYGON BKR JMB LVD 5S</t>
+  </si>
+  <si>
+    <t>20110145</t>
+  </si>
+  <si>
+    <t>VAPE NY.BK L.SMO5'S</t>
+  </si>
+  <si>
+    <t>20128711</t>
+  </si>
+  <si>
+    <t>AUTAN LOT.JRK&amp;LMN 50</t>
+  </si>
+  <si>
+    <t>20106983</t>
+  </si>
+  <si>
+    <t>AUTAN LOT.SAKURA 50</t>
+  </si>
+  <si>
+    <t>20054250</t>
+  </si>
+  <si>
+    <t>AUTAN REFRESH/S 100</t>
+  </si>
+  <si>
+    <t>20128713</t>
+  </si>
+  <si>
+    <t>SOFEL LOT.KRN/SMR 60</t>
+  </si>
+  <si>
+    <t>20078241</t>
+  </si>
+  <si>
+    <t>SOFFELL LOT.APEL 60G</t>
+  </si>
+  <si>
+    <t>10040202</t>
+  </si>
+  <si>
+    <t>SOFFELL A.NYMK K/J60</t>
+  </si>
+  <si>
+    <t>10037280</t>
+  </si>
+  <si>
+    <t>BAGUS KAPUR AJAIB</t>
+  </si>
+  <si>
+    <t>20109069</t>
+  </si>
+  <si>
+    <t>BAGUS LEM TIKUS PCS</t>
+  </si>
+  <si>
+    <t>10003479</t>
+  </si>
+  <si>
+    <t>GAJAH LEM TIKUS KT70</t>
+  </si>
+  <si>
+    <t>20139525</t>
+  </si>
+  <si>
+    <t>VAPE DORA LEM TIKUS</t>
+  </si>
+  <si>
+    <t>10037275</t>
+  </si>
+  <si>
+    <t>SWALLOW KMPR BTR 300</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>20027997</t>
+  </si>
+  <si>
+    <t>IDM KAMPER NAPTLN150</t>
+  </si>
+  <si>
+    <t>20131886</t>
+  </si>
+  <si>
+    <t>IDM KMPR DEO SKRA 5S</t>
+  </si>
+  <si>
+    <t>20131885</t>
+  </si>
+  <si>
+    <t>IDM KMPR DEO CFFE 5S</t>
+  </si>
+  <si>
+    <t>20079794</t>
+  </si>
+  <si>
+    <t>IDM KAMPER TOILET 5S</t>
+  </si>
+  <si>
+    <t>20139963</t>
+  </si>
+  <si>
+    <t>LARISST CTRONELLA 5S</t>
+  </si>
+  <si>
+    <t>10000279</t>
+  </si>
+  <si>
+    <t>SWALLOW TLT.BALL 5'S</t>
+  </si>
+  <si>
+    <t>10000482</t>
+  </si>
+  <si>
+    <t>SWALLOW K/DEO BAL105</t>
+  </si>
+  <si>
+    <t>20017478</t>
+  </si>
+  <si>
+    <t>SWALLOW ORG S-160</t>
+  </si>
+  <si>
+    <t>20122471</t>
+  </si>
+  <si>
+    <t>STELLA LAV.GRD 42+13</t>
+  </si>
+  <si>
+    <t>20136409</t>
+  </si>
+  <si>
+    <t>STELLA BALI JAS42+13</t>
+  </si>
+  <si>
+    <t>20109616</t>
+  </si>
+  <si>
+    <t>STELLA CAFF.LATTE 42</t>
+  </si>
+  <si>
+    <t>20075791</t>
+  </si>
+  <si>
+    <t>STELLA POCKET ORG 10</t>
+  </si>
+  <si>
+    <t>20075798</t>
+  </si>
+  <si>
+    <t>STLLA POCKET PRPL 10</t>
+  </si>
+  <si>
+    <t>20091307</t>
+  </si>
+  <si>
+    <t>STELLA POCKET BLU 10</t>
+  </si>
+  <si>
+    <t>20138481</t>
+  </si>
+  <si>
+    <t>STELLA EXO.FRUIT 10G</t>
+  </si>
+  <si>
+    <t>20138482</t>
+  </si>
+  <si>
+    <t>STELLA LUX.FLOWR 10G</t>
+  </si>
+  <si>
+    <t>20105573</t>
+  </si>
+  <si>
+    <t>STELLA AF REF JPS160</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>20037058</t>
+  </si>
+  <si>
+    <t>STELLA AF REF FLW160</t>
+  </si>
+  <si>
+    <t>20036827</t>
+  </si>
+  <si>
+    <t>STELLA AF REF GRN160</t>
+  </si>
+  <si>
+    <t>20044100</t>
+  </si>
+  <si>
+    <t>STELLA AF REF APL160</t>
+  </si>
+  <si>
+    <t>20135485</t>
+  </si>
+  <si>
+    <t>STELLA AF REF BAL160</t>
+  </si>
+  <si>
+    <t>20046210</t>
+  </si>
+  <si>
+    <t>GLADE OCN ESCPE 146G</t>
+  </si>
+  <si>
+    <t>10023003</t>
+  </si>
+  <si>
+    <t>GLADE PNY&amp;BRY BLS 70</t>
+  </si>
+  <si>
+    <t>10023002</t>
+  </si>
+  <si>
+    <t>GLADE FRESH ONE EF70</t>
+  </si>
+  <si>
+    <t>20096642</t>
+  </si>
+  <si>
+    <t>IDM FRSHNS LEMON 50</t>
+  </si>
+  <si>
+    <t>20096641</t>
+  </si>
+  <si>
+    <t>IDM FRSHNS ORANGE 50</t>
+  </si>
+  <si>
+    <t>10005428</t>
+  </si>
+  <si>
+    <t>STELLA IN ONE ORG 42</t>
+  </si>
+  <si>
+    <t>10005427</t>
+  </si>
+  <si>
+    <t>STELLA IN ONE LMN 42</t>
+  </si>
+  <si>
+    <t>20022902</t>
+  </si>
+  <si>
+    <t>HIT SPRAY ORG 180</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>20064216</t>
+  </si>
+  <si>
+    <t>HIT INS.SPRY LILY180</t>
+  </si>
+  <si>
+    <t>20139144</t>
+  </si>
+  <si>
+    <t>HIT XPRES PINK BL.35</t>
+  </si>
+  <si>
+    <t>20131161</t>
+  </si>
+  <si>
+    <t>HIT REF XPRES APLE35</t>
+  </si>
+  <si>
+    <t>20095744</t>
+  </si>
+  <si>
+    <t>HIT REF EXPRT FRS 35</t>
+  </si>
+  <si>
+    <t>20039183</t>
+  </si>
+  <si>
+    <t>HIT ALAT+REF EXP APL</t>
+  </si>
+  <si>
+    <t>10034732</t>
+  </si>
+  <si>
+    <t>HIT MAT ELECTRK 48'S</t>
+  </si>
+  <si>
+    <t>10027329</t>
+  </si>
+  <si>
+    <t>HIT ALT NYAMUK ELC 5</t>
+  </si>
+  <si>
+    <t>20084568</t>
+  </si>
+  <si>
+    <t>VAPE LIQ.SKR BLOSM45</t>
+  </si>
+  <si>
+    <t>20008748</t>
+  </si>
+  <si>
+    <t>VAPE LIQUID REF 45ML</t>
+  </si>
+  <si>
+    <t>20023870</t>
+  </si>
+  <si>
+    <t>VAPE LIQUID ELEKTRIK</t>
+  </si>
+  <si>
+    <t>20030445</t>
+  </si>
+  <si>
+    <t>VAPE SPRAY 1XSMP ORG</t>
+  </si>
+  <si>
+    <t>20073974</t>
+  </si>
+  <si>
+    <t>VAPE SPRAY 1XSMP SKR</t>
+  </si>
+  <si>
+    <t>20124418</t>
+  </si>
+  <si>
+    <t>VAPE SWEET PWDR 200</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>20076987</t>
+  </si>
+  <si>
+    <t>BAYGON FLOW.GRDN 200</t>
+  </si>
+  <si>
+    <t>10015526</t>
+  </si>
+  <si>
+    <t>BAYGON SPRY LVND 750</t>
+  </si>
+  <si>
+    <t>20124346</t>
+  </si>
+  <si>
+    <t>BAYGON JPNSE&amp;PCH 600</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>20098605</t>
+  </si>
+  <si>
+    <t>BYGON SPRY CHR.BL600</t>
+  </si>
+  <si>
+    <t>10003272</t>
+  </si>
+  <si>
+    <t>BAYGON SPRY CITRS675</t>
+  </si>
+  <si>
+    <t>20071775</t>
+  </si>
+  <si>
+    <t>BAYGON FLO.GRDN 675</t>
+  </si>
+  <si>
+    <t>20139154</t>
+  </si>
+  <si>
+    <t>HIT COTTON PWD 600ML</t>
+  </si>
+  <si>
+    <t>20054151</t>
+  </si>
+  <si>
+    <t>HIT INS.SPRY LILY600</t>
+  </si>
+  <si>
+    <t>10005198</t>
+  </si>
+  <si>
+    <t>HIT INS.SPRAY ORG600</t>
+  </si>
+  <si>
+    <t>20109613</t>
+  </si>
+  <si>
+    <t>HIT SPRY.P/BLOSM 600</t>
+  </si>
+  <si>
+    <t>20080868</t>
+  </si>
+  <si>
+    <t>HIT FRESH CITRUS 600</t>
+  </si>
+  <si>
+    <t>20131365</t>
+  </si>
+  <si>
+    <t>HIT SPRY JPN.SKR 600</t>
+  </si>
+  <si>
+    <t>20139446</t>
+  </si>
+  <si>
+    <t>BAYGON CTRS FRSH 400</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>20128132</t>
+  </si>
+  <si>
+    <t>BAYGON FLO.GRDN 400</t>
+  </si>
+  <si>
+    <t>20135247</t>
+  </si>
+  <si>
+    <t>BAYGON FLRL.FNTSY500</t>
+  </si>
+  <si>
+    <t>20135248</t>
+  </si>
+  <si>
+    <t>BAYGON CHRRY BRRY500</t>
+  </si>
+  <si>
+    <t>20088715</t>
+  </si>
+  <si>
+    <t>HIT SPRAY LILY 400ML</t>
+  </si>
+  <si>
+    <t>20022498</t>
+  </si>
+  <si>
+    <t>HIT SPRAY ORG 400ML</t>
+  </si>
+  <si>
+    <t>20134237</t>
+  </si>
+  <si>
+    <t>HIT SPRY.P/BLOSM 400</t>
+  </si>
+  <si>
+    <t>20136130</t>
+  </si>
+  <si>
+    <t>VAPE FLO.BUBBLE 600</t>
+  </si>
+  <si>
+    <t>20124850</t>
+  </si>
+  <si>
+    <t>VAPE SPRY SWET PD600</t>
+  </si>
+  <si>
+    <t>20136134</t>
+  </si>
+  <si>
+    <t>VAPE CANDY FLO 600</t>
+  </si>
+  <si>
+    <t>10006651</t>
+  </si>
+  <si>
+    <t>VAPE FMK ORANGE 600</t>
+  </si>
+  <si>
+    <t>20142133</t>
+  </si>
+  <si>
+    <t>VAPE MILK TEA 600ML</t>
   </si>
   <si>
     <t>20126740</t>
@@ -601,133 +2005,7 @@
     <t>MOLTO FRSH.CSBLCA650</t>
   </si>
   <si>
-    <t>20094735</t>
-  </si>
-  <si>
-    <t>DOWNY SUNRISE 950</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>PT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20094733</t>
-  </si>
-  <si>
-    <t>DOWNY MYSTIQUE 900</t>
-  </si>
-  <si>
-    <t>20140221</t>
-  </si>
-  <si>
-    <t>DOWNY PASSION 875ML</t>
-  </si>
-  <si>
-    <t>20141324</t>
-  </si>
-  <si>
-    <t>DOWNY SUNSHINE 500ML</t>
-  </si>
-  <si>
-    <t>20141323</t>
-  </si>
-  <si>
-    <t>DOWNY MIDNIGHT 500ML</t>
-  </si>
-  <si>
-    <t>20080360</t>
-  </si>
-  <si>
-    <t>DOWNY MYSTIQUE 550ML</t>
-  </si>
-  <si>
-    <t>20080361</t>
-  </si>
-  <si>
-    <t>DOWNY PASSION 550ML</t>
-  </si>
-  <si>
-    <t>20074226</t>
-  </si>
-  <si>
-    <t>DOWNY SUN.FRSH 550</t>
-  </si>
-  <si>
-    <t>20139145</t>
-  </si>
-  <si>
-    <t>DOWNY MLKY TOUCH 500</t>
-  </si>
-  <si>
-    <t>20140003</t>
-  </si>
-  <si>
-    <t>RNSO PWD ROSE.F 1.44</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20093521</t>
-  </si>
-  <si>
-    <t>RINSO+MOLTO ESC1440G</t>
-  </si>
-  <si>
-    <t>20139609</t>
-  </si>
-  <si>
-    <t>RNSO JPN PEAC 1440G</t>
-  </si>
-  <si>
-    <t>20140002</t>
-  </si>
-  <si>
-    <t>RINSO PWD PURE 1440G</t>
-  </si>
-  <si>
-    <t>20064413</t>
-  </si>
-  <si>
-    <t>ATCK JAZ1 S/CNTA 1.5</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20064414</t>
-  </si>
-  <si>
-    <t>ATTACK JAZ1 P/SGR1.5</t>
-  </si>
-  <si>
-    <t>20130527</t>
-  </si>
-  <si>
-    <t>ATTACK DET+SF RB 1.4</t>
-  </si>
-  <si>
-    <t>20138108</t>
-  </si>
-  <si>
-    <t>JAZ 1 PRPL BLS 1.4KG</t>
-  </si>
-  <si>
-    <t>20071827</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD ROSE 700</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20085113</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD PRFM 700</t>
+    <t>999</t>
   </si>
   <si>
     <t>20123256</t>
@@ -736,1276 +2014,10 @@
     <t>RINSO+MLT KRN STW700</t>
   </si>
   <si>
-    <t>20105968</t>
-  </si>
-  <si>
-    <t>RNSO PWD JPN PC 700G</t>
-  </si>
-  <si>
-    <t>20131516</t>
-  </si>
-  <si>
-    <t>LARIST DET.FRS BT450</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20113183</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD ROSE 380</t>
-  </si>
-  <si>
-    <t>20121372</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD PRFM 380</t>
-  </si>
-  <si>
-    <t>20128719</t>
-  </si>
-  <si>
-    <t>SOKLIN LVD&amp;LILY 425G</t>
-  </si>
-  <si>
-    <t>20042466</t>
-  </si>
-  <si>
-    <t>DAIA DET+SOFT 470G</t>
-  </si>
-  <si>
-    <t>20139595</t>
-  </si>
-  <si>
-    <t>MOLTO TRKA BDD 3X300</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20133398</t>
-  </si>
-  <si>
-    <t>TRKA PURE 300ML</t>
-  </si>
-  <si>
-    <t>10011440</t>
-  </si>
-  <si>
-    <t>RAPIKA LVDR SPLAS300</t>
-  </si>
-  <si>
-    <t>20084780</t>
-  </si>
-  <si>
-    <t>RAPIKA GOLD 250ML</t>
-  </si>
-  <si>
-    <t>20093193</t>
-  </si>
-  <si>
-    <t>RAPIKA PINK SKR 300</t>
-  </si>
-  <si>
-    <t>20138071</t>
-  </si>
-  <si>
-    <t>KISPRAY KASTURI 280</t>
-  </si>
-  <si>
-    <t>20074721</t>
-  </si>
-  <si>
-    <t>KISPRAY GLM.GOLD 280</t>
-  </si>
-  <si>
-    <t>20116685</t>
-  </si>
-  <si>
-    <t>KISPRAY ELG.SAPH 200</t>
-  </si>
-  <si>
-    <t>20032250</t>
-  </si>
-  <si>
-    <t>KISPRAY VIOLET PC280</t>
-  </si>
-  <si>
-    <t>20000980</t>
-  </si>
-  <si>
-    <t>KISPRAY VIOLET 318ML</t>
-  </si>
-  <si>
-    <t>20138470</t>
-  </si>
-  <si>
-    <t>SO KLN PWNG RED 1.7L</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>10005803</t>
-  </si>
-  <si>
-    <t>SOKLIN PWNGI RED 780</t>
-  </si>
-  <si>
-    <t>10007389</t>
-  </si>
-  <si>
-    <t>SOKLIN PWNGI PINK780</t>
-  </si>
-  <si>
-    <t>10008104</t>
-  </si>
-  <si>
-    <t>SO KLIN PWG BLUE 780</t>
-  </si>
-  <si>
-    <t>20108418</t>
-  </si>
-  <si>
-    <t>SOKLIN PWG HJB GR780</t>
-  </si>
-  <si>
-    <t>10005802</t>
-  </si>
-  <si>
-    <t>SOKLIN PEWANGI VL780</t>
-  </si>
-  <si>
-    <t>20141985</t>
-  </si>
-  <si>
-    <t>SO KLN TROP SUMR 780</t>
-  </si>
-  <si>
-    <t>20134526</t>
-  </si>
-  <si>
-    <t>SOKLIN PWG COT.FN780</t>
-  </si>
-  <si>
-    <t>20129370</t>
-  </si>
-  <si>
-    <t>MOLTO MORNING FRS550</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20129160</t>
-  </si>
-  <si>
-    <t>MOLTO LUXURY PRF 650</t>
-  </si>
-  <si>
-    <t>20128919</t>
-  </si>
-  <si>
-    <t>MOLTO SFTNR PURE 550</t>
-  </si>
-  <si>
-    <t>20087464</t>
-  </si>
-  <si>
-    <t>IDM PWNG PINK.PAS720</t>
-  </si>
-  <si>
-    <t>20137582</t>
-  </si>
-  <si>
-    <t>IDM PWNG ROM.AURA720</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20137581</t>
-  </si>
-  <si>
-    <t>IDM PWNG EXO.BLUE720</t>
-  </si>
-  <si>
-    <t>20020245</t>
-  </si>
-  <si>
-    <t>MOLTO PWNGI BLUE 765</t>
-  </si>
-  <si>
-    <t>20020226</t>
-  </si>
-  <si>
-    <t>MOLTO PWNGI PINK 765</t>
-  </si>
-  <si>
-    <t>20106821</t>
-  </si>
-  <si>
-    <t>MOLTO PURPLE 765ML</t>
-  </si>
-  <si>
-    <t>20135847</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT SUMMR600</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>20135846</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT SPRNG600</t>
-  </si>
-  <si>
-    <t>20014403</t>
-  </si>
-  <si>
-    <t>BAYCLIN REGLR 1000ML</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>20082581</t>
-  </si>
-  <si>
-    <t>VANISH CAIR WHT 425</t>
-  </si>
-  <si>
-    <t>20052662</t>
-  </si>
-  <si>
-    <t>VANISH CAIR PCH 425</t>
-  </si>
-  <si>
-    <t>20089665</t>
-  </si>
-  <si>
-    <t>IDM PHLANG NODA 450</t>
-  </si>
-  <si>
-    <t>20079788</t>
-  </si>
-  <si>
-    <t>PROCLIN PCH 400ML</t>
-  </si>
-  <si>
-    <t>10025646</t>
-  </si>
-  <si>
-    <t>YURI TAF LMN&amp;LIME500</t>
-  </si>
-  <si>
-    <t>10014263</t>
-  </si>
-  <si>
-    <t>WIPOL KARBOL CMR 720</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>20001645</t>
-  </si>
-  <si>
-    <t>WIPOL KARBOL LMN 720</t>
-  </si>
-  <si>
-    <t>20090066</t>
-  </si>
-  <si>
-    <t>WIPOL SRH + JRK 720</t>
-  </si>
-  <si>
-    <t>20122478</t>
-  </si>
-  <si>
-    <t>WIPOL CITRUS FRS 390</t>
-  </si>
-  <si>
-    <t>20023111</t>
-  </si>
-  <si>
-    <t>SOS KARBOL CLS PN725</t>
-  </si>
-  <si>
-    <t>10013107</t>
-  </si>
-  <si>
-    <t>SUPERSOL PINE 720G</t>
-  </si>
-  <si>
-    <t>20104030</t>
-  </si>
-  <si>
-    <t>SUPER SOL SEREH720G</t>
-  </si>
-  <si>
-    <t>20132664</t>
-  </si>
-  <si>
-    <t>VIXAL KUAT SEGAR 600</t>
-  </si>
-  <si>
-    <t>10004612</t>
-  </si>
-  <si>
-    <t>SOS P.LNT ORANGE 700</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10004610</t>
-  </si>
-  <si>
-    <t>SOS P/LT APLL REF700</t>
-  </si>
-  <si>
-    <t>10010480</t>
-  </si>
-  <si>
-    <t>SPR PELL FRS.APEL760</t>
-  </si>
-  <si>
-    <t>20121373</t>
-  </si>
-  <si>
-    <t>SPR PELL AB CTRS 500</t>
-  </si>
-  <si>
-    <t>20137408</t>
-  </si>
-  <si>
-    <t>SPR PELL SAKURA 740</t>
-  </si>
-  <si>
-    <t>20001407</t>
-  </si>
-  <si>
-    <t>IDM P'LANTAI LAV 800</t>
-  </si>
-  <si>
-    <t>20001402</t>
-  </si>
-  <si>
-    <t>IDM P'LANTAI APL 800</t>
-  </si>
-  <si>
-    <t>20028779</t>
-  </si>
-  <si>
-    <t>IDM KRBOL WNG650(BR)</t>
-  </si>
-  <si>
-    <t>20089486</t>
-  </si>
-  <si>
-    <t>IDM KRBL SRH CTR 650</t>
-  </si>
-  <si>
-    <t>20128125</t>
-  </si>
-  <si>
-    <t>IDM PURPOSE CLN 375</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>20027963</t>
-  </si>
-  <si>
-    <t>IDM PMBERSH KACA 400</t>
-  </si>
-  <si>
-    <t>10003706</t>
-  </si>
-  <si>
-    <t>MR.MUSCLE ORGNL 400</t>
-  </si>
-  <si>
-    <t>10012548</t>
-  </si>
-  <si>
-    <t>SOKLIN RLX/LAV RF770</t>
-  </si>
-  <si>
-    <t>10003646</t>
-  </si>
-  <si>
-    <t>SO KLIN P/L APPLE770</t>
-  </si>
-  <si>
-    <t>10003645</t>
-  </si>
-  <si>
-    <t>SO KLIN P/L LMN 780</t>
-  </si>
-  <si>
-    <t>20101095</t>
-  </si>
-  <si>
-    <t>SO KLN LNT SEREH 770</t>
-  </si>
-  <si>
-    <t>20131223</t>
-  </si>
-  <si>
-    <t>SO KLN LNT CT.GRD700</t>
-  </si>
-  <si>
-    <t>20131788</t>
-  </si>
-  <si>
-    <t>MAMA LMN JR.NPS 950</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>20141956</t>
-  </si>
-  <si>
-    <t>EKONOMI NANAS 920G</t>
-  </si>
-  <si>
-    <t>,(E-1B)</t>
-  </si>
-  <si>
-    <t>20136124</t>
-  </si>
-  <si>
-    <t>EKNOMI LIQ N&amp;JN 675G</t>
-  </si>
-  <si>
-    <t>20092331</t>
-  </si>
-  <si>
-    <t>EKONOMI LIQ JR.NP650</t>
-  </si>
-  <si>
-    <t>20123812</t>
-  </si>
-  <si>
-    <t>EKONOMI LQ.SEREH 650</t>
-  </si>
-  <si>
-    <t>20107240</t>
-  </si>
-  <si>
-    <t>EKONOMI LIQ.SW&amp;JR650</t>
-  </si>
-  <si>
-    <t>20129722</t>
-  </si>
-  <si>
-    <t>BUKRIM LIQ.JRK NP550</t>
-  </si>
-  <si>
-    <t>20138518</t>
-  </si>
-  <si>
-    <t>KILAU NIPIS 630ML</t>
-  </si>
-  <si>
-    <t>20034450</t>
-  </si>
-  <si>
-    <t>MAMA/L JERUK NPS 690</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>10004067</t>
-  </si>
-  <si>
-    <t>MAMA/L PCH LEMON 690</t>
-  </si>
-  <si>
-    <t>20099424</t>
-  </si>
-  <si>
-    <t>MAMA LIME CHARCO 690</t>
-  </si>
-  <si>
-    <t>20052031</t>
-  </si>
-  <si>
-    <t>MAMA LIME GRN TEA690</t>
-  </si>
-  <si>
-    <t>10004068</t>
-  </si>
-  <si>
-    <t>MAMA LIME POUCH 690</t>
-  </si>
-  <si>
-    <t>20134303</t>
-  </si>
-  <si>
-    <t>MAMA/L REF YUZU 690</t>
-  </si>
-  <si>
     <t>20137792</t>
   </si>
   <si>
     <t>MAMA LIME GREEN 690</t>
-  </si>
-  <si>
-    <t>20034449</t>
-  </si>
-  <si>
-    <t>MAMA/L JERUK NPS 430</t>
-  </si>
-  <si>
-    <t>20090067</t>
-  </si>
-  <si>
-    <t>SNLGHT MINT A.BAU600</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>20086172</t>
-  </si>
-  <si>
-    <t>SNLIGHT MND.ORGE 600</t>
-  </si>
-  <si>
-    <t>20112492</t>
-  </si>
-  <si>
-    <t>SUNLIGHT JRK NPS400G</t>
-  </si>
-  <si>
-    <t>20128374</t>
-  </si>
-  <si>
-    <t>LFEBUOY REF LIME 650</t>
-  </si>
-  <si>
-    <t>20134576</t>
-  </si>
-  <si>
-    <t>LFEBUOY REF LEMON650</t>
-  </si>
-  <si>
-    <t>20141345</t>
-  </si>
-  <si>
-    <t>LARISST S/PCC PRG650</t>
-  </si>
-  <si>
-    <t>20073425</t>
-  </si>
-  <si>
-    <t>IDM P.PRNG JRK.N 650</t>
-  </si>
-  <si>
-    <t>20141204</t>
-  </si>
-  <si>
-    <t>IDM P.PRG JR.NPS 950</t>
-  </si>
-  <si>
-    <t>20112491</t>
-  </si>
-  <si>
-    <t>SNLIGHT LIME PCH 910</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>20139728</t>
-  </si>
-  <si>
-    <t>SNLGHT BIO BLBR 870G</t>
-  </si>
-  <si>
-    <t>10005482</t>
-  </si>
-  <si>
-    <t>SNLIGHT LIME PCH 660</t>
-  </si>
-  <si>
-    <t>20135144</t>
-  </si>
-  <si>
-    <t>SNLGHT BIO NATURE600</t>
-  </si>
-  <si>
-    <t>10013205</t>
-  </si>
-  <si>
-    <t>SUNLIGHT J/NIPIS.750</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>20139947</t>
-  </si>
-  <si>
-    <t>SNLGHT BIO BLBR 675G</t>
-  </si>
-  <si>
-    <t>20139948</t>
-  </si>
-  <si>
-    <t>SNLGHT BERY&amp;LIME 675</t>
-  </si>
-  <si>
-    <t>20135845</t>
-  </si>
-  <si>
-    <t>EKNOMI LIQ JR&amp;LMN650</t>
-  </si>
-  <si>
-    <t>20093919</t>
-  </si>
-  <si>
-    <t>IDM PURPOSE CLN 400</t>
-  </si>
-  <si>
-    <t>10003498</t>
-  </si>
-  <si>
-    <t>CLEAR PUMP ORIGNL500</t>
-  </si>
-  <si>
-    <t>10034652</t>
-  </si>
-  <si>
-    <t>GLADE OCEAN ESCP 350</t>
-  </si>
-  <si>
-    <t>20105576</t>
-  </si>
-  <si>
-    <t>STELLA A/F SAKURA350</t>
-  </si>
-  <si>
-    <t>10029632</t>
-  </si>
-  <si>
-    <t>STELLA ALAT MATIC</t>
-  </si>
-  <si>
-    <t>10004032</t>
-  </si>
-  <si>
-    <t>VIXAL KUAT HARUM 720</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>10004034</t>
-  </si>
-  <si>
-    <t>VIXAL KMR MD KUAT720</t>
-  </si>
-  <si>
-    <t>10003359</t>
-  </si>
-  <si>
-    <t>WIPOL CEMARA BTL 730</t>
-  </si>
-  <si>
-    <t>10000955</t>
-  </si>
-  <si>
-    <t>PORSTEX N.PARFUM 1L</t>
-  </si>
-  <si>
-    <t>10018962</t>
-  </si>
-  <si>
-    <t>YURI PORSTEX OB.B700</t>
-  </si>
-  <si>
-    <t>10005246</t>
-  </si>
-  <si>
-    <t>WING PRCLN CLN BR750</t>
-  </si>
-  <si>
-    <t>20040315</t>
-  </si>
-  <si>
-    <t>IDM PORSELEN BTL 800</t>
-  </si>
-  <si>
-    <t>20015040</t>
-  </si>
-  <si>
-    <t>HARPIC TRIPLE ACT450</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20095746</t>
-  </si>
-  <si>
-    <t>HRPC PNG.KRK CTR 405</t>
-  </si>
-  <si>
-    <t>20042956</t>
-  </si>
-  <si>
-    <t>HARPIC PWR PLS CT450</t>
-  </si>
-  <si>
-    <t>20134373</t>
-  </si>
-  <si>
-    <t>STELLA ALAT+REFILL25</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>20134374</t>
-  </si>
-  <si>
-    <t>STELLA ELCTRIC LAV25</t>
-  </si>
-  <si>
-    <t>10010232</t>
-  </si>
-  <si>
-    <t>KIWI LIQ.SHOE BLCK75</t>
-  </si>
-  <si>
-    <t>10007934</t>
-  </si>
-  <si>
-    <t>KIWI PASTE BLACK 45M</t>
-  </si>
-  <si>
-    <t>20012183</t>
-  </si>
-  <si>
-    <t>BAYGON BKR D.DRH 5'S</t>
-  </si>
-  <si>
-    <t>20014401</t>
-  </si>
-  <si>
-    <t>BYGON BKR JMB LVD 5S</t>
-  </si>
-  <si>
-    <t>20128711</t>
-  </si>
-  <si>
-    <t>AUTAN LOT.JRK&amp;LMN 50</t>
-  </si>
-  <si>
-    <t>20106983</t>
-  </si>
-  <si>
-    <t>AUTAN LOT.SAKURA 50</t>
-  </si>
-  <si>
-    <t>20054250</t>
-  </si>
-  <si>
-    <t>AUTAN REFRESH/S 100</t>
-  </si>
-  <si>
-    <t>20128713</t>
-  </si>
-  <si>
-    <t>SOFEL LOT.KRN/SMR 60</t>
-  </si>
-  <si>
-    <t>20078241</t>
-  </si>
-  <si>
-    <t>SOFFELL LOT.APEL 60G</t>
-  </si>
-  <si>
-    <t>10040202</t>
-  </si>
-  <si>
-    <t>SOFFELL A.NYMK K/J60</t>
-  </si>
-  <si>
-    <t>10037280</t>
-  </si>
-  <si>
-    <t>BAGUS KAPUR AJAIB</t>
-  </si>
-  <si>
-    <t>20109069</t>
-  </si>
-  <si>
-    <t>BAGUS LEM TIKUS PCS</t>
-  </si>
-  <si>
-    <t>10003479</t>
-  </si>
-  <si>
-    <t>GAJAH LEM TIKUS KT70</t>
-  </si>
-  <si>
-    <t>20139525</t>
-  </si>
-  <si>
-    <t>VAPE DORA LEM TIKUS</t>
-  </si>
-  <si>
-    <t>10037275</t>
-  </si>
-  <si>
-    <t>SWALLOW KMPR BTR 300</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>20027997</t>
-  </si>
-  <si>
-    <t>IDM KAMPER NAPTLN150</t>
-  </si>
-  <si>
-    <t>20131886</t>
-  </si>
-  <si>
-    <t>IDM KMPR DEO SKRA 5S</t>
-  </si>
-  <si>
-    <t>20131885</t>
-  </si>
-  <si>
-    <t>IDM KMPR DEO CFFE 5S</t>
-  </si>
-  <si>
-    <t>20079794</t>
-  </si>
-  <si>
-    <t>IDM KAMPER TOILET 5S</t>
-  </si>
-  <si>
-    <t>20139963</t>
-  </si>
-  <si>
-    <t>LARISST CTRONELLA 5S</t>
-  </si>
-  <si>
-    <t>10000279</t>
-  </si>
-  <si>
-    <t>SWALLOW TLT.BALL 5'S</t>
-  </si>
-  <si>
-    <t>10000482</t>
-  </si>
-  <si>
-    <t>SWALLOW K/DEO BAL105</t>
-  </si>
-  <si>
-    <t>20017478</t>
-  </si>
-  <si>
-    <t>SWALLOW ORG S-160</t>
-  </si>
-  <si>
-    <t>20122471</t>
-  </si>
-  <si>
-    <t>STELLA LAV.GRD 42+13</t>
-  </si>
-  <si>
-    <t>20136409</t>
-  </si>
-  <si>
-    <t>STELLA BALI JAS42+13</t>
-  </si>
-  <si>
-    <t>20109616</t>
-  </si>
-  <si>
-    <t>STELLA CAFF.LATTE 42</t>
-  </si>
-  <si>
-    <t>20075791</t>
-  </si>
-  <si>
-    <t>STELLA POCKET ORG 10</t>
-  </si>
-  <si>
-    <t>20075798</t>
-  </si>
-  <si>
-    <t>STLLA POCKET PRPL 10</t>
-  </si>
-  <si>
-    <t>20091307</t>
-  </si>
-  <si>
-    <t>STELLA POCKET BLU 10</t>
-  </si>
-  <si>
-    <t>20138481</t>
-  </si>
-  <si>
-    <t>STELLA EXO.FRUIT 10G</t>
-  </si>
-  <si>
-    <t>20138482</t>
-  </si>
-  <si>
-    <t>STELLA LUX.FLOWR 10G</t>
-  </si>
-  <si>
-    <t>20105573</t>
-  </si>
-  <si>
-    <t>STELLA AF REF JPS160</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>20037058</t>
-  </si>
-  <si>
-    <t>STELLA AF REF FLW160</t>
-  </si>
-  <si>
-    <t>20036827</t>
-  </si>
-  <si>
-    <t>STELLA AF REF GRN160</t>
-  </si>
-  <si>
-    <t>20044100</t>
-  </si>
-  <si>
-    <t>STELLA AF REF APL160</t>
-  </si>
-  <si>
-    <t>20135485</t>
-  </si>
-  <si>
-    <t>STELLA AF REF BAL160</t>
-  </si>
-  <si>
-    <t>20046210</t>
-  </si>
-  <si>
-    <t>GLADE OCN ESCPE 146G</t>
-  </si>
-  <si>
-    <t>10023003</t>
-  </si>
-  <si>
-    <t>GLADE PNY&amp;BRY BLS 70</t>
-  </si>
-  <si>
-    <t>10023002</t>
-  </si>
-  <si>
-    <t>GLADE FRESH ONE EF70</t>
-  </si>
-  <si>
-    <t>20096642</t>
-  </si>
-  <si>
-    <t>IDM FRSHNS LEMON 50</t>
-  </si>
-  <si>
-    <t>20096641</t>
-  </si>
-  <si>
-    <t>IDM FRSHNS ORANGE 50</t>
-  </si>
-  <si>
-    <t>10005428</t>
-  </si>
-  <si>
-    <t>STELLA IN ONE ORG 42</t>
-  </si>
-  <si>
-    <t>10005427</t>
-  </si>
-  <si>
-    <t>STELLA IN ONE LMN 42</t>
-  </si>
-  <si>
-    <t>20022902</t>
-  </si>
-  <si>
-    <t>HIT SPRAY ORG 180</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>20064216</t>
-  </si>
-  <si>
-    <t>HIT INS.SPRY LILY180</t>
-  </si>
-  <si>
-    <t>20139144</t>
-  </si>
-  <si>
-    <t>HIT XPRES PINK BL.35</t>
-  </si>
-  <si>
-    <t>20131161</t>
-  </si>
-  <si>
-    <t>HIT REF XPRES APLE35</t>
-  </si>
-  <si>
-    <t>20095744</t>
-  </si>
-  <si>
-    <t>HIT REF EXPRT FRS 35</t>
-  </si>
-  <si>
-    <t>20039183</t>
-  </si>
-  <si>
-    <t>HIT ALAT+REF EXP APL</t>
-  </si>
-  <si>
-    <t>10034732</t>
-  </si>
-  <si>
-    <t>HIT MAT ELECTRK 48'S</t>
-  </si>
-  <si>
-    <t>10027329</t>
-  </si>
-  <si>
-    <t>HIT ALT NYAMUK ELC 5</t>
-  </si>
-  <si>
-    <t>20084568</t>
-  </si>
-  <si>
-    <t>VAPE LIQ.SKR BLOSM45</t>
-  </si>
-  <si>
-    <t>20008748</t>
-  </si>
-  <si>
-    <t>VAPE LIQUID REF 45ML</t>
-  </si>
-  <si>
-    <t>20023870</t>
-  </si>
-  <si>
-    <t>VAPE LIQUID ELEKTRIK</t>
-  </si>
-  <si>
-    <t>20030445</t>
-  </si>
-  <si>
-    <t>VAPE SPRAY 1XSMP ORG</t>
-  </si>
-  <si>
-    <t>20073974</t>
-  </si>
-  <si>
-    <t>VAPE SPRAY 1XSMP SKR</t>
-  </si>
-  <si>
-    <t>20124418</t>
-  </si>
-  <si>
-    <t>VAPE SWEET PWDR 200</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>20076987</t>
-  </si>
-  <si>
-    <t>BAYGON FLOW.GRDN 200</t>
-  </si>
-  <si>
-    <t>10015526</t>
-  </si>
-  <si>
-    <t>BAYGON SPRY LVND 750</t>
-  </si>
-  <si>
-    <t>20124346</t>
-  </si>
-  <si>
-    <t>BAYGON JPNSE&amp;PCH 600</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20098605</t>
-  </si>
-  <si>
-    <t>BYGON SPRY CHR.BL600</t>
-  </si>
-  <si>
-    <t>10003272</t>
-  </si>
-  <si>
-    <t>BAYGON SPRY CITRS675</t>
-  </si>
-  <si>
-    <t>20071775</t>
-  </si>
-  <si>
-    <t>BAYGON FLO.GRDN 675</t>
-  </si>
-  <si>
-    <t>20139154</t>
-  </si>
-  <si>
-    <t>HIT COTTON PWD 600ML</t>
-  </si>
-  <si>
-    <t>20054151</t>
-  </si>
-  <si>
-    <t>HIT INS.SPRY LILY600</t>
-  </si>
-  <si>
-    <t>10005198</t>
-  </si>
-  <si>
-    <t>HIT INS.SPRAY ORG600</t>
-  </si>
-  <si>
-    <t>20109613</t>
-  </si>
-  <si>
-    <t>HIT SPRY.P/BLOSM 600</t>
-  </si>
-  <si>
-    <t>20080868</t>
-  </si>
-  <si>
-    <t>HIT FRESH CITRUS 600</t>
-  </si>
-  <si>
-    <t>20131365</t>
-  </si>
-  <si>
-    <t>HIT SPRY JPN.SKR 600</t>
-  </si>
-  <si>
-    <t>20139446</t>
-  </si>
-  <si>
-    <t>BAYGON CTRS FRSH 400</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>20128132</t>
-  </si>
-  <si>
-    <t>BAYGON FLO.GRDN 400</t>
-  </si>
-  <si>
-    <t>20135247</t>
-  </si>
-  <si>
-    <t>BAYGON FLRL.FNTSY500</t>
-  </si>
-  <si>
-    <t>20135248</t>
-  </si>
-  <si>
-    <t>BAYGON CHRRY BRRY500</t>
-  </si>
-  <si>
-    <t>20088715</t>
-  </si>
-  <si>
-    <t>HIT SPRAY LILY 400ML</t>
-  </si>
-  <si>
-    <t>20022498</t>
-  </si>
-  <si>
-    <t>HIT SPRAY ORG 400ML</t>
-  </si>
-  <si>
-    <t>20134237</t>
-  </si>
-  <si>
-    <t>HIT SPRY.P/BLOSM 400</t>
-  </si>
-  <si>
-    <t>20136130</t>
-  </si>
-  <si>
-    <t>VAPE FLO.BUBBLE 600</t>
-  </si>
-  <si>
-    <t>20124850</t>
-  </si>
-  <si>
-    <t>VAPE SPRY SWET PD600</t>
-  </si>
-  <si>
-    <t>20136134</t>
-  </si>
-  <si>
-    <t>VAPE CANDY FLO 600</t>
-  </si>
-  <si>
-    <t>10006651</t>
-  </si>
-  <si>
-    <t>VAPE FMK ORANGE 600</t>
-  </si>
-  <si>
-    <t>20142133</t>
-  </si>
-  <si>
-    <t>VAPE MILK TEA 600ML</t>
-  </si>
-  <si>
-    <t>20125391</t>
-  </si>
-  <si>
-    <t>SOKLIN PWG AC/SPT780</t>
-  </si>
-  <si>
-    <t>999</t>
-  </si>
-  <si>
-    <t>20098312</t>
-  </si>
-  <si>
-    <t>ROYALE PINK STN 600</t>
   </si>
 </sst>
 </file>
@@ -2398,7 +2410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F306"/>
+  <dimension ref="A1:F308"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2566,7 +2578,7 @@
         <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2686,7 +2698,7 @@
         <v>38</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2886,7 +2898,7 @@
         <v>4</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2966,7 +2978,7 @@
         <v>18</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -3180,10 +3192,10 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -3200,10 +3212,10 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -3223,7 +3235,7 @@
         <v>32</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -3243,7 +3255,7 @@
         <v>32</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -3263,18 +3275,18 @@
         <v>32</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -3283,7 +3295,7 @@
         <v>32</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -3291,10 +3303,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -3303,10 +3315,10 @@
         <v>32</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>104</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -3320,10 +3332,10 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -3340,10 +3352,10 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -3363,10 +3375,10 @@
         <v>35</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -3383,7 +3395,7 @@
         <v>35</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -3403,10 +3415,10 @@
         <v>35</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>104</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -3423,7 +3435,7 @@
         <v>35</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -3443,7 +3455,7 @@
         <v>35</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -3460,10 +3472,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -3480,10 +3492,10 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -3503,10 +3515,10 @@
         <v>38</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3523,10 +3535,10 @@
         <v>38</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3540,13 +3552,13 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>104</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -3560,13 +3572,13 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>104</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -3583,7 +3595,7 @@
         <v>58</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -3603,7 +3615,7 @@
         <v>58</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -3620,30 +3632,30 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>58</v>
+        <v>137</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="E62" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -3651,22 +3663,22 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>104</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -3680,10 +3692,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3700,13 +3712,13 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -3720,10 +3732,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3731,39 +3743,39 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="E67" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>104</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -3780,10 +3792,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -3800,10 +3812,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -3820,10 +3832,10 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -3831,62 +3843,62 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="E72" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>164</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="C74" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F74" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3900,13 +3912,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>5</v>
+        <v>166</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3920,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3940,13 +3952,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3960,13 +3972,13 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3980,10 +3992,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3991,19 +4003,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="E80" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -4020,10 +4032,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -4040,10 +4052,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -4060,10 +4072,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -4080,10 +4092,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -4100,10 +4112,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -4120,10 +4132,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -4140,13 +4152,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -4160,33 +4172,33 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>21</v>
+        <v>197</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="E89" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>199</v>
+        <v>15</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -4200,10 +4212,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>15</v>
@@ -4220,10 +4232,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>15</v>
@@ -4240,10 +4252,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>15</v>
@@ -4260,13 +4272,13 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>15</v>
+        <v>197</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -4280,13 +4292,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -4300,13 +4312,13 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -4320,13 +4332,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>199</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -4340,30 +4352,30 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="E98" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>21</v>
@@ -4380,10 +4392,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>21</v>
@@ -4400,10 +4412,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>21</v>
@@ -4420,33 +4432,33 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>21</v>
+        <v>100</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="E102" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -4460,13 +4472,13 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -4480,13 +4492,13 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -4500,30 +4512,30 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>236</v>
-      </c>
       <c r="E106" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>21</v>
@@ -4540,10 +4552,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>21</v>
@@ -4560,13 +4572,13 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -4580,13 +4592,13 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4806,7 +4818,7 @@
         <v>32</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4826,7 +4838,7 @@
         <v>35</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4846,7 +4858,7 @@
         <v>38</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4866,7 +4878,7 @@
         <v>58</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4883,10 +4895,10 @@
         <v>256</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -5106,7 +5118,7 @@
         <v>11</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>21</v>
+        <v>166</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -5126,15 +5138,15 @@
         <v>14</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>164</v>
+        <v>302</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
@@ -5146,7 +5158,7 @@
         <v>18</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -5166,7 +5178,7 @@
         <v>32</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>304</v>
+        <v>21</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -5226,21 +5238,21 @@
         <v>58</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>21</v>
+        <v>313</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>4</v>
@@ -5251,16 +5263,16 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>315</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>8</v>
@@ -5271,96 +5283,96 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>35</v>
@@ -5371,16 +5383,16 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>38</v>
@@ -5391,22 +5403,22 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>21</v>
+        <v>166</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -5420,10 +5432,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>21</v>
@@ -5431,19 +5443,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>333</v>
-      </c>
       <c r="E152" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>21</v>
@@ -5451,19 +5463,19 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>21</v>
@@ -5471,39 +5483,39 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -5511,119 +5523,119 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>104</v>
+        <v>5</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>21</v>
+        <v>100</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>351</v>
+        <v>21</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B159" s="1" t="s">
+      <c r="C159" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="C159" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="E159" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>304</v>
+        <v>354</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>21</v>
+        <v>302</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>21</v>
@@ -5631,122 +5643,122 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>164</v>
+        <v>15</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -5760,70 +5772,70 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D169" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B169" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>370</v>
-      </c>
       <c r="E169" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>104</v>
+        <v>166</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5831,19 +5843,19 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5851,19 +5863,19 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5871,19 +5883,19 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5891,19 +5903,19 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5920,13 +5932,13 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>390</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5940,13 +5952,13 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5960,13 +5972,13 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -5980,10 +5992,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -6000,10 +6012,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -6020,10 +6032,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -6040,13 +6052,13 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -6060,30 +6072,30 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="B184" s="1" t="s">
+      <c r="C184" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D184" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="C184" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>405</v>
-      </c>
       <c r="E184" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -6100,10 +6112,10 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -6120,10 +6132,10 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -6140,10 +6152,10 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -6160,13 +6172,13 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6180,10 +6192,10 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>83</v>
@@ -6200,10 +6212,10 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -6326,7 +6338,7 @@
         <v>32</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -6346,7 +6358,7 @@
         <v>35</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -6366,7 +6378,7 @@
         <v>38</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -6466,7 +6478,7 @@
         <v>4</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>21</v>
+        <v>100</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -6526,7 +6538,7 @@
         <v>14</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -6546,7 +6558,7 @@
         <v>18</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>164</v>
+        <v>5</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -6566,7 +6578,7 @@
         <v>32</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -6586,7 +6598,7 @@
         <v>35</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -6606,7 +6618,7 @@
         <v>38</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -6626,7 +6638,7 @@
         <v>58</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -6726,7 +6738,7 @@
         <v>18</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -6766,7 +6778,7 @@
         <v>35</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -6806,7 +6818,7 @@
         <v>58</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -6823,7 +6835,7 @@
         <v>467</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>482</v>
@@ -6886,7 +6898,7 @@
         <v>11</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -6906,7 +6918,7 @@
         <v>14</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -6926,7 +6938,7 @@
         <v>18</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -6946,7 +6958,7 @@
         <v>32</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -6966,7 +6978,7 @@
         <v>35</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -6986,7 +6998,7 @@
         <v>38</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -7006,7 +7018,7 @@
         <v>58</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -7023,10 +7035,10 @@
         <v>489</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>351</v>
+        <v>302</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -7043,10 +7055,10 @@
         <v>489</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>320</v>
+        <v>354</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -7063,10 +7075,10 @@
         <v>489</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -7083,10 +7095,10 @@
         <v>489</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>83</v>
+        <v>321</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -7103,10 +7115,10 @@
         <v>489</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -7123,10 +7135,10 @@
         <v>489</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>320</v>
+        <v>100</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -7143,10 +7155,10 @@
         <v>489</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>104</v>
+        <v>321</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -7160,33 +7172,33 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>4</v>
+        <v>234</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="B239" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="B239" s="1" t="s">
+      <c r="C239" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D239" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="C239" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D239" s="1" t="s">
-        <v>522</v>
-      </c>
       <c r="E239" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -7200,13 +7212,13 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -7220,13 +7232,13 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -7240,13 +7252,13 @@
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -7260,13 +7272,13 @@
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -7280,13 +7292,13 @@
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>83</v>
+        <v>302</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -7300,10 +7312,10 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>83</v>
@@ -7320,10 +7332,10 @@
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>83</v>
@@ -7340,13 +7352,13 @@
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -7360,10 +7372,10 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>5</v>
@@ -7380,10 +7392,10 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="F249" s="1" t="s">
         <v>5</v>
@@ -7400,13 +7412,13 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>304</v>
+        <v>5</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -7420,13 +7432,13 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -7440,13 +7452,13 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7460,13 +7472,13 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>83</v>
+        <v>302</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -7480,10 +7492,10 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>83</v>
@@ -7500,33 +7512,33 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>557</v>
+        <v>524</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>4</v>
+        <v>177</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>351</v>
+        <v>83</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="B256" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="B256" s="1" t="s">
+      <c r="C256" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D256" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="C256" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D256" s="1" t="s">
-        <v>557</v>
-      </c>
       <c r="E256" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>320</v>
+        <v>354</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -7540,13 +7552,13 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -7560,13 +7572,13 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -7580,13 +7592,13 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>5</v>
+        <v>321</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -7600,13 +7612,13 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>104</v>
+        <v>5</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -7620,13 +7632,13 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -7640,13 +7652,13 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -7660,13 +7672,13 @@
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>257</v>
+        <v>100</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -7680,10 +7692,10 @@
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="F264" s="1" t="s">
         <v>257</v>
@@ -7700,13 +7712,13 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>320</v>
+        <v>257</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -7720,13 +7732,13 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -7740,33 +7752,33 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>4</v>
+        <v>159</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B268" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="B268" s="1" t="s">
+      <c r="C268" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D268" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="C268" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D268" s="1" t="s">
-        <v>582</v>
-      </c>
       <c r="E268" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -7780,13 +7792,13 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -7800,13 +7812,13 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -7820,13 +7832,13 @@
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -7840,13 +7852,13 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -7860,13 +7872,13 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -7880,13 +7892,13 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -7900,13 +7912,13 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>5</v>
+        <v>321</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -7920,10 +7932,10 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>5</v>
@@ -7940,10 +7952,10 @@
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>5</v>
@@ -7960,13 +7972,13 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -7980,10 +7992,10 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>83</v>
@@ -8000,33 +8012,33 @@
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>609</v>
+        <v>584</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>4</v>
+        <v>177</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="B281" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="B281" s="1" t="s">
+      <c r="C281" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D281" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="C281" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D281" s="1" t="s">
-        <v>609</v>
-      </c>
       <c r="E281" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>320</v>
+        <v>5</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -8040,13 +8052,13 @@
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -8060,33 +8072,33 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>616</v>
+        <v>321</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="B284" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="B284" s="1" t="s">
+      <c r="C284" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D284" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="E284" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F284" s="1" t="s">
         <v>618</v>
-      </c>
-      <c r="C284" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D284" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="E284" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F284" s="1" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -8100,13 +8112,13 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -8120,13 +8132,13 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -8140,13 +8152,13 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>5</v>
+        <v>321</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -8160,13 +8172,13 @@
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>320</v>
+        <v>5</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -8180,13 +8192,13 @@
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -8200,13 +8212,13 @@
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>5</v>
+        <v>321</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -8220,10 +8232,10 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="F291" s="1" t="s">
         <v>5</v>
@@ -8240,13 +8252,13 @@
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>320</v>
+        <v>5</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8260,33 +8272,33 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>637</v>
+        <v>611</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>4</v>
+        <v>177</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>351</v>
+        <v>321</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="B294" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="B294" s="1" t="s">
+      <c r="C294" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D294" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="C294" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D294" s="1" t="s">
-        <v>637</v>
-      </c>
       <c r="E294" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>320</v>
+        <v>354</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8300,13 +8312,13 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8320,13 +8332,13 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8340,13 +8352,13 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -8360,13 +8372,13 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -8380,13 +8392,13 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>5</v>
+        <v>321</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8400,10 +8412,10 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>5</v>
@@ -8420,10 +8432,10 @@
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>5</v>
@@ -8440,10 +8452,10 @@
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>5</v>
@@ -8460,13 +8472,13 @@
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>104</v>
+        <v>5</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -8480,13 +8492,13 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -8500,10 +8512,10 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>662</v>
+        <v>639</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>8</v>
+        <v>159</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>5</v>
@@ -8511,22 +8523,62 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="B306" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="B306" s="1" t="s">
+      <c r="C306" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D306" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="C306" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D306" s="1" t="s">
-        <v>662</v>
-      </c>
       <c r="E306" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F306" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A307" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B307" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="C307" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D307" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="E307" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F307" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A308" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B308" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="C308" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D308" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="E308" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F306" s="1" t="s">
-        <v>5</v>
+      <c r="F308" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/DND05S.xlsx
+++ b/DND05S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1824" uniqueCount="660">
   <si>
     <t/>
   </si>
@@ -346,6 +346,12 @@
     <t>SOKLN GR.TEA&amp;JSM 700</t>
   </si>
   <si>
+    <t>20142134</t>
+  </si>
+  <si>
+    <t>SO KLN BLU PETAL 700</t>
+  </si>
+  <si>
     <t>20113567</t>
   </si>
   <si>
@@ -505,21 +511,15 @@
     <t>SAYANG LIQ ROSE 510</t>
   </si>
   <si>
-    <t>20090425</t>
-  </si>
-  <si>
-    <t>IDM SOFT DET BTK 450</t>
+    <t>20097739</t>
+  </si>
+  <si>
+    <t>IDM DET.CAIR PCH 700</t>
   </si>
   <si>
     <t>PT,(E-2B)</t>
   </si>
   <si>
-    <t>20097739</t>
-  </si>
-  <si>
-    <t>IDM DET.CAIR PCH 700</t>
-  </si>
-  <si>
     <t>20067586</t>
   </si>
   <si>
@@ -952,9 +952,6 @@
     <t>MLTO GNTL FRSH 765ML</t>
   </si>
   <si>
-    <t>,(E-1B)</t>
-  </si>
-  <si>
     <t>20135847</t>
   </si>
   <si>
@@ -991,12 +988,6 @@
     <t>VANISH CAIR PCH 425</t>
   </si>
   <si>
-    <t>20089665</t>
-  </si>
-  <si>
-    <t>IDM PHLANG NODA 450</t>
-  </si>
-  <si>
     <t>20079788</t>
   </si>
   <si>
@@ -1267,12 +1258,6 @@
     <t>MAMA/L REF YUZU 690</t>
   </si>
   <si>
-    <t>20034449</t>
-  </si>
-  <si>
-    <t>MAMA/L JERUK NPS 430</t>
-  </si>
-  <si>
     <t>20090067</t>
   </si>
   <si>
@@ -1999,25 +1984,13 @@
     <t>VAPE MILK TEA 600ML</t>
   </si>
   <si>
-    <t>20126740</t>
-  </si>
-  <si>
-    <t>MOLTO FRSH.CSBLCA650</t>
+    <t>20137792</t>
+  </si>
+  <si>
+    <t>MAMA LIME GREEN 690</t>
   </si>
   <si>
     <t>999</t>
-  </si>
-  <si>
-    <t>20123256</t>
-  </si>
-  <si>
-    <t>RINSO+MLT KRN STW700</t>
-  </si>
-  <si>
-    <t>20137792</t>
-  </si>
-  <si>
-    <t>MAMA LIME GREEN 690</t>
   </si>
 </sst>
 </file>
@@ -2410,7 +2383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F308"/>
+  <dimension ref="A1:F304"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3472,10 +3445,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -3495,7 +3468,7 @@
         <v>38</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -3515,10 +3488,10 @@
         <v>38</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>100</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3535,7 +3508,7 @@
         <v>38</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>100</v>
@@ -3552,13 +3525,13 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -3575,7 +3548,7 @@
         <v>58</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -3595,7 +3568,7 @@
         <v>58</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -3615,7 +3588,7 @@
         <v>58</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -3632,33 +3605,33 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>137</v>
+        <v>58</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>100</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="E62" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -3672,10 +3645,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -3692,10 +3665,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3712,13 +3685,13 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>100</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -3732,30 +3705,30 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="C67" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="E67" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -3772,10 +3745,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -3792,10 +3765,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -3812,10 +3785,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -3832,10 +3805,10 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -3843,22 +3816,22 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="C72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="E72" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3872,13 +3845,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -3892,33 +3865,33 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>166</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>168</v>
-      </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3932,7 +3905,7 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>32</v>
@@ -3952,7 +3925,7 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>35</v>
@@ -3972,7 +3945,7 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>38</v>
@@ -4895,7 +4868,7 @@
         <v>256</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>100</v>
@@ -5118,7 +5091,7 @@
         <v>11</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -5238,21 +5211,21 @@
         <v>58</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>313</v>
+        <v>15</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B142" s="1" t="s">
+      <c r="C142" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D142" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>316</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>4</v>
@@ -5263,16 +5236,16 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>8</v>
@@ -5283,99 +5256,99 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>327</v>
-      </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>166</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>329</v>
-      </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -5383,42 +5356,42 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>331</v>
-      </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>5</v>
+        <v>168</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B150" s="1" t="s">
+      <c r="C150" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="C150" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>316</v>
-      </c>
       <c r="E150" s="1" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>166</v>
+        <v>21</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -5432,10 +5405,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>21</v>
@@ -5443,19 +5416,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>21</v>
@@ -5463,19 +5436,19 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>340</v>
-      </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>21</v>
@@ -5483,39 +5456,39 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>342</v>
-      </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -5523,119 +5496,119 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>100</v>
+        <v>21</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B158" s="1" t="s">
+      <c r="C158" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="C158" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="E158" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>21</v>
+        <v>351</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>354</v>
+        <v>302</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>356</v>
-      </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>302</v>
+        <v>21</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>358</v>
-      </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>21</v>
@@ -5643,122 +5616,122 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>360</v>
-      </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>15</v>
+        <v>168</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>364</v>
-      </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>366</v>
-      </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>368</v>
-      </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="B167" s="1" t="s">
+      <c r="C167" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="C167" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>353</v>
-      </c>
       <c r="E167" s="1" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -5772,70 +5745,70 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="B169" s="1" t="s">
-        <v>375</v>
-      </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>166</v>
+        <v>100</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>377</v>
-      </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>100</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>379</v>
-      </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5843,19 +5816,19 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>381</v>
-      </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5863,19 +5836,19 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>383</v>
-      </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5883,19 +5856,19 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B174" s="1" t="s">
-        <v>385</v>
-      </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5903,19 +5876,19 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B175" s="1" t="s">
+      <c r="C175" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="C175" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>373</v>
-      </c>
       <c r="E175" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5932,10 +5905,10 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5943,59 +5916,59 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>392</v>
-      </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>396</v>
-      </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -6003,19 +5976,19 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -6023,19 +5996,19 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B181" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -6043,42 +6016,42 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>402</v>
-      </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="C183" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="C183" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>390</v>
-      </c>
       <c r="E183" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6092,10 +6065,10 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -6103,19 +6076,19 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>409</v>
-      </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -6123,19 +6096,19 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>411</v>
-      </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -6143,19 +6116,19 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="B187" s="1" t="s">
-        <v>413</v>
-      </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -6163,42 +6136,42 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="B188" s="1" t="s">
-        <v>415</v>
-      </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B189" s="1" t="s">
+      <c r="C189" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D189" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="C189" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>407</v>
-      </c>
       <c r="E189" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -6212,13 +6185,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>5</v>
+        <v>257</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -6232,10 +6205,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>21</v>
@@ -6243,39 +6216,39 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B192" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="B192" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>257</v>
+        <v>21</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>426</v>
-      </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>21</v>
@@ -6283,82 +6256,82 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B194" s="1" t="s">
-        <v>428</v>
-      </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>21</v>
+        <v>168</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B195" s="1" t="s">
-        <v>430</v>
-      </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>21</v>
+        <v>168</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B196" s="1" t="s">
-        <v>432</v>
-      </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="B197" s="1" t="s">
+      <c r="C197" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D197" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="C197" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D197" s="1" t="s">
-        <v>422</v>
-      </c>
       <c r="E197" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>166</v>
+        <v>21</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -6372,13 +6345,13 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>166</v>
+        <v>21</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -6392,10 +6365,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>21</v>
@@ -6403,19 +6376,19 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="B200" s="1" t="s">
-        <v>441</v>
-      </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>21</v>
@@ -6423,22 +6396,22 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="B201" s="1" t="s">
+      <c r="C201" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D201" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="C201" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D201" s="1" t="s">
-        <v>439</v>
-      </c>
       <c r="E201" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>21</v>
+        <v>100</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -6452,10 +6425,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>21</v>
@@ -6472,30 +6445,30 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>100</v>
+        <v>21</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="B204" s="1" t="s">
-        <v>450</v>
-      </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>21</v>
@@ -6503,122 +6476,122 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B205" s="1" t="s">
-        <v>452</v>
-      </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B206" s="1" t="s">
-        <v>454</v>
-      </c>
       <c r="C206" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>456</v>
-      </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="B208" s="1" t="s">
-        <v>458</v>
-      </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>83</v>
+        <v>351</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="B209" s="1" t="s">
-        <v>460</v>
-      </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>100</v>
+        <v>320</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B210" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="B210" s="1" t="s">
+      <c r="C210" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D210" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="C210" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D210" s="1" t="s">
-        <v>448</v>
-      </c>
       <c r="E210" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>354</v>
+        <v>21</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -6632,13 +6605,13 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>321</v>
+        <v>21</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -6652,10 +6625,10 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>21</v>
@@ -6663,102 +6636,102 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="B213" s="1" t="s">
-        <v>469</v>
-      </c>
       <c r="C213" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>471</v>
-      </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>21</v>
+        <v>302</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="B215" s="1" t="s">
-        <v>473</v>
-      </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="B216" s="1" t="s">
-        <v>475</v>
-      </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>302</v>
+        <v>168</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="B217" s="1" t="s">
+      <c r="C217" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D217" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F217" s="1" t="s">
         <v>477</v>
-      </c>
-      <c r="C217" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D217" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="E217" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F217" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -6772,13 +6745,13 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>166</v>
+        <v>320</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -6792,33 +6765,33 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>38</v>
+        <v>139</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B220" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="B220" s="1" t="s">
+      <c r="C220" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D220" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="C220" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D220" s="1" t="s">
-        <v>467</v>
-      </c>
       <c r="E220" s="1" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>321</v>
+        <v>5</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -6832,13 +6805,13 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>467</v>
+        <v>484</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>137</v>
+        <v>8</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>482</v>
+        <v>5</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -6852,150 +6825,150 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B223" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="B223" s="1" t="s">
-        <v>491</v>
-      </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B224" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="B224" s="1" t="s">
-        <v>493</v>
-      </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="B225" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="B225" s="1" t="s">
-        <v>495</v>
-      </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>321</v>
+        <v>351</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B226" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="B226" s="1" t="s">
-        <v>497</v>
-      </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>321</v>
+        <v>83</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="B227" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="B227" s="1" t="s">
-        <v>499</v>
-      </c>
       <c r="C227" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>354</v>
+        <v>302</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B228" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="B228" s="1" t="s">
-        <v>501</v>
-      </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>83</v>
+        <v>320</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="B229" s="1" t="s">
-        <v>503</v>
-      </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>38</v>
+        <v>139</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>302</v>
@@ -7003,139 +6976,139 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="B230" s="1" t="s">
-        <v>505</v>
-      </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>58</v>
+        <v>150</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>321</v>
+        <v>351</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B231" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="B231" s="1" t="s">
-        <v>507</v>
-      </c>
       <c r="C231" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B232" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="B232" s="1" t="s">
-        <v>509</v>
-      </c>
       <c r="C232" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>148</v>
+        <v>177</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>354</v>
+        <v>320</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B233" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="B233" s="1" t="s">
-        <v>511</v>
-      </c>
       <c r="C233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>159</v>
+        <v>196</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>321</v>
+        <v>83</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B234" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="B234" s="1" t="s">
-        <v>513</v>
-      </c>
       <c r="C234" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>177</v>
+        <v>216</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>321</v>
+        <v>100</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B235" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="B235" s="1" t="s">
-        <v>515</v>
-      </c>
       <c r="C235" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>83</v>
+        <v>320</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B236" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="B236" s="1" t="s">
-        <v>517</v>
-      </c>
       <c r="C236" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>100</v>
@@ -7143,22 +7116,22 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B237" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="B237" s="1" t="s">
+      <c r="C237" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D237" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="C237" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D237" s="1" t="s">
-        <v>489</v>
-      </c>
       <c r="E237" s="1" t="s">
-        <v>225</v>
+        <v>4</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>321</v>
+        <v>83</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -7172,13 +7145,13 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>489</v>
+        <v>519</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>234</v>
+        <v>8</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>100</v>
+        <v>302</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -7192,30 +7165,30 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>83</v>
+        <v>302</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="B240" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="B240" s="1" t="s">
-        <v>526</v>
-      </c>
       <c r="C240" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F240" s="1" t="s">
         <v>302</v>
@@ -7223,19 +7196,19 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="B241" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="B241" s="1" t="s">
-        <v>528</v>
-      </c>
       <c r="C241" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F241" s="1" t="s">
         <v>302</v>
@@ -7243,19 +7216,19 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="B242" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="B242" s="1" t="s">
-        <v>530</v>
-      </c>
       <c r="C242" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F242" s="1" t="s">
         <v>302</v>
@@ -7263,59 +7236,59 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="B243" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="B243" s="1" t="s">
-        <v>532</v>
-      </c>
       <c r="C243" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>302</v>
+        <v>83</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="B244" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="B244" s="1" t="s">
-        <v>534</v>
-      </c>
       <c r="C244" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>302</v>
+        <v>83</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="B245" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="B245" s="1" t="s">
-        <v>536</v>
-      </c>
       <c r="C245" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>83</v>
@@ -7323,59 +7296,59 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="B246" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="B246" s="1" t="s">
-        <v>538</v>
-      </c>
       <c r="C246" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>38</v>
+        <v>139</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="B247" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="B247" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="C247" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>58</v>
+        <v>150</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="B248" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="B248" s="1" t="s">
-        <v>542</v>
-      </c>
       <c r="C248" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>5</v>
@@ -7383,56 +7356,56 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="B249" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="B249" s="1" t="s">
-        <v>544</v>
-      </c>
       <c r="C249" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>148</v>
+        <v>177</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>5</v>
+        <v>302</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B250" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="B250" s="1" t="s">
-        <v>546</v>
-      </c>
       <c r="C250" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>5</v>
+        <v>302</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="B251" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="B251" s="1" t="s">
-        <v>548</v>
-      </c>
       <c r="C251" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E251" s="1" t="s">
         <v>177</v>
@@ -7443,62 +7416,62 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B252" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="B252" s="1" t="s">
-        <v>550</v>
-      </c>
       <c r="C252" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E252" s="1" t="s">
         <v>177</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>302</v>
+        <v>83</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="B253" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="B253" s="1" t="s">
-        <v>552</v>
-      </c>
       <c r="C253" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E253" s="1" t="s">
         <v>177</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>302</v>
+        <v>83</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="B254" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="B254" s="1" t="s">
+      <c r="C254" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D254" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="C254" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D254" s="1" t="s">
-        <v>524</v>
-      </c>
       <c r="E254" s="1" t="s">
-        <v>177</v>
+        <v>4</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>83</v>
+        <v>351</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -7512,13 +7485,13 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>524</v>
+        <v>554</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>177</v>
+        <v>8</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>83</v>
+        <v>320</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -7532,110 +7505,110 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>354</v>
+        <v>320</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="B257" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="B257" s="1" t="s">
-        <v>561</v>
-      </c>
       <c r="C257" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="B258" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="B258" s="1" t="s">
-        <v>563</v>
-      </c>
       <c r="C258" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>321</v>
+        <v>5</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B259" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="B259" s="1" t="s">
-        <v>565</v>
-      </c>
       <c r="C259" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>321</v>
+        <v>100</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="B260" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="B260" s="1" t="s">
-        <v>567</v>
-      </c>
       <c r="C260" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B261" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="B261" s="1" t="s">
-        <v>569</v>
-      </c>
       <c r="C261" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F261" s="1" t="s">
         <v>100</v>
@@ -7643,102 +7616,102 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="B262" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="B262" s="1" t="s">
-        <v>571</v>
-      </c>
       <c r="C262" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>100</v>
+        <v>257</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B263" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="B263" s="1" t="s">
-        <v>573</v>
-      </c>
       <c r="C263" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>38</v>
+        <v>139</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>100</v>
+        <v>257</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="B264" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="B264" s="1" t="s">
-        <v>575</v>
-      </c>
       <c r="C264" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>58</v>
+        <v>150</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>257</v>
+        <v>320</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="B265" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="B265" s="1" t="s">
-        <v>577</v>
-      </c>
       <c r="C265" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>257</v>
+        <v>320</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="B266" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="B266" s="1" t="s">
+      <c r="C266" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D266" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="C266" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D266" s="1" t="s">
-        <v>559</v>
-      </c>
       <c r="E266" s="1" t="s">
-        <v>148</v>
+        <v>4</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -7752,13 +7725,13 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>559</v>
+        <v>579</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>159</v>
+        <v>8</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -7772,170 +7745,170 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="B269" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="B269" s="1" t="s">
-        <v>586</v>
-      </c>
       <c r="C269" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="B270" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="B270" s="1" t="s">
-        <v>588</v>
-      </c>
       <c r="C270" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="B271" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="B271" s="1" t="s">
-        <v>590</v>
-      </c>
       <c r="C271" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="B272" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="B272" s="1" t="s">
-        <v>592</v>
-      </c>
       <c r="C272" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="B273" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="B273" s="1" t="s">
-        <v>594</v>
-      </c>
       <c r="C273" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="B274" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="B274" s="1" t="s">
-        <v>596</v>
-      </c>
       <c r="C274" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>321</v>
+        <v>5</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="B275" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="B275" s="1" t="s">
-        <v>598</v>
-      </c>
       <c r="C275" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>38</v>
+        <v>139</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>321</v>
+        <v>5</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="B276" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="B276" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="C276" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>58</v>
+        <v>150</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>5</v>
@@ -7943,62 +7916,62 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B277" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="B277" s="1" t="s">
-        <v>602</v>
-      </c>
       <c r="C277" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="B278" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="B278" s="1" t="s">
-        <v>604</v>
-      </c>
       <c r="C278" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>148</v>
+        <v>177</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="B279" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="B279" s="1" t="s">
+      <c r="C279" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D279" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="C279" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D279" s="1" t="s">
-        <v>584</v>
-      </c>
       <c r="E279" s="1" t="s">
-        <v>159</v>
+        <v>4</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -8012,13 +7985,13 @@
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>584</v>
+        <v>606</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>177</v>
+        <v>8</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>83</v>
+        <v>320</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -8032,33 +8005,33 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="B282" s="1" t="s">
         <v>612</v>
       </c>
-      <c r="B282" s="1" t="s">
+      <c r="C282" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D282" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E282" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F282" s="1" t="s">
         <v>613</v>
-      </c>
-      <c r="C282" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D282" s="1" t="s">
-        <v>611</v>
-      </c>
-      <c r="E282" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F282" s="1" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -8072,13 +8045,13 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -8092,173 +8065,173 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>618</v>
+        <v>320</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B285" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="B285" s="1" t="s">
-        <v>620</v>
-      </c>
       <c r="C285" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="B286" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="B286" s="1" t="s">
-        <v>622</v>
-      </c>
       <c r="C286" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>321</v>
+        <v>5</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="B287" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="B287" s="1" t="s">
-        <v>624</v>
-      </c>
       <c r="C287" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="B288" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="B288" s="1" t="s">
-        <v>626</v>
-      </c>
       <c r="C288" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>38</v>
+        <v>139</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="B289" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="B289" s="1" t="s">
-        <v>628</v>
-      </c>
       <c r="C289" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>58</v>
+        <v>150</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>321</v>
+        <v>5</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B290" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="B290" s="1" t="s">
-        <v>630</v>
-      </c>
       <c r="C290" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>321</v>
+        <v>5</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="B291" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="B291" s="1" t="s">
-        <v>632</v>
-      </c>
       <c r="C291" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>148</v>
+        <v>177</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="B292" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="B292" s="1" t="s">
+      <c r="C292" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D292" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="C292" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D292" s="1" t="s">
-        <v>611</v>
-      </c>
       <c r="E292" s="1" t="s">
-        <v>159</v>
+        <v>4</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>5</v>
+        <v>351</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8272,13 +8245,13 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>611</v>
+        <v>634</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>177</v>
+        <v>8</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8292,130 +8265,130 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>354</v>
+        <v>320</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="B295" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="B295" s="1" t="s">
-        <v>641</v>
-      </c>
       <c r="C295" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="B296" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="B296" s="1" t="s">
-        <v>643</v>
-      </c>
       <c r="C296" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="B297" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="B297" s="1" t="s">
-        <v>645</v>
-      </c>
       <c r="C297" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="B298" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="B298" s="1" t="s">
-        <v>647</v>
-      </c>
       <c r="C298" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>321</v>
+        <v>5</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="B299" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="B299" s="1" t="s">
-        <v>649</v>
-      </c>
       <c r="C299" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>321</v>
+        <v>5</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="B300" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="B300" s="1" t="s">
-        <v>651</v>
-      </c>
       <c r="C300" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>5</v>
@@ -8423,19 +8396,19 @@
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="B301" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="B301" s="1" t="s">
-        <v>653</v>
-      </c>
       <c r="C301" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>38</v>
+        <v>139</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>5</v>
@@ -8443,39 +8416,39 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="B302" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="B302" s="1" t="s">
-        <v>655</v>
-      </c>
       <c r="C302" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>58</v>
+        <v>150</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B303" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="B303" s="1" t="s">
-        <v>657</v>
-      </c>
       <c r="C303" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>5</v>
@@ -8483,101 +8456,21 @@
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="B304" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="B304" s="1" t="s">
+      <c r="C304" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D304" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="C304" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D304" s="1" t="s">
-        <v>639</v>
-      </c>
       <c r="E304" s="1" t="s">
-        <v>148</v>
+        <v>11</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A305" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="B305" s="1" t="s">
-        <v>661</v>
-      </c>
-      <c r="C305" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D305" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="E305" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F305" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A306" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="B306" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="C306" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D306" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="E306" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F306" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A307" s="1" t="s">
-        <v>665</v>
-      </c>
-      <c r="B307" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="C307" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D307" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="E307" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F307" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A308" s="1" t="s">
-        <v>667</v>
-      </c>
-      <c r="B308" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="C308" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D308" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="E308" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F308" s="1" t="s">
         <v>83</v>
       </c>
     </row>

--- a/DND05S.xlsx
+++ b/DND05S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1836" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="652">
   <si>
     <t/>
   </si>
@@ -979,12 +979,6 @@
     <t>PROCLIN PCH 400ML</t>
   </si>
   <si>
-    <t>10025646</t>
-  </si>
-  <si>
-    <t>YURI TAF LMN&amp;LIME500</t>
-  </si>
-  <si>
     <t>20093919</t>
   </si>
   <si>
@@ -1973,39 +1967,6 @@
   </si>
   <si>
     <t>VAPE MILK TEA 600ML</t>
-  </si>
-  <si>
-    <t>20137792</t>
-  </si>
-  <si>
-    <t>MAMA LIME GREEN 690</t>
-  </si>
-  <si>
-    <t>999</t>
-  </si>
-  <si>
-    <t>20131792</t>
-  </si>
-  <si>
-    <t>BOOM DET.BBK LVND770</t>
-  </si>
-  <si>
-    <t>20133213</t>
-  </si>
-  <si>
-    <t>BOOM DET.CAIR LAV510</t>
-  </si>
-  <si>
-    <t>20123022</t>
-  </si>
-  <si>
-    <t>SAYANG PWDR ROSE 770</t>
-  </si>
-  <si>
-    <t>20123019</t>
-  </si>
-  <si>
-    <t>SAYANG LIQ ROSE 510</t>
   </si>
 </sst>
 </file>
@@ -2398,14 +2359,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F306"/>
+  <dimension ref="A1:F300"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="5" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
+    <col min="4" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5303,10 +5263,10 @@
         <v>310</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>5</v>
+        <v>163</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -5320,30 +5280,30 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>163</v>
+        <v>21</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>328</v>
-      </c>
       <c r="E147" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>21</v>
@@ -5360,10 +5320,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>21</v>
@@ -5380,10 +5340,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>21</v>
@@ -5400,13 +5360,13 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -5420,10 +5380,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -5440,13 +5400,13 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -5460,13 +5420,13 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -5480,33 +5440,33 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>21</v>
+        <v>344</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>345</v>
-      </c>
       <c r="E155" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -5520,13 +5480,13 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>297</v>
+        <v>21</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -5540,10 +5500,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>21</v>
@@ -5560,13 +5520,13 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -5580,13 +5540,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>15</v>
+        <v>163</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -5600,10 +5560,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>163</v>
@@ -5620,10 +5580,10 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>163</v>
@@ -5640,10 +5600,10 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>163</v>
@@ -5660,10 +5620,10 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>163</v>
@@ -5671,19 +5631,19 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>365</v>
-      </c>
       <c r="E164" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>163</v>
@@ -5700,13 +5660,13 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>163</v>
+        <v>98</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -5720,13 +5680,13 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -5740,10 +5700,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5760,10 +5720,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5780,10 +5740,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5800,10 +5760,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5820,10 +5780,10 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5831,22 +5791,22 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D172" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="E172" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5860,13 +5820,13 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5880,10 +5840,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5900,10 +5860,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5920,10 +5880,10 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5940,13 +5900,13 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5960,30 +5920,30 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="E179" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -6000,10 +5960,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -6020,10 +5980,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -6040,10 +6000,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -6060,10 +6020,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -6080,10 +6040,10 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -6100,13 +6060,13 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -6120,33 +6080,33 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D187" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="B187" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>414</v>
-      </c>
       <c r="E187" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>21</v>
+        <v>252</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -6160,13 +6120,13 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>252</v>
+        <v>21</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6180,10 +6140,10 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>21</v>
@@ -6200,10 +6160,10 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>21</v>
@@ -6220,13 +6180,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>21</v>
+        <v>163</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -6240,10 +6200,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>163</v>
@@ -6260,10 +6220,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>163</v>
@@ -6280,30 +6240,30 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>163</v>
+        <v>21</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D195" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B195" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>431</v>
-      </c>
       <c r="E195" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>21</v>
@@ -6320,10 +6280,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>21</v>
@@ -6340,10 +6300,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>21</v>
@@ -6360,33 +6320,33 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>21</v>
+        <v>98</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D199" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="B199" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="C199" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D199" s="1" t="s">
-        <v>440</v>
-      </c>
       <c r="E199" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -6400,10 +6360,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>21</v>
@@ -6420,10 +6380,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>21</v>
@@ -6440,13 +6400,13 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -6460,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -6480,13 +6440,13 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -6500,13 +6460,13 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>98</v>
+        <v>344</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -6520,13 +6480,13 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>346</v>
+        <v>315</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -6540,30 +6500,30 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>440</v>
+        <v>457</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>315</v>
+        <v>21</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="B208" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>459</v>
-      </c>
       <c r="E208" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>21</v>
@@ -6580,10 +6540,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>21</v>
@@ -6600,13 +6560,13 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -6620,13 +6580,13 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>81</v>
+        <v>297</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -6640,13 +6600,13 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>297</v>
+        <v>5</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -6660,13 +6620,13 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>5</v>
+        <v>163</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -6680,33 +6640,33 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>163</v>
+        <v>472</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>474</v>
+        <v>315</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -6720,13 +6680,13 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>315</v>
+        <v>472</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -6740,30 +6700,30 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>137</v>
+        <v>4</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>474</v>
+        <v>5</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D218" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="B218" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="C218" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D218" s="1" t="s">
-        <v>481</v>
-      </c>
       <c r="E218" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>5</v>
@@ -6780,13 +6740,13 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>5</v>
+        <v>315</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -6800,10 +6760,10 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>315</v>
@@ -6820,10 +6780,10 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>315</v>
@@ -6840,13 +6800,13 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>315</v>
+        <v>344</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -6860,13 +6820,13 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>346</v>
+        <v>81</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -6880,13 +6840,13 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>81</v>
+        <v>297</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -6900,13 +6860,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -6920,13 +6880,13 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>315</v>
+        <v>297</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -6940,13 +6900,13 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>297</v>
+        <v>344</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -6960,13 +6920,13 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>346</v>
+        <v>315</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -6980,10 +6940,10 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>315</v>
@@ -7000,13 +6960,13 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>315</v>
+        <v>81</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -7020,13 +6980,13 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -7040,13 +7000,13 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>98</v>
+        <v>315</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -7060,13 +7020,13 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>315</v>
+        <v>98</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -7080,33 +7040,33 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>481</v>
+        <v>514</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>229</v>
+        <v>4</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D235" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="B235" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="C235" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D235" s="1" t="s">
-        <v>516</v>
-      </c>
       <c r="E235" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>81</v>
+        <v>297</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -7120,10 +7080,10 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>297</v>
@@ -7140,10 +7100,10 @@
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>297</v>
@@ -7160,10 +7120,10 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F238" s="1" t="s">
         <v>297</v>
@@ -7180,10 +7140,10 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F239" s="1" t="s">
         <v>297</v>
@@ -7200,13 +7160,13 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>297</v>
+        <v>81</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -7220,10 +7180,10 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F241" s="1" t="s">
         <v>81</v>
@@ -7240,10 +7200,10 @@
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="F242" s="1" t="s">
         <v>81</v>
@@ -7260,13 +7220,13 @@
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -7280,10 +7240,10 @@
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="F244" s="1" t="s">
         <v>5</v>
@@ -7300,10 +7260,10 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>5</v>
@@ -7320,13 +7280,13 @@
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>5</v>
+        <v>297</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -7340,7 +7300,7 @@
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E247" s="1" t="s">
         <v>172</v>
@@ -7360,7 +7320,7 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E248" s="1" t="s">
         <v>172</v>
@@ -7380,13 +7340,13 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E249" s="1" t="s">
         <v>172</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>297</v>
+        <v>81</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -7400,7 +7360,7 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>172</v>
@@ -7420,33 +7380,33 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>516</v>
+        <v>549</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>172</v>
+        <v>4</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>81</v>
+        <v>344</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="B252" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D252" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="B252" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="C252" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D252" s="1" t="s">
-        <v>551</v>
-      </c>
       <c r="E252" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>346</v>
+        <v>315</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7460,10 +7420,10 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F253" s="1" t="s">
         <v>315</v>
@@ -7480,10 +7440,10 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>315</v>
@@ -7500,13 +7460,13 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>315</v>
+        <v>5</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -7520,13 +7480,13 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -7540,10 +7500,10 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>98</v>
@@ -7560,10 +7520,10 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>98</v>
@@ -7580,13 +7540,13 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>98</v>
+        <v>252</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -7600,10 +7560,10 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="F260" s="1" t="s">
         <v>252</v>
@@ -7620,13 +7580,13 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>252</v>
+        <v>315</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -7640,10 +7600,10 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="F262" s="1" t="s">
         <v>315</v>
@@ -7660,10 +7620,10 @@
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>551</v>
+        <v>574</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>158</v>
+        <v>4</v>
       </c>
       <c r="F263" s="1" t="s">
         <v>315</v>
@@ -7671,19 +7631,19 @@
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="B264" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D264" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="B264" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="C264" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D264" s="1" t="s">
-        <v>576</v>
-      </c>
       <c r="E264" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F264" s="1" t="s">
         <v>315</v>
@@ -7700,10 +7660,10 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>315</v>
@@ -7720,10 +7680,10 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>315</v>
@@ -7740,10 +7700,10 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>315</v>
@@ -7760,10 +7720,10 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>315</v>
@@ -7780,10 +7740,10 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>315</v>
@@ -7800,10 +7760,10 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>315</v>
@@ -7820,13 +7780,13 @@
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>315</v>
+        <v>5</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -7840,10 +7800,10 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>5</v>
@@ -7860,10 +7820,10 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>5</v>
@@ -7880,13 +7840,13 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -7900,10 +7860,10 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>81</v>
@@ -7920,33 +7880,33 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>576</v>
+        <v>601</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>172</v>
+        <v>4</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="B277" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="C277" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D277" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="B277" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="C277" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D277" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="E277" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>5</v>
+        <v>315</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -7960,10 +7920,10 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>315</v>
@@ -7980,33 +7940,33 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>315</v>
+        <v>608</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>610</v>
+        <v>315</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -8020,10 +7980,10 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>315</v>
@@ -8040,10 +8000,10 @@
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>315</v>
@@ -8060,13 +8020,13 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>315</v>
+        <v>5</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -8080,13 +8040,13 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>5</v>
+        <v>315</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -8100,10 +8060,10 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>315</v>
@@ -8120,13 +8080,13 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>315</v>
+        <v>5</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -8140,10 +8100,10 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>5</v>
@@ -8160,13 +8120,13 @@
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>5</v>
+        <v>315</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -8180,33 +8140,33 @@
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>603</v>
+        <v>629</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>172</v>
+        <v>4</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>315</v>
+        <v>344</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="B290" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="C290" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D290" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="B290" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="C290" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D290" s="1" t="s">
-        <v>631</v>
-      </c>
       <c r="E290" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>346</v>
+        <v>315</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -8220,10 +8180,10 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F291" s="1" t="s">
         <v>315</v>
@@ -8240,10 +8200,10 @@
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F292" s="1" t="s">
         <v>315</v>
@@ -8260,10 +8220,10 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F293" s="1" t="s">
         <v>315</v>
@@ -8280,10 +8240,10 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F294" s="1" t="s">
         <v>315</v>
@@ -8300,13 +8260,13 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>315</v>
+        <v>5</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8320,10 +8280,10 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F296" s="1" t="s">
         <v>5</v>
@@ -8340,10 +8300,10 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="F297" s="1" t="s">
         <v>5</v>
@@ -8360,10 +8320,10 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="F298" s="1" t="s">
         <v>5</v>
@@ -8380,13 +8340,13 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8400,132 +8360,12 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A301" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="B301" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="C301" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D301" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="E301" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="F301" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A302" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="B302" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="C302" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D302" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="E302" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F302" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A303" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="B303" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="C303" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D303" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="E303" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F303" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A304" s="1" t="s">
-        <v>659</v>
-      </c>
-      <c r="B304" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="C304" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D304" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="E304" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F304" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A305" s="1" t="s">
-        <v>661</v>
-      </c>
-      <c r="B305" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="C305" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D305" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="E305" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F305" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A306" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="B306" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="C306" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D306" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="E306" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F306" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/DND05S.xlsx
+++ b/DND05S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="651">
   <si>
     <t/>
   </si>
@@ -425,9 +425,6 @@
   </si>
   <si>
     <t>10</t>
-  </si>
-  <si>
-    <t>,(E-1B)</t>
   </si>
   <si>
     <t>10014547</t>
@@ -3586,15 +3583,15 @@
         <v>4</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>138</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -3611,10 +3608,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -3631,10 +3628,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -3651,16 +3648,16 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="C65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>147</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>4</v>
@@ -3671,16 +3668,16 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>8</v>
@@ -3691,16 +3688,16 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>11</v>
@@ -3711,16 +3708,16 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>14</v>
@@ -3731,16 +3728,16 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>18</v>
@@ -3751,16 +3748,16 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="C70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>158</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>4</v>
@@ -3771,16 +3768,16 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>160</v>
-      </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>8</v>
@@ -3791,36 +3788,36 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>18</v>
@@ -3831,16 +3828,16 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>32</v>
@@ -3851,16 +3848,16 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>35</v>
@@ -3871,16 +3868,16 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>4</v>
@@ -3891,16 +3888,16 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>8</v>
@@ -3911,16 +3908,16 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>176</v>
-      </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>11</v>
@@ -3931,16 +3928,16 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>178</v>
-      </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>14</v>
@@ -3951,16 +3948,16 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>18</v>
@@ -3971,16 +3968,16 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>32</v>
@@ -3991,16 +3988,16 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>35</v>
@@ -4011,16 +4008,16 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>38</v>
@@ -4031,16 +4028,16 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>74</v>
@@ -4051,36 +4048,36 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="C85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>191</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>8</v>
@@ -4091,16 +4088,16 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>11</v>
@@ -4111,16 +4108,16 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>14</v>
@@ -4131,16 +4128,16 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>18</v>
@@ -4151,76 +4148,76 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>74</v>
@@ -4231,16 +4228,16 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="C94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>211</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>4</v>
@@ -4251,16 +4248,16 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>213</v>
-      </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>8</v>
@@ -4271,16 +4268,16 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>215</v>
-      </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>11</v>
@@ -4291,16 +4288,16 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>14</v>
@@ -4311,16 +4308,16 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="C98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>220</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>4</v>
@@ -4331,16 +4328,16 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>8</v>
@@ -4351,16 +4348,16 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>224</v>
-      </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>11</v>
@@ -4371,16 +4368,16 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>14</v>
@@ -4391,16 +4388,16 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="C102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>228</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>229</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>4</v>
@@ -4411,16 +4408,16 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>231</v>
-      </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>8</v>
@@ -4431,16 +4428,16 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>11</v>
@@ -4451,16 +4448,16 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>14</v>
@@ -4471,16 +4468,16 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>237</v>
-      </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>18</v>
@@ -4491,16 +4488,16 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="C107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>240</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>4</v>
@@ -4511,16 +4508,16 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>8</v>
@@ -4531,16 +4528,16 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>11</v>
@@ -4551,16 +4548,16 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>14</v>
@@ -4571,16 +4568,16 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>18</v>
@@ -4591,36 +4588,36 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="C112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>251</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>254</v>
-      </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>8</v>
@@ -4631,16 +4628,16 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>11</v>
@@ -4651,16 +4648,16 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>14</v>
@@ -4671,16 +4668,16 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>18</v>
@@ -4691,16 +4688,16 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>262</v>
-      </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>32</v>
@@ -4711,16 +4708,16 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>35</v>
@@ -4731,16 +4728,16 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>266</v>
-      </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>38</v>
@@ -4751,16 +4748,16 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>268</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>74</v>
@@ -4771,16 +4768,16 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>137</v>
@@ -4791,16 +4788,16 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="C122" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>273</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>4</v>
@@ -4811,16 +4808,16 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>8</v>
@@ -4831,16 +4828,16 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>11</v>
@@ -4851,16 +4848,16 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>14</v>
@@ -4871,16 +4868,16 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>18</v>
@@ -4891,16 +4888,16 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>32</v>
@@ -4911,16 +4908,16 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>285</v>
-      </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>35</v>
@@ -4931,16 +4928,16 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>38</v>
@@ -4951,16 +4948,16 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="C130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>290</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>4</v>
@@ -4971,16 +4968,16 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>292</v>
-      </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>8</v>
@@ -4991,76 +4988,76 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>294</v>
-      </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>32</v>
@@ -5071,16 +5068,16 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>35</v>
@@ -5091,16 +5088,16 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>38</v>
@@ -5111,16 +5108,16 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>74</v>
@@ -5131,16 +5128,16 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>310</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>4</v>
@@ -5151,16 +5148,16 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>312</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>8</v>
@@ -5171,76 +5168,76 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>321</v>
-      </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>35</v>
@@ -5251,36 +5248,36 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>74</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B146" s="1" t="s">
+      <c r="C146" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>326</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>4</v>
@@ -5291,16 +5288,16 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>328</v>
-      </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>8</v>
@@ -5311,16 +5308,16 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>11</v>
@@ -5331,16 +5328,16 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>14</v>
@@ -5351,16 +5348,16 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>334</v>
-      </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>18</v>
@@ -5371,16 +5368,16 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>32</v>
@@ -5391,16 +5388,16 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>35</v>
@@ -5411,16 +5408,16 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>340</v>
-      </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>38</v>
@@ -5431,56 +5428,56 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B154" s="1" t="s">
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>343</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>11</v>
@@ -5491,16 +5488,16 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>14</v>
@@ -5511,16 +5508,16 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>352</v>
-      </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>18</v>
@@ -5531,136 +5528,136 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>354</v>
-      </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>356</v>
-      </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>358</v>
-      </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>360</v>
-      </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>74</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B163" s="1" t="s">
+      <c r="C163" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>363</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>365</v>
-      </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>367</v>
-      </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>11</v>
@@ -5671,16 +5668,16 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>369</v>
-      </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>14</v>
@@ -5691,16 +5688,16 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>371</v>
-      </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>18</v>
@@ -5711,16 +5708,16 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>373</v>
-      </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>32</v>
@@ -5731,16 +5728,16 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="B169" s="1" t="s">
-        <v>375</v>
-      </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>35</v>
@@ -5751,16 +5748,16 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>377</v>
-      </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>38</v>
@@ -5771,16 +5768,16 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B171" s="1" t="s">
+      <c r="C171" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>380</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>4</v>
@@ -5791,16 +5788,16 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>8</v>
@@ -5811,16 +5808,16 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>384</v>
-      </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>11</v>
@@ -5831,16 +5828,16 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="B174" s="1" t="s">
-        <v>386</v>
-      </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>14</v>
@@ -5851,16 +5848,16 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B175" s="1" t="s">
-        <v>388</v>
-      </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>18</v>
@@ -5871,16 +5868,16 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>390</v>
-      </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>32</v>
@@ -5891,16 +5888,16 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>392</v>
-      </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>35</v>
@@ -5911,16 +5908,16 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>395</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>4</v>
@@ -5931,16 +5928,16 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>8</v>
@@ -5951,16 +5948,16 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>11</v>
@@ -5971,16 +5968,16 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="B181" s="1" t="s">
-        <v>401</v>
-      </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>14</v>
@@ -5991,16 +5988,16 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>403</v>
-      </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>18</v>
@@ -6011,16 +6008,16 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="B183" s="1" t="s">
-        <v>405</v>
-      </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>32</v>
@@ -6031,16 +6028,16 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="B184" s="1" t="s">
-        <v>407</v>
-      </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>35</v>
@@ -6051,16 +6048,16 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>409</v>
-      </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>38</v>
@@ -6071,16 +6068,16 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B186" s="1" t="s">
+      <c r="C186" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>411</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>412</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>4</v>
@@ -6091,36 +6088,36 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B187" s="1" t="s">
-        <v>414</v>
-      </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="B188" s="1" t="s">
-        <v>416</v>
-      </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>11</v>
@@ -6131,16 +6128,16 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>418</v>
-      </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>14</v>
@@ -6151,16 +6148,16 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B190" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>18</v>
@@ -6171,76 +6168,76 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B191" s="1" t="s">
-        <v>422</v>
-      </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B192" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="B192" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>426</v>
-      </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B194" s="1" t="s">
+      <c r="C194" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D194" s="1" t="s">
         <v>428</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D194" s="1" t="s">
-        <v>429</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>4</v>
@@ -6251,16 +6248,16 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="B195" s="1" t="s">
-        <v>431</v>
-      </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E195" s="1" t="s">
         <v>8</v>
@@ -6271,16 +6268,16 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="B196" s="1" t="s">
-        <v>433</v>
-      </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>11</v>
@@ -6291,16 +6288,16 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="B197" s="1" t="s">
-        <v>435</v>
-      </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E197" s="1" t="s">
         <v>14</v>
@@ -6311,16 +6308,16 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="B198" s="1" t="s">
+      <c r="C198" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D198" s="1" t="s">
         <v>437</v>
-      </c>
-      <c r="C198" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D198" s="1" t="s">
-        <v>438</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>4</v>
@@ -6331,16 +6328,16 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B199" s="1" t="s">
-        <v>440</v>
-      </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>8</v>
@@ -6351,16 +6348,16 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="B200" s="1" t="s">
-        <v>442</v>
-      </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>11</v>
@@ -6371,16 +6368,16 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="B201" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>14</v>
@@ -6391,16 +6388,16 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="B202" s="1" t="s">
-        <v>446</v>
-      </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>18</v>
@@ -6411,16 +6408,16 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="B203" s="1" t="s">
-        <v>448</v>
-      </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>32</v>
@@ -6431,16 +6428,16 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="B204" s="1" t="s">
-        <v>450</v>
-      </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>35</v>
@@ -6451,56 +6448,56 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B205" s="1" t="s">
-        <v>452</v>
-      </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E205" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B206" s="1" t="s">
-        <v>454</v>
-      </c>
       <c r="C206" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>74</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="B207" s="1" t="s">
+      <c r="C207" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D207" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>457</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>4</v>
@@ -6511,16 +6508,16 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="B208" s="1" t="s">
-        <v>459</v>
-      </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>8</v>
@@ -6531,16 +6528,16 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="B209" s="1" t="s">
-        <v>461</v>
-      </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>11</v>
@@ -6551,16 +6548,16 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B210" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="B210" s="1" t="s">
-        <v>463</v>
-      </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>14</v>
@@ -6571,36 +6568,36 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B211" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="B211" s="1" t="s">
-        <v>465</v>
-      </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B212" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="B212" s="1" t="s">
-        <v>467</v>
-      </c>
       <c r="C212" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>32</v>
@@ -6611,96 +6608,96 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="B213" s="1" t="s">
-        <v>469</v>
-      </c>
       <c r="C213" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>471</v>
-      </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="B215" s="1" t="s">
-        <v>474</v>
-      </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E215" s="1" t="s">
         <v>74</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="B216" s="1" t="s">
-        <v>476</v>
-      </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>137</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="B217" s="1" t="s">
+      <c r="C217" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D217" s="1" t="s">
         <v>478</v>
-      </c>
-      <c r="C217" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D217" s="1" t="s">
-        <v>479</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>4</v>
@@ -6711,16 +6708,16 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="B218" s="1" t="s">
-        <v>481</v>
-      </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E218" s="1" t="s">
         <v>8</v>
@@ -6731,96 +6728,96 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B219" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="B219" s="1" t="s">
-        <v>483</v>
-      </c>
       <c r="C219" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B220" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="B220" s="1" t="s">
-        <v>485</v>
-      </c>
       <c r="C220" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B221" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="B221" s="1" t="s">
-        <v>487</v>
-      </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="B222" s="1" t="s">
-        <v>489</v>
-      </c>
       <c r="C222" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B223" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="B223" s="1" t="s">
-        <v>491</v>
-      </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>35</v>
@@ -6831,139 +6828,139 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B224" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="B224" s="1" t="s">
-        <v>493</v>
-      </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="B225" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="B225" s="1" t="s">
-        <v>495</v>
-      </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>74</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B226" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="B226" s="1" t="s">
-        <v>497</v>
-      </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>137</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="B227" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="B227" s="1" t="s">
-        <v>499</v>
-      </c>
       <c r="C227" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B228" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="B228" s="1" t="s">
-        <v>501</v>
-      </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="B229" s="1" t="s">
-        <v>503</v>
-      </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="B230" s="1" t="s">
-        <v>505</v>
-      </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>81</v>
@@ -6971,19 +6968,19 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B231" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="B231" s="1" t="s">
-        <v>507</v>
-      </c>
       <c r="C231" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>98</v>
@@ -6991,39 +6988,39 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B232" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="B232" s="1" t="s">
-        <v>509</v>
-      </c>
       <c r="C232" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B233" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="B233" s="1" t="s">
-        <v>511</v>
-      </c>
       <c r="C233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>98</v>
@@ -7031,16 +7028,16 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B234" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="B234" s="1" t="s">
+      <c r="C234" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D234" s="1" t="s">
         <v>513</v>
-      </c>
-      <c r="C234" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D234" s="1" t="s">
-        <v>514</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>4</v>
@@ -7051,116 +7048,116 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="B235" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B235" s="1" t="s">
-        <v>516</v>
-      </c>
       <c r="C235" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="B236" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="B236" s="1" t="s">
-        <v>518</v>
-      </c>
       <c r="C236" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="B237" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="B237" s="1" t="s">
-        <v>520</v>
-      </c>
       <c r="C237" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="B238" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="B238" s="1" t="s">
-        <v>522</v>
-      </c>
       <c r="C238" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="B239" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="B239" s="1" t="s">
-        <v>524</v>
-      </c>
       <c r="C239" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="B240" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="B240" s="1" t="s">
-        <v>526</v>
-      </c>
       <c r="C240" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E240" s="1" t="s">
         <v>35</v>
@@ -7171,16 +7168,16 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="B241" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="B241" s="1" t="s">
-        <v>528</v>
-      </c>
       <c r="C241" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E241" s="1" t="s">
         <v>38</v>
@@ -7191,16 +7188,16 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="B242" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="B242" s="1" t="s">
-        <v>530</v>
-      </c>
       <c r="C242" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E242" s="1" t="s">
         <v>74</v>
@@ -7211,16 +7208,16 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="B243" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="B243" s="1" t="s">
-        <v>532</v>
-      </c>
       <c r="C243" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E243" s="1" t="s">
         <v>137</v>
@@ -7231,19 +7228,19 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="B244" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="B244" s="1" t="s">
-        <v>534</v>
-      </c>
       <c r="C244" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F244" s="1" t="s">
         <v>5</v>
@@ -7251,19 +7248,19 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="B245" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="B245" s="1" t="s">
-        <v>536</v>
-      </c>
       <c r="C245" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>5</v>
@@ -7271,79 +7268,79 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="B246" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="B246" s="1" t="s">
-        <v>538</v>
-      </c>
       <c r="C246" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="B247" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="B247" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="C247" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="B248" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="B248" s="1" t="s">
-        <v>542</v>
-      </c>
       <c r="C248" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="B249" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="B249" s="1" t="s">
-        <v>544</v>
-      </c>
       <c r="C249" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F249" s="1" t="s">
         <v>81</v>
@@ -7351,19 +7348,19 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B250" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="B250" s="1" t="s">
-        <v>546</v>
-      </c>
       <c r="C250" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F250" s="1" t="s">
         <v>81</v>
@@ -7371,96 +7368,96 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="B251" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="B251" s="1" t="s">
+      <c r="C251" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D251" s="1" t="s">
         <v>548</v>
-      </c>
-      <c r="C251" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D251" s="1" t="s">
-        <v>549</v>
       </c>
       <c r="E251" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B252" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="B252" s="1" t="s">
-        <v>551</v>
-      </c>
       <c r="C252" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E252" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="B253" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="B253" s="1" t="s">
-        <v>553</v>
-      </c>
       <c r="C253" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E253" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B254" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="B254" s="1" t="s">
-        <v>555</v>
-      </c>
       <c r="C254" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E254" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="B255" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="B255" s="1" t="s">
-        <v>557</v>
-      </c>
       <c r="C255" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E255" s="1" t="s">
         <v>18</v>
@@ -7471,16 +7468,16 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="B256" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="B256" s="1" t="s">
-        <v>559</v>
-      </c>
       <c r="C256" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E256" s="1" t="s">
         <v>32</v>
@@ -7491,16 +7488,16 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="B257" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="B257" s="1" t="s">
-        <v>561</v>
-      </c>
       <c r="C257" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>35</v>
@@ -7511,16 +7508,16 @@
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="B258" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="B258" s="1" t="s">
-        <v>563</v>
-      </c>
       <c r="C258" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E258" s="1" t="s">
         <v>38</v>
@@ -7531,256 +7528,256 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B259" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="B259" s="1" t="s">
-        <v>565</v>
-      </c>
       <c r="C259" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E259" s="1" t="s">
         <v>74</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="B260" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="B260" s="1" t="s">
-        <v>567</v>
-      </c>
       <c r="C260" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E260" s="1" t="s">
         <v>137</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B261" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="B261" s="1" t="s">
-        <v>569</v>
-      </c>
       <c r="C261" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="B262" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="B262" s="1" t="s">
-        <v>571</v>
-      </c>
       <c r="C262" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B263" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="B263" s="1" t="s">
+      <c r="C263" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D263" s="1" t="s">
         <v>573</v>
-      </c>
-      <c r="C263" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D263" s="1" t="s">
-        <v>574</v>
       </c>
       <c r="E263" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B264" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="B264" s="1" t="s">
-        <v>576</v>
-      </c>
       <c r="C264" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E264" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B265" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="B265" s="1" t="s">
-        <v>578</v>
-      </c>
       <c r="C265" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E265" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B266" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="B266" s="1" t="s">
-        <v>580</v>
-      </c>
       <c r="C266" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E266" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="B267" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="B267" s="1" t="s">
-        <v>582</v>
-      </c>
       <c r="C267" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E267" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B268" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="B268" s="1" t="s">
-        <v>584</v>
-      </c>
       <c r="C268" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E268" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="B269" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="B269" s="1" t="s">
-        <v>586</v>
-      </c>
       <c r="C269" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E269" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="B270" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="B270" s="1" t="s">
-        <v>588</v>
-      </c>
       <c r="C270" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E270" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="B271" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="B271" s="1" t="s">
-        <v>590</v>
-      </c>
       <c r="C271" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E271" s="1" t="s">
         <v>74</v>
@@ -7791,16 +7788,16 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="B272" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="B272" s="1" t="s">
-        <v>592</v>
-      </c>
       <c r="C272" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E272" s="1" t="s">
         <v>137</v>
@@ -7811,19 +7808,19 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="B273" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="B273" s="1" t="s">
-        <v>594</v>
-      </c>
       <c r="C273" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>5</v>
@@ -7831,19 +7828,19 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="B274" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="B274" s="1" t="s">
-        <v>596</v>
-      </c>
       <c r="C274" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>81</v>
@@ -7851,19 +7848,19 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="B275" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="B275" s="1" t="s">
-        <v>598</v>
-      </c>
       <c r="C275" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>81</v>
@@ -7871,16 +7868,16 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="B276" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="B276" s="1" t="s">
+      <c r="C276" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D276" s="1" t="s">
         <v>600</v>
-      </c>
-      <c r="C276" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D276" s="1" t="s">
-        <v>601</v>
       </c>
       <c r="E276" s="1" t="s">
         <v>4</v>
@@ -7891,136 +7888,136 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B277" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="B277" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="C277" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E277" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="B278" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="B278" s="1" t="s">
-        <v>605</v>
-      </c>
       <c r="C278" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E278" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="B279" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="B279" s="1" t="s">
-        <v>607</v>
-      </c>
       <c r="C279" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E279" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="B280" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="B280" s="1" t="s">
-        <v>610</v>
-      </c>
       <c r="C280" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E280" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="B281" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="B281" s="1" t="s">
-        <v>612</v>
-      </c>
       <c r="C281" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E281" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="B282" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="B282" s="1" t="s">
-        <v>614</v>
-      </c>
       <c r="C282" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E282" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B283" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="B283" s="1" t="s">
-        <v>616</v>
-      </c>
       <c r="C283" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E283" s="1" t="s">
         <v>38</v>
@@ -8031,59 +8028,59 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="B284" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="B284" s="1" t="s">
-        <v>618</v>
-      </c>
       <c r="C284" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E284" s="1" t="s">
         <v>74</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B285" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="B285" s="1" t="s">
-        <v>620</v>
-      </c>
       <c r="C285" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>137</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="B286" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="B286" s="1" t="s">
-        <v>622</v>
-      </c>
       <c r="C286" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>5</v>
@@ -8091,19 +8088,19 @@
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="B287" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="B287" s="1" t="s">
-        <v>624</v>
-      </c>
       <c r="C287" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>5</v>
@@ -8111,156 +8108,156 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="B288" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="B288" s="1" t="s">
-        <v>626</v>
-      </c>
       <c r="C288" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="B289" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="B289" s="1" t="s">
+      <c r="C289" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D289" s="1" t="s">
         <v>628</v>
-      </c>
-      <c r="C289" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D289" s="1" t="s">
-        <v>629</v>
       </c>
       <c r="E289" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="B290" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="B290" s="1" t="s">
-        <v>631</v>
-      </c>
       <c r="C290" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E290" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="B291" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="B291" s="1" t="s">
-        <v>633</v>
-      </c>
       <c r="C291" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="B292" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="B292" s="1" t="s">
-        <v>635</v>
-      </c>
       <c r="C292" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="B293" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="B293" s="1" t="s">
-        <v>637</v>
-      </c>
       <c r="C293" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="B294" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="B294" s="1" t="s">
-        <v>639</v>
-      </c>
       <c r="C294" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="B295" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="B295" s="1" t="s">
-        <v>641</v>
-      </c>
       <c r="C295" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>35</v>
@@ -8271,16 +8268,16 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="B296" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="B296" s="1" t="s">
-        <v>643</v>
-      </c>
       <c r="C296" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E296" s="1" t="s">
         <v>38</v>
@@ -8291,16 +8288,16 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="B297" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="B297" s="1" t="s">
-        <v>645</v>
-      </c>
       <c r="C297" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>74</v>
@@ -8311,16 +8308,16 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="B298" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="B298" s="1" t="s">
-        <v>647</v>
-      </c>
       <c r="C298" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>137</v>
@@ -8331,19 +8328,19 @@
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="B299" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="B299" s="1" t="s">
-        <v>649</v>
-      </c>
       <c r="C299" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F299" s="1" t="s">
         <v>98</v>
@@ -8351,19 +8348,19 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="B300" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="B300" s="1" t="s">
-        <v>651</v>
-      </c>
       <c r="C300" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>5</v>

--- a/DND05S.xlsx
+++ b/DND05S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="653">
   <si>
     <t/>
   </si>
@@ -310,6 +310,12 @@
     <t>RT</t>
   </si>
   <si>
+    <t>20133333</t>
+  </si>
+  <si>
+    <t>GENTLE GEN A/KRGT700</t>
+  </si>
+  <si>
     <t>20141371</t>
   </si>
   <si>
@@ -346,6 +352,15 @@
     <t>SO KLN BLU PETAL 700</t>
   </si>
   <si>
+    <t>20142132</t>
+  </si>
+  <si>
+    <t>SO KLN MAISON DE 700</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
     <t>20113567</t>
   </si>
   <si>
@@ -364,12 +379,6 @@
     <t>GENTLE GEN PRS.G 700</t>
   </si>
   <si>
-    <t>20133333</t>
-  </si>
-  <si>
-    <t>GENTLE GEN A/KRGT700</t>
-  </si>
-  <si>
     <t>20073805</t>
   </si>
   <si>
@@ -1040,9 +1049,6 @@
   </si>
   <si>
     <t>24</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
   </si>
   <si>
     <t>10004610</t>
@@ -2356,7 +2362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F300"/>
+  <dimension ref="A1:F301"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3257,10 +3263,10 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -3280,7 +3286,7 @@
         <v>35</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -3300,10 +3306,10 @@
         <v>35</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -3320,10 +3326,10 @@
         <v>35</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -3340,7 +3346,7 @@
         <v>35</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -3360,18 +3366,18 @@
         <v>35</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>5</v>
+        <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -3380,7 +3386,7 @@
         <v>35</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -3388,10 +3394,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -3400,7 +3406,7 @@
         <v>35</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -3408,19 +3414,19 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -3428,10 +3434,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -3440,7 +3446,7 @@
         <v>38</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -3448,10 +3454,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -3460,18 +3466,18 @@
         <v>38</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -3480,7 +3486,7 @@
         <v>38</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>98</v>
@@ -3488,30 +3494,30 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -3520,7 +3526,7 @@
         <v>74</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -3528,10 +3534,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -3540,7 +3546,7 @@
         <v>74</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -3548,10 +3554,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -3560,7 +3566,7 @@
         <v>74</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -3568,19 +3574,19 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>137</v>
+        <v>74</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -3597,50 +3603,50 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="E63" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3648,19 +3654,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -3677,10 +3683,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3688,19 +3694,19 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="E67" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -3708,19 +3714,19 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -3728,19 +3734,19 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -3748,19 +3754,19 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -3777,33 +3783,33 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="E72" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>162</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3817,73 +3823,73 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>5</v>
+        <v>165</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3897,10 +3903,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3908,19 +3914,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="E78" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3928,19 +3934,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3948,19 +3954,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3968,19 +3974,19 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3988,19 +3994,19 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -4008,19 +4014,19 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -4028,79 +4034,79 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="C86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="E86" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>15</v>
+        <v>194</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>15</v>
@@ -4108,19 +4114,19 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>15</v>
@@ -4128,19 +4134,19 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>15</v>
@@ -4148,102 +4154,102 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>15</v>
+        <v>194</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -4257,10 +4263,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>21</v>
@@ -4268,19 +4274,19 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="E96" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>21</v>
@@ -4288,19 +4294,19 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>21</v>
@@ -4308,22 +4314,22 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -4337,10 +4343,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>98</v>
@@ -4348,19 +4354,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="E100" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>98</v>
@@ -4368,19 +4374,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>98</v>
@@ -4388,22 +4394,22 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>21</v>
+        <v>98</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -4417,10 +4423,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>21</v>
@@ -4428,19 +4434,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="E104" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>21</v>
@@ -4448,62 +4454,62 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>15</v>
+        <v>98</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -4517,30 +4523,30 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>21</v>
@@ -4548,39 +4554,39 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -4588,79 +4594,79 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>251</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="C113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="C113" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="E113" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>21</v>
+        <v>254</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -4668,19 +4674,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -4688,39 +4694,39 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>98</v>
@@ -4728,19 +4734,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>98</v>
@@ -4748,19 +4754,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>98</v>
@@ -4768,19 +4774,19 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>137</v>
+        <v>74</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>98</v>
@@ -4788,22 +4794,22 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>4</v>
+        <v>140</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4817,10 +4823,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -4828,19 +4834,19 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>272</v>
-      </c>
       <c r="E124" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -4848,19 +4854,19 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -4868,19 +4874,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -4888,19 +4894,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4908,19 +4914,19 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4928,19 +4934,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4948,22 +4954,22 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4977,10 +4983,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>21</v>
@@ -4988,42 +4994,42 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="E132" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>162</v>
+        <v>21</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>296</v>
+        <v>165</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -5037,50 +5043,50 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F135" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>21</v>
@@ -5088,19 +5094,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>21</v>
@@ -5108,42 +5114,42 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -5157,10 +5163,10 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>5</v>
@@ -5168,22 +5174,22 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="E141" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>314</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -5197,93 +5203,93 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F143" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>5</v>
+        <v>317</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>162</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>21</v>
+        <v>165</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -5297,10 +5303,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>21</v>
@@ -5308,19 +5314,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="E148" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>21</v>
@@ -5328,19 +5334,19 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>21</v>
@@ -5348,39 +5354,39 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -5388,82 +5394,82 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>21</v>
+        <v>98</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>343</v>
+        <v>21</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C155" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>342</v>
-      </c>
       <c r="E155" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>296</v>
+        <v>115</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -5477,13 +5483,13 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>21</v>
+        <v>299</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -5497,10 +5503,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>21</v>
@@ -5517,13 +5523,13 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -5537,13 +5543,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>162</v>
+        <v>15</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -5557,13 +5563,13 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -5577,13 +5583,13 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -5597,13 +5603,13 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -5617,33 +5623,33 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B164" s="1" t="s">
+      <c r="C164" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="C164" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="E164" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -5657,13 +5663,13 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>98</v>
+        <v>165</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -5677,13 +5683,13 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -5697,10 +5703,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5717,10 +5723,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5737,10 +5743,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5757,10 +5763,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5777,10 +5783,10 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5788,22 +5794,22 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B172" s="1" t="s">
+      <c r="C172" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D172" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="C172" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>379</v>
-      </c>
       <c r="E172" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5817,13 +5823,13 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5837,10 +5843,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5857,10 +5863,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5877,10 +5883,10 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5897,13 +5903,13 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5917,30 +5923,30 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B179" s="1" t="s">
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C179" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="E179" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5957,10 +5963,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5977,10 +5983,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5997,10 +6003,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -6017,10 +6023,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -6037,10 +6043,10 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -6057,13 +6063,13 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -6077,33 +6083,33 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="B187" s="1" t="s">
+      <c r="C187" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D187" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="C187" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>411</v>
-      </c>
       <c r="E187" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>251</v>
+        <v>21</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -6117,13 +6123,13 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>21</v>
+        <v>254</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6137,10 +6143,10 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>21</v>
@@ -6157,10 +6163,10 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>21</v>
@@ -6177,13 +6183,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>162</v>
+        <v>21</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -6197,13 +6203,13 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -6217,13 +6223,13 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -6237,30 +6243,30 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>21</v>
+        <v>165</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B195" s="1" t="s">
+      <c r="C195" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D195" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C195" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>428</v>
-      </c>
       <c r="E195" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>21</v>
@@ -6277,10 +6283,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>21</v>
@@ -6297,10 +6303,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>21</v>
@@ -6317,33 +6323,33 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="B199" s="1" t="s">
+      <c r="C199" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D199" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="C199" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D199" s="1" t="s">
-        <v>437</v>
-      </c>
       <c r="E199" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>21</v>
+        <v>98</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -6357,10 +6363,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>21</v>
@@ -6377,10 +6383,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>21</v>
@@ -6397,13 +6403,13 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -6417,13 +6423,13 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -6437,13 +6443,13 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -6457,13 +6463,13 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>343</v>
+        <v>98</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -6477,13 +6483,13 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>314</v>
+        <v>115</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -6497,30 +6503,30 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>456</v>
+        <v>439</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>21</v>
+        <v>317</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="B208" s="1" t="s">
+      <c r="C208" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="C208" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>456</v>
-      </c>
       <c r="E208" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>21</v>
@@ -6537,10 +6543,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>21</v>
@@ -6557,13 +6563,13 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -6577,13 +6583,13 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>296</v>
+        <v>81</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -6597,13 +6603,13 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>5</v>
+        <v>299</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -6617,13 +6623,13 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>162</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -6637,33 +6643,33 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>471</v>
+        <v>165</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="B215" s="1" t="s">
+      <c r="C215" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F215" s="1" t="s">
         <v>473</v>
-      </c>
-      <c r="C215" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D215" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="E215" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F215" s="1" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -6677,13 +6683,13 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>137</v>
+        <v>74</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>471</v>
+        <v>317</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -6697,30 +6703,30 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>478</v>
+        <v>458</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>4</v>
+        <v>140</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>5</v>
+        <v>473</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="B218" s="1" t="s">
+      <c r="C218" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D218" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="C218" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D218" s="1" t="s">
-        <v>478</v>
-      </c>
       <c r="E218" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>5</v>
@@ -6737,13 +6743,13 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>314</v>
+        <v>5</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -6757,13 +6763,13 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -6777,13 +6783,13 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -6797,13 +6803,13 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>343</v>
+        <v>317</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -6817,13 +6823,13 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -6837,13 +6843,13 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>296</v>
+        <v>81</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -6857,13 +6863,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -6877,13 +6883,13 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>137</v>
+        <v>74</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -6897,13 +6903,13 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>343</v>
+        <v>299</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -6917,13 +6923,13 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>314</v>
+        <v>115</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -6937,13 +6943,13 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -6957,13 +6963,13 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>81</v>
+        <v>317</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -6977,13 +6983,13 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -6997,13 +7003,13 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>314</v>
+        <v>98</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -7017,13 +7023,13 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>98</v>
+        <v>317</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -7037,33 +7043,33 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>513</v>
+        <v>480</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>4</v>
+        <v>231</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B235" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="B235" s="1" t="s">
+      <c r="C235" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D235" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="C235" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D235" s="1" t="s">
-        <v>513</v>
-      </c>
       <c r="E235" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>296</v>
+        <v>81</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -7077,13 +7083,13 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -7097,13 +7103,13 @@
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -7117,13 +7123,13 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -7137,13 +7143,13 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -7157,13 +7163,13 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>81</v>
+        <v>299</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -7177,10 +7183,10 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F241" s="1" t="s">
         <v>81</v>
@@ -7197,10 +7203,10 @@
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="F242" s="1" t="s">
         <v>81</v>
@@ -7217,13 +7223,13 @@
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>137</v>
+        <v>74</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -7237,10 +7243,10 @@
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="F244" s="1" t="s">
         <v>5</v>
@@ -7257,10 +7263,10 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>5</v>
@@ -7277,13 +7283,13 @@
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>296</v>
+        <v>5</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -7297,13 +7303,13 @@
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -7317,13 +7323,13 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -7337,13 +7343,13 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>81</v>
+        <v>299</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -7357,10 +7363,10 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F250" s="1" t="s">
         <v>81</v>
@@ -7377,33 +7383,33 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>548</v>
+        <v>515</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>4</v>
+        <v>174</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>343</v>
+        <v>81</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B252" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="B252" s="1" t="s">
+      <c r="C252" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D252" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="C252" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D252" s="1" t="s">
-        <v>548</v>
-      </c>
       <c r="E252" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>314</v>
+        <v>115</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7417,13 +7423,13 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -7437,13 +7443,13 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -7457,13 +7463,13 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>5</v>
+        <v>317</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -7477,13 +7483,13 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -7497,10 +7503,10 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>98</v>
@@ -7517,10 +7523,10 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>98</v>
@@ -7537,13 +7543,13 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>251</v>
+        <v>98</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -7557,13 +7563,13 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>137</v>
+        <v>74</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -7577,13 +7583,13 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>314</v>
+        <v>254</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -7597,13 +7603,13 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -7617,33 +7623,33 @@
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>573</v>
+        <v>550</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>4</v>
+        <v>160</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="B264" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="B264" s="1" t="s">
+      <c r="C264" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D264" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="C264" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D264" s="1" t="s">
-        <v>573</v>
-      </c>
       <c r="E264" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -7657,13 +7663,13 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -7677,13 +7683,13 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -7697,13 +7703,13 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -7717,13 +7723,13 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -7737,13 +7743,13 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -7757,13 +7763,13 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -7777,13 +7783,13 @@
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>5</v>
+        <v>317</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -7797,10 +7803,10 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>137</v>
+        <v>74</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>5</v>
@@ -7817,10 +7823,10 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>5</v>
@@ -7837,13 +7843,13 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -7857,10 +7863,10 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>81</v>
@@ -7877,33 +7883,33 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>600</v>
+        <v>575</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>4</v>
+        <v>174</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B277" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="B277" s="1" t="s">
+      <c r="C277" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D277" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="C277" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D277" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="E277" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>314</v>
+        <v>5</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -7917,13 +7923,13 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -7937,33 +7943,33 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>607</v>
+        <v>317</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="B280" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="B280" s="1" t="s">
+      <c r="C280" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D280" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E280" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F280" s="1" t="s">
         <v>609</v>
-      </c>
-      <c r="C280" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D280" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="E280" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F280" s="1" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -7977,13 +7983,13 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -7997,13 +8003,13 @@
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -8017,13 +8023,13 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>5</v>
+        <v>317</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -8037,13 +8043,13 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>314</v>
+        <v>5</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -8057,13 +8063,13 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>137</v>
+        <v>74</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -8077,13 +8083,13 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>5</v>
+        <v>317</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -8097,10 +8103,10 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>5</v>
@@ -8117,13 +8123,13 @@
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>314</v>
+        <v>5</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -8137,33 +8143,33 @@
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>628</v>
+        <v>602</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>4</v>
+        <v>174</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>343</v>
+        <v>317</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B290" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="B290" s="1" t="s">
+      <c r="C290" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D290" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="C290" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D290" s="1" t="s">
-        <v>628</v>
-      </c>
       <c r="E290" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>314</v>
+        <v>115</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -8177,13 +8183,13 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -8197,13 +8203,13 @@
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8217,13 +8223,13 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8237,13 +8243,13 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8257,13 +8263,13 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>5</v>
+        <v>317</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8277,10 +8283,10 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F296" s="1" t="s">
         <v>5</v>
@@ -8297,10 +8303,10 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="F297" s="1" t="s">
         <v>5</v>
@@ -8317,10 +8323,10 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>137</v>
+        <v>74</v>
       </c>
       <c r="F298" s="1" t="s">
         <v>5</v>
@@ -8337,13 +8343,13 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8357,12 +8363,32 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F300" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A301" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="B301" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="C301" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D301" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="E301" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F301" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/DND05S.xlsx
+++ b/DND05S.xlsx
@@ -358,697 +358,697 @@
     <t>SO KLN MAISON DE 700</t>
   </si>
   <si>
+    <t>20113567</t>
+  </si>
+  <si>
+    <t>GENTLE GEN MR.BRZ700</t>
+  </si>
+  <si>
+    <t>20115959</t>
+  </si>
+  <si>
+    <t>GENTLE GEN FR.PE 700</t>
+  </si>
+  <si>
+    <t>20115958</t>
+  </si>
+  <si>
+    <t>GENTLE GEN PRS.G 700</t>
+  </si>
+  <si>
+    <t>20073805</t>
+  </si>
+  <si>
+    <t>SOKLN RED/MG&amp;B1.44KG</t>
+  </si>
+  <si>
+    <t>20041483</t>
+  </si>
+  <si>
+    <t>SO/KLN SOFT P/RS1.44</t>
+  </si>
+  <si>
+    <t>20140806</t>
+  </si>
+  <si>
+    <t>SO KLN EDP D.LS 144</t>
+  </si>
+  <si>
+    <t>20140804</t>
+  </si>
+  <si>
+    <t>SO KLN EDP BLNC 1.44</t>
+  </si>
+  <si>
+    <t>20091352</t>
+  </si>
+  <si>
+    <t>DAIA+SOFT VIOLET 1.5</t>
+  </si>
+  <si>
+    <t>20052321</t>
+  </si>
+  <si>
+    <t>DAIA+SOFT PINK 1.5KG</t>
+  </si>
+  <si>
+    <t>20030446</t>
+  </si>
+  <si>
+    <t>DAIA PUTIH 1.5KG</t>
+  </si>
+  <si>
+    <t>20121050</t>
+  </si>
+  <si>
+    <t>DAIA HIJAB C&amp;F 1.5G</t>
+  </si>
+  <si>
+    <t>20142276</t>
+  </si>
+  <si>
+    <t>DAIA LILY JSMN 1.5KG</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>10014547</t>
+  </si>
+  <si>
+    <t>DAIA DTRG.BBK BGA1.5</t>
+  </si>
+  <si>
+    <t>20012007</t>
+  </si>
+  <si>
+    <t>DAIA DET.BBK PTH 800</t>
+  </si>
+  <si>
+    <t>10005245</t>
+  </si>
+  <si>
+    <t>DAIA BBK FLORAL 800G</t>
+  </si>
+  <si>
+    <t>20053796</t>
+  </si>
+  <si>
+    <t>SOKLN SOFTG PRPL 720</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20073499</t>
+  </si>
+  <si>
+    <t>SO KLN MGNL&amp;BRY 720G</t>
+  </si>
+  <si>
+    <t>20012188</t>
+  </si>
+  <si>
+    <t>SOKLN SOFTR ROSY 720</t>
+  </si>
+  <si>
+    <t>20061748</t>
+  </si>
+  <si>
+    <t>DAIA DET+SFT VLT 800</t>
+  </si>
+  <si>
+    <t>20036047</t>
+  </si>
+  <si>
+    <t>DAIA DET+SOFT  800G</t>
+  </si>
+  <si>
+    <t>20113809</t>
+  </si>
+  <si>
+    <t>OXYKLIN DTRG LIQ 700</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20129837</t>
+  </si>
+  <si>
+    <t>LARIST SPR.GRD 750ML</t>
+  </si>
+  <si>
+    <t>20097739</t>
+  </si>
+  <si>
+    <t>IDM DET.CAIR PCH 700</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20067586</t>
+  </si>
+  <si>
+    <t>SOKLIN LIQ.BM TOP700</t>
+  </si>
+  <si>
+    <t>20054610</t>
+  </si>
+  <si>
+    <t>RINSO LIQ FRONT 1.45</t>
+  </si>
+  <si>
+    <t>10030924</t>
+  </si>
+  <si>
+    <t>SOKLIN MTC F/LD 900G</t>
+  </si>
+  <si>
+    <t>20081448</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT H.SM 600</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20081449</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT P.DW 600</t>
+  </si>
+  <si>
+    <t>20104951</t>
+  </si>
+  <si>
+    <t>ROYALE HJB BLCK.V600</t>
+  </si>
+  <si>
+    <t>20091457</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT BS 600</t>
+  </si>
+  <si>
+    <t>20113101</t>
+  </si>
+  <si>
+    <t>ROYALE SWT FLORL 600</t>
+  </si>
+  <si>
+    <t>20128706</t>
+  </si>
+  <si>
+    <t>ROYALE LNVDR VNL 600</t>
+  </si>
+  <si>
+    <t>20113093</t>
+  </si>
+  <si>
+    <t>ROYALE SUNNY DAY 600</t>
+  </si>
+  <si>
+    <t>20142010</t>
+  </si>
+  <si>
+    <t>ROYALE MTCHA BLS 600</t>
+  </si>
+  <si>
+    <t>20128919</t>
+  </si>
+  <si>
+    <t>MOLTO SFTNR PURE 550</t>
+  </si>
+  <si>
+    <t>20094735</t>
+  </si>
+  <si>
+    <t>DOWNY SUNRISE 950</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>PT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20094733</t>
+  </si>
+  <si>
+    <t>DOWNY MYSTIQUE 900</t>
+  </si>
+  <si>
+    <t>20140221</t>
+  </si>
+  <si>
+    <t>DOWNY PASSION 875ML</t>
+  </si>
+  <si>
+    <t>20141324</t>
+  </si>
+  <si>
+    <t>DOWNY SUNSHINE 500ML</t>
+  </si>
+  <si>
+    <t>20141323</t>
+  </si>
+  <si>
+    <t>DOWNY MIDNIGHT 500ML</t>
+  </si>
+  <si>
+    <t>20080360</t>
+  </si>
+  <si>
+    <t>DOWNY MYSTIQUE 550ML</t>
+  </si>
+  <si>
+    <t>20080361</t>
+  </si>
+  <si>
+    <t>DOWNY PASSION 550ML</t>
+  </si>
+  <si>
+    <t>20074226</t>
+  </si>
+  <si>
+    <t>DOWNY SUN.FRSH 550</t>
+  </si>
+  <si>
+    <t>20139145</t>
+  </si>
+  <si>
+    <t>DOWNY MLKY TOUCH 500</t>
+  </si>
+  <si>
+    <t>20140003</t>
+  </si>
+  <si>
+    <t>RNSO PWD ROSE.F 1.44</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20093521</t>
+  </si>
+  <si>
+    <t>RINSO+MOLTO ESC1440G</t>
+  </si>
+  <si>
+    <t>20139609</t>
+  </si>
+  <si>
+    <t>RNSO JPN PEAC 1440G</t>
+  </si>
+  <si>
+    <t>20140002</t>
+  </si>
+  <si>
+    <t>RINSO PWD PURE 1440G</t>
+  </si>
+  <si>
+    <t>20064413</t>
+  </si>
+  <si>
+    <t>ATCK JAZ1 S/CNTA 1.5</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20064414</t>
+  </si>
+  <si>
+    <t>ATTACK JAZ1 P/SGR1.5</t>
+  </si>
+  <si>
+    <t>20130527</t>
+  </si>
+  <si>
+    <t>ATTACK DET+SF RB 1.4</t>
+  </si>
+  <si>
+    <t>20138108</t>
+  </si>
+  <si>
+    <t>JAZ 1 PRPL BLS 1.4KG</t>
+  </si>
+  <si>
+    <t>20071827</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD ROSE 700</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20085113</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD PRFM 700</t>
+  </si>
+  <si>
+    <t>20105968</t>
+  </si>
+  <si>
+    <t>RNSO PWD JPN PC 700G</t>
+  </si>
+  <si>
+    <t>20074992</t>
+  </si>
+  <si>
+    <t>BUKRIM OXY/K VIOL700</t>
+  </si>
+  <si>
+    <t>20119238</t>
+  </si>
+  <si>
+    <t>TOTAL DET.PERFUME750</t>
+  </si>
+  <si>
+    <t>20131516</t>
+  </si>
+  <si>
+    <t>LARIST DET.FRS BT450</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20113183</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD ROSE 380</t>
+  </si>
+  <si>
+    <t>20121372</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD PRFM 380</t>
+  </si>
+  <si>
+    <t>20128719</t>
+  </si>
+  <si>
+    <t>SOKLIN LVD&amp;LILY 425G</t>
+  </si>
+  <si>
+    <t>20042466</t>
+  </si>
+  <si>
+    <t>DAIA DET+SOFT 470G</t>
+  </si>
+  <si>
+    <t>20139595</t>
+  </si>
+  <si>
+    <t>MOLTO TRKA BDD 3X300</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20133398</t>
+  </si>
+  <si>
+    <t>TRKA PURE 300ML</t>
+  </si>
+  <si>
+    <t>10011440</t>
+  </si>
+  <si>
+    <t>RAPIKA LVDR SPLAS300</t>
+  </si>
+  <si>
+    <t>20084780</t>
+  </si>
+  <si>
+    <t>RAPIKA GOLD 250ML</t>
+  </si>
+  <si>
+    <t>20093193</t>
+  </si>
+  <si>
+    <t>RAPIKA PINK SKR 300</t>
+  </si>
+  <si>
+    <t>20138071</t>
+  </si>
+  <si>
+    <t>KISPRAY KASTURI 280</t>
+  </si>
+  <si>
+    <t>20074721</t>
+  </si>
+  <si>
+    <t>KISPRAY GLM.GOLD 280</t>
+  </si>
+  <si>
+    <t>20116685</t>
+  </si>
+  <si>
+    <t>KISPRAY ELG.SAPH 200</t>
+  </si>
+  <si>
+    <t>20032250</t>
+  </si>
+  <si>
+    <t>KISPRAY VIOLET PC280</t>
+  </si>
+  <si>
+    <t>20000980</t>
+  </si>
+  <si>
+    <t>KISPRAY VIOLET 318ML</t>
+  </si>
+  <si>
+    <t>20138470</t>
+  </si>
+  <si>
+    <t>SO KLN PWNG RED 1.7L</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>10005803</t>
+  </si>
+  <si>
+    <t>SOKLIN PWNGI RED 780</t>
+  </si>
+  <si>
+    <t>10007389</t>
+  </si>
+  <si>
+    <t>SOKLIN PWNGI PINK780</t>
+  </si>
+  <si>
+    <t>10008104</t>
+  </si>
+  <si>
+    <t>SO KLIN PWG BLUE 780</t>
+  </si>
+  <si>
+    <t>20108418</t>
+  </si>
+  <si>
+    <t>SOKLIN PWG HJB GR780</t>
+  </si>
+  <si>
+    <t>10005802</t>
+  </si>
+  <si>
+    <t>SOKLIN PEWANGI VL780</t>
+  </si>
+  <si>
+    <t>20141985</t>
+  </si>
+  <si>
+    <t>SO KLN TROP SUMR 780</t>
+  </si>
+  <si>
+    <t>20134526</t>
+  </si>
+  <si>
+    <t>SOKLIN PWG COT.FN780</t>
+  </si>
+  <si>
+    <t>20129370</t>
+  </si>
+  <si>
+    <t>MOLTO MORNING FRS550</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20129160</t>
+  </si>
+  <si>
+    <t>MOLTO LUXURY PRF 650</t>
+  </si>
+  <si>
+    <t>20087464</t>
+  </si>
+  <si>
+    <t>IDM PWNG PINK.PAS720</t>
+  </si>
+  <si>
+    <t>20137582</t>
+  </si>
+  <si>
+    <t>IDM PWNG ROM.AURA720</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20137581</t>
+  </si>
+  <si>
+    <t>IDM PWNG EXO.BLUE720</t>
+  </si>
+  <si>
+    <t>20020245</t>
+  </si>
+  <si>
+    <t>MOLTO PWNGI BLUE 765</t>
+  </si>
+  <si>
+    <t>20020226</t>
+  </si>
+  <si>
+    <t>MOLTO PWNGI PINK 765</t>
+  </si>
+  <si>
+    <t>20106821</t>
+  </si>
+  <si>
+    <t>MOLTO PURPLE 765ML</t>
+  </si>
+  <si>
+    <t>20142219</t>
+  </si>
+  <si>
+    <t>MLTO GNTL FRSH 765ML</t>
+  </si>
+  <si>
+    <t>20135847</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT SUMMR600</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20135846</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT SPRNG600</t>
+  </si>
+  <si>
+    <t>20014403</t>
+  </si>
+  <si>
+    <t>BAYCLIN REGLR 1000ML</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>20082581</t>
+  </si>
+  <si>
+    <t>VANISH CAIR WHT 425</t>
+  </si>
+  <si>
+    <t>20052662</t>
+  </si>
+  <si>
+    <t>VANISH CAIR PCH 425</t>
+  </si>
+  <si>
+    <t>20079788</t>
+  </si>
+  <si>
+    <t>PROCLIN PCH 400ML</t>
+  </si>
+  <si>
+    <t>20093919</t>
+  </si>
+  <si>
+    <t>IDM PURPOSE CLN 400</t>
+  </si>
+  <si>
+    <t>10014263</t>
+  </si>
+  <si>
+    <t>WIPOL KARBOL CMR 720</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>20001645</t>
+  </si>
+  <si>
+    <t>WIPOL KARBOL LMN 720</t>
+  </si>
+  <si>
+    <t>20090066</t>
+  </si>
+  <si>
+    <t>WIPOL SRH + JRK 720</t>
+  </si>
+  <si>
+    <t>20122478</t>
+  </si>
+  <si>
+    <t>WIPOL CITRUS FRS 390</t>
+  </si>
+  <si>
+    <t>20023111</t>
+  </si>
+  <si>
+    <t>SOS KARBOL CLS PN725</t>
+  </si>
+  <si>
+    <t>10013107</t>
+  </si>
+  <si>
+    <t>SUPERSOL PINE 720G</t>
+  </si>
+  <si>
+    <t>20104030</t>
+  </si>
+  <si>
+    <t>SUPER SOL SEREH720G</t>
+  </si>
+  <si>
+    <t>20132664</t>
+  </si>
+  <si>
+    <t>VIXAL KUAT SEGAR 600</t>
+  </si>
+  <si>
+    <t>10004612</t>
+  </si>
+  <si>
+    <t>SOS P.LNT ORANGE 700</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
     <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20113567</t>
-  </si>
-  <si>
-    <t>GENTLE GEN MR.BRZ700</t>
-  </si>
-  <si>
-    <t>20115959</t>
-  </si>
-  <si>
-    <t>GENTLE GEN FR.PE 700</t>
-  </si>
-  <si>
-    <t>20115958</t>
-  </si>
-  <si>
-    <t>GENTLE GEN PRS.G 700</t>
-  </si>
-  <si>
-    <t>20073805</t>
-  </si>
-  <si>
-    <t>SOKLN RED/MG&amp;B1.44KG</t>
-  </si>
-  <si>
-    <t>20041483</t>
-  </si>
-  <si>
-    <t>SO/KLN SOFT P/RS1.44</t>
-  </si>
-  <si>
-    <t>20140806</t>
-  </si>
-  <si>
-    <t>SO KLN EDP D.LS 144</t>
-  </si>
-  <si>
-    <t>20140804</t>
-  </si>
-  <si>
-    <t>SO KLN EDP BLNC 1.44</t>
-  </si>
-  <si>
-    <t>20091352</t>
-  </si>
-  <si>
-    <t>DAIA+SOFT VIOLET 1.5</t>
-  </si>
-  <si>
-    <t>20052321</t>
-  </si>
-  <si>
-    <t>DAIA+SOFT PINK 1.5KG</t>
-  </si>
-  <si>
-    <t>20030446</t>
-  </si>
-  <si>
-    <t>DAIA PUTIH 1.5KG</t>
-  </si>
-  <si>
-    <t>20121050</t>
-  </si>
-  <si>
-    <t>DAIA HIJAB C&amp;F 1.5G</t>
-  </si>
-  <si>
-    <t>20142276</t>
-  </si>
-  <si>
-    <t>DAIA LILY JSMN 1.5KG</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>10014547</t>
-  </si>
-  <si>
-    <t>DAIA DTRG.BBK BGA1.5</t>
-  </si>
-  <si>
-    <t>20012007</t>
-  </si>
-  <si>
-    <t>DAIA DET.BBK PTH 800</t>
-  </si>
-  <si>
-    <t>10005245</t>
-  </si>
-  <si>
-    <t>DAIA BBK FLORAL 800G</t>
-  </si>
-  <si>
-    <t>20053796</t>
-  </si>
-  <si>
-    <t>SOKLN SOFTG PRPL 720</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20073499</t>
-  </si>
-  <si>
-    <t>SO KLN MGNL&amp;BRY 720G</t>
-  </si>
-  <si>
-    <t>20012188</t>
-  </si>
-  <si>
-    <t>SOKLN SOFTR ROSY 720</t>
-  </si>
-  <si>
-    <t>20061748</t>
-  </si>
-  <si>
-    <t>DAIA DET+SFT VLT 800</t>
-  </si>
-  <si>
-    <t>20036047</t>
-  </si>
-  <si>
-    <t>DAIA DET+SOFT  800G</t>
-  </si>
-  <si>
-    <t>20113809</t>
-  </si>
-  <si>
-    <t>OXYKLIN DTRG LIQ 700</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20129837</t>
-  </si>
-  <si>
-    <t>LARIST SPR.GRD 750ML</t>
-  </si>
-  <si>
-    <t>20097739</t>
-  </si>
-  <si>
-    <t>IDM DET.CAIR PCH 700</t>
-  </si>
-  <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20067586</t>
-  </si>
-  <si>
-    <t>SOKLIN LIQ.BM TOP700</t>
-  </si>
-  <si>
-    <t>20054610</t>
-  </si>
-  <si>
-    <t>RINSO LIQ FRONT 1.45</t>
-  </si>
-  <si>
-    <t>10030924</t>
-  </si>
-  <si>
-    <t>SOKLIN MTC F/LD 900G</t>
-  </si>
-  <si>
-    <t>20081448</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT H.SM 600</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20081449</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT P.DW 600</t>
-  </si>
-  <si>
-    <t>20104951</t>
-  </si>
-  <si>
-    <t>ROYALE HJB BLCK.V600</t>
-  </si>
-  <si>
-    <t>20091457</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT BS 600</t>
-  </si>
-  <si>
-    <t>20113101</t>
-  </si>
-  <si>
-    <t>ROYALE SWT FLORL 600</t>
-  </si>
-  <si>
-    <t>20128706</t>
-  </si>
-  <si>
-    <t>ROYALE LNVDR VNL 600</t>
-  </si>
-  <si>
-    <t>20113093</t>
-  </si>
-  <si>
-    <t>ROYALE SUNNY DAY 600</t>
-  </si>
-  <si>
-    <t>20142010</t>
-  </si>
-  <si>
-    <t>ROYALE MTCHA BLS 600</t>
-  </si>
-  <si>
-    <t>20128919</t>
-  </si>
-  <si>
-    <t>MOLTO SFTNR PURE 550</t>
-  </si>
-  <si>
-    <t>20094735</t>
-  </si>
-  <si>
-    <t>DOWNY SUNRISE 950</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>PT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20094733</t>
-  </si>
-  <si>
-    <t>DOWNY MYSTIQUE 900</t>
-  </si>
-  <si>
-    <t>20140221</t>
-  </si>
-  <si>
-    <t>DOWNY PASSION 875ML</t>
-  </si>
-  <si>
-    <t>20141324</t>
-  </si>
-  <si>
-    <t>DOWNY SUNSHINE 500ML</t>
-  </si>
-  <si>
-    <t>20141323</t>
-  </si>
-  <si>
-    <t>DOWNY MIDNIGHT 500ML</t>
-  </si>
-  <si>
-    <t>20080360</t>
-  </si>
-  <si>
-    <t>DOWNY MYSTIQUE 550ML</t>
-  </si>
-  <si>
-    <t>20080361</t>
-  </si>
-  <si>
-    <t>DOWNY PASSION 550ML</t>
-  </si>
-  <si>
-    <t>20074226</t>
-  </si>
-  <si>
-    <t>DOWNY SUN.FRSH 550</t>
-  </si>
-  <si>
-    <t>20139145</t>
-  </si>
-  <si>
-    <t>DOWNY MLKY TOUCH 500</t>
-  </si>
-  <si>
-    <t>20140003</t>
-  </si>
-  <si>
-    <t>RNSO PWD ROSE.F 1.44</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20093521</t>
-  </si>
-  <si>
-    <t>RINSO+MOLTO ESC1440G</t>
-  </si>
-  <si>
-    <t>20139609</t>
-  </si>
-  <si>
-    <t>RNSO JPN PEAC 1440G</t>
-  </si>
-  <si>
-    <t>20140002</t>
-  </si>
-  <si>
-    <t>RINSO PWD PURE 1440G</t>
-  </si>
-  <si>
-    <t>20064413</t>
-  </si>
-  <si>
-    <t>ATCK JAZ1 S/CNTA 1.5</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20064414</t>
-  </si>
-  <si>
-    <t>ATTACK JAZ1 P/SGR1.5</t>
-  </si>
-  <si>
-    <t>20130527</t>
-  </si>
-  <si>
-    <t>ATTACK DET+SF RB 1.4</t>
-  </si>
-  <si>
-    <t>20138108</t>
-  </si>
-  <si>
-    <t>JAZ 1 PRPL BLS 1.4KG</t>
-  </si>
-  <si>
-    <t>20071827</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD ROSE 700</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20085113</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD PRFM 700</t>
-  </si>
-  <si>
-    <t>20105968</t>
-  </si>
-  <si>
-    <t>RNSO PWD JPN PC 700G</t>
-  </si>
-  <si>
-    <t>20074992</t>
-  </si>
-  <si>
-    <t>BUKRIM OXY/K VIOL700</t>
-  </si>
-  <si>
-    <t>20119238</t>
-  </si>
-  <si>
-    <t>TOTAL DET.PERFUME750</t>
-  </si>
-  <si>
-    <t>20131516</t>
-  </si>
-  <si>
-    <t>LARIST DET.FRS BT450</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20113183</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD ROSE 380</t>
-  </si>
-  <si>
-    <t>20121372</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD PRFM 380</t>
-  </si>
-  <si>
-    <t>20128719</t>
-  </si>
-  <si>
-    <t>SOKLIN LVD&amp;LILY 425G</t>
-  </si>
-  <si>
-    <t>20042466</t>
-  </si>
-  <si>
-    <t>DAIA DET+SOFT 470G</t>
-  </si>
-  <si>
-    <t>20139595</t>
-  </si>
-  <si>
-    <t>MOLTO TRKA BDD 3X300</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20133398</t>
-  </si>
-  <si>
-    <t>TRKA PURE 300ML</t>
-  </si>
-  <si>
-    <t>10011440</t>
-  </si>
-  <si>
-    <t>RAPIKA LVDR SPLAS300</t>
-  </si>
-  <si>
-    <t>20084780</t>
-  </si>
-  <si>
-    <t>RAPIKA GOLD 250ML</t>
-  </si>
-  <si>
-    <t>20093193</t>
-  </si>
-  <si>
-    <t>RAPIKA PINK SKR 300</t>
-  </si>
-  <si>
-    <t>20138071</t>
-  </si>
-  <si>
-    <t>KISPRAY KASTURI 280</t>
-  </si>
-  <si>
-    <t>20074721</t>
-  </si>
-  <si>
-    <t>KISPRAY GLM.GOLD 280</t>
-  </si>
-  <si>
-    <t>20116685</t>
-  </si>
-  <si>
-    <t>KISPRAY ELG.SAPH 200</t>
-  </si>
-  <si>
-    <t>20032250</t>
-  </si>
-  <si>
-    <t>KISPRAY VIOLET PC280</t>
-  </si>
-  <si>
-    <t>20000980</t>
-  </si>
-  <si>
-    <t>KISPRAY VIOLET 318ML</t>
-  </si>
-  <si>
-    <t>20138470</t>
-  </si>
-  <si>
-    <t>SO KLN PWNG RED 1.7L</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>10005803</t>
-  </si>
-  <si>
-    <t>SOKLIN PWNGI RED 780</t>
-  </si>
-  <si>
-    <t>10007389</t>
-  </si>
-  <si>
-    <t>SOKLIN PWNGI PINK780</t>
-  </si>
-  <si>
-    <t>10008104</t>
-  </si>
-  <si>
-    <t>SO KLIN PWG BLUE 780</t>
-  </si>
-  <si>
-    <t>20108418</t>
-  </si>
-  <si>
-    <t>SOKLIN PWG HJB GR780</t>
-  </si>
-  <si>
-    <t>10005802</t>
-  </si>
-  <si>
-    <t>SOKLIN PEWANGI VL780</t>
-  </si>
-  <si>
-    <t>20141985</t>
-  </si>
-  <si>
-    <t>SO KLN TROP SUMR 780</t>
-  </si>
-  <si>
-    <t>20134526</t>
-  </si>
-  <si>
-    <t>SOKLIN PWG COT.FN780</t>
-  </si>
-  <si>
-    <t>20129370</t>
-  </si>
-  <si>
-    <t>MOLTO MORNING FRS550</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20129160</t>
-  </si>
-  <si>
-    <t>MOLTO LUXURY PRF 650</t>
-  </si>
-  <si>
-    <t>20087464</t>
-  </si>
-  <si>
-    <t>IDM PWNG PINK.PAS720</t>
-  </si>
-  <si>
-    <t>20137582</t>
-  </si>
-  <si>
-    <t>IDM PWNG ROM.AURA720</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20137581</t>
-  </si>
-  <si>
-    <t>IDM PWNG EXO.BLUE720</t>
-  </si>
-  <si>
-    <t>20020245</t>
-  </si>
-  <si>
-    <t>MOLTO PWNGI BLUE 765</t>
-  </si>
-  <si>
-    <t>20020226</t>
-  </si>
-  <si>
-    <t>MOLTO PWNGI PINK 765</t>
-  </si>
-  <si>
-    <t>20106821</t>
-  </si>
-  <si>
-    <t>MOLTO PURPLE 765ML</t>
-  </si>
-  <si>
-    <t>20142219</t>
-  </si>
-  <si>
-    <t>MLTO GNTL FRSH 765ML</t>
-  </si>
-  <si>
-    <t>20135847</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT SUMMR600</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>20135846</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT SPRNG600</t>
-  </si>
-  <si>
-    <t>20014403</t>
-  </si>
-  <si>
-    <t>BAYCLIN REGLR 1000ML</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>20082581</t>
-  </si>
-  <si>
-    <t>VANISH CAIR WHT 425</t>
-  </si>
-  <si>
-    <t>20052662</t>
-  </si>
-  <si>
-    <t>VANISH CAIR PCH 425</t>
-  </si>
-  <si>
-    <t>20079788</t>
-  </si>
-  <si>
-    <t>PROCLIN PCH 400ML</t>
-  </si>
-  <si>
-    <t>20093919</t>
-  </si>
-  <si>
-    <t>IDM PURPOSE CLN 400</t>
-  </si>
-  <si>
-    <t>10014263</t>
-  </si>
-  <si>
-    <t>WIPOL KARBOL CMR 720</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>20001645</t>
-  </si>
-  <si>
-    <t>WIPOL KARBOL LMN 720</t>
-  </si>
-  <si>
-    <t>20090066</t>
-  </si>
-  <si>
-    <t>WIPOL SRH + JRK 720</t>
-  </si>
-  <si>
-    <t>20122478</t>
-  </si>
-  <si>
-    <t>WIPOL CITRUS FRS 390</t>
-  </si>
-  <si>
-    <t>20023111</t>
-  </si>
-  <si>
-    <t>SOS KARBOL CLS PN725</t>
-  </si>
-  <si>
-    <t>10013107</t>
-  </si>
-  <si>
-    <t>SUPERSOL PINE 720G</t>
-  </si>
-  <si>
-    <t>20104030</t>
-  </si>
-  <si>
-    <t>SUPER SOL SEREH720G</t>
-  </si>
-  <si>
-    <t>20132664</t>
-  </si>
-  <si>
-    <t>VIXAL KUAT SEGAR 600</t>
-  </si>
-  <si>
-    <t>10004612</t>
-  </si>
-  <si>
-    <t>SOS P.LNT ORANGE 700</t>
-  </si>
-  <si>
-    <t>24</t>
   </si>
   <si>
     <t>10004610</t>
@@ -3369,15 +3369,15 @@
         <v>18</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>115</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -3394,10 +3394,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -3414,10 +3414,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -3474,10 +3474,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>127</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>129</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -3514,10 +3514,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -3534,10 +3534,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>133</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -3554,10 +3554,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -3574,10 +3574,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>4</v>
@@ -3614,16 +3614,16 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>142</v>
-      </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>8</v>
@@ -3634,16 +3634,16 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>11</v>
@@ -3654,16 +3654,16 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>14</v>
@@ -3674,16 +3674,16 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="C66" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>149</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>4</v>
@@ -3694,16 +3694,16 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>8</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>11</v>
@@ -3734,16 +3734,16 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>14</v>
@@ -3754,16 +3754,16 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>18</v>
@@ -3774,16 +3774,16 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="C71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>4</v>
@@ -3794,16 +3794,16 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>8</v>
@@ -3814,36 +3814,36 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>18</v>
@@ -3854,16 +3854,16 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>32</v>
@@ -3874,16 +3874,16 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>35</v>
@@ -3894,16 +3894,16 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="C77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>174</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>4</v>
@@ -3914,16 +3914,16 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>176</v>
-      </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>8</v>
@@ -3934,16 +3934,16 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>178</v>
-      </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>11</v>
@@ -3954,16 +3954,16 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>14</v>
@@ -3974,16 +3974,16 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>18</v>
@@ -3994,16 +3994,16 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>32</v>
@@ -4014,16 +4014,16 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>35</v>
@@ -4034,16 +4034,16 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>38</v>
@@ -4054,16 +4054,16 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>74</v>
@@ -4074,36 +4074,36 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="C86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>193</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>8</v>
@@ -4114,16 +4114,16 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>11</v>
@@ -4134,16 +4134,16 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>14</v>
@@ -4154,16 +4154,16 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>18</v>
@@ -4174,76 +4174,76 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>74</v>
@@ -4254,16 +4254,16 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="C95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>4</v>
@@ -4274,16 +4274,16 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>215</v>
-      </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>8</v>
@@ -4294,16 +4294,16 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>11</v>
@@ -4314,16 +4314,16 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>14</v>
@@ -4334,16 +4334,16 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="C99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>222</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>4</v>
@@ -4354,16 +4354,16 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>224</v>
-      </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>8</v>
@@ -4374,16 +4374,16 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>11</v>
@@ -4394,16 +4394,16 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>14</v>
@@ -4414,16 +4414,16 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>231</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>4</v>
@@ -4434,16 +4434,16 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>8</v>
@@ -4454,16 +4454,16 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>11</v>
@@ -4474,16 +4474,16 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>237</v>
-      </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>14</v>
@@ -4494,16 +4494,16 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>18</v>
@@ -4514,16 +4514,16 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>242</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>4</v>
@@ -4534,16 +4534,16 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>8</v>
@@ -4554,16 +4554,16 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>11</v>
@@ -4574,16 +4574,16 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>14</v>
@@ -4594,16 +4594,16 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>18</v>
@@ -4614,36 +4614,36 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="C113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>253</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>8</v>
@@ -4654,16 +4654,16 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>11</v>
@@ -4674,16 +4674,16 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>14</v>
@@ -4694,16 +4694,16 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>262</v>
-      </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>18</v>
@@ -4714,16 +4714,16 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>32</v>
@@ -4734,16 +4734,16 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>266</v>
-      </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>35</v>
@@ -4754,16 +4754,16 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>268</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>38</v>
@@ -4774,16 +4774,16 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>74</v>
@@ -4794,19 +4794,19 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>272</v>
-      </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>98</v>
@@ -4814,16 +4814,16 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="C123" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>275</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>4</v>
@@ -4834,16 +4834,16 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>8</v>
@@ -4854,16 +4854,16 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>11</v>
@@ -4874,16 +4874,16 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>14</v>
@@ -4894,16 +4894,16 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>18</v>
@@ -4914,16 +4914,16 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>285</v>
-      </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>32</v>
@@ -4934,16 +4934,16 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>35</v>
@@ -4954,16 +4954,16 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>38</v>
@@ -4974,16 +4974,16 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>292</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>4</v>
@@ -4994,16 +4994,16 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>294</v>
-      </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>8</v>
@@ -5014,76 +5014,76 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>298</v>
-      </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>32</v>
@@ -5094,16 +5094,16 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>35</v>
@@ -5114,16 +5114,16 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>38</v>
@@ -5134,16 +5134,16 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>74</v>
@@ -5154,16 +5154,16 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>312</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>4</v>
@@ -5174,16 +5174,16 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>8</v>
@@ -5194,76 +5194,76 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>316</v>
-      </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>321</v>
-      </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>35</v>
@@ -5274,36 +5274,36 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>74</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B147" s="1" t="s">
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>328</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>4</v>
@@ -5314,16 +5314,16 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>8</v>
@@ -5334,16 +5334,16 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>11</v>
@@ -5354,16 +5354,16 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>334</v>
-      </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>14</v>
@@ -5374,16 +5374,16 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>18</v>
@@ -5394,16 +5394,16 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>32</v>
@@ -5414,16 +5414,16 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>340</v>
-      </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>35</v>
@@ -5434,16 +5434,16 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>342</v>
-      </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>38</v>
@@ -5454,22 +5454,22 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>345</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>115</v>
+        <v>345</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -5483,13 +5483,13 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -5503,7 +5503,7 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>11</v>
@@ -5523,7 +5523,7 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>14</v>
@@ -5543,7 +5543,7 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>18</v>
@@ -5563,13 +5563,13 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -5583,13 +5583,13 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -5603,13 +5603,13 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -5623,13 +5623,13 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>74</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -5649,7 +5649,7 @@
         <v>4</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -5669,7 +5669,7 @@
         <v>8</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -6129,7 +6129,7 @@
         <v>8</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6209,7 +6209,7 @@
         <v>32</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -6229,7 +6229,7 @@
         <v>35</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -6249,7 +6249,7 @@
         <v>38</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -6489,7 +6489,7 @@
         <v>38</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>115</v>
+        <v>345</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -6509,7 +6509,7 @@
         <v>74</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -6609,7 +6609,7 @@
         <v>18</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -6649,7 +6649,7 @@
         <v>35</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -6689,7 +6689,7 @@
         <v>74</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -6706,7 +6706,7 @@
         <v>458</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>473</v>
@@ -6769,7 +6769,7 @@
         <v>11</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -6789,7 +6789,7 @@
         <v>14</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -6809,7 +6809,7 @@
         <v>18</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -6829,7 +6829,7 @@
         <v>32</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>115</v>
+        <v>345</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -6869,7 +6869,7 @@
         <v>38</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -6889,7 +6889,7 @@
         <v>74</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -6906,10 +6906,10 @@
         <v>480</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -6926,10 +6926,10 @@
         <v>480</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>115</v>
+        <v>345</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -6946,10 +6946,10 @@
         <v>480</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -6966,10 +6966,10 @@
         <v>480</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -6986,7 +6986,7 @@
         <v>480</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>81</v>
@@ -7006,7 +7006,7 @@
         <v>480</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F232" s="1" t="s">
         <v>98</v>
@@ -7026,10 +7026,10 @@
         <v>480</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -7046,7 +7046,7 @@
         <v>480</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F234" s="1" t="s">
         <v>98</v>
@@ -7089,7 +7089,7 @@
         <v>8</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -7109,7 +7109,7 @@
         <v>11</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -7129,7 +7129,7 @@
         <v>14</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -7149,7 +7149,7 @@
         <v>18</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -7169,7 +7169,7 @@
         <v>32</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -7246,7 +7246,7 @@
         <v>515</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F244" s="1" t="s">
         <v>5</v>
@@ -7266,7 +7266,7 @@
         <v>515</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>5</v>
@@ -7286,7 +7286,7 @@
         <v>515</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>5</v>
@@ -7306,10 +7306,10 @@
         <v>515</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -7326,10 +7326,10 @@
         <v>515</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -7346,10 +7346,10 @@
         <v>515</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -7366,7 +7366,7 @@
         <v>515</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F250" s="1" t="s">
         <v>81</v>
@@ -7386,7 +7386,7 @@
         <v>515</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>81</v>
@@ -7409,7 +7409,7 @@
         <v>4</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>115</v>
+        <v>345</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7429,7 +7429,7 @@
         <v>8</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -7449,7 +7449,7 @@
         <v>11</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -7469,7 +7469,7 @@
         <v>14</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -7569,7 +7569,7 @@
         <v>74</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -7586,10 +7586,10 @@
         <v>550</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -7606,10 +7606,10 @@
         <v>550</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -7626,10 +7626,10 @@
         <v>550</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -7649,7 +7649,7 @@
         <v>4</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -7669,7 +7669,7 @@
         <v>8</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -7689,7 +7689,7 @@
         <v>11</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -7709,7 +7709,7 @@
         <v>14</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -7729,7 +7729,7 @@
         <v>18</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -7749,7 +7749,7 @@
         <v>32</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -7769,7 +7769,7 @@
         <v>35</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -7789,7 +7789,7 @@
         <v>38</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -7826,7 +7826,7 @@
         <v>575</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>5</v>
@@ -7846,7 +7846,7 @@
         <v>575</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>5</v>
@@ -7866,7 +7866,7 @@
         <v>575</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>81</v>
@@ -7886,7 +7886,7 @@
         <v>575</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>81</v>
@@ -7929,7 +7929,7 @@
         <v>8</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -7949,7 +7949,7 @@
         <v>11</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -7989,7 +7989,7 @@
         <v>18</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -8009,7 +8009,7 @@
         <v>32</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -8029,7 +8029,7 @@
         <v>35</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -8069,7 +8069,7 @@
         <v>74</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -8086,10 +8086,10 @@
         <v>602</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -8106,7 +8106,7 @@
         <v>602</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>5</v>
@@ -8126,7 +8126,7 @@
         <v>602</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F288" s="1" t="s">
         <v>5</v>
@@ -8146,10 +8146,10 @@
         <v>602</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -8169,7 +8169,7 @@
         <v>4</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>115</v>
+        <v>345</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -8189,7 +8189,7 @@
         <v>8</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -8209,7 +8209,7 @@
         <v>11</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8229,7 +8229,7 @@
         <v>14</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8249,7 +8249,7 @@
         <v>18</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8269,7 +8269,7 @@
         <v>32</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8346,7 +8346,7 @@
         <v>630</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F299" s="1" t="s">
         <v>5</v>
@@ -8366,7 +8366,7 @@
         <v>630</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>98</v>
@@ -8386,7 +8386,7 @@
         <v>630</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>5</v>

--- a/DND05S.xlsx
+++ b/DND05S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="651">
   <si>
     <t/>
   </si>
@@ -163,18 +163,6 @@
     <t>BOOM DET.CAIR RSE510</t>
   </si>
   <si>
-    <t>20134103</t>
-  </si>
-  <si>
-    <t>ATTACK GEL S.CNTA515</t>
-  </si>
-  <si>
-    <t>20138111</t>
-  </si>
-  <si>
-    <t>JAZ 1 ROSE BERY 515G</t>
-  </si>
-  <si>
     <t>20131373</t>
   </si>
   <si>
@@ -313,19 +301,19 @@
     <t>20133333</t>
   </si>
   <si>
-    <t>GENTLE GEN A/KRGT700</t>
+    <t>GENGEN DECA A 700 ML</t>
   </si>
   <si>
     <t>20141371</t>
   </si>
   <si>
-    <t>GNTLE GEN CMLLIA 700</t>
+    <t>GENGEN DECA CA 700 G</t>
   </si>
   <si>
     <t>20141372</t>
   </si>
   <si>
-    <t>GENTLE GEN LILAC 700</t>
+    <t>GENGEN DECA LI 700 G</t>
   </si>
   <si>
     <t>20135245</t>
@@ -361,19 +349,19 @@
     <t>20113567</t>
   </si>
   <si>
-    <t>GENTLE GEN MR.BRZ700</t>
+    <t>GENGEN DECA M 700 ML</t>
   </si>
   <si>
     <t>20115959</t>
   </si>
   <si>
-    <t>GENTLE GEN FR.PE 700</t>
+    <t>GENGEN DECASI 700 ML</t>
   </si>
   <si>
     <t>20115958</t>
   </si>
   <si>
-    <t>GENTLE GEN PRS.G 700</t>
+    <t>GENGEN DECA P 700 ML</t>
   </si>
   <si>
     <t>20073805</t>
@@ -403,31 +391,31 @@
     <t>20091352</t>
   </si>
   <si>
-    <t>DAIA+SOFT VIOLET 1.5</t>
+    <t>DAIA +SFT VLT 1.5 KG</t>
   </si>
   <si>
     <t>20052321</t>
   </si>
   <si>
-    <t>DAIA+SOFT PINK 1.5KG</t>
+    <t>DAIA SFT PINK 1.5 KG</t>
   </si>
   <si>
     <t>20030446</t>
   </si>
   <si>
-    <t>DAIA PUTIH 1.5KG</t>
+    <t>DAIA PUTIH 1.5 KG</t>
   </si>
   <si>
     <t>20121050</t>
   </si>
   <si>
-    <t>DAIA HIJAB C&amp;F 1.5G</t>
+    <t>DAIA HIJAB CF 1.5 KG</t>
   </si>
   <si>
     <t>20142276</t>
   </si>
   <si>
-    <t>DAIA LILY JSMN 1.5KG</t>
+    <t>DAIA LLY JSMN 1.5 KG</t>
   </si>
   <si>
     <t>10</t>
@@ -436,7 +424,7 @@
     <t>10014547</t>
   </si>
   <si>
-    <t>DAIA DTRG.BBK BGA1.5</t>
+    <t>DAIA B/FLWRL 1.5 KG</t>
   </si>
   <si>
     <t>20012007</t>
@@ -673,7 +661,7 @@
     <t>20064413</t>
   </si>
   <si>
-    <t>ATCK JAZ1 S/CNTA 1.5</t>
+    <t>KAOATT DP SC 1.5 KG</t>
   </si>
   <si>
     <t>16</t>
@@ -682,19 +670,19 @@
     <t>20064414</t>
   </si>
   <si>
-    <t>ATTACK JAZ1 P/SGR1.5</t>
+    <t>KAOATT DP PS 1.5 KG</t>
   </si>
   <si>
     <t>20130527</t>
   </si>
   <si>
-    <t>ATTACK DET+SF RB 1.4</t>
+    <t>KAOATT DP RB 1.4 KG</t>
   </si>
   <si>
     <t>20138108</t>
   </si>
   <si>
-    <t>JAZ 1 PRPL BLS 1.4KG</t>
+    <t>KAOATT DP PB 1.4 KG</t>
   </si>
   <si>
     <t>20071827</t>
@@ -1213,37 +1201,37 @@
     <t>20034450</t>
   </si>
   <si>
-    <t>MAMA/L JERUK NPS 690</t>
+    <t>M/LMN JRK NPS 690 G</t>
   </si>
   <si>
     <t>10004067</t>
   </si>
   <si>
-    <t>MAMA/L PCH LEMON 690</t>
+    <t>M/LMN PCH LMN 690 G</t>
   </si>
   <si>
     <t>20099424</t>
   </si>
   <si>
-    <t>MAMA LIME CHARCO 690</t>
+    <t>M/LIME CHARCO 690 G</t>
   </si>
   <si>
     <t>20052031</t>
   </si>
   <si>
-    <t>MAMA LIME GRN TEA690</t>
+    <t>M/LIME GRN TEA 690 G</t>
   </si>
   <si>
     <t>10004068</t>
   </si>
   <si>
-    <t>MAMA LIME POUCH 690</t>
+    <t>M/LIME POUCH 690 G</t>
   </si>
   <si>
     <t>20134303</t>
   </si>
   <si>
-    <t>MAMA/L REF YUZU 690</t>
+    <t>M/LMN RE YUZU 690 G</t>
   </si>
   <si>
     <t>20090067</t>
@@ -1294,7 +1282,7 @@
     <t>20141204</t>
   </si>
   <si>
-    <t>IDM P.PRG JR.NPS 950</t>
+    <t>IDM P.PRG JNP 950 ML</t>
   </si>
   <si>
     <t>20112491</t>
@@ -1354,7 +1342,7 @@
     <t>20142277</t>
   </si>
   <si>
-    <t>MAMA LM GRN BTL 690</t>
+    <t>M/LIME JRK BTL 690 G</t>
   </si>
   <si>
     <t>20135845</t>
@@ -1363,547 +1351,553 @@
     <t>EKNOMI LIQ JR&amp;LMN650</t>
   </si>
   <si>
+    <t>10029632</t>
+  </si>
+  <si>
+    <t>STELLA ALAT MATIC</t>
+  </si>
+  <si>
+    <t>20105576</t>
+  </si>
+  <si>
+    <t>STELLA A/F SAKURA350</t>
+  </si>
+  <si>
+    <t>20142869</t>
+  </si>
+  <si>
+    <t>STELA A/F RJ AMPT350</t>
+  </si>
+  <si>
+    <t>10004032</t>
+  </si>
+  <si>
+    <t>VIXAL KUAT HARUM 720</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>10004034</t>
+  </si>
+  <si>
+    <t>VIXAL KMR MD KUAT720</t>
+  </si>
+  <si>
+    <t>10003359</t>
+  </si>
+  <si>
+    <t>WIPOL CEMARA BTL 730</t>
+  </si>
+  <si>
+    <t>10000955</t>
+  </si>
+  <si>
+    <t>PORSTEX N.PARFUM 1L</t>
+  </si>
+  <si>
+    <t>10018962</t>
+  </si>
+  <si>
+    <t>YURI PORSTEX OB.B700</t>
+  </si>
+  <si>
+    <t>10005246</t>
+  </si>
+  <si>
+    <t>WING PRCLN CLN BR750</t>
+  </si>
+  <si>
+    <t>20040315</t>
+  </si>
+  <si>
+    <t>IDM PORSELEN BTL 800</t>
+  </si>
+  <si>
+    <t>20015040</t>
+  </si>
+  <si>
+    <t>HARPIC TRIPLE ACT450</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20095746</t>
+  </si>
+  <si>
+    <t>HRPC PNG.KRK CTR 405</t>
+  </si>
+  <si>
+    <t>20042956</t>
+  </si>
+  <si>
+    <t>HARPIC PWR PLS CT450</t>
+  </si>
+  <si>
+    <t>20134373</t>
+  </si>
+  <si>
+    <t>STELLA ALAT+REFILL25</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>20134374</t>
+  </si>
+  <si>
+    <t>STELLA ELCTRIC LAV25</t>
+  </si>
+  <si>
+    <t>10010232</t>
+  </si>
+  <si>
+    <t>KIWI LIQ.SHOE BLCK75</t>
+  </si>
+  <si>
+    <t>10007934</t>
+  </si>
+  <si>
+    <t>KIWI PASTE BLACK 45M</t>
+  </si>
+  <si>
+    <t>20012183</t>
+  </si>
+  <si>
+    <t>BAYGON BKR D.DRH 5'S</t>
+  </si>
+  <si>
+    <t>20014401</t>
+  </si>
+  <si>
+    <t>BYGON BKR JMB LVD 5S</t>
+  </si>
+  <si>
+    <t>20110145</t>
+  </si>
+  <si>
+    <t>VAPE NY.BK L.SMO5'S</t>
+  </si>
+  <si>
+    <t>20128711</t>
+  </si>
+  <si>
+    <t>AUTAN LOT.JRK&amp;LMN 50</t>
+  </si>
+  <si>
+    <t>20106983</t>
+  </si>
+  <si>
+    <t>AUTAN LOT.SAKURA 50</t>
+  </si>
+  <si>
+    <t>20054250</t>
+  </si>
+  <si>
+    <t>AUTAN REFRESH/S 100</t>
+  </si>
+  <si>
+    <t>20128713</t>
+  </si>
+  <si>
+    <t>SOFEL LOT.KRN/SMR 60</t>
+  </si>
+  <si>
+    <t>20078241</t>
+  </si>
+  <si>
+    <t>SOFFELL LOT.APEL 60G</t>
+  </si>
+  <si>
+    <t>10040202</t>
+  </si>
+  <si>
+    <t>SOFFELL A.NYMK K/J60</t>
+  </si>
+  <si>
+    <t>10037280</t>
+  </si>
+  <si>
+    <t>BAGUS KAPUR AJAIB</t>
+  </si>
+  <si>
+    <t>20109069</t>
+  </si>
+  <si>
+    <t>BAGUS LEM TIKUS PCS</t>
+  </si>
+  <si>
+    <t>10003479</t>
+  </si>
+  <si>
+    <t>GAJAH LEM TIKUS KT70</t>
+  </si>
+  <si>
+    <t>20139525</t>
+  </si>
+  <si>
+    <t>VAPE DORA LEM TIKUS</t>
+  </si>
+  <si>
+    <t>10037275</t>
+  </si>
+  <si>
+    <t>SWALLOW KMPR BTR 300</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>20027997</t>
+  </si>
+  <si>
+    <t>IDM KAMPER NAPTLN150</t>
+  </si>
+  <si>
+    <t>20131886</t>
+  </si>
+  <si>
+    <t>IDM KMPR DEO SKRA 5S</t>
+  </si>
+  <si>
+    <t>20131885</t>
+  </si>
+  <si>
+    <t>IDM KMPR DEO CFFE 5S</t>
+  </si>
+  <si>
+    <t>20079794</t>
+  </si>
+  <si>
+    <t>IDM KAMPER TOILET 5S</t>
+  </si>
+  <si>
+    <t>20139963</t>
+  </si>
+  <si>
+    <t>LARISST CTRONELLA 5S</t>
+  </si>
+  <si>
+    <t>10000279</t>
+  </si>
+  <si>
+    <t>SWALLOW TLT.BALL 5'S</t>
+  </si>
+  <si>
+    <t>10000482</t>
+  </si>
+  <si>
+    <t>SWALLOW K/DEO BAL105</t>
+  </si>
+  <si>
+    <t>20017478</t>
+  </si>
+  <si>
+    <t>SWALLOW ORG S-160</t>
+  </si>
+  <si>
+    <t>20122471</t>
+  </si>
+  <si>
+    <t>STELLA LAV.GRD 42+13</t>
+  </si>
+  <si>
+    <t>20136409</t>
+  </si>
+  <si>
+    <t>STELLA BALI JAS42+13</t>
+  </si>
+  <si>
+    <t>20109616</t>
+  </si>
+  <si>
+    <t>STELLA CAFF.LATTE 42</t>
+  </si>
+  <si>
+    <t>20075791</t>
+  </si>
+  <si>
+    <t>STELLA POCKET ORG 10</t>
+  </si>
+  <si>
+    <t>20075798</t>
+  </si>
+  <si>
+    <t>STLLA POCKET PRPL 10</t>
+  </si>
+  <si>
+    <t>20091307</t>
+  </si>
+  <si>
+    <t>STELLA POCKET BLU 10</t>
+  </si>
+  <si>
+    <t>20138481</t>
+  </si>
+  <si>
+    <t>STELLA EXO.FRUIT 10G</t>
+  </si>
+  <si>
+    <t>20138482</t>
+  </si>
+  <si>
+    <t>STELLA LUX.FLOWR 10G</t>
+  </si>
+  <si>
+    <t>20105573</t>
+  </si>
+  <si>
+    <t>STELLA AF REF JPS160</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>20037058</t>
+  </si>
+  <si>
+    <t>STELLA AF REF FLW160</t>
+  </si>
+  <si>
+    <t>20036827</t>
+  </si>
+  <si>
+    <t>STELLA AF REF GRN160</t>
+  </si>
+  <si>
+    <t>20044100</t>
+  </si>
+  <si>
+    <t>STELLA AF REF APL160</t>
+  </si>
+  <si>
+    <t>20135485</t>
+  </si>
+  <si>
+    <t>STELLA AF REF BAL160</t>
+  </si>
+  <si>
+    <t>20046210</t>
+  </si>
+  <si>
+    <t>GLADE OCN ESCPE 146G</t>
+  </si>
+  <si>
+    <t>10023003</t>
+  </si>
+  <si>
+    <t>GLADE PNY&amp;BRY BLS 70</t>
+  </si>
+  <si>
+    <t>10023002</t>
+  </si>
+  <si>
+    <t>GLADE FRESH ONE EF70</t>
+  </si>
+  <si>
+    <t>20096642</t>
+  </si>
+  <si>
+    <t>IDM FRSHNS LEMON 50</t>
+  </si>
+  <si>
+    <t>20096641</t>
+  </si>
+  <si>
+    <t>IDM FRSHNS ORANGE 50</t>
+  </si>
+  <si>
+    <t>10005428</t>
+  </si>
+  <si>
+    <t>STELLA IN ONE ORG 42</t>
+  </si>
+  <si>
+    <t>10005427</t>
+  </si>
+  <si>
+    <t>STELLA IN ONE LMN 42</t>
+  </si>
+  <si>
+    <t>20022902</t>
+  </si>
+  <si>
+    <t>HIT SPRAY ORG 180</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>20064216</t>
+  </si>
+  <si>
+    <t>HIT INS.SPRY LILY180</t>
+  </si>
+  <si>
+    <t>20139144</t>
+  </si>
+  <si>
+    <t>HIT XPRES PINK BL.35</t>
+  </si>
+  <si>
+    <t>20131161</t>
+  </si>
+  <si>
+    <t>HIT REF XPRES APLE35</t>
+  </si>
+  <si>
+    <t>20095744</t>
+  </si>
+  <si>
+    <t>HIT REF EXPRT FRS 35</t>
+  </si>
+  <si>
+    <t>20039183</t>
+  </si>
+  <si>
+    <t>HIT ALAT+REF EXP APL</t>
+  </si>
+  <si>
+    <t>10034732</t>
+  </si>
+  <si>
+    <t>HIT MAT ELECTRK 48'S</t>
+  </si>
+  <si>
+    <t>10027329</t>
+  </si>
+  <si>
+    <t>HIT ALT NYAMUK ELC 5</t>
+  </si>
+  <si>
+    <t>20084568</t>
+  </si>
+  <si>
+    <t>VAPE LIQ.SKR BLOSM45</t>
+  </si>
+  <si>
+    <t>20008748</t>
+  </si>
+  <si>
+    <t>VAPE LIQUID REF 45ML</t>
+  </si>
+  <si>
+    <t>20023870</t>
+  </si>
+  <si>
+    <t>VAPE LIQUID ELEKTRIK</t>
+  </si>
+  <si>
+    <t>20030445</t>
+  </si>
+  <si>
+    <t>VAPE SPRAY 1XSMP ORG</t>
+  </si>
+  <si>
+    <t>20073974</t>
+  </si>
+  <si>
+    <t>VAPE SPRAY 1XSMP SKR</t>
+  </si>
+  <si>
+    <t>20124418</t>
+  </si>
+  <si>
+    <t>VAPE SWEET PWDR 200</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>20076987</t>
+  </si>
+  <si>
+    <t>BAYGON FLOW.GRDN 200</t>
+  </si>
+  <si>
+    <t>10015526</t>
+  </si>
+  <si>
+    <t>BAYGON SPRY LVND 750</t>
+  </si>
+  <si>
+    <t>20124346</t>
+  </si>
+  <si>
+    <t>BAYGON JP&amp;PCH 600 ML</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>20098605</t>
+  </si>
+  <si>
+    <t>BAYGON CH BLO 600 ML</t>
+  </si>
+  <si>
+    <t>10003272</t>
+  </si>
+  <si>
+    <t>BAYGON CTR FH 675 ML</t>
+  </si>
+  <si>
+    <t>20071775</t>
+  </si>
+  <si>
+    <t>BAYGON FLO.GN 675 ML</t>
+  </si>
+  <si>
+    <t>20139154</t>
+  </si>
+  <si>
+    <t>HIT COTTON PWD 600ML</t>
+  </si>
+  <si>
+    <t>20054151</t>
+  </si>
+  <si>
+    <t>HIT INS.SPRY LILY600</t>
+  </si>
+  <si>
+    <t>10005198</t>
+  </si>
+  <si>
+    <t>HIT INS.SPRAY ORG600</t>
+  </si>
+  <si>
+    <t>20109613</t>
+  </si>
+  <si>
+    <t>HIT SPRY.P/BLOSM 600</t>
+  </si>
+  <si>
+    <t>20080868</t>
+  </si>
+  <si>
+    <t>HIT FRESH CITRUS 600</t>
+  </si>
+  <si>
+    <t>20131365</t>
+  </si>
+  <si>
+    <t>HIT SPRY JPN.SKR 600</t>
+  </si>
+  <si>
     <t>10034652</t>
   </si>
   <si>
     <t>GLADE OCEAN ESCP 350</t>
   </si>
   <si>
-    <t>20105576</t>
-  </si>
-  <si>
-    <t>STELLA A/F SAKURA350</t>
-  </si>
-  <si>
-    <t>10029632</t>
-  </si>
-  <si>
-    <t>STELLA ALAT MATIC</t>
-  </si>
-  <si>
-    <t>10004032</t>
-  </si>
-  <si>
-    <t>VIXAL KUAT HARUM 720</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>10004034</t>
-  </si>
-  <si>
-    <t>VIXAL KMR MD KUAT720</t>
-  </si>
-  <si>
-    <t>10003359</t>
-  </si>
-  <si>
-    <t>WIPOL CEMARA BTL 730</t>
-  </si>
-  <si>
-    <t>10000955</t>
-  </si>
-  <si>
-    <t>PORSTEX N.PARFUM 1L</t>
-  </si>
-  <si>
-    <t>10018962</t>
-  </si>
-  <si>
-    <t>YURI PORSTEX OB.B700</t>
-  </si>
-  <si>
-    <t>10005246</t>
-  </si>
-  <si>
-    <t>WING PRCLN CLN BR750</t>
-  </si>
-  <si>
-    <t>20040315</t>
-  </si>
-  <si>
-    <t>IDM PORSELEN BTL 800</t>
-  </si>
-  <si>
-    <t>20015040</t>
-  </si>
-  <si>
-    <t>HARPIC TRIPLE ACT450</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20095746</t>
-  </si>
-  <si>
-    <t>HRPC PNG.KRK CTR 405</t>
-  </si>
-  <si>
-    <t>20042956</t>
-  </si>
-  <si>
-    <t>HARPIC PWR PLS CT450</t>
-  </si>
-  <si>
-    <t>20134373</t>
-  </si>
-  <si>
-    <t>STELLA ALAT+REFILL25</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>20134374</t>
-  </si>
-  <si>
-    <t>STELLA ELCTRIC LAV25</t>
-  </si>
-  <si>
-    <t>10010232</t>
-  </si>
-  <si>
-    <t>KIWI LIQ.SHOE BLCK75</t>
-  </si>
-  <si>
-    <t>10007934</t>
-  </si>
-  <si>
-    <t>KIWI PASTE BLACK 45M</t>
-  </si>
-  <si>
-    <t>20012183</t>
-  </si>
-  <si>
-    <t>BAYGON BKR D.DRH 5'S</t>
-  </si>
-  <si>
-    <t>20014401</t>
-  </si>
-  <si>
-    <t>BYGON BKR JMB LVD 5S</t>
-  </si>
-  <si>
-    <t>20110145</t>
-  </si>
-  <si>
-    <t>VAPE NY.BK L.SMO5'S</t>
-  </si>
-  <si>
-    <t>20128711</t>
-  </si>
-  <si>
-    <t>AUTAN LOT.JRK&amp;LMN 50</t>
-  </si>
-  <si>
-    <t>20106983</t>
-  </si>
-  <si>
-    <t>AUTAN LOT.SAKURA 50</t>
-  </si>
-  <si>
-    <t>20054250</t>
-  </si>
-  <si>
-    <t>AUTAN REFRESH/S 100</t>
-  </si>
-  <si>
-    <t>20128713</t>
-  </si>
-  <si>
-    <t>SOFEL LOT.KRN/SMR 60</t>
-  </si>
-  <si>
-    <t>20078241</t>
-  </si>
-  <si>
-    <t>SOFFELL LOT.APEL 60G</t>
-  </si>
-  <si>
-    <t>10040202</t>
-  </si>
-  <si>
-    <t>SOFFELL A.NYMK K/J60</t>
-  </si>
-  <si>
-    <t>10037280</t>
-  </si>
-  <si>
-    <t>BAGUS KAPUR AJAIB</t>
-  </si>
-  <si>
-    <t>20109069</t>
-  </si>
-  <si>
-    <t>BAGUS LEM TIKUS PCS</t>
-  </si>
-  <si>
-    <t>10003479</t>
-  </si>
-  <si>
-    <t>GAJAH LEM TIKUS KT70</t>
-  </si>
-  <si>
-    <t>20139525</t>
-  </si>
-  <si>
-    <t>VAPE DORA LEM TIKUS</t>
-  </si>
-  <si>
-    <t>10037275</t>
-  </si>
-  <si>
-    <t>SWALLOW KMPR BTR 300</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>20027997</t>
-  </si>
-  <si>
-    <t>IDM KAMPER NAPTLN150</t>
-  </si>
-  <si>
-    <t>20131886</t>
-  </si>
-  <si>
-    <t>IDM KMPR DEO SKRA 5S</t>
-  </si>
-  <si>
-    <t>20131885</t>
-  </si>
-  <si>
-    <t>IDM KMPR DEO CFFE 5S</t>
-  </si>
-  <si>
-    <t>20079794</t>
-  </si>
-  <si>
-    <t>IDM KAMPER TOILET 5S</t>
-  </si>
-  <si>
-    <t>20139963</t>
-  </si>
-  <si>
-    <t>LARISST CTRONELLA 5S</t>
-  </si>
-  <si>
-    <t>10000279</t>
-  </si>
-  <si>
-    <t>SWALLOW TLT.BALL 5'S</t>
-  </si>
-  <si>
-    <t>10000482</t>
-  </si>
-  <si>
-    <t>SWALLOW K/DEO BAL105</t>
-  </si>
-  <si>
-    <t>20017478</t>
-  </si>
-  <si>
-    <t>SWALLOW ORG S-160</t>
-  </si>
-  <si>
-    <t>20122471</t>
-  </si>
-  <si>
-    <t>STELLA LAV.GRD 42+13</t>
-  </si>
-  <si>
-    <t>20136409</t>
-  </si>
-  <si>
-    <t>STELLA BALI JAS42+13</t>
-  </si>
-  <si>
-    <t>20109616</t>
-  </si>
-  <si>
-    <t>STELLA CAFF.LATTE 42</t>
-  </si>
-  <si>
-    <t>20075791</t>
-  </si>
-  <si>
-    <t>STELLA POCKET ORG 10</t>
-  </si>
-  <si>
-    <t>20075798</t>
-  </si>
-  <si>
-    <t>STLLA POCKET PRPL 10</t>
-  </si>
-  <si>
-    <t>20091307</t>
-  </si>
-  <si>
-    <t>STELLA POCKET BLU 10</t>
-  </si>
-  <si>
-    <t>20138481</t>
-  </si>
-  <si>
-    <t>STELLA EXO.FRUIT 10G</t>
-  </si>
-  <si>
-    <t>20138482</t>
-  </si>
-  <si>
-    <t>STELLA LUX.FLOWR 10G</t>
-  </si>
-  <si>
-    <t>20105573</t>
-  </si>
-  <si>
-    <t>STELLA AF REF JPS160</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>20037058</t>
-  </si>
-  <si>
-    <t>STELLA AF REF FLW160</t>
-  </si>
-  <si>
-    <t>20036827</t>
-  </si>
-  <si>
-    <t>STELLA AF REF GRN160</t>
-  </si>
-  <si>
-    <t>20044100</t>
-  </si>
-  <si>
-    <t>STELLA AF REF APL160</t>
-  </si>
-  <si>
-    <t>20135485</t>
-  </si>
-  <si>
-    <t>STELLA AF REF BAL160</t>
-  </si>
-  <si>
-    <t>20046210</t>
-  </si>
-  <si>
-    <t>GLADE OCN ESCPE 146G</t>
-  </si>
-  <si>
-    <t>10023003</t>
-  </si>
-  <si>
-    <t>GLADE PNY&amp;BRY BLS 70</t>
-  </si>
-  <si>
-    <t>10023002</t>
-  </si>
-  <si>
-    <t>GLADE FRESH ONE EF70</t>
-  </si>
-  <si>
-    <t>20096642</t>
-  </si>
-  <si>
-    <t>IDM FRSHNS LEMON 50</t>
-  </si>
-  <si>
-    <t>20096641</t>
-  </si>
-  <si>
-    <t>IDM FRSHNS ORANGE 50</t>
-  </si>
-  <si>
-    <t>10005428</t>
-  </si>
-  <si>
-    <t>STELLA IN ONE ORG 42</t>
-  </si>
-  <si>
-    <t>10005427</t>
-  </si>
-  <si>
-    <t>STELLA IN ONE LMN 42</t>
-  </si>
-  <si>
-    <t>20022902</t>
-  </si>
-  <si>
-    <t>HIT SPRAY ORG 180</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>20064216</t>
-  </si>
-  <si>
-    <t>HIT INS.SPRY LILY180</t>
-  </si>
-  <si>
-    <t>20139144</t>
-  </si>
-  <si>
-    <t>HIT XPRES PINK BL.35</t>
-  </si>
-  <si>
-    <t>20131161</t>
-  </si>
-  <si>
-    <t>HIT REF XPRES APLE35</t>
-  </si>
-  <si>
-    <t>20095744</t>
-  </si>
-  <si>
-    <t>HIT REF EXPRT FRS 35</t>
-  </si>
-  <si>
-    <t>20039183</t>
-  </si>
-  <si>
-    <t>HIT ALAT+REF EXP APL</t>
-  </si>
-  <si>
-    <t>10034732</t>
-  </si>
-  <si>
-    <t>HIT MAT ELECTRK 48'S</t>
-  </si>
-  <si>
-    <t>10027329</t>
-  </si>
-  <si>
-    <t>HIT ALT NYAMUK ELC 5</t>
-  </si>
-  <si>
-    <t>20084568</t>
-  </si>
-  <si>
-    <t>VAPE LIQ.SKR BLOSM45</t>
-  </si>
-  <si>
-    <t>20008748</t>
-  </si>
-  <si>
-    <t>VAPE LIQUID REF 45ML</t>
-  </si>
-  <si>
-    <t>20023870</t>
-  </si>
-  <si>
-    <t>VAPE LIQUID ELEKTRIK</t>
-  </si>
-  <si>
-    <t>20030445</t>
-  </si>
-  <si>
-    <t>VAPE SPRAY 1XSMP ORG</t>
-  </si>
-  <si>
-    <t>20073974</t>
-  </si>
-  <si>
-    <t>VAPE SPRAY 1XSMP SKR</t>
-  </si>
-  <si>
-    <t>20124418</t>
-  </si>
-  <si>
-    <t>VAPE SWEET PWDR 200</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>20076987</t>
-  </si>
-  <si>
-    <t>BAYGON FLOW.GRDN 200</t>
-  </si>
-  <si>
-    <t>10015526</t>
-  </si>
-  <si>
-    <t>BAYGON SPRY LVND 750</t>
-  </si>
-  <si>
-    <t>20124346</t>
-  </si>
-  <si>
-    <t>BAYGON JPNSE&amp;PCH 600</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20098605</t>
-  </si>
-  <si>
-    <t>BYGON SPRY CHR.BL600</t>
-  </si>
-  <si>
-    <t>10003272</t>
-  </si>
-  <si>
-    <t>BAYGON SPRY CITRS675</t>
-  </si>
-  <si>
-    <t>20071775</t>
-  </si>
-  <si>
-    <t>BAYGON FLO.GRDN 675</t>
-  </si>
-  <si>
-    <t>20139154</t>
-  </si>
-  <si>
-    <t>HIT COTTON PWD 600ML</t>
-  </si>
-  <si>
-    <t>20054151</t>
-  </si>
-  <si>
-    <t>HIT INS.SPRY LILY600</t>
-  </si>
-  <si>
-    <t>10005198</t>
-  </si>
-  <si>
-    <t>HIT INS.SPRAY ORG600</t>
-  </si>
-  <si>
-    <t>20109613</t>
-  </si>
-  <si>
-    <t>HIT SPRY.P/BLOSM 600</t>
-  </si>
-  <si>
-    <t>20080868</t>
-  </si>
-  <si>
-    <t>HIT FRESH CITRUS 600</t>
-  </si>
-  <si>
-    <t>20131365</t>
-  </si>
-  <si>
-    <t>HIT SPRY JPN.SKR 600</t>
+    <t>37</t>
   </si>
   <si>
     <t>20139446</t>
   </si>
   <si>
     <t>BAYGON CTRS FRSH 400</t>
-  </si>
-  <si>
-    <t>37</t>
   </si>
   <si>
     <t>20128132</t>
@@ -2362,7 +2356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F301"/>
+  <dimension ref="A1:F300"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2766,7 +2760,7 @@
         <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -2783,13 +2777,13 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2803,13 +2797,13 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2826,10 +2820,10 @@
         <v>14</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2846,7 +2840,7 @@
         <v>14</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>21</v>
@@ -2866,7 +2860,7 @@
         <v>14</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>21</v>
@@ -2886,10 +2880,10 @@
         <v>14</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2906,10 +2900,10 @@
         <v>14</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2926,7 +2920,7 @@
         <v>14</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -2946,7 +2940,7 @@
         <v>14</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -2954,42 +2948,42 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -3006,18 +3000,18 @@
         <v>18</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -3026,18 +3020,18 @@
         <v>18</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -3046,10 +3040,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>81</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -3066,10 +3060,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -3083,13 +3077,13 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -3103,10 +3097,10 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -3126,7 +3120,7 @@
         <v>32</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -3146,7 +3140,7 @@
         <v>32</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -3166,18 +3160,18 @@
         <v>32</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>5</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -3186,7 +3180,7 @@
         <v>32</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -3194,10 +3188,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -3206,10 +3200,10 @@
         <v>32</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -3226,7 +3220,7 @@
         <v>32</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -3243,10 +3237,10 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -3263,10 +3257,10 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -3286,10 +3280,10 @@
         <v>35</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>5</v>
+        <v>94</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -3306,7 +3300,7 @@
         <v>35</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -3326,10 +3320,10 @@
         <v>35</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -3346,7 +3340,7 @@
         <v>35</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -3366,7 +3360,7 @@
         <v>35</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -3386,7 +3380,7 @@
         <v>35</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -3403,10 +3397,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -3423,10 +3417,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -3446,10 +3440,10 @@
         <v>38</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>5</v>
+        <v>94</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -3466,10 +3460,10 @@
         <v>38</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>5</v>
+        <v>94</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3483,13 +3477,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3503,13 +3497,13 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -3523,10 +3517,10 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -3543,10 +3537,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -3563,10 +3557,10 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -3574,39 +3568,39 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="E61" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>5</v>
+        <v>94</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -3623,13 +3617,13 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -3643,10 +3637,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3654,19 +3648,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="E65" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -3674,19 +3668,19 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3703,10 +3697,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -3723,10 +3717,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -3743,10 +3737,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -3754,82 +3748,82 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="E70" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>5</v>
+        <v>160</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>164</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -3843,13 +3837,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>5</v>
+        <v>94</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3863,50 +3857,50 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="E76" s="1" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3923,10 +3917,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3943,10 +3937,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3963,10 +3957,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3983,10 +3977,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -4003,10 +3997,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -4023,13 +4017,13 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -4043,53 +4037,53 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>5</v>
+        <v>189</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="E85" s="1" t="s">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>193</v>
+        <v>15</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -4103,10 +4097,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>15</v>
@@ -4123,10 +4117,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>15</v>
@@ -4143,13 +4137,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>15</v>
+        <v>189</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -4163,13 +4157,13 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>15</v>
+        <v>189</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -4183,13 +4177,13 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -4203,13 +4197,13 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>193</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -4223,50 +4217,50 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>193</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="E94" s="1" t="s">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>21</v>
@@ -4283,10 +4277,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>21</v>
@@ -4303,53 +4297,53 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="E98" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -4363,13 +4357,13 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -4383,50 +4377,50 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="E102" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>21</v>
@@ -4443,13 +4437,13 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -4463,13 +4457,13 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -4483,53 +4477,53 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="E107" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -4543,13 +4537,13 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4563,13 +4557,13 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -4583,53 +4577,53 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>5</v>
+        <v>249</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="E112" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>253</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -4643,13 +4637,13 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -4663,10 +4657,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -4683,13 +4677,13 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>5</v>
+        <v>94</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -4703,13 +4697,13 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>5</v>
+        <v>94</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4723,13 +4717,13 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4743,13 +4737,13 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4763,13 +4757,13 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>38</v>
+        <v>135</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4783,50 +4777,50 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>252</v>
-      </c>
       <c r="E122" s="1" t="s">
-        <v>139</v>
+        <v>8</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -4843,10 +4837,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -4863,10 +4857,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -4883,10 +4877,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -4903,10 +4897,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4923,10 +4917,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4943,53 +4937,53 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>274</v>
-      </c>
       <c r="E130" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>21</v>
+        <v>160</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -5003,53 +4997,53 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>21</v>
+        <v>294</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F133" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>298</v>
+        <v>21</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -5063,13 +5057,13 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>298</v>
+        <v>21</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -5083,10 +5077,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>21</v>
@@ -5103,13 +5097,13 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -5123,93 +5117,93 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>291</v>
-      </c>
       <c r="E139" s="1" t="s">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>5</v>
+        <v>312</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F141" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F141" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -5223,13 +5217,13 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>316</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -5243,13 +5237,13 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>316</v>
+        <v>160</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -5263,50 +5257,50 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="E146" s="1" t="s">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>164</v>
+        <v>21</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>21</v>
@@ -5323,10 +5317,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>21</v>
@@ -5343,13 +5337,13 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -5363,13 +5357,13 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -5383,13 +5377,13 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>5</v>
+        <v>94</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -5403,13 +5397,13 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -5423,53 +5417,53 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>98</v>
+        <v>341</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>327</v>
-      </c>
       <c r="E154" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>21</v>
+        <v>294</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>345</v>
+        <v>21</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -5483,13 +5477,13 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>298</v>
+        <v>21</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -5503,13 +5497,13 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -5523,13 +5517,13 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>21</v>
+        <v>160</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -5543,13 +5537,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>15</v>
+        <v>160</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -5563,13 +5557,13 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -5583,13 +5577,13 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -5603,53 +5597,53 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>344</v>
+        <v>360</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="E163" s="1" t="s">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>164</v>
+        <v>94</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -5663,13 +5657,13 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>164</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -5683,13 +5677,13 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -5703,10 +5697,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5723,10 +5717,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5743,10 +5737,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5763,10 +5757,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>364</v>
+        <v>377</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5774,39 +5768,39 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>364</v>
-      </c>
       <c r="E171" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5823,13 +5817,13 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5843,10 +5837,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5863,10 +5857,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5883,13 +5877,13 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5903,10 +5897,10 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5914,39 +5908,39 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>381</v>
-      </c>
       <c r="E178" s="1" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5963,10 +5957,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5983,10 +5977,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -6003,10 +5997,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -6023,10 +6017,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -6043,13 +6037,13 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -6063,50 +6057,50 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>396</v>
-      </c>
       <c r="E186" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>81</v>
+        <v>249</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>21</v>
@@ -6123,13 +6117,13 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>253</v>
+        <v>21</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6143,10 +6137,10 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>21</v>
@@ -6163,13 +6157,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>21</v>
+        <v>160</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -6183,13 +6177,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>21</v>
+        <v>160</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -6203,13 +6197,13 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -6223,50 +6217,50 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>164</v>
+        <v>21</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D194" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B194" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D194" s="1" t="s">
-        <v>413</v>
-      </c>
       <c r="E194" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>164</v>
+        <v>21</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>21</v>
@@ -6283,10 +6277,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>21</v>
@@ -6303,30 +6297,30 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D198" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="B198" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="C198" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D198" s="1" t="s">
-        <v>430</v>
-      </c>
       <c r="E198" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>21</v>
@@ -6334,22 +6328,22 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -6363,10 +6357,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>21</v>
@@ -6383,13 +6377,13 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -6403,13 +6397,13 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -6423,13 +6417,13 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>5</v>
+        <v>312</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -6443,13 +6437,13 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>81</v>
+        <v>341</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -6463,13 +6457,13 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>98</v>
+        <v>341</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -6483,50 +6477,50 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>345</v>
+        <v>21</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D207" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>439</v>
-      </c>
       <c r="E207" s="1" t="s">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>316</v>
+        <v>21</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>21</v>
@@ -6543,13 +6537,13 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -6563,13 +6557,13 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>21</v>
+        <v>294</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -6583,13 +6577,13 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -6603,13 +6597,13 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>298</v>
+        <v>160</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -6623,53 +6617,53 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>5</v>
+        <v>469</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>164</v>
+        <v>312</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>38</v>
+        <v>135</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -6683,53 +6677,53 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>458</v>
+        <v>476</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>316</v>
+        <v>5</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D217" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="B217" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="C217" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D217" s="1" t="s">
-        <v>458</v>
-      </c>
       <c r="E217" s="1" t="s">
-        <v>139</v>
+        <v>8</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>473</v>
+        <v>5</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>5</v>
+        <v>312</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -6743,13 +6737,13 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>5</v>
+        <v>312</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -6763,13 +6757,13 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -6783,13 +6777,13 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>316</v>
+        <v>341</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -6803,13 +6797,13 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>316</v>
+        <v>77</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -6823,13 +6817,13 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>345</v>
+        <v>294</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -6843,13 +6837,13 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>81</v>
+        <v>312</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -6863,13 +6857,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>38</v>
+        <v>135</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -6883,13 +6877,13 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>74</v>
+        <v>144</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>316</v>
+        <v>341</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -6903,13 +6897,13 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -6923,13 +6917,13 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>345</v>
+        <v>312</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -6943,13 +6937,13 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>316</v>
+        <v>77</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -6963,13 +6957,13 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>173</v>
+        <v>208</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>316</v>
+        <v>94</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -6983,13 +6977,13 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>81</v>
+        <v>312</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -7003,13 +6997,13 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -7023,53 +7017,53 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>480</v>
+        <v>511</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>221</v>
+        <v>4</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>316</v>
+        <v>77</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D234" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="B234" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="C234" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D234" s="1" t="s">
-        <v>480</v>
-      </c>
       <c r="E234" s="1" t="s">
-        <v>230</v>
+        <v>8</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>98</v>
+        <v>294</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>81</v>
+        <v>294</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -7083,13 +7077,13 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -7103,13 +7097,13 @@
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -7123,13 +7117,13 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -7143,13 +7137,13 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>298</v>
+        <v>77</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -7163,13 +7157,13 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>298</v>
+        <v>77</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -7183,13 +7177,13 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -7203,13 +7197,13 @@
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>38</v>
+        <v>135</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -7223,13 +7217,13 @@
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>74</v>
+        <v>144</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -7243,10 +7237,10 @@
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="F244" s="1" t="s">
         <v>5</v>
@@ -7263,13 +7257,13 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>5</v>
+        <v>294</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -7283,13 +7277,13 @@
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>5</v>
+        <v>294</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -7303,13 +7297,13 @@
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -7323,13 +7317,13 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>298</v>
+        <v>77</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -7343,13 +7337,13 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>298</v>
+        <v>77</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -7363,53 +7357,53 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>515</v>
+        <v>546</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>173</v>
+        <v>4</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>81</v>
+        <v>341</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B251" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D251" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="B251" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="C251" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D251" s="1" t="s">
-        <v>515</v>
-      </c>
       <c r="E251" s="1" t="s">
-        <v>173</v>
+        <v>8</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>81</v>
+        <v>312</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>345</v>
+        <v>312</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7423,13 +7417,13 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -7443,13 +7437,13 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>316</v>
+        <v>5</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -7463,13 +7457,13 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>316</v>
+        <v>94</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -7483,13 +7477,13 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>5</v>
+        <v>94</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -7503,13 +7497,13 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -7523,13 +7517,13 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>98</v>
+        <v>249</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -7543,13 +7537,13 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>38</v>
+        <v>135</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>98</v>
+        <v>249</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -7563,13 +7557,13 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>74</v>
+        <v>144</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>253</v>
+        <v>312</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -7583,13 +7577,13 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>253</v>
+        <v>312</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -7603,53 +7597,53 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>550</v>
+        <v>571</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>148</v>
+        <v>4</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D263" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="B263" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="C263" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D263" s="1" t="s">
-        <v>550</v>
-      </c>
       <c r="E263" s="1" t="s">
-        <v>159</v>
+        <v>8</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -7663,13 +7657,13 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -7683,13 +7677,13 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -7703,13 +7697,13 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -7723,13 +7717,13 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -7743,13 +7737,13 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -7763,13 +7757,13 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>316</v>
+        <v>5</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -7783,13 +7777,13 @@
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>38</v>
+        <v>135</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>316</v>
+        <v>5</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -7803,10 +7797,10 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>74</v>
+        <v>144</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>5</v>
@@ -7823,13 +7817,13 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -7843,13 +7837,13 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -7863,53 +7857,53 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>575</v>
+        <v>598</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>159</v>
+        <v>4</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B276" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D276" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="B276" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="C276" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D276" s="1" t="s">
-        <v>575</v>
-      </c>
       <c r="E276" s="1" t="s">
-        <v>173</v>
+        <v>8</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>81</v>
+        <v>312</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>5</v>
+        <v>312</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -7923,53 +7917,53 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>316</v>
+        <v>605</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>609</v>
+        <v>312</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -7983,13 +7977,13 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -8003,13 +7997,13 @@
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>316</v>
+        <v>5</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -8023,13 +8017,13 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -8043,13 +8037,13 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>38</v>
+        <v>135</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>5</v>
+        <v>312</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -8063,13 +8057,13 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>74</v>
+        <v>144</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>316</v>
+        <v>5</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -8083,13 +8077,13 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>316</v>
+        <v>5</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -8103,13 +8097,13 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>5</v>
+        <v>312</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -8123,53 +8117,53 @@
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>602</v>
+        <v>626</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>159</v>
+        <v>4</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>5</v>
+        <v>94</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="B289" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="C289" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D289" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="B289" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="C289" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D289" s="1" t="s">
-        <v>602</v>
-      </c>
       <c r="E289" s="1" t="s">
-        <v>173</v>
+        <v>8</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>316</v>
+        <v>341</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>345</v>
+        <v>312</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -8183,13 +8177,13 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -8203,13 +8197,13 @@
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8223,13 +8217,13 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8243,13 +8237,13 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8263,13 +8257,13 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>316</v>
+        <v>5</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8283,10 +8277,10 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F296" s="1" t="s">
         <v>5</v>
@@ -8303,10 +8297,10 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>38</v>
+        <v>135</v>
       </c>
       <c r="F297" s="1" t="s">
         <v>5</v>
@@ -8323,10 +8317,10 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>74</v>
+        <v>144</v>
       </c>
       <c r="F298" s="1" t="s">
         <v>5</v>
@@ -8343,13 +8337,13 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>5</v>
+        <v>94</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8363,32 +8357,12 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A301" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="B301" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="C301" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D301" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="E301" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F301" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/DND05S.xlsx
+++ b/DND05S.xlsx
@@ -301,19 +301,19 @@
     <t>20133333</t>
   </si>
   <si>
-    <t>GENGEN DECA A 700 ML</t>
+    <t>GENTLE GEN A/KRGT700</t>
   </si>
   <si>
     <t>20141371</t>
   </si>
   <si>
-    <t>GENGEN DECA CA 700 G</t>
+    <t>GNTLE GEN CMLLIA 700</t>
   </si>
   <si>
     <t>20141372</t>
   </si>
   <si>
-    <t>GENGEN DECA LI 700 G</t>
+    <t>GENTLE GEN LILAC 700</t>
   </si>
   <si>
     <t>20135245</t>
@@ -349,19 +349,19 @@
     <t>20113567</t>
   </si>
   <si>
-    <t>GENGEN DECA M 700 ML</t>
+    <t>GENTLE GEN MR.BRZ700</t>
   </si>
   <si>
     <t>20115959</t>
   </si>
   <si>
-    <t>GENGEN DECASI 700 ML</t>
+    <t>GENTLE GEN FR.PE 700</t>
   </si>
   <si>
     <t>20115958</t>
   </si>
   <si>
-    <t>GENGEN DECA P 700 ML</t>
+    <t>GENTLE GEN PRS.G 700</t>
   </si>
   <si>
     <t>20073805</t>
@@ -391,31 +391,31 @@
     <t>20091352</t>
   </si>
   <si>
-    <t>DAIA +SFT VLT 1.5 KG</t>
+    <t>DAIA+SOFT VIOLET 1.5</t>
   </si>
   <si>
     <t>20052321</t>
   </si>
   <si>
-    <t>DAIA SFT PINK 1.5 KG</t>
+    <t>DAIA+SOFT PINK 1.5KG</t>
   </si>
   <si>
     <t>20030446</t>
   </si>
   <si>
-    <t>DAIA PUTIH 1.5 KG</t>
+    <t>DAIA PUTIH 1.5KG</t>
   </si>
   <si>
     <t>20121050</t>
   </si>
   <si>
-    <t>DAIA HIJAB CF 1.5 KG</t>
+    <t>DAIA HIJAB C&amp;F 1.5G</t>
   </si>
   <si>
     <t>20142276</t>
   </si>
   <si>
-    <t>DAIA LLY JSMN 1.5 KG</t>
+    <t>DAIA LILY JSMN 1.5KG</t>
   </si>
   <si>
     <t>10</t>
@@ -424,7 +424,7 @@
     <t>10014547</t>
   </si>
   <si>
-    <t>DAIA B/FLWRL 1.5 KG</t>
+    <t>DAIA DTRG.BBK BGA1.5</t>
   </si>
   <si>
     <t>20012007</t>
@@ -661,7 +661,7 @@
     <t>20064413</t>
   </si>
   <si>
-    <t>KAOATT DP SC 1.5 KG</t>
+    <t>ATCK JAZ1 S/CNTA 1.5</t>
   </si>
   <si>
     <t>16</t>
@@ -670,19 +670,19 @@
     <t>20064414</t>
   </si>
   <si>
-    <t>KAOATT DP PS 1.5 KG</t>
+    <t>ATTACK JAZ1 P/SGR1.5</t>
   </si>
   <si>
     <t>20130527</t>
   </si>
   <si>
-    <t>KAOATT DP RB 1.4 KG</t>
+    <t>ATTACK DET+SF RB 1.4</t>
   </si>
   <si>
     <t>20138108</t>
   </si>
   <si>
-    <t>KAOATT DP PB 1.4 KG</t>
+    <t>JAZ 1 PRPL BLS 1.4KG</t>
   </si>
   <si>
     <t>20071827</t>
@@ -1201,37 +1201,37 @@
     <t>20034450</t>
   </si>
   <si>
-    <t>M/LMN JRK NPS 690 G</t>
+    <t>MAMA/L JERUK NPS 690</t>
   </si>
   <si>
     <t>10004067</t>
   </si>
   <si>
-    <t>M/LMN PCH LMN 690 G</t>
+    <t>MAMA/L PCH LEMON 690</t>
   </si>
   <si>
     <t>20099424</t>
   </si>
   <si>
-    <t>M/LIME CHARCO 690 G</t>
+    <t>MAMA LIME CHARCO 690</t>
   </si>
   <si>
     <t>20052031</t>
   </si>
   <si>
-    <t>M/LIME GRN TEA 690 G</t>
+    <t>MAMA LIME GRN TEA690</t>
   </si>
   <si>
     <t>10004068</t>
   </si>
   <si>
-    <t>M/LIME POUCH 690 G</t>
+    <t>MAMA LIME POUCH 690</t>
   </si>
   <si>
     <t>20134303</t>
   </si>
   <si>
-    <t>M/LMN RE YUZU 690 G</t>
+    <t>MAMA/L REF YUZU 690</t>
   </si>
   <si>
     <t>20090067</t>
@@ -1282,7 +1282,7 @@
     <t>20141204</t>
   </si>
   <si>
-    <t>IDM P.PRG JNP 950 ML</t>
+    <t>IDM P.PRG JR.NPS 950</t>
   </si>
   <si>
     <t>20112491</t>
@@ -1342,7 +1342,7 @@
     <t>20142277</t>
   </si>
   <si>
-    <t>M/LIME JRK BTL 690 G</t>
+    <t>MAMA LM GRN BTL 690</t>
   </si>
   <si>
     <t>20135845</t>
@@ -1435,13 +1435,193 @@
     <t>HARPIC PWR PLS CT450</t>
   </si>
   <si>
+    <t>10037275</t>
+  </si>
+  <si>
+    <t>SWALLOW KMPR BTR 300</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>20027997</t>
+  </si>
+  <si>
+    <t>IDM KAMPER NAPTLN150</t>
+  </si>
+  <si>
+    <t>20131886</t>
+  </si>
+  <si>
+    <t>IDM KMPR DEO SKRA 5S</t>
+  </si>
+  <si>
+    <t>20131885</t>
+  </si>
+  <si>
+    <t>IDM KMPR DEO CFFE 5S</t>
+  </si>
+  <si>
+    <t>20079794</t>
+  </si>
+  <si>
+    <t>IDM KAMPER TOILET 5S</t>
+  </si>
+  <si>
+    <t>20139963</t>
+  </si>
+  <si>
+    <t>LARISST CTRONELLA 5S</t>
+  </si>
+  <si>
+    <t>10000279</t>
+  </si>
+  <si>
+    <t>SWALLOW TLT.BALL 5'S</t>
+  </si>
+  <si>
+    <t>10000482</t>
+  </si>
+  <si>
+    <t>SWALLOW K/DEO BAL105</t>
+  </si>
+  <si>
+    <t>20017478</t>
+  </si>
+  <si>
+    <t>SWALLOW ORG S-160</t>
+  </si>
+  <si>
+    <t>20122471</t>
+  </si>
+  <si>
+    <t>STELLA LAV.GRD 42+13</t>
+  </si>
+  <si>
+    <t>20136409</t>
+  </si>
+  <si>
+    <t>STELLA BALI JAS42+13</t>
+  </si>
+  <si>
+    <t>20109616</t>
+  </si>
+  <si>
+    <t>STELLA CAFF.LATTE 42</t>
+  </si>
+  <si>
+    <t>20075791</t>
+  </si>
+  <si>
+    <t>STELLA POCKET ORG 10</t>
+  </si>
+  <si>
+    <t>20075798</t>
+  </si>
+  <si>
+    <t>STLLA POCKET PRPL 10</t>
+  </si>
+  <si>
+    <t>20091307</t>
+  </si>
+  <si>
+    <t>STELLA POCKET BLU 10</t>
+  </si>
+  <si>
+    <t>20138481</t>
+  </si>
+  <si>
+    <t>STELLA EXO.FRUIT 10G</t>
+  </si>
+  <si>
+    <t>20138482</t>
+  </si>
+  <si>
+    <t>STELLA LUX.FLOWR 10G</t>
+  </si>
+  <si>
+    <t>20105573</t>
+  </si>
+  <si>
+    <t>STELLA AF REF JPS160</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>20037058</t>
+  </si>
+  <si>
+    <t>STELLA AF REF FLW160</t>
+  </si>
+  <si>
+    <t>20036827</t>
+  </si>
+  <si>
+    <t>STELLA AF REF GRN160</t>
+  </si>
+  <si>
+    <t>20044100</t>
+  </si>
+  <si>
+    <t>STELLA AF REF APL160</t>
+  </si>
+  <si>
+    <t>20135485</t>
+  </si>
+  <si>
+    <t>STELLA AF REF BAL160</t>
+  </si>
+  <si>
+    <t>20046210</t>
+  </si>
+  <si>
+    <t>GLADE OCN ESCPE 146G</t>
+  </si>
+  <si>
+    <t>10023003</t>
+  </si>
+  <si>
+    <t>GLADE PNY&amp;BRY BLS 70</t>
+  </si>
+  <si>
+    <t>10023002</t>
+  </si>
+  <si>
+    <t>GLADE FRESH ONE EF70</t>
+  </si>
+  <si>
+    <t>20096642</t>
+  </si>
+  <si>
+    <t>IDM FRSHNS LEMON 50</t>
+  </si>
+  <si>
+    <t>20096641</t>
+  </si>
+  <si>
+    <t>IDM FRSHNS ORANGE 50</t>
+  </si>
+  <si>
+    <t>10005428</t>
+  </si>
+  <si>
+    <t>STELLA IN ONE ORG 42</t>
+  </si>
+  <si>
+    <t>10005427</t>
+  </si>
+  <si>
+    <t>STELLA IN ONE LMN 42</t>
+  </si>
+  <si>
     <t>20134373</t>
   </si>
   <si>
     <t>STELLA ALAT+REFILL25</t>
   </si>
   <si>
-    <t>32</t>
+    <t>34</t>
   </si>
   <si>
     <t>20134374</t>
@@ -1540,186 +1720,6 @@
     <t>VAPE DORA LEM TIKUS</t>
   </si>
   <si>
-    <t>10037275</t>
-  </si>
-  <si>
-    <t>SWALLOW KMPR BTR 300</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>20027997</t>
-  </si>
-  <si>
-    <t>IDM KAMPER NAPTLN150</t>
-  </si>
-  <si>
-    <t>20131886</t>
-  </si>
-  <si>
-    <t>IDM KMPR DEO SKRA 5S</t>
-  </si>
-  <si>
-    <t>20131885</t>
-  </si>
-  <si>
-    <t>IDM KMPR DEO CFFE 5S</t>
-  </si>
-  <si>
-    <t>20079794</t>
-  </si>
-  <si>
-    <t>IDM KAMPER TOILET 5S</t>
-  </si>
-  <si>
-    <t>20139963</t>
-  </si>
-  <si>
-    <t>LARISST CTRONELLA 5S</t>
-  </si>
-  <si>
-    <t>10000279</t>
-  </si>
-  <si>
-    <t>SWALLOW TLT.BALL 5'S</t>
-  </si>
-  <si>
-    <t>10000482</t>
-  </si>
-  <si>
-    <t>SWALLOW K/DEO BAL105</t>
-  </si>
-  <si>
-    <t>20017478</t>
-  </si>
-  <si>
-    <t>SWALLOW ORG S-160</t>
-  </si>
-  <si>
-    <t>20122471</t>
-  </si>
-  <si>
-    <t>STELLA LAV.GRD 42+13</t>
-  </si>
-  <si>
-    <t>20136409</t>
-  </si>
-  <si>
-    <t>STELLA BALI JAS42+13</t>
-  </si>
-  <si>
-    <t>20109616</t>
-  </si>
-  <si>
-    <t>STELLA CAFF.LATTE 42</t>
-  </si>
-  <si>
-    <t>20075791</t>
-  </si>
-  <si>
-    <t>STELLA POCKET ORG 10</t>
-  </si>
-  <si>
-    <t>20075798</t>
-  </si>
-  <si>
-    <t>STLLA POCKET PRPL 10</t>
-  </si>
-  <si>
-    <t>20091307</t>
-  </si>
-  <si>
-    <t>STELLA POCKET BLU 10</t>
-  </si>
-  <si>
-    <t>20138481</t>
-  </si>
-  <si>
-    <t>STELLA EXO.FRUIT 10G</t>
-  </si>
-  <si>
-    <t>20138482</t>
-  </si>
-  <si>
-    <t>STELLA LUX.FLOWR 10G</t>
-  </si>
-  <si>
-    <t>20105573</t>
-  </si>
-  <si>
-    <t>STELLA AF REF JPS160</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>20037058</t>
-  </si>
-  <si>
-    <t>STELLA AF REF FLW160</t>
-  </si>
-  <si>
-    <t>20036827</t>
-  </si>
-  <si>
-    <t>STELLA AF REF GRN160</t>
-  </si>
-  <si>
-    <t>20044100</t>
-  </si>
-  <si>
-    <t>STELLA AF REF APL160</t>
-  </si>
-  <si>
-    <t>20135485</t>
-  </si>
-  <si>
-    <t>STELLA AF REF BAL160</t>
-  </si>
-  <si>
-    <t>20046210</t>
-  </si>
-  <si>
-    <t>GLADE OCN ESCPE 146G</t>
-  </si>
-  <si>
-    <t>10023003</t>
-  </si>
-  <si>
-    <t>GLADE PNY&amp;BRY BLS 70</t>
-  </si>
-  <si>
-    <t>10023002</t>
-  </si>
-  <si>
-    <t>GLADE FRESH ONE EF70</t>
-  </si>
-  <si>
-    <t>20096642</t>
-  </si>
-  <si>
-    <t>IDM FRSHNS LEMON 50</t>
-  </si>
-  <si>
-    <t>20096641</t>
-  </si>
-  <si>
-    <t>IDM FRSHNS ORANGE 50</t>
-  </si>
-  <si>
-    <t>10005428</t>
-  </si>
-  <si>
-    <t>STELLA IN ONE ORG 42</t>
-  </si>
-  <si>
-    <t>10005427</t>
-  </si>
-  <si>
-    <t>STELLA IN ONE LMN 42</t>
-  </si>
-  <si>
     <t>20022902</t>
   </si>
   <si>
@@ -1825,7 +1825,7 @@
     <t>20124346</t>
   </si>
   <si>
-    <t>BAYGON JP&amp;PCH 600 ML</t>
+    <t>BAYGON JPNSE&amp;PCH 600</t>
   </si>
   <si>
     <t>RT,(E-6B)</t>
@@ -1834,19 +1834,19 @@
     <t>20098605</t>
   </si>
   <si>
-    <t>BAYGON CH BLO 600 ML</t>
+    <t>BYGON SPRY CHR.BL600</t>
   </si>
   <si>
     <t>10003272</t>
   </si>
   <si>
-    <t>BAYGON CTR FH 675 ML</t>
+    <t>BAYGON SPRY CITRS675</t>
   </si>
   <si>
     <t>20071775</t>
   </si>
   <si>
-    <t>BAYGON FLO.GN 675 ML</t>
+    <t>BAYGON FLO.GRDN 675</t>
   </si>
   <si>
     <t>20139154</t>
@@ -2760,7 +2760,7 @@
         <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -6683,7 +6683,7 @@
         <v>4</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -6703,7 +6703,7 @@
         <v>8</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>5</v>
+        <v>294</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -6723,7 +6723,7 @@
         <v>11</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -6743,7 +6743,7 @@
         <v>14</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -6763,7 +6763,7 @@
         <v>18</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -6783,7 +6783,7 @@
         <v>32</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -6823,7 +6823,7 @@
         <v>38</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>294</v>
+        <v>77</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -6843,7 +6843,7 @@
         <v>70</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>312</v>
+        <v>77</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -6863,7 +6863,7 @@
         <v>135</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>294</v>
+        <v>5</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -6883,7 +6883,7 @@
         <v>144</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>341</v>
+        <v>5</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -6903,7 +6903,7 @@
         <v>155</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>312</v>
+        <v>5</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -6923,7 +6923,7 @@
         <v>169</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -6940,10 +6940,10 @@
         <v>476</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>77</v>
+        <v>294</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -6960,10 +6960,10 @@
         <v>476</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>94</v>
+        <v>294</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -6980,10 +6980,10 @@
         <v>476</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>217</v>
+        <v>169</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>312</v>
+        <v>77</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -7000,10 +7000,10 @@
         <v>476</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>226</v>
+        <v>169</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -7023,7 +7023,7 @@
         <v>4</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>77</v>
+        <v>341</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -7043,7 +7043,7 @@
         <v>8</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -7063,7 +7063,7 @@
         <v>11</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -7083,7 +7083,7 @@
         <v>14</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -7103,7 +7103,7 @@
         <v>18</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>294</v>
+        <v>5</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -7123,7 +7123,7 @@
         <v>32</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>294</v>
+        <v>94</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -7143,7 +7143,7 @@
         <v>35</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -7163,7 +7163,7 @@
         <v>38</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -7183,7 +7183,7 @@
         <v>70</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>77</v>
+        <v>249</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -7203,7 +7203,7 @@
         <v>135</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>5</v>
+        <v>249</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -7223,7 +7223,7 @@
         <v>144</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>5</v>
+        <v>312</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -7243,7 +7243,7 @@
         <v>155</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>5</v>
+        <v>312</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -7257,110 +7257,110 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>511</v>
+        <v>536</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>169</v>
+        <v>4</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>294</v>
+        <v>5</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D246" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="B246" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="C246" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D246" s="1" t="s">
-        <v>511</v>
-      </c>
       <c r="E246" s="1" t="s">
-        <v>169</v>
+        <v>8</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>294</v>
+        <v>5</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>511</v>
+        <v>536</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>511</v>
+        <v>536</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>169</v>
+        <v>14</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>77</v>
+        <v>312</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>511</v>
+        <v>536</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>169</v>
+        <v>18</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>77</v>
+        <v>312</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F250" s="1" t="s">
         <v>341</v>
@@ -7377,13 +7377,13 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>312</v>
+        <v>77</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -7397,13 +7397,13 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7417,10 +7417,10 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="F253" s="1" t="s">
         <v>312</v>
@@ -7437,13 +7437,13 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>18</v>
+        <v>135</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>5</v>
+        <v>294</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -7457,13 +7457,13 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>94</v>
+        <v>341</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -7477,13 +7477,13 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>35</v>
+        <v>155</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>94</v>
+        <v>312</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -7497,13 +7497,13 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>38</v>
+        <v>169</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>94</v>
+        <v>312</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -7517,13 +7517,13 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>70</v>
+        <v>188</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>249</v>
+        <v>77</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -7537,13 +7537,13 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>135</v>
+        <v>208</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>249</v>
+        <v>94</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -7557,10 +7557,10 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>144</v>
+        <v>217</v>
       </c>
       <c r="F260" s="1" t="s">
         <v>312</v>
@@ -7577,13 +7577,13 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>155</v>
+        <v>226</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>312</v>
+        <v>94</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">

--- a/DND05S.xlsx
+++ b/DND05S.xlsx
@@ -64,7 +64,7 @@
     <t>20099414</t>
   </si>
   <si>
-    <t>SOKLIN SOFT PRPL1.44</t>
+    <t>SOKLIN SOFT PRPL1.3</t>
   </si>
   <si>
     <t>5</t>
@@ -1201,37 +1201,37 @@
     <t>20034450</t>
   </si>
   <si>
-    <t>MAMA/L JERUK NPS 690</t>
+    <t>MAMA/L JERUK NPS 650</t>
   </si>
   <si>
     <t>10004067</t>
   </si>
   <si>
-    <t>MAMA/L PCH LEMON 690</t>
+    <t>MAMA/L PCH LEMON 650</t>
   </si>
   <si>
     <t>20099424</t>
   </si>
   <si>
-    <t>MAMA LIME CHARCO 690</t>
+    <t>MAMA LIME CHARCO 650</t>
   </si>
   <si>
     <t>20052031</t>
   </si>
   <si>
-    <t>MAMA LIME GRN TEA690</t>
+    <t>MAMA LIME GRN TEA650</t>
   </si>
   <si>
     <t>10004068</t>
   </si>
   <si>
-    <t>MAMA LIME POUCH 690</t>
+    <t>MAMA LIME POUCH 650</t>
   </si>
   <si>
     <t>20134303</t>
   </si>
   <si>
-    <t>MAMA/L REF YUZU 690</t>
+    <t>MAMA/L YUZU+J/NPS650</t>
   </si>
   <si>
     <t>20090067</t>

--- a/DND05S.xlsx
+++ b/DND05S.xlsx
@@ -88,25 +88,25 @@
     <t>20109454</t>
   </si>
   <si>
-    <t>SOKLIN CAIR SCRLT1.6</t>
+    <t>SKLIN LQD S/BLSM1.45</t>
   </si>
   <si>
     <t>20099420</t>
   </si>
   <si>
-    <t>SOKLIN CAIR VIO 1.6L</t>
+    <t>SKLIN LQD V/BLSM1.45</t>
   </si>
   <si>
     <t>20067585</t>
   </si>
   <si>
-    <t>SOKLN LIQ RED SB 700</t>
+    <t>SKLN LQD SC/BLOSM675</t>
   </si>
   <si>
     <t>20054747</t>
   </si>
   <si>
-    <t>SO KLIN VL/BLSOM 700</t>
+    <t>SKLIN LQD V/BLSOM675</t>
   </si>
   <si>
     <t>6</t>
@@ -115,7 +115,7 @@
     <t>20046548</t>
   </si>
   <si>
-    <t>SOKLIN SOFT CAIR 700</t>
+    <t>SKLIN LQD SFTRGN 675</t>
   </si>
   <si>
     <t>7</t>
@@ -202,25 +202,25 @@
     <t>20093627</t>
   </si>
   <si>
-    <t>SOKLN LIQ SAKURA 510</t>
+    <t>SKLN LQD SKR STRW500</t>
   </si>
   <si>
     <t>20123818</t>
   </si>
   <si>
-    <t>SOKLN LIQ LVNDR 510</t>
+    <t>SKLN LQD PROV LVD500</t>
   </si>
   <si>
     <t>20091870</t>
   </si>
   <si>
-    <t>SO KLN LIQ WH&amp;BR 510</t>
+    <t>SKLN LQ WHT&amp;BRGHT500</t>
   </si>
   <si>
     <t>20114428</t>
   </si>
   <si>
-    <t>SOKLN LIQ KOREAN 510</t>
+    <t>SKLN LQD KOR CMLA500</t>
   </si>
   <si>
     <t>9</t>
@@ -367,55 +367,55 @@
     <t>20073805</t>
   </si>
   <si>
-    <t>SOKLN RED/MG&amp;B1.44KG</t>
+    <t>SOKLN MGNLA&amp;BRES1.3</t>
   </si>
   <si>
     <t>20041483</t>
   </si>
   <si>
-    <t>SO/KLN SOFT P/RS1.44</t>
+    <t>SO/KLN SOFT P/RS1.3</t>
   </si>
   <si>
     <t>20140806</t>
   </si>
   <si>
-    <t>SO KLN EDP D.LS 144</t>
+    <t>SKLN EDP FL.DELIS1.3</t>
   </si>
   <si>
     <t>20140804</t>
   </si>
   <si>
-    <t>SO KLN EDP BLNC 1.44</t>
+    <t>SKLN EDP FLR BLNC1.3</t>
   </si>
   <si>
     <t>20091352</t>
   </si>
   <si>
-    <t>DAIA+SOFT VIOLET 1.5</t>
+    <t>DAIA PWDR VLT PSN1.4</t>
   </si>
   <si>
     <t>20052321</t>
   </si>
   <si>
-    <t>DAIA+SOFT PINK 1.5KG</t>
+    <t>DAIA PWDR ROM/PNK1.4</t>
   </si>
   <si>
     <t>20030446</t>
   </si>
   <si>
-    <t>DAIA PUTIH 1.5KG</t>
+    <t>DAIA PWDR PUTIH1.4KG</t>
   </si>
   <si>
     <t>20121050</t>
   </si>
   <si>
-    <t>DAIA HIJAB C&amp;F 1.5G</t>
+    <t>DAIA HJB CLN&amp;FRSH1.4</t>
   </si>
   <si>
     <t>20142276</t>
   </si>
   <si>
-    <t>DAIA LILY JSMN 1.5KG</t>
+    <t>DAIA PWDR LLY&amp;JSM1.4</t>
   </si>
   <si>
     <t>10</t>
@@ -424,13 +424,13 @@
     <t>10014547</t>
   </si>
   <si>
-    <t>DAIA DTRG.BBK BGA1.5</t>
+    <t>DAIA PWDR FLORAL1.4</t>
   </si>
   <si>
     <t>20012007</t>
   </si>
   <si>
-    <t>DAIA DET.BBK PTH 800</t>
+    <t>DAIA PWDR PUTIH 725G</t>
   </si>
   <si>
     <t>10005245</t>
@@ -442,7 +442,7 @@
     <t>20053796</t>
   </si>
   <si>
-    <t>SOKLN SOFTG PRPL 720</t>
+    <t>SKLN SFTG LVD&amp;LLY650</t>
   </si>
   <si>
     <t>11</t>
@@ -451,25 +451,25 @@
     <t>20073499</t>
   </si>
   <si>
-    <t>SO KLN MGNL&amp;BRY 720G</t>
+    <t>SO KLN MGNL&amp;BRY 650G</t>
   </si>
   <si>
     <t>20012188</t>
   </si>
   <si>
-    <t>SOKLN SOFTR ROSY 720</t>
+    <t>SOKLN SOFTR ROSY 650</t>
   </si>
   <si>
     <t>20061748</t>
   </si>
   <si>
-    <t>DAIA DET+SFT VLT 800</t>
+    <t>DAIA PWDR VLT PSN725</t>
   </si>
   <si>
     <t>20036047</t>
   </si>
   <si>
-    <t>DAIA DET+SOFT  800G</t>
+    <t>DAIA PWDR ROM/PNK725</t>
   </si>
   <si>
     <t>20113809</t>
@@ -742,13 +742,13 @@
     <t>20128719</t>
   </si>
   <si>
-    <t>SOKLIN LVD&amp;LILY 425G</t>
+    <t>SOKLIN LVD&amp;LILY 375G</t>
   </si>
   <si>
     <t>20042466</t>
   </si>
   <si>
-    <t>DAIA DET+SOFT 470G</t>
+    <t>DAIA PWDR ROM/PNK390</t>
   </si>
   <si>
     <t>20139595</t>
@@ -5240,7 +5240,7 @@
         <v>307</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>160</v>

--- a/DND05S.xlsx
+++ b/DND05S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="659">
   <si>
     <t/>
   </si>
@@ -169,6 +169,12 @@
     <t>GENTLE GEN FR.PE 360</t>
   </si>
   <si>
+    <t>20143096</t>
+  </si>
+  <si>
+    <t>RNSO RSE FRSH 2X510G</t>
+  </si>
+  <si>
     <t>20137793</t>
   </si>
   <si>
@@ -193,1777 +199,1795 @@
     <t>RNSO MLTO KRN STR510</t>
   </si>
   <si>
+    <t>20093627</t>
+  </si>
+  <si>
+    <t>SKLN LQD SKR STRW500</t>
+  </si>
+  <si>
+    <t>20123818</t>
+  </si>
+  <si>
+    <t>SKLN LQD PROV LVD500</t>
+  </si>
+  <si>
+    <t>20091870</t>
+  </si>
+  <si>
+    <t>SKLN LQ WHT&amp;BRGHT500</t>
+  </si>
+  <si>
+    <t>20114428</t>
+  </si>
+  <si>
+    <t>SKLN LQD KOR CMLA500</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20141373</t>
+  </si>
+  <si>
+    <t>RINSO PW.CLN BTL 650</t>
+  </si>
+  <si>
+    <t>20141369</t>
+  </si>
+  <si>
+    <t>RINSO P.BRZE BTL 650</t>
+  </si>
+  <si>
+    <t>20131730</t>
+  </si>
+  <si>
+    <t>SYANG LIQ R/ROSE 700</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20132442</t>
+  </si>
+  <si>
+    <t>SYANG LIQ ORIGNAL700</t>
+  </si>
+  <si>
+    <t>20135849</t>
+  </si>
+  <si>
+    <t>LARIST SMR.BRZ 700ML</t>
+  </si>
+  <si>
+    <t>20139955</t>
+  </si>
+  <si>
+    <t>BU KRM JNHAE CB700ML</t>
+  </si>
+  <si>
+    <t>20120180</t>
+  </si>
+  <si>
+    <t>SO SOFT RS&amp;WTRLY 700</t>
+  </si>
+  <si>
+    <t>20121364</t>
+  </si>
+  <si>
+    <t>SO SOFT SKR BLSM 700</t>
+  </si>
+  <si>
+    <t>20135246</t>
+  </si>
+  <si>
+    <t>SO SOFT SWT PEONY700</t>
+  </si>
+  <si>
+    <t>20128720</t>
+  </si>
+  <si>
+    <t>SO SOFT FLO BRS 700</t>
+  </si>
+  <si>
+    <t>20140325</t>
+  </si>
+  <si>
+    <t>SO SOFT FLO LILY 700</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20133333</t>
+  </si>
+  <si>
+    <t>GENTLE GEN A/KRGT700</t>
+  </si>
+  <si>
+    <t>20141371</t>
+  </si>
+  <si>
+    <t>GNTLE GEN CMLLIA 700</t>
+  </si>
+  <si>
+    <t>20141372</t>
+  </si>
+  <si>
+    <t>GENTLE GEN LILAC 700</t>
+  </si>
+  <si>
+    <t>20135245</t>
+  </si>
+  <si>
+    <t>SO KLIN LIQ FRNCH700</t>
+  </si>
+  <si>
+    <t>20133798</t>
+  </si>
+  <si>
+    <t>SO KLIN LIQ EN.RS700</t>
+  </si>
+  <si>
+    <t>20139729</t>
+  </si>
+  <si>
+    <t>SOKLN GR.TEA&amp;JSM 700</t>
+  </si>
+  <si>
+    <t>20142134</t>
+  </si>
+  <si>
+    <t>SO KLN BLU PETAL 700</t>
+  </si>
+  <si>
+    <t>20142132</t>
+  </si>
+  <si>
+    <t>SO KLN MAISON DE 700</t>
+  </si>
+  <si>
+    <t>20113567</t>
+  </si>
+  <si>
+    <t>GENTLE GEN MR.BRZ700</t>
+  </si>
+  <si>
+    <t>20115959</t>
+  </si>
+  <si>
+    <t>GENTLE GEN FR.PE 700</t>
+  </si>
+  <si>
+    <t>20115958</t>
+  </si>
+  <si>
+    <t>GENTLE GEN PRS.G 700</t>
+  </si>
+  <si>
+    <t>20073805</t>
+  </si>
+  <si>
+    <t>SOKLN MGNLA&amp;BRES1.3</t>
+  </si>
+  <si>
+    <t>20041483</t>
+  </si>
+  <si>
+    <t>SO/KLN SOFT P/RS1.3</t>
+  </si>
+  <si>
+    <t>20140806</t>
+  </si>
+  <si>
+    <t>SKLN EDP FL.DELIS1.3</t>
+  </si>
+  <si>
+    <t>20140804</t>
+  </si>
+  <si>
+    <t>SKLN EDP FLR BLNC1.3</t>
+  </si>
+  <si>
+    <t>20091352</t>
+  </si>
+  <si>
+    <t>DAIA PWDR VLT PSN1.4</t>
+  </si>
+  <si>
+    <t>20052321</t>
+  </si>
+  <si>
+    <t>DAIA PWDR ROM/PNK1.4</t>
+  </si>
+  <si>
+    <t>20030446</t>
+  </si>
+  <si>
+    <t>DAIA PWDR PUTIH1.4KG</t>
+  </si>
+  <si>
+    <t>20121050</t>
+  </si>
+  <si>
+    <t>DAIA HJB CLN&amp;FRSH1.4</t>
+  </si>
+  <si>
+    <t>20142276</t>
+  </si>
+  <si>
+    <t>DAIA PWDR LLY&amp;JSM1.4</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>10014547</t>
+  </si>
+  <si>
+    <t>DAIA PWDR FLORAL1.4</t>
+  </si>
+  <si>
+    <t>20012007</t>
+  </si>
+  <si>
+    <t>DAIA PWDR PUTIH 725G</t>
+  </si>
+  <si>
+    <t>10005245</t>
+  </si>
+  <si>
+    <t>DAIA BBK FLORAL 725G</t>
+  </si>
+  <si>
+    <t>20053796</t>
+  </si>
+  <si>
+    <t>SKLN SFTG LVD&amp;LLY650</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20073499</t>
+  </si>
+  <si>
+    <t>SO KLN MGNL&amp;BRY 650G</t>
+  </si>
+  <si>
+    <t>20012188</t>
+  </si>
+  <si>
+    <t>SOKLN SOFTR ROSY 650</t>
+  </si>
+  <si>
+    <t>20061748</t>
+  </si>
+  <si>
+    <t>DAIA PWDR VLT PSN725</t>
+  </si>
+  <si>
+    <t>20036047</t>
+  </si>
+  <si>
+    <t>DAIA PWDR ROM/PNK725</t>
+  </si>
+  <si>
+    <t>20113809</t>
+  </si>
+  <si>
+    <t>OXYKLIN DTRG LIQ 700</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20129837</t>
+  </si>
+  <si>
+    <t>LARIST SPR.GRD 750ML</t>
+  </si>
+  <si>
+    <t>20097739</t>
+  </si>
+  <si>
+    <t>IDM DET.CAIR PCH 700</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20067586</t>
+  </si>
+  <si>
+    <t>SOKLIN LIQ.BM TOP700</t>
+  </si>
+  <si>
+    <t>20054610</t>
+  </si>
+  <si>
+    <t>RINSO LIQ FRONT 1.45</t>
+  </si>
+  <si>
+    <t>10030924</t>
+  </si>
+  <si>
+    <t>SOKLIN MTC F/LD 900G</t>
+  </si>
+  <si>
+    <t>20081448</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT H.SM 600</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20081449</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT P.DW 600</t>
+  </si>
+  <si>
+    <t>20104951</t>
+  </si>
+  <si>
+    <t>ROYALE HJB BLCK.V600</t>
+  </si>
+  <si>
+    <t>20091457</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT BS 600</t>
+  </si>
+  <si>
+    <t>20113101</t>
+  </si>
+  <si>
+    <t>ROYALE SWT FLORL 600</t>
+  </si>
+  <si>
+    <t>20128706</t>
+  </si>
+  <si>
+    <t>ROYALE LNVDR VNL 600</t>
+  </si>
+  <si>
+    <t>20113093</t>
+  </si>
+  <si>
+    <t>ROYALE SUNNY DAY 600</t>
+  </si>
+  <si>
+    <t>20142010</t>
+  </si>
+  <si>
+    <t>ROYALE MTCHA BLS 600</t>
+  </si>
+  <si>
+    <t>20128919</t>
+  </si>
+  <si>
+    <t>MOLTO SFTNR PURE 550</t>
+  </si>
+  <si>
+    <t>20094735</t>
+  </si>
+  <si>
+    <t>DOWNY SUNRISE 950</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>PT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20094733</t>
+  </si>
+  <si>
+    <t>DOWNY MYSTIQUE 900</t>
+  </si>
+  <si>
+    <t>20140221</t>
+  </si>
+  <si>
+    <t>DOWNY PASSION 875ML</t>
+  </si>
+  <si>
+    <t>20141324</t>
+  </si>
+  <si>
+    <t>DOWNY SUNSHINE 500ML</t>
+  </si>
+  <si>
+    <t>20141323</t>
+  </si>
+  <si>
+    <t>DOWNY MIDNIGHT 500ML</t>
+  </si>
+  <si>
+    <t>20080360</t>
+  </si>
+  <si>
+    <t>DOWNY MYSTIQUE 550ML</t>
+  </si>
+  <si>
+    <t>20080361</t>
+  </si>
+  <si>
+    <t>DOWNY PASSION 550ML</t>
+  </si>
+  <si>
+    <t>20074226</t>
+  </si>
+  <si>
+    <t>DOWNY SUN.FRSH 550</t>
+  </si>
+  <si>
+    <t>20139145</t>
+  </si>
+  <si>
+    <t>DOWNY MLKY TOUCH 500</t>
+  </si>
+  <si>
+    <t>20140003</t>
+  </si>
+  <si>
+    <t>RNSO PWD ROSE.F 1.44</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20093521</t>
+  </si>
+  <si>
+    <t>RINSO+MOLTO ESC1440G</t>
+  </si>
+  <si>
+    <t>20139609</t>
+  </si>
+  <si>
+    <t>RNSO JPN PEAC 1440G</t>
+  </si>
+  <si>
+    <t>20140002</t>
+  </si>
+  <si>
+    <t>RINSO PWD PURE 1440G</t>
+  </si>
+  <si>
+    <t>20064413</t>
+  </si>
+  <si>
+    <t>ATCK JAZ1 S/CNTA 1.4</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20064414</t>
+  </si>
+  <si>
+    <t>ATTACK JAZ1 P/SGR1.4</t>
+  </si>
+  <si>
+    <t>20130527</t>
+  </si>
+  <si>
+    <t>ATTACK DET+SF RB 1.4</t>
+  </si>
+  <si>
+    <t>20138108</t>
+  </si>
+  <si>
+    <t>JAZ 1 PRPL BLS 1.4KG</t>
+  </si>
+  <si>
+    <t>20071827</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD ROSE 700</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20085113</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD PRFM 700</t>
+  </si>
+  <si>
+    <t>20105968</t>
+  </si>
+  <si>
+    <t>RNSO PWD JPN PC 700G</t>
+  </si>
+  <si>
+    <t>20074992</t>
+  </si>
+  <si>
+    <t>BUKRIM OXY/K VIOL700</t>
+  </si>
+  <si>
+    <t>20119238</t>
+  </si>
+  <si>
+    <t>TOTAL DET.PERFUME750</t>
+  </si>
+  <si>
+    <t>20131516</t>
+  </si>
+  <si>
+    <t>LARIST DET.FRS BT450</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20113183</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD ROSE 380</t>
+  </si>
+  <si>
+    <t>20121372</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD PRFM 380</t>
+  </si>
+  <si>
+    <t>20128719</t>
+  </si>
+  <si>
+    <t>SOKLIN LVD&amp;LILY 375G</t>
+  </si>
+  <si>
+    <t>20042466</t>
+  </si>
+  <si>
+    <t>DAIA PWDR ROM/PNK390</t>
+  </si>
+  <si>
+    <t>20139595</t>
+  </si>
+  <si>
+    <t>MOLTO TRKA BDD 3X300</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20133398</t>
+  </si>
+  <si>
+    <t>TRKA PURE 300ML</t>
+  </si>
+  <si>
+    <t>10011440</t>
+  </si>
+  <si>
+    <t>RAPIKA LVDR SPLAS300</t>
+  </si>
+  <si>
+    <t>20084780</t>
+  </si>
+  <si>
+    <t>RAPIKA GOLD 250ML</t>
+  </si>
+  <si>
+    <t>20093193</t>
+  </si>
+  <si>
+    <t>RAPIKA PINK SKR 300</t>
+  </si>
+  <si>
+    <t>20138071</t>
+  </si>
+  <si>
+    <t>KISPRAY KASTURI 280</t>
+  </si>
+  <si>
+    <t>20074721</t>
+  </si>
+  <si>
+    <t>KISPRAY GLM.GOLD 280</t>
+  </si>
+  <si>
+    <t>20116685</t>
+  </si>
+  <si>
+    <t>KISPRAY ELG.SAPH 200</t>
+  </si>
+  <si>
+    <t>20032250</t>
+  </si>
+  <si>
+    <t>KISPRAY VIOLET PC280</t>
+  </si>
+  <si>
+    <t>20000980</t>
+  </si>
+  <si>
+    <t>KISPRAY VIOLET 318ML</t>
+  </si>
+  <si>
+    <t>20138470</t>
+  </si>
+  <si>
+    <t>SO KLN PWNG RED 1.7L</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>10005803</t>
+  </si>
+  <si>
+    <t>SOKLIN PWNGI RED 780</t>
+  </si>
+  <si>
+    <t>10007389</t>
+  </si>
+  <si>
+    <t>SOKLIN PWNGI PINK780</t>
+  </si>
+  <si>
+    <t>10008104</t>
+  </si>
+  <si>
+    <t>SO KLIN PWG BLUE 780</t>
+  </si>
+  <si>
+    <t>20108418</t>
+  </si>
+  <si>
+    <t>SOKLIN PWG HJB GR780</t>
+  </si>
+  <si>
+    <t>10005802</t>
+  </si>
+  <si>
+    <t>SOKLIN PEWANGI VL780</t>
+  </si>
+  <si>
+    <t>20141985</t>
+  </si>
+  <si>
+    <t>SO KLN TROP SUMR 780</t>
+  </si>
+  <si>
+    <t>20134526</t>
+  </si>
+  <si>
+    <t>SOKLIN PWG COT.FN780</t>
+  </si>
+  <si>
+    <t>20129370</t>
+  </si>
+  <si>
+    <t>MOLTO MORNING FRS550</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20129160</t>
+  </si>
+  <si>
+    <t>MOLTO LUXURY PRF 650</t>
+  </si>
+  <si>
+    <t>20087464</t>
+  </si>
+  <si>
+    <t>IDM PWNG PINK.PAS720</t>
+  </si>
+  <si>
+    <t>20137582</t>
+  </si>
+  <si>
+    <t>IDM PWNG ROM.AURA720</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20137581</t>
+  </si>
+  <si>
+    <t>IDM PWNG EXO.BLUE720</t>
+  </si>
+  <si>
+    <t>20020245</t>
+  </si>
+  <si>
+    <t>MOLTO PWNGI BLUE 765</t>
+  </si>
+  <si>
+    <t>20020226</t>
+  </si>
+  <si>
+    <t>MOLTO PWNGI PINK 765</t>
+  </si>
+  <si>
+    <t>20106821</t>
+  </si>
+  <si>
+    <t>MOLTO PURPLE 765ML</t>
+  </si>
+  <si>
+    <t>20142219</t>
+  </si>
+  <si>
+    <t>MLTO GNTL FRSH 765ML</t>
+  </si>
+  <si>
+    <t>20135847</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT SUMMR600</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20135846</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT SPRNG600</t>
+  </si>
+  <si>
+    <t>20014403</t>
+  </si>
+  <si>
+    <t>BAYCLIN REGLR 1000ML</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>20082581</t>
+  </si>
+  <si>
+    <t>VANISH CAIR WHT 425</t>
+  </si>
+  <si>
+    <t>20052662</t>
+  </si>
+  <si>
+    <t>VANISH CAIR PCH 425</t>
+  </si>
+  <si>
+    <t>20079788</t>
+  </si>
+  <si>
+    <t>PROCLIN PCH 400ML</t>
+  </si>
+  <si>
+    <t>20093919</t>
+  </si>
+  <si>
+    <t>IDM PURPOSE CLN 400</t>
+  </si>
+  <si>
+    <t>10014263</t>
+  </si>
+  <si>
+    <t>WIPOL KARBOL CMR 720</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>20001645</t>
+  </si>
+  <si>
+    <t>WIPOL KARBOL LMN 720</t>
+  </si>
+  <si>
+    <t>20090066</t>
+  </si>
+  <si>
+    <t>WIPOL SRH + JRK 720</t>
+  </si>
+  <si>
+    <t>20122478</t>
+  </si>
+  <si>
+    <t>WIPOL CITRUS FRS 390</t>
+  </si>
+  <si>
+    <t>20023111</t>
+  </si>
+  <si>
+    <t>SOS KARBOL CLS PN725</t>
+  </si>
+  <si>
+    <t>10013107</t>
+  </si>
+  <si>
+    <t>SUPERSOL PINE 720G</t>
+  </si>
+  <si>
+    <t>20104030</t>
+  </si>
+  <si>
+    <t>SUPER SOL SEREH720G</t>
+  </si>
+  <si>
+    <t>10004612</t>
+  </si>
+  <si>
+    <t>SOS P.LNT ORANGE 700</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10004610</t>
+  </si>
+  <si>
+    <t>SOS P/LT APLL REF700</t>
+  </si>
+  <si>
+    <t>10010480</t>
+  </si>
+  <si>
+    <t>SPR PELL FRS.APEL760</t>
+  </si>
+  <si>
+    <t>20121373</t>
+  </si>
+  <si>
+    <t>SPR PELL AB CTRS 500</t>
+  </si>
+  <si>
+    <t>20137408</t>
+  </si>
+  <si>
+    <t>SPR PELL SAKURA 760</t>
+  </si>
+  <si>
+    <t>20001407</t>
+  </si>
+  <si>
+    <t>IDM P'LANTAI LAV 800</t>
+  </si>
+  <si>
+    <t>20001402</t>
+  </si>
+  <si>
+    <t>IDM P'LANTAI APL 800</t>
+  </si>
+  <si>
+    <t>20028779</t>
+  </si>
+  <si>
+    <t>IDM KRBOL WNG650(BR)</t>
+  </si>
+  <si>
+    <t>20089486</t>
+  </si>
+  <si>
+    <t>IDM KRBL SRH CTR 650</t>
+  </si>
+  <si>
+    <t>20128125</t>
+  </si>
+  <si>
+    <t>IDM PURPOSE CLN 375</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>20027963</t>
+  </si>
+  <si>
+    <t>IDM PMBERSH KACA 400</t>
+  </si>
+  <si>
+    <t>10003706</t>
+  </si>
+  <si>
+    <t>MR.MUSCLE ORGNL 400</t>
+  </si>
+  <si>
+    <t>10012548</t>
+  </si>
+  <si>
+    <t>SOKLIN RLX/LAV RF770</t>
+  </si>
+  <si>
+    <t>10003646</t>
+  </si>
+  <si>
+    <t>SO KLIN P/L APPLE770</t>
+  </si>
+  <si>
+    <t>10003645</t>
+  </si>
+  <si>
+    <t>SO KLIN P/L LMN 780</t>
+  </si>
+  <si>
+    <t>20101095</t>
+  </si>
+  <si>
+    <t>SO KLN LNT SEREH 770</t>
+  </si>
+  <si>
+    <t>20131223</t>
+  </si>
+  <si>
+    <t>SO KLN LNT CT.GRD700</t>
+  </si>
+  <si>
+    <t>20141956</t>
+  </si>
+  <si>
+    <t>EKONOMI NANAS 920G</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>20136124</t>
+  </si>
+  <si>
+    <t>EKNOMI LIQ N&amp;JN 675G</t>
+  </si>
+  <si>
+    <t>20092331</t>
+  </si>
+  <si>
+    <t>EKONOMI LIQ JR.NP675</t>
+  </si>
+  <si>
+    <t>20123812</t>
+  </si>
+  <si>
+    <t>EKONOMI LQ.SEREH 675</t>
+  </si>
+  <si>
+    <t>20107240</t>
+  </si>
+  <si>
+    <t>EKONOMI LIQ.SW&amp;JR675</t>
+  </si>
+  <si>
+    <t>20129722</t>
+  </si>
+  <si>
+    <t>BUKRIM LIQ.JRK NP550</t>
+  </si>
+  <si>
+    <t>20138518</t>
+  </si>
+  <si>
+    <t>KILAU NIPIS 630ML</t>
+  </si>
+  <si>
+    <t>20131788</t>
+  </si>
+  <si>
+    <t>MAMA LMN JR.NPS 950</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>20142275</t>
+  </si>
+  <si>
+    <t>MAMA LIME CHARCO 950</t>
+  </si>
+  <si>
+    <t>20034450</t>
+  </si>
+  <si>
+    <t>MAMA/L JERUK NPS 650</t>
+  </si>
+  <si>
+    <t>10004067</t>
+  </si>
+  <si>
+    <t>MAMA/L PCH LEMON 650</t>
+  </si>
+  <si>
+    <t>20099424</t>
+  </si>
+  <si>
+    <t>MAMA LIME CHARCO 650</t>
+  </si>
+  <si>
+    <t>20052031</t>
+  </si>
+  <si>
+    <t>MAMA LIME GRN TEA650</t>
+  </si>
+  <si>
+    <t>10004068</t>
+  </si>
+  <si>
+    <t>MAMA LIME POUCH 650</t>
+  </si>
+  <si>
+    <t>20134303</t>
+  </si>
+  <si>
+    <t>MAMA/L YUZU+J/NPS650</t>
+  </si>
+  <si>
+    <t>20090067</t>
+  </si>
+  <si>
+    <t>SNLGHT MINT A.BAU600</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>20086172</t>
+  </si>
+  <si>
+    <t>SNLIGHT MND.ORGE 600</t>
+  </si>
+  <si>
+    <t>20112492</t>
+  </si>
+  <si>
+    <t>SUNLIGHT JRK NPS400G</t>
+  </si>
+  <si>
+    <t>20143097</t>
+  </si>
+  <si>
+    <t>LFBY CC PRG LME2X610</t>
+  </si>
+  <si>
+    <t>TG,(E-1B)</t>
+  </si>
+  <si>
+    <t>20134576</t>
+  </si>
+  <si>
+    <t>LFEBUOY REF LEMON650</t>
+  </si>
+  <si>
+    <t>20141345</t>
+  </si>
+  <si>
+    <t>LARISST S/PCC PRG650</t>
+  </si>
+  <si>
+    <t>20073425</t>
+  </si>
+  <si>
+    <t>IDM P.PRNG JRK.N 650</t>
+  </si>
+  <si>
+    <t>20141204</t>
+  </si>
+  <si>
+    <t>IDM P.PRG JR.NPS 950</t>
+  </si>
+  <si>
+    <t>20112491</t>
+  </si>
+  <si>
+    <t>SNLIGHT LIME PCH 910</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>20139728</t>
+  </si>
+  <si>
+    <t>SNLGHT BIO BLBR 870G</t>
+  </si>
+  <si>
+    <t>10005482</t>
+  </si>
+  <si>
+    <t>SNLIGHT LIME PCH 660</t>
+  </si>
+  <si>
+    <t>20143091</t>
+  </si>
+  <si>
+    <t>SNLGHT JRK NPS 2X650</t>
+  </si>
+  <si>
+    <t>20135144</t>
+  </si>
+  <si>
+    <t>SNLGHT BIO NATURE600</t>
+  </si>
+  <si>
+    <t>10003498</t>
+  </si>
+  <si>
+    <t>CLEAR PUMP ORIGNL500</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>10013205</t>
+  </si>
+  <si>
+    <t>SUNLIGHT J/NIPIS.750</t>
+  </si>
+  <si>
+    <t>20139947</t>
+  </si>
+  <si>
+    <t>SNLGHT BIO BLBR 675G</t>
+  </si>
+  <si>
+    <t>20139948</t>
+  </si>
+  <si>
+    <t>SNLGHT BERY&amp;LIME 675</t>
+  </si>
+  <si>
+    <t>20142277</t>
+  </si>
+  <si>
+    <t>MAMA LM GRN BTL 690</t>
+  </si>
+  <si>
+    <t>20135845</t>
+  </si>
+  <si>
+    <t>EKNOMI LIQ JR&amp;LMN650</t>
+  </si>
+  <si>
+    <t>10029632</t>
+  </si>
+  <si>
+    <t>STELLA ALAT MATIC</t>
+  </si>
+  <si>
+    <t>20105576</t>
+  </si>
+  <si>
+    <t>STELLA A/F SAKURA350</t>
+  </si>
+  <si>
+    <t>20142869</t>
+  </si>
+  <si>
+    <t>STELA A/F RJ AMPT350</t>
+  </si>
+  <si>
+    <t>10004032</t>
+  </si>
+  <si>
+    <t>VIXAL KUAT HARUM 700</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>10004034</t>
+  </si>
+  <si>
+    <t>VIXAL KMR MD KUAT720</t>
+  </si>
+  <si>
+    <t>10003359</t>
+  </si>
+  <si>
+    <t>WIPOL CEMARA BTL 730</t>
+  </si>
+  <si>
+    <t>10000955</t>
+  </si>
+  <si>
+    <t>PORSTEX N.PARFUM 1L</t>
+  </si>
+  <si>
+    <t>10018962</t>
+  </si>
+  <si>
+    <t>YURI PORSTEX OB.B700</t>
+  </si>
+  <si>
+    <t>10005246</t>
+  </si>
+  <si>
+    <t>WING PRCLN CLN BR750</t>
+  </si>
+  <si>
+    <t>20040315</t>
+  </si>
+  <si>
+    <t>IDM PORSELEN BTL 800</t>
+  </si>
+  <si>
+    <t>20015040</t>
+  </si>
+  <si>
+    <t>HARPIC TRIPLE ACT450</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20095746</t>
+  </si>
+  <si>
+    <t>HRPC PNG.KRK CTR 405</t>
+  </si>
+  <si>
+    <t>20042956</t>
+  </si>
+  <si>
+    <t>HARPIC PWR PLS CT450</t>
+  </si>
+  <si>
+    <t>10037275</t>
+  </si>
+  <si>
+    <t>SWALLOW KMPR BTR 300</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>20027997</t>
+  </si>
+  <si>
+    <t>IDM KAMPER NAPTLN150</t>
+  </si>
+  <si>
+    <t>20131886</t>
+  </si>
+  <si>
+    <t>IDM KMPR DEO SKRA 5S</t>
+  </si>
+  <si>
+    <t>20131885</t>
+  </si>
+  <si>
+    <t>IDM KMPR DEO CFFE 5S</t>
+  </si>
+  <si>
+    <t>20079794</t>
+  </si>
+  <si>
+    <t>IDM KAMPER TOILET 5S</t>
+  </si>
+  <si>
+    <t>20139963</t>
+  </si>
+  <si>
+    <t>LARISST CTRONELLA 5S</t>
+  </si>
+  <si>
+    <t>10000279</t>
+  </si>
+  <si>
+    <t>SWALLOW TLT.BALL 5'S</t>
+  </si>
+  <si>
+    <t>10000482</t>
+  </si>
+  <si>
+    <t>SWALLOW K/DEO BAL105</t>
+  </si>
+  <si>
+    <t>20017478</t>
+  </si>
+  <si>
+    <t>SWALLOW ORG S-160</t>
+  </si>
+  <si>
+    <t>20122471</t>
+  </si>
+  <si>
+    <t>STELLA LAV.GRD 42+13</t>
+  </si>
+  <si>
+    <t>20136409</t>
+  </si>
+  <si>
+    <t>STELLA BALI JAS42+13</t>
+  </si>
+  <si>
+    <t>20109616</t>
+  </si>
+  <si>
+    <t>STELLA CAFF.LATTE 42</t>
+  </si>
+  <si>
+    <t>20075791</t>
+  </si>
+  <si>
+    <t>STELLA POCKET ORG 10</t>
+  </si>
+  <si>
+    <t>20075798</t>
+  </si>
+  <si>
+    <t>STLLA POCKET PRPL 10</t>
+  </si>
+  <si>
+    <t>20091307</t>
+  </si>
+  <si>
+    <t>STELLA POCKET BLU 10</t>
+  </si>
+  <si>
+    <t>20138481</t>
+  </si>
+  <si>
+    <t>STELLA EXO.FRUIT 10G</t>
+  </si>
+  <si>
+    <t>20138482</t>
+  </si>
+  <si>
+    <t>STELLA LUX.FLOWR 10G</t>
+  </si>
+  <si>
+    <t>20105573</t>
+  </si>
+  <si>
+    <t>STELLA AF REF JPS160</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>20037058</t>
+  </si>
+  <si>
+    <t>STELLA AF REF FLW160</t>
+  </si>
+  <si>
+    <t>20036827</t>
+  </si>
+  <si>
+    <t>STELLA AF REF GRN160</t>
+  </si>
+  <si>
+    <t>20044100</t>
+  </si>
+  <si>
+    <t>STELLA AF REF APL160</t>
+  </si>
+  <si>
+    <t>20135485</t>
+  </si>
+  <si>
+    <t>STELLA AF REF BAL160</t>
+  </si>
+  <si>
+    <t>20046210</t>
+  </si>
+  <si>
+    <t>GLADE OCN ESCPE 146G</t>
+  </si>
+  <si>
+    <t>10023003</t>
+  </si>
+  <si>
+    <t>GLADE PNY&amp;BRY BLS 70</t>
+  </si>
+  <si>
+    <t>10023002</t>
+  </si>
+  <si>
+    <t>GLADE FRESH ONE EF70</t>
+  </si>
+  <si>
+    <t>20096642</t>
+  </si>
+  <si>
+    <t>IDM FRSHNS LEMON 50</t>
+  </si>
+  <si>
+    <t>20096641</t>
+  </si>
+  <si>
+    <t>IDM FRSHNS ORANGE 50</t>
+  </si>
+  <si>
+    <t>10005428</t>
+  </si>
+  <si>
+    <t>STELLA IN ONE ORG 42</t>
+  </si>
+  <si>
+    <t>10005427</t>
+  </si>
+  <si>
+    <t>STELLA IN ONE LMN 42</t>
+  </si>
+  <si>
+    <t>20134373</t>
+  </si>
+  <si>
+    <t>STELLA ALAT+REFILL25</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>20134374</t>
+  </si>
+  <si>
+    <t>STELLA ELCTRIC LAV25</t>
+  </si>
+  <si>
+    <t>10010232</t>
+  </si>
+  <si>
+    <t>KIWI LIQ.SHOE BLCK75</t>
+  </si>
+  <si>
+    <t>10007934</t>
+  </si>
+  <si>
+    <t>KIWI PASTE BLACK 45M</t>
+  </si>
+  <si>
+    <t>20012183</t>
+  </si>
+  <si>
+    <t>BAYGON BKR D.DRH 5'S</t>
+  </si>
+  <si>
+    <t>20014401</t>
+  </si>
+  <si>
+    <t>BYGON BKR JMB LVD 5S</t>
+  </si>
+  <si>
+    <t>20110145</t>
+  </si>
+  <si>
+    <t>VAPE NY.BK L.SMO5'S</t>
+  </si>
+  <si>
+    <t>20128711</t>
+  </si>
+  <si>
+    <t>AUTAN LOT.JRK&amp;LMN 50</t>
+  </si>
+  <si>
+    <t>20106983</t>
+  </si>
+  <si>
+    <t>AUTAN LOT.SAKURA 50</t>
+  </si>
+  <si>
+    <t>20054250</t>
+  </si>
+  <si>
+    <t>AUTAN REFRESH/S 100</t>
+  </si>
+  <si>
+    <t>20128713</t>
+  </si>
+  <si>
+    <t>SOFEL LOT.KRN/SMR 60</t>
+  </si>
+  <si>
+    <t>20078241</t>
+  </si>
+  <si>
+    <t>SOFFELL LOT.APEL 60G</t>
+  </si>
+  <si>
+    <t>10040202</t>
+  </si>
+  <si>
+    <t>SOFFELL A.NYMK K/J60</t>
+  </si>
+  <si>
+    <t>10037280</t>
+  </si>
+  <si>
+    <t>BAGUS KAPUR AJAIB</t>
+  </si>
+  <si>
+    <t>20109069</t>
+  </si>
+  <si>
+    <t>BAGUS LEM TIKUS PCS</t>
+  </si>
+  <si>
+    <t>10003479</t>
+  </si>
+  <si>
+    <t>GAJAH LEM TIKUS KT70</t>
+  </si>
+  <si>
+    <t>20139525</t>
+  </si>
+  <si>
+    <t>VAPE DORA LEM TIKUS</t>
+  </si>
+  <si>
+    <t>20022902</t>
+  </si>
+  <si>
+    <t>HIT SPRAY ORG 180</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>20064216</t>
+  </si>
+  <si>
+    <t>HIT INS.SPRY LILY180</t>
+  </si>
+  <si>
+    <t>20139144</t>
+  </si>
+  <si>
+    <t>HIT XPRES PINK BL.35</t>
+  </si>
+  <si>
+    <t>20131161</t>
+  </si>
+  <si>
+    <t>HIT REF XPRES APLE35</t>
+  </si>
+  <si>
+    <t>20095744</t>
+  </si>
+  <si>
+    <t>HIT REF EXPRT FRS 35</t>
+  </si>
+  <si>
+    <t>20039183</t>
+  </si>
+  <si>
+    <t>HIT ALAT+REF EXP APL</t>
+  </si>
+  <si>
+    <t>10034732</t>
+  </si>
+  <si>
+    <t>HIT MAT ELECTRK 48'S</t>
+  </si>
+  <si>
+    <t>10027329</t>
+  </si>
+  <si>
+    <t>HIT ALT NYAMUK ELC 5</t>
+  </si>
+  <si>
+    <t>20084568</t>
+  </si>
+  <si>
+    <t>VAPE LIQ.SKR BLOSM45</t>
+  </si>
+  <si>
+    <t>20008748</t>
+  </si>
+  <si>
+    <t>VAPE LIQUID REF 45ML</t>
+  </si>
+  <si>
+    <t>20023870</t>
+  </si>
+  <si>
+    <t>VAPE LIQUID ELEKTRIK</t>
+  </si>
+  <si>
+    <t>20030445</t>
+  </si>
+  <si>
+    <t>VAPE SPRAY 1XSMP ORG</t>
+  </si>
+  <si>
+    <t>20073974</t>
+  </si>
+  <si>
+    <t>VAPE SPRAY 1XSMP SKR</t>
+  </si>
+  <si>
+    <t>20124418</t>
+  </si>
+  <si>
+    <t>VAPE SWEET PWDR 200</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>20076987</t>
+  </si>
+  <si>
+    <t>BAYGON FLOW.GRDN 200</t>
+  </si>
+  <si>
+    <t>10015526</t>
+  </si>
+  <si>
+    <t>BAYGON SPRY LVND 750</t>
+  </si>
+  <si>
+    <t>20124346</t>
+  </si>
+  <si>
+    <t>BAYGON JPNSE&amp;PCH 600</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>20098605</t>
+  </si>
+  <si>
+    <t>BYGON SPRY CHR.BL600</t>
+  </si>
+  <si>
+    <t>10003272</t>
+  </si>
+  <si>
+    <t>BAYGON SPRY CITRS675</t>
+  </si>
+  <si>
+    <t>20071775</t>
+  </si>
+  <si>
+    <t>BAYGON FLO.GRDN 675</t>
+  </si>
+  <si>
+    <t>20139154</t>
+  </si>
+  <si>
+    <t>HIT COTTON PWD 600ML</t>
+  </si>
+  <si>
+    <t>20054151</t>
+  </si>
+  <si>
+    <t>HIT INS.SPRY LILY600</t>
+  </si>
+  <si>
+    <t>10005198</t>
+  </si>
+  <si>
+    <t>HIT INS.SPRAY ORG600</t>
+  </si>
+  <si>
+    <t>20109613</t>
+  </si>
+  <si>
+    <t>HIT SPRY.P/BLOSM 600</t>
+  </si>
+  <si>
+    <t>20080868</t>
+  </si>
+  <si>
+    <t>HIT FRESH CITRUS 600</t>
+  </si>
+  <si>
+    <t>20131365</t>
+  </si>
+  <si>
+    <t>HIT SPRY JPN.SKR 600</t>
+  </si>
+  <si>
+    <t>10034652</t>
+  </si>
+  <si>
+    <t>GLADE OCEAN ESCP 350</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>20139446</t>
+  </si>
+  <si>
+    <t>BAYGON CTRS FRSH 400</t>
+  </si>
+  <si>
+    <t>20128132</t>
+  </si>
+  <si>
+    <t>BAYGON FLO.GRDN 400</t>
+  </si>
+  <si>
+    <t>20135247</t>
+  </si>
+  <si>
+    <t>BAYGON FLRL.FNTSY500</t>
+  </si>
+  <si>
+    <t>20135248</t>
+  </si>
+  <si>
+    <t>BAYGON CHRRY BRRY500</t>
+  </si>
+  <si>
+    <t>20088715</t>
+  </si>
+  <si>
+    <t>HIT SPRAY LILY 400ML</t>
+  </si>
+  <si>
+    <t>20022498</t>
+  </si>
+  <si>
+    <t>HIT SPRAY ORG 400ML</t>
+  </si>
+  <si>
+    <t>20134237</t>
+  </si>
+  <si>
+    <t>HIT SPRY.P/BLOSM 400</t>
+  </si>
+  <si>
+    <t>20136130</t>
+  </si>
+  <si>
+    <t>VAPE FLO.BUBBLE 600</t>
+  </si>
+  <si>
+    <t>20124850</t>
+  </si>
+  <si>
+    <t>VAPE SPRY SWET PD600</t>
+  </si>
+  <si>
+    <t>20136134</t>
+  </si>
+  <si>
+    <t>VAPE CANDY FLO 600</t>
+  </si>
+  <si>
+    <t>10006651</t>
+  </si>
+  <si>
+    <t>VAPE FMK ORANGE 600</t>
+  </si>
+  <si>
+    <t>20142133</t>
+  </si>
+  <si>
+    <t>VAPE MILK TEA 600ML</t>
+  </si>
+  <si>
+    <t>20128374</t>
+  </si>
+  <si>
+    <t>LFEBUOY REF LIME 650</t>
+  </si>
+  <si>
+    <t>999</t>
+  </si>
+  <si>
     <t>20104950</t>
   </si>
   <si>
     <t>RINSO MLTO JP/PCH510</t>
   </si>
   <si>
-    <t>20093627</t>
-  </si>
-  <si>
-    <t>SKLN LQD SKR STRW500</t>
-  </si>
-  <si>
-    <t>20123818</t>
-  </si>
-  <si>
-    <t>SKLN LQD PROV LVD500</t>
-  </si>
-  <si>
-    <t>20091870</t>
-  </si>
-  <si>
-    <t>SKLN LQ WHT&amp;BRGHT500</t>
-  </si>
-  <si>
-    <t>20114428</t>
-  </si>
-  <si>
-    <t>SKLN LQD KOR CMLA500</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20141373</t>
-  </si>
-  <si>
-    <t>RINSO PW.CLN BTL 650</t>
-  </si>
-  <si>
-    <t>20141369</t>
-  </si>
-  <si>
-    <t>RINSO P.BRZE BTL 650</t>
-  </si>
-  <si>
-    <t>20131730</t>
-  </si>
-  <si>
-    <t>SYANG LIQ R/ROSE 700</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20132442</t>
-  </si>
-  <si>
-    <t>SYANG LIQ ORIGNAL700</t>
-  </si>
-  <si>
-    <t>20135849</t>
-  </si>
-  <si>
-    <t>LARIST SMR.BRZ 700ML</t>
-  </si>
-  <si>
-    <t>20139955</t>
-  </si>
-  <si>
-    <t>BU KRM JNHAE CB700ML</t>
-  </si>
-  <si>
-    <t>20120180</t>
-  </si>
-  <si>
-    <t>SO SOFT RS&amp;WTRLY 700</t>
-  </si>
-  <si>
-    <t>20121364</t>
-  </si>
-  <si>
-    <t>SO SOFT SKR BLSM 700</t>
-  </si>
-  <si>
-    <t>20135246</t>
-  </si>
-  <si>
-    <t>SO SOFT SWT PEONY700</t>
-  </si>
-  <si>
-    <t>20128720</t>
-  </si>
-  <si>
-    <t>SO SOFT FLO BRS 700</t>
-  </si>
-  <si>
-    <t>20140325</t>
-  </si>
-  <si>
-    <t>SO SOFT FLO LILY 700</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20133333</t>
-  </si>
-  <si>
-    <t>GENTLE GEN A/KRGT700</t>
-  </si>
-  <si>
-    <t>20141371</t>
-  </si>
-  <si>
-    <t>GNTLE GEN CMLLIA 700</t>
-  </si>
-  <si>
-    <t>20141372</t>
-  </si>
-  <si>
-    <t>GENTLE GEN LILAC 700</t>
-  </si>
-  <si>
-    <t>20135245</t>
-  </si>
-  <si>
-    <t>SO KLIN LIQ FRNCH700</t>
-  </si>
-  <si>
-    <t>20133798</t>
-  </si>
-  <si>
-    <t>SO KLIN LIQ EN.RS700</t>
-  </si>
-  <si>
-    <t>20139729</t>
-  </si>
-  <si>
-    <t>SOKLN GR.TEA&amp;JSM 700</t>
-  </si>
-  <si>
-    <t>20142134</t>
-  </si>
-  <si>
-    <t>SO KLN BLU PETAL 700</t>
-  </si>
-  <si>
-    <t>20142132</t>
-  </si>
-  <si>
-    <t>SO KLN MAISON DE 700</t>
-  </si>
-  <si>
-    <t>20113567</t>
-  </si>
-  <si>
-    <t>GENTLE GEN MR.BRZ700</t>
-  </si>
-  <si>
-    <t>20115959</t>
-  </si>
-  <si>
-    <t>GENTLE GEN FR.PE 700</t>
-  </si>
-  <si>
-    <t>20115958</t>
-  </si>
-  <si>
-    <t>GENTLE GEN PRS.G 700</t>
-  </si>
-  <si>
-    <t>20073805</t>
-  </si>
-  <si>
-    <t>SOKLN MGNLA&amp;BRES1.3</t>
-  </si>
-  <si>
-    <t>20041483</t>
-  </si>
-  <si>
-    <t>SO/KLN SOFT P/RS1.3</t>
-  </si>
-  <si>
-    <t>20140806</t>
-  </si>
-  <si>
-    <t>SKLN EDP FL.DELIS1.3</t>
-  </si>
-  <si>
-    <t>20140804</t>
-  </si>
-  <si>
-    <t>SKLN EDP FLR BLNC1.3</t>
-  </si>
-  <si>
-    <t>20091352</t>
-  </si>
-  <si>
-    <t>DAIA PWDR VLT PSN1.4</t>
-  </si>
-  <si>
-    <t>20052321</t>
-  </si>
-  <si>
-    <t>DAIA PWDR ROM/PNK1.4</t>
-  </si>
-  <si>
-    <t>20030446</t>
-  </si>
-  <si>
-    <t>DAIA PWDR PUTIH1.4KG</t>
-  </si>
-  <si>
-    <t>20121050</t>
-  </si>
-  <si>
-    <t>DAIA HJB CLN&amp;FRSH1.4</t>
-  </si>
-  <si>
-    <t>20142276</t>
-  </si>
-  <si>
-    <t>DAIA PWDR LLY&amp;JSM1.4</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>10014547</t>
-  </si>
-  <si>
-    <t>DAIA PWDR FLORAL1.4</t>
-  </si>
-  <si>
-    <t>20012007</t>
-  </si>
-  <si>
-    <t>DAIA PWDR PUTIH 725G</t>
-  </si>
-  <si>
-    <t>10005245</t>
-  </si>
-  <si>
-    <t>DAIA BBK FLORAL 800G</t>
-  </si>
-  <si>
-    <t>20053796</t>
-  </si>
-  <si>
-    <t>SKLN SFTG LVD&amp;LLY650</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20073499</t>
-  </si>
-  <si>
-    <t>SO KLN MGNL&amp;BRY 650G</t>
-  </si>
-  <si>
-    <t>20012188</t>
-  </si>
-  <si>
-    <t>SOKLN SOFTR ROSY 650</t>
-  </si>
-  <si>
-    <t>20061748</t>
-  </si>
-  <si>
-    <t>DAIA PWDR VLT PSN725</t>
-  </si>
-  <si>
-    <t>20036047</t>
-  </si>
-  <si>
-    <t>DAIA PWDR ROM/PNK725</t>
-  </si>
-  <si>
-    <t>20113809</t>
-  </si>
-  <si>
-    <t>OXYKLIN DTRG LIQ 700</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20129837</t>
-  </si>
-  <si>
-    <t>LARIST SPR.GRD 750ML</t>
-  </si>
-  <si>
-    <t>20097739</t>
-  </si>
-  <si>
-    <t>IDM DET.CAIR PCH 700</t>
-  </si>
-  <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20067586</t>
-  </si>
-  <si>
-    <t>SOKLIN LIQ.BM TOP700</t>
-  </si>
-  <si>
-    <t>20054610</t>
-  </si>
-  <si>
-    <t>RINSO LIQ FRONT 1.45</t>
-  </si>
-  <si>
-    <t>10030924</t>
-  </si>
-  <si>
-    <t>SOKLIN MTC F/LD 900G</t>
-  </si>
-  <si>
-    <t>20081448</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT H.SM 600</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20081449</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT P.DW 600</t>
-  </si>
-  <si>
-    <t>20104951</t>
-  </si>
-  <si>
-    <t>ROYALE HJB BLCK.V600</t>
-  </si>
-  <si>
-    <t>20091457</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT BS 600</t>
-  </si>
-  <si>
-    <t>20113101</t>
-  </si>
-  <si>
-    <t>ROYALE SWT FLORL 600</t>
-  </si>
-  <si>
-    <t>20128706</t>
-  </si>
-  <si>
-    <t>ROYALE LNVDR VNL 600</t>
-  </si>
-  <si>
-    <t>20113093</t>
-  </si>
-  <si>
-    <t>ROYALE SUNNY DAY 600</t>
-  </si>
-  <si>
-    <t>20142010</t>
-  </si>
-  <si>
-    <t>ROYALE MTCHA BLS 600</t>
-  </si>
-  <si>
-    <t>20128919</t>
-  </si>
-  <si>
-    <t>MOLTO SFTNR PURE 550</t>
-  </si>
-  <si>
-    <t>20094735</t>
-  </si>
-  <si>
-    <t>DOWNY SUNRISE 950</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>PT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20094733</t>
-  </si>
-  <si>
-    <t>DOWNY MYSTIQUE 900</t>
-  </si>
-  <si>
-    <t>20140221</t>
-  </si>
-  <si>
-    <t>DOWNY PASSION 875ML</t>
-  </si>
-  <si>
-    <t>20141324</t>
-  </si>
-  <si>
-    <t>DOWNY SUNSHINE 500ML</t>
-  </si>
-  <si>
-    <t>20141323</t>
-  </si>
-  <si>
-    <t>DOWNY MIDNIGHT 500ML</t>
-  </si>
-  <si>
-    <t>20080360</t>
-  </si>
-  <si>
-    <t>DOWNY MYSTIQUE 550ML</t>
-  </si>
-  <si>
-    <t>20080361</t>
-  </si>
-  <si>
-    <t>DOWNY PASSION 550ML</t>
-  </si>
-  <si>
-    <t>20074226</t>
-  </si>
-  <si>
-    <t>DOWNY SUN.FRSH 550</t>
-  </si>
-  <si>
-    <t>20139145</t>
-  </si>
-  <si>
-    <t>DOWNY MLKY TOUCH 500</t>
-  </si>
-  <si>
-    <t>20140003</t>
-  </si>
-  <si>
-    <t>RNSO PWD ROSE.F 1.44</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20093521</t>
-  </si>
-  <si>
-    <t>RINSO+MOLTO ESC1440G</t>
-  </si>
-  <si>
-    <t>20139609</t>
-  </si>
-  <si>
-    <t>RNSO JPN PEAC 1440G</t>
-  </si>
-  <si>
-    <t>20140002</t>
-  </si>
-  <si>
-    <t>RINSO PWD PURE 1440G</t>
-  </si>
-  <si>
-    <t>20064413</t>
-  </si>
-  <si>
-    <t>ATCK JAZ1 S/CNTA 1.5</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20064414</t>
-  </si>
-  <si>
-    <t>ATTACK JAZ1 P/SGR1.5</t>
-  </si>
-  <si>
-    <t>20130527</t>
-  </si>
-  <si>
-    <t>ATTACK DET+SF RB 1.4</t>
-  </si>
-  <si>
-    <t>20138108</t>
-  </si>
-  <si>
-    <t>JAZ 1 PRPL BLS 1.4KG</t>
-  </si>
-  <si>
-    <t>20071827</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD ROSE 700</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20085113</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD PRFM 700</t>
-  </si>
-  <si>
-    <t>20105968</t>
-  </si>
-  <si>
-    <t>RNSO PWD JPN PC 700G</t>
-  </si>
-  <si>
-    <t>20074992</t>
-  </si>
-  <si>
-    <t>BUKRIM OXY/K VIOL700</t>
-  </si>
-  <si>
-    <t>20119238</t>
-  </si>
-  <si>
-    <t>TOTAL DET.PERFUME750</t>
-  </si>
-  <si>
-    <t>20131516</t>
-  </si>
-  <si>
-    <t>LARIST DET.FRS BT450</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20113183</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD ROSE 380</t>
-  </si>
-  <si>
-    <t>20121372</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD PRFM 380</t>
-  </si>
-  <si>
-    <t>20128719</t>
-  </si>
-  <si>
-    <t>SOKLIN LVD&amp;LILY 375G</t>
-  </si>
-  <si>
-    <t>20042466</t>
-  </si>
-  <si>
-    <t>DAIA PWDR ROM/PNK390</t>
-  </si>
-  <si>
-    <t>20139595</t>
-  </si>
-  <si>
-    <t>MOLTO TRKA BDD 3X300</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20133398</t>
-  </si>
-  <si>
-    <t>TRKA PURE 300ML</t>
-  </si>
-  <si>
-    <t>10011440</t>
-  </si>
-  <si>
-    <t>RAPIKA LVDR SPLAS300</t>
-  </si>
-  <si>
-    <t>20084780</t>
-  </si>
-  <si>
-    <t>RAPIKA GOLD 250ML</t>
-  </si>
-  <si>
-    <t>20093193</t>
-  </si>
-  <si>
-    <t>RAPIKA PINK SKR 300</t>
-  </si>
-  <si>
-    <t>20138071</t>
-  </si>
-  <si>
-    <t>KISPRAY KASTURI 280</t>
-  </si>
-  <si>
-    <t>20074721</t>
-  </si>
-  <si>
-    <t>KISPRAY GLM.GOLD 280</t>
-  </si>
-  <si>
-    <t>20116685</t>
-  </si>
-  <si>
-    <t>KISPRAY ELG.SAPH 200</t>
-  </si>
-  <si>
-    <t>20032250</t>
-  </si>
-  <si>
-    <t>KISPRAY VIOLET PC280</t>
-  </si>
-  <si>
-    <t>20000980</t>
-  </si>
-  <si>
-    <t>KISPRAY VIOLET 318ML</t>
-  </si>
-  <si>
-    <t>20138470</t>
-  </si>
-  <si>
-    <t>SO KLN PWNG RED 1.7L</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>10005803</t>
-  </si>
-  <si>
-    <t>SOKLIN PWNGI RED 780</t>
-  </si>
-  <si>
-    <t>10007389</t>
-  </si>
-  <si>
-    <t>SOKLIN PWNGI PINK780</t>
-  </si>
-  <si>
-    <t>10008104</t>
-  </si>
-  <si>
-    <t>SO KLIN PWG BLUE 780</t>
-  </si>
-  <si>
-    <t>20108418</t>
-  </si>
-  <si>
-    <t>SOKLIN PWG HJB GR780</t>
-  </si>
-  <si>
-    <t>10005802</t>
-  </si>
-  <si>
-    <t>SOKLIN PEWANGI VL780</t>
-  </si>
-  <si>
-    <t>20141985</t>
-  </si>
-  <si>
-    <t>SO KLN TROP SUMR 780</t>
-  </si>
-  <si>
-    <t>20134526</t>
-  </si>
-  <si>
-    <t>SOKLIN PWG COT.FN780</t>
-  </si>
-  <si>
-    <t>20129370</t>
-  </si>
-  <si>
-    <t>MOLTO MORNING FRS550</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20129160</t>
-  </si>
-  <si>
-    <t>MOLTO LUXURY PRF 650</t>
-  </si>
-  <si>
-    <t>20087464</t>
-  </si>
-  <si>
-    <t>IDM PWNG PINK.PAS720</t>
-  </si>
-  <si>
-    <t>20137582</t>
-  </si>
-  <si>
-    <t>IDM PWNG ROM.AURA720</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20137581</t>
-  </si>
-  <si>
-    <t>IDM PWNG EXO.BLUE720</t>
-  </si>
-  <si>
-    <t>20020245</t>
-  </si>
-  <si>
-    <t>MOLTO PWNGI BLUE 765</t>
-  </si>
-  <si>
-    <t>20020226</t>
-  </si>
-  <si>
-    <t>MOLTO PWNGI PINK 765</t>
-  </si>
-  <si>
-    <t>20106821</t>
-  </si>
-  <si>
-    <t>MOLTO PURPLE 765ML</t>
-  </si>
-  <si>
-    <t>20142219</t>
-  </si>
-  <si>
-    <t>MLTO GNTL FRSH 765ML</t>
-  </si>
-  <si>
-    <t>20135847</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT SUMMR600</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>20135846</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT SPRNG600</t>
-  </si>
-  <si>
-    <t>20014403</t>
-  </si>
-  <si>
-    <t>BAYCLIN REGLR 1000ML</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>20082581</t>
-  </si>
-  <si>
-    <t>VANISH CAIR WHT 425</t>
-  </si>
-  <si>
-    <t>20052662</t>
-  </si>
-  <si>
-    <t>VANISH CAIR PCH 425</t>
-  </si>
-  <si>
-    <t>20079788</t>
-  </si>
-  <si>
-    <t>PROCLIN PCH 400ML</t>
-  </si>
-  <si>
-    <t>20093919</t>
-  </si>
-  <si>
-    <t>IDM PURPOSE CLN 400</t>
-  </si>
-  <si>
-    <t>10014263</t>
-  </si>
-  <si>
-    <t>WIPOL KARBOL CMR 720</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>20001645</t>
-  </si>
-  <si>
-    <t>WIPOL KARBOL LMN 720</t>
-  </si>
-  <si>
-    <t>20090066</t>
-  </si>
-  <si>
-    <t>WIPOL SRH + JRK 720</t>
-  </si>
-  <si>
-    <t>20122478</t>
-  </si>
-  <si>
-    <t>WIPOL CITRUS FRS 390</t>
-  </si>
-  <si>
-    <t>20023111</t>
-  </si>
-  <si>
-    <t>SOS KARBOL CLS PN725</t>
-  </si>
-  <si>
-    <t>10013107</t>
-  </si>
-  <si>
-    <t>SUPERSOL PINE 720G</t>
-  </si>
-  <si>
-    <t>20104030</t>
-  </si>
-  <si>
-    <t>SUPER SOL SEREH720G</t>
-  </si>
-  <si>
     <t>20132664</t>
   </si>
   <si>
     <t>VIXAL KUAT SEGAR 600</t>
-  </si>
-  <si>
-    <t>10004612</t>
-  </si>
-  <si>
-    <t>SOS P.LNT ORANGE 700</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10004610</t>
-  </si>
-  <si>
-    <t>SOS P/LT APLL REF700</t>
-  </si>
-  <si>
-    <t>10010480</t>
-  </si>
-  <si>
-    <t>SPR PELL FRS.APEL760</t>
-  </si>
-  <si>
-    <t>20121373</t>
-  </si>
-  <si>
-    <t>SPR PELL AB CTRS 500</t>
-  </si>
-  <si>
-    <t>20137408</t>
-  </si>
-  <si>
-    <t>SPR PELL SAKURA 740</t>
-  </si>
-  <si>
-    <t>20001407</t>
-  </si>
-  <si>
-    <t>IDM P'LANTAI LAV 800</t>
-  </si>
-  <si>
-    <t>20001402</t>
-  </si>
-  <si>
-    <t>IDM P'LANTAI APL 800</t>
-  </si>
-  <si>
-    <t>20028779</t>
-  </si>
-  <si>
-    <t>IDM KRBOL WNG650(BR)</t>
-  </si>
-  <si>
-    <t>20089486</t>
-  </si>
-  <si>
-    <t>IDM KRBL SRH CTR 650</t>
-  </si>
-  <si>
-    <t>20128125</t>
-  </si>
-  <si>
-    <t>IDM PURPOSE CLN 375</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>20027963</t>
-  </si>
-  <si>
-    <t>IDM PMBERSH KACA 400</t>
-  </si>
-  <si>
-    <t>10003706</t>
-  </si>
-  <si>
-    <t>MR.MUSCLE ORGNL 400</t>
-  </si>
-  <si>
-    <t>10012548</t>
-  </si>
-  <si>
-    <t>SOKLIN RLX/LAV RF770</t>
-  </si>
-  <si>
-    <t>10003646</t>
-  </si>
-  <si>
-    <t>SO KLIN P/L APPLE770</t>
-  </si>
-  <si>
-    <t>10003645</t>
-  </si>
-  <si>
-    <t>SO KLIN P/L LMN 780</t>
-  </si>
-  <si>
-    <t>20101095</t>
-  </si>
-  <si>
-    <t>SO KLN LNT SEREH 770</t>
-  </si>
-  <si>
-    <t>20131223</t>
-  </si>
-  <si>
-    <t>SO KLN LNT CT.GRD700</t>
-  </si>
-  <si>
-    <t>20141956</t>
-  </si>
-  <si>
-    <t>EKONOMI NANAS 920G</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>20136124</t>
-  </si>
-  <si>
-    <t>EKNOMI LIQ N&amp;JN 675G</t>
-  </si>
-  <si>
-    <t>20092331</t>
-  </si>
-  <si>
-    <t>EKONOMI LIQ JR.NP650</t>
-  </si>
-  <si>
-    <t>20123812</t>
-  </si>
-  <si>
-    <t>EKONOMI LQ.SEREH 650</t>
-  </si>
-  <si>
-    <t>20107240</t>
-  </si>
-  <si>
-    <t>EKONOMI LIQ.SW&amp;JR650</t>
-  </si>
-  <si>
-    <t>20129722</t>
-  </si>
-  <si>
-    <t>BUKRIM LIQ.JRK NP550</t>
-  </si>
-  <si>
-    <t>20138518</t>
-  </si>
-  <si>
-    <t>KILAU NIPIS 630ML</t>
-  </si>
-  <si>
-    <t>20131788</t>
-  </si>
-  <si>
-    <t>MAMA LMN JR.NPS 950</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>20142275</t>
-  </si>
-  <si>
-    <t>MAMA LIME CHARCO 950</t>
-  </si>
-  <si>
-    <t>20034450</t>
-  </si>
-  <si>
-    <t>MAMA/L JERUK NPS 650</t>
-  </si>
-  <si>
-    <t>10004067</t>
-  </si>
-  <si>
-    <t>MAMA/L PCH LEMON 650</t>
-  </si>
-  <si>
-    <t>20099424</t>
-  </si>
-  <si>
-    <t>MAMA LIME CHARCO 650</t>
-  </si>
-  <si>
-    <t>20052031</t>
-  </si>
-  <si>
-    <t>MAMA LIME GRN TEA650</t>
-  </si>
-  <si>
-    <t>10004068</t>
-  </si>
-  <si>
-    <t>MAMA LIME POUCH 650</t>
-  </si>
-  <si>
-    <t>20134303</t>
-  </si>
-  <si>
-    <t>MAMA/L YUZU+J/NPS650</t>
-  </si>
-  <si>
-    <t>20090067</t>
-  </si>
-  <si>
-    <t>SNLGHT MINT A.BAU600</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>20086172</t>
-  </si>
-  <si>
-    <t>SNLIGHT MND.ORGE 600</t>
-  </si>
-  <si>
-    <t>20112492</t>
-  </si>
-  <si>
-    <t>SUNLIGHT JRK NPS400G</t>
-  </si>
-  <si>
-    <t>20128374</t>
-  </si>
-  <si>
-    <t>LFEBUOY REF LIME 650</t>
-  </si>
-  <si>
-    <t>20134576</t>
-  </si>
-  <si>
-    <t>LFEBUOY REF LEMON650</t>
-  </si>
-  <si>
-    <t>20141345</t>
-  </si>
-  <si>
-    <t>LARISST S/PCC PRG650</t>
-  </si>
-  <si>
-    <t>20073425</t>
-  </si>
-  <si>
-    <t>IDM P.PRNG JRK.N 650</t>
-  </si>
-  <si>
-    <t>20141204</t>
-  </si>
-  <si>
-    <t>IDM P.PRG JR.NPS 950</t>
-  </si>
-  <si>
-    <t>20112491</t>
-  </si>
-  <si>
-    <t>SNLIGHT LIME PCH 910</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>20139728</t>
-  </si>
-  <si>
-    <t>SNLGHT BIO BLBR 870G</t>
-  </si>
-  <si>
-    <t>10005482</t>
-  </si>
-  <si>
-    <t>SNLIGHT LIME PCH 660</t>
-  </si>
-  <si>
-    <t>20135144</t>
-  </si>
-  <si>
-    <t>SNLGHT BIO NATURE600</t>
-  </si>
-  <si>
-    <t>10003498</t>
-  </si>
-  <si>
-    <t>CLEAR PUMP ORIGNL500</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>10013205</t>
-  </si>
-  <si>
-    <t>SUNLIGHT J/NIPIS.750</t>
-  </si>
-  <si>
-    <t>20139947</t>
-  </si>
-  <si>
-    <t>SNLGHT BIO BLBR 675G</t>
-  </si>
-  <si>
-    <t>20139948</t>
-  </si>
-  <si>
-    <t>SNLGHT BERY&amp;LIME 675</t>
-  </si>
-  <si>
-    <t>20142277</t>
-  </si>
-  <si>
-    <t>MAMA LM GRN BTL 690</t>
-  </si>
-  <si>
-    <t>20135845</t>
-  </si>
-  <si>
-    <t>EKNOMI LIQ JR&amp;LMN650</t>
-  </si>
-  <si>
-    <t>10029632</t>
-  </si>
-  <si>
-    <t>STELLA ALAT MATIC</t>
-  </si>
-  <si>
-    <t>20105576</t>
-  </si>
-  <si>
-    <t>STELLA A/F SAKURA350</t>
-  </si>
-  <si>
-    <t>20142869</t>
-  </si>
-  <si>
-    <t>STELA A/F RJ AMPT350</t>
-  </si>
-  <si>
-    <t>10004032</t>
-  </si>
-  <si>
-    <t>VIXAL KUAT HARUM 720</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>10004034</t>
-  </si>
-  <si>
-    <t>VIXAL KMR MD KUAT720</t>
-  </si>
-  <si>
-    <t>10003359</t>
-  </si>
-  <si>
-    <t>WIPOL CEMARA BTL 730</t>
-  </si>
-  <si>
-    <t>10000955</t>
-  </si>
-  <si>
-    <t>PORSTEX N.PARFUM 1L</t>
-  </si>
-  <si>
-    <t>10018962</t>
-  </si>
-  <si>
-    <t>YURI PORSTEX OB.B700</t>
-  </si>
-  <si>
-    <t>10005246</t>
-  </si>
-  <si>
-    <t>WING PRCLN CLN BR750</t>
-  </si>
-  <si>
-    <t>20040315</t>
-  </si>
-  <si>
-    <t>IDM PORSELEN BTL 800</t>
-  </si>
-  <si>
-    <t>20015040</t>
-  </si>
-  <si>
-    <t>HARPIC TRIPLE ACT450</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20095746</t>
-  </si>
-  <si>
-    <t>HRPC PNG.KRK CTR 405</t>
-  </si>
-  <si>
-    <t>20042956</t>
-  </si>
-  <si>
-    <t>HARPIC PWR PLS CT450</t>
-  </si>
-  <si>
-    <t>10037275</t>
-  </si>
-  <si>
-    <t>SWALLOW KMPR BTR 300</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>20027997</t>
-  </si>
-  <si>
-    <t>IDM KAMPER NAPTLN150</t>
-  </si>
-  <si>
-    <t>20131886</t>
-  </si>
-  <si>
-    <t>IDM KMPR DEO SKRA 5S</t>
-  </si>
-  <si>
-    <t>20131885</t>
-  </si>
-  <si>
-    <t>IDM KMPR DEO CFFE 5S</t>
-  </si>
-  <si>
-    <t>20079794</t>
-  </si>
-  <si>
-    <t>IDM KAMPER TOILET 5S</t>
-  </si>
-  <si>
-    <t>20139963</t>
-  </si>
-  <si>
-    <t>LARISST CTRONELLA 5S</t>
-  </si>
-  <si>
-    <t>10000279</t>
-  </si>
-  <si>
-    <t>SWALLOW TLT.BALL 5'S</t>
-  </si>
-  <si>
-    <t>10000482</t>
-  </si>
-  <si>
-    <t>SWALLOW K/DEO BAL105</t>
-  </si>
-  <si>
-    <t>20017478</t>
-  </si>
-  <si>
-    <t>SWALLOW ORG S-160</t>
-  </si>
-  <si>
-    <t>20122471</t>
-  </si>
-  <si>
-    <t>STELLA LAV.GRD 42+13</t>
-  </si>
-  <si>
-    <t>20136409</t>
-  </si>
-  <si>
-    <t>STELLA BALI JAS42+13</t>
-  </si>
-  <si>
-    <t>20109616</t>
-  </si>
-  <si>
-    <t>STELLA CAFF.LATTE 42</t>
-  </si>
-  <si>
-    <t>20075791</t>
-  </si>
-  <si>
-    <t>STELLA POCKET ORG 10</t>
-  </si>
-  <si>
-    <t>20075798</t>
-  </si>
-  <si>
-    <t>STLLA POCKET PRPL 10</t>
-  </si>
-  <si>
-    <t>20091307</t>
-  </si>
-  <si>
-    <t>STELLA POCKET BLU 10</t>
-  </si>
-  <si>
-    <t>20138481</t>
-  </si>
-  <si>
-    <t>STELLA EXO.FRUIT 10G</t>
-  </si>
-  <si>
-    <t>20138482</t>
-  </si>
-  <si>
-    <t>STELLA LUX.FLOWR 10G</t>
-  </si>
-  <si>
-    <t>20105573</t>
-  </si>
-  <si>
-    <t>STELLA AF REF JPS160</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>20037058</t>
-  </si>
-  <si>
-    <t>STELLA AF REF FLW160</t>
-  </si>
-  <si>
-    <t>20036827</t>
-  </si>
-  <si>
-    <t>STELLA AF REF GRN160</t>
-  </si>
-  <si>
-    <t>20044100</t>
-  </si>
-  <si>
-    <t>STELLA AF REF APL160</t>
-  </si>
-  <si>
-    <t>20135485</t>
-  </si>
-  <si>
-    <t>STELLA AF REF BAL160</t>
-  </si>
-  <si>
-    <t>20046210</t>
-  </si>
-  <si>
-    <t>GLADE OCN ESCPE 146G</t>
-  </si>
-  <si>
-    <t>10023003</t>
-  </si>
-  <si>
-    <t>GLADE PNY&amp;BRY BLS 70</t>
-  </si>
-  <si>
-    <t>10023002</t>
-  </si>
-  <si>
-    <t>GLADE FRESH ONE EF70</t>
-  </si>
-  <si>
-    <t>20096642</t>
-  </si>
-  <si>
-    <t>IDM FRSHNS LEMON 50</t>
-  </si>
-  <si>
-    <t>20096641</t>
-  </si>
-  <si>
-    <t>IDM FRSHNS ORANGE 50</t>
-  </si>
-  <si>
-    <t>10005428</t>
-  </si>
-  <si>
-    <t>STELLA IN ONE ORG 42</t>
-  </si>
-  <si>
-    <t>10005427</t>
-  </si>
-  <si>
-    <t>STELLA IN ONE LMN 42</t>
-  </si>
-  <si>
-    <t>20134373</t>
-  </si>
-  <si>
-    <t>STELLA ALAT+REFILL25</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>20134374</t>
-  </si>
-  <si>
-    <t>STELLA ELCTRIC LAV25</t>
-  </si>
-  <si>
-    <t>10010232</t>
-  </si>
-  <si>
-    <t>KIWI LIQ.SHOE BLCK75</t>
-  </si>
-  <si>
-    <t>10007934</t>
-  </si>
-  <si>
-    <t>KIWI PASTE BLACK 45M</t>
-  </si>
-  <si>
-    <t>20012183</t>
-  </si>
-  <si>
-    <t>BAYGON BKR D.DRH 5'S</t>
-  </si>
-  <si>
-    <t>20014401</t>
-  </si>
-  <si>
-    <t>BYGON BKR JMB LVD 5S</t>
-  </si>
-  <si>
-    <t>20110145</t>
-  </si>
-  <si>
-    <t>VAPE NY.BK L.SMO5'S</t>
-  </si>
-  <si>
-    <t>20128711</t>
-  </si>
-  <si>
-    <t>AUTAN LOT.JRK&amp;LMN 50</t>
-  </si>
-  <si>
-    <t>20106983</t>
-  </si>
-  <si>
-    <t>AUTAN LOT.SAKURA 50</t>
-  </si>
-  <si>
-    <t>20054250</t>
-  </si>
-  <si>
-    <t>AUTAN REFRESH/S 100</t>
-  </si>
-  <si>
-    <t>20128713</t>
-  </si>
-  <si>
-    <t>SOFEL LOT.KRN/SMR 60</t>
-  </si>
-  <si>
-    <t>20078241</t>
-  </si>
-  <si>
-    <t>SOFFELL LOT.APEL 60G</t>
-  </si>
-  <si>
-    <t>10040202</t>
-  </si>
-  <si>
-    <t>SOFFELL A.NYMK K/J60</t>
-  </si>
-  <si>
-    <t>10037280</t>
-  </si>
-  <si>
-    <t>BAGUS KAPUR AJAIB</t>
-  </si>
-  <si>
-    <t>20109069</t>
-  </si>
-  <si>
-    <t>BAGUS LEM TIKUS PCS</t>
-  </si>
-  <si>
-    <t>10003479</t>
-  </si>
-  <si>
-    <t>GAJAH LEM TIKUS KT70</t>
-  </si>
-  <si>
-    <t>20139525</t>
-  </si>
-  <si>
-    <t>VAPE DORA LEM TIKUS</t>
-  </si>
-  <si>
-    <t>20022902</t>
-  </si>
-  <si>
-    <t>HIT SPRAY ORG 180</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>20064216</t>
-  </si>
-  <si>
-    <t>HIT INS.SPRY LILY180</t>
-  </si>
-  <si>
-    <t>20139144</t>
-  </si>
-  <si>
-    <t>HIT XPRES PINK BL.35</t>
-  </si>
-  <si>
-    <t>20131161</t>
-  </si>
-  <si>
-    <t>HIT REF XPRES APLE35</t>
-  </si>
-  <si>
-    <t>20095744</t>
-  </si>
-  <si>
-    <t>HIT REF EXPRT FRS 35</t>
-  </si>
-  <si>
-    <t>20039183</t>
-  </si>
-  <si>
-    <t>HIT ALAT+REF EXP APL</t>
-  </si>
-  <si>
-    <t>10034732</t>
-  </si>
-  <si>
-    <t>HIT MAT ELECTRK 48'S</t>
-  </si>
-  <si>
-    <t>10027329</t>
-  </si>
-  <si>
-    <t>HIT ALT NYAMUK ELC 5</t>
-  </si>
-  <si>
-    <t>20084568</t>
-  </si>
-  <si>
-    <t>VAPE LIQ.SKR BLOSM45</t>
-  </si>
-  <si>
-    <t>20008748</t>
-  </si>
-  <si>
-    <t>VAPE LIQUID REF 45ML</t>
-  </si>
-  <si>
-    <t>20023870</t>
-  </si>
-  <si>
-    <t>VAPE LIQUID ELEKTRIK</t>
-  </si>
-  <si>
-    <t>20030445</t>
-  </si>
-  <si>
-    <t>VAPE SPRAY 1XSMP ORG</t>
-  </si>
-  <si>
-    <t>20073974</t>
-  </si>
-  <si>
-    <t>VAPE SPRAY 1XSMP SKR</t>
-  </si>
-  <si>
-    <t>20124418</t>
-  </si>
-  <si>
-    <t>VAPE SWEET PWDR 200</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>20076987</t>
-  </si>
-  <si>
-    <t>BAYGON FLOW.GRDN 200</t>
-  </si>
-  <si>
-    <t>10015526</t>
-  </si>
-  <si>
-    <t>BAYGON SPRY LVND 750</t>
-  </si>
-  <si>
-    <t>20124346</t>
-  </si>
-  <si>
-    <t>BAYGON JPNSE&amp;PCH 600</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20098605</t>
-  </si>
-  <si>
-    <t>BYGON SPRY CHR.BL600</t>
-  </si>
-  <si>
-    <t>10003272</t>
-  </si>
-  <si>
-    <t>BAYGON SPRY CITRS675</t>
-  </si>
-  <si>
-    <t>20071775</t>
-  </si>
-  <si>
-    <t>BAYGON FLO.GRDN 675</t>
-  </si>
-  <si>
-    <t>20139154</t>
-  </si>
-  <si>
-    <t>HIT COTTON PWD 600ML</t>
-  </si>
-  <si>
-    <t>20054151</t>
-  </si>
-  <si>
-    <t>HIT INS.SPRY LILY600</t>
-  </si>
-  <si>
-    <t>10005198</t>
-  </si>
-  <si>
-    <t>HIT INS.SPRAY ORG600</t>
-  </si>
-  <si>
-    <t>20109613</t>
-  </si>
-  <si>
-    <t>HIT SPRY.P/BLOSM 600</t>
-  </si>
-  <si>
-    <t>20080868</t>
-  </si>
-  <si>
-    <t>HIT FRESH CITRUS 600</t>
-  </si>
-  <si>
-    <t>20131365</t>
-  </si>
-  <si>
-    <t>HIT SPRY JPN.SKR 600</t>
-  </si>
-  <si>
-    <t>10034652</t>
-  </si>
-  <si>
-    <t>GLADE OCEAN ESCP 350</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>20139446</t>
-  </si>
-  <si>
-    <t>BAYGON CTRS FRSH 400</t>
-  </si>
-  <si>
-    <t>20128132</t>
-  </si>
-  <si>
-    <t>BAYGON FLO.GRDN 400</t>
-  </si>
-  <si>
-    <t>20135247</t>
-  </si>
-  <si>
-    <t>BAYGON FLRL.FNTSY500</t>
-  </si>
-  <si>
-    <t>20135248</t>
-  </si>
-  <si>
-    <t>BAYGON CHRRY BRRY500</t>
-  </si>
-  <si>
-    <t>20088715</t>
-  </si>
-  <si>
-    <t>HIT SPRAY LILY 400ML</t>
-  </si>
-  <si>
-    <t>20022498</t>
-  </si>
-  <si>
-    <t>HIT SPRAY ORG 400ML</t>
-  </si>
-  <si>
-    <t>20134237</t>
-  </si>
-  <si>
-    <t>HIT SPRY.P/BLOSM 400</t>
-  </si>
-  <si>
-    <t>20136130</t>
-  </si>
-  <si>
-    <t>VAPE FLO.BUBBLE 600</t>
-  </si>
-  <si>
-    <t>20124850</t>
-  </si>
-  <si>
-    <t>VAPE SPRY SWET PD600</t>
-  </si>
-  <si>
-    <t>20136134</t>
-  </si>
-  <si>
-    <t>VAPE CANDY FLO 600</t>
-  </si>
-  <si>
-    <t>10006651</t>
-  </si>
-  <si>
-    <t>VAPE FMK ORANGE 600</t>
-  </si>
-  <si>
-    <t>20142133</t>
-  </si>
-  <si>
-    <t>VAPE MILK TEA 600ML</t>
   </si>
 </sst>
 </file>
@@ -2356,13 +2380,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F300"/>
+  <dimension ref="A1:F303"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="5" width="4" customWidth="1"/>
+    <col min="4" max="4" width="5" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2803,7 +2828,7 @@
         <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -5397,33 +5422,33 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>21</v>
+        <v>339</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D153" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>340</v>
-      </c>
       <c r="E153" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -5437,13 +5462,13 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>294</v>
+        <v>21</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -5457,10 +5482,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>21</v>
@@ -5477,13 +5502,13 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -5497,13 +5522,13 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>15</v>
+        <v>160</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -5517,10 +5542,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>160</v>
@@ -5537,10 +5562,10 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>160</v>
@@ -5557,10 +5582,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>160</v>
@@ -5577,10 +5602,10 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>160</v>
@@ -5588,19 +5613,19 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D162" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>360</v>
-      </c>
       <c r="E162" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>160</v>
@@ -5617,13 +5642,13 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>160</v>
+        <v>94</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -5637,13 +5662,13 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -5657,10 +5682,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5677,10 +5702,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5697,10 +5722,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5717,10 +5742,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5737,10 +5762,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5748,22 +5773,22 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D170" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>377</v>
-      </c>
       <c r="E170" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5777,13 +5802,13 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5797,10 +5822,10 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5817,10 +5842,10 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5837,10 +5862,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5857,13 +5882,13 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5877,30 +5902,30 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D177" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>392</v>
-      </c>
       <c r="E177" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5917,10 +5942,10 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5937,10 +5962,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5957,10 +5982,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5977,10 +6002,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5997,10 +6022,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -6017,13 +6042,13 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6037,33 +6062,33 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D185" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>409</v>
-      </c>
       <c r="E185" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>21</v>
+        <v>249</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -6077,13 +6102,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>249</v>
+        <v>21</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -6097,30 +6122,30 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>21</v>
+        <v>414</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>21</v>
@@ -6128,39 +6153,39 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>21</v>
+        <v>160</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>160</v>
@@ -6168,19 +6193,19 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>160</v>
@@ -6188,39 +6213,39 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>160</v>
+        <v>21</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B193" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D193" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="C193" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>426</v>
-      </c>
       <c r="E193" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>21</v>
@@ -6228,19 +6253,19 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>21</v>
@@ -6248,39 +6273,39 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>21</v>
@@ -6288,16 +6313,16 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E197" s="1" t="s">
         <v>4</v>
@@ -6308,16 +6333,16 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D198" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="B198" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="C198" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D198" s="1" t="s">
-        <v>435</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>8</v>
@@ -6328,16 +6353,16 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>11</v>
@@ -6348,16 +6373,16 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>14</v>
@@ -6368,16 +6393,16 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>18</v>
@@ -6388,16 +6413,16 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>32</v>
@@ -6408,16 +6433,16 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>35</v>
@@ -6428,56 +6453,56 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>70</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E205" s="1" t="s">
         <v>135</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>4</v>
@@ -6488,16 +6513,16 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D207" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="B207" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>454</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>8</v>
@@ -6508,16 +6533,16 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>11</v>
@@ -6528,16 +6553,16 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>14</v>
@@ -6548,16 +6573,16 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>18</v>
@@ -6568,16 +6593,16 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>32</v>
@@ -6588,16 +6613,16 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>35</v>
@@ -6608,36 +6633,36 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>70</v>
@@ -6648,36 +6673,36 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E215" s="1" t="s">
         <v>135</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>4</v>
@@ -6688,16 +6713,16 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D217" s="1" t="s">
         <v>477</v>
-      </c>
-      <c r="B217" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="C217" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D217" s="1" t="s">
-        <v>476</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>8</v>
@@ -6708,16 +6733,16 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E218" s="1" t="s">
         <v>11</v>
@@ -6728,16 +6753,16 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>14</v>
@@ -6748,16 +6773,16 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>18</v>
@@ -6768,16 +6793,16 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>32</v>
@@ -6788,16 +6813,16 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>35</v>
@@ -6808,16 +6833,16 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>38</v>
@@ -6828,16 +6853,16 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>70</v>
@@ -6848,16 +6873,16 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>135</v>
@@ -6868,16 +6893,16 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>144</v>
@@ -6888,16 +6913,16 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>155</v>
@@ -6908,16 +6933,16 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>169</v>
@@ -6928,16 +6953,16 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>169</v>
@@ -6948,16 +6973,16 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>169</v>
@@ -6968,16 +6993,16 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>169</v>
@@ -6988,16 +7013,16 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>169</v>
@@ -7008,36 +7033,36 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D234" s="1" t="s">
         <v>512</v>
-      </c>
-      <c r="B234" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="C234" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D234" s="1" t="s">
-        <v>511</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>8</v>
@@ -7048,16 +7073,16 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>11</v>
@@ -7068,16 +7093,16 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>14</v>
@@ -7088,16 +7113,16 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>18</v>
@@ -7108,16 +7133,16 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>32</v>
@@ -7128,16 +7153,16 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>35</v>
@@ -7148,16 +7173,16 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E240" s="1" t="s">
         <v>38</v>
@@ -7168,16 +7193,16 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E241" s="1" t="s">
         <v>70</v>
@@ -7188,16 +7213,16 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E242" s="1" t="s">
         <v>135</v>
@@ -7208,16 +7233,16 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E243" s="1" t="s">
         <v>144</v>
@@ -7228,16 +7253,16 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E244" s="1" t="s">
         <v>155</v>
@@ -7248,16 +7273,16 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E245" s="1" t="s">
         <v>4</v>
@@ -7268,16 +7293,16 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D246" s="1" t="s">
         <v>537</v>
-      </c>
-      <c r="B246" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="C246" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D246" s="1" t="s">
-        <v>536</v>
       </c>
       <c r="E246" s="1" t="s">
         <v>8</v>
@@ -7288,16 +7313,16 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E247" s="1" t="s">
         <v>11</v>
@@ -7308,16 +7333,16 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E248" s="1" t="s">
         <v>14</v>
@@ -7328,16 +7353,16 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E249" s="1" t="s">
         <v>18</v>
@@ -7348,36 +7373,36 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E251" s="1" t="s">
         <v>35</v>
@@ -7388,16 +7413,16 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E252" s="1" t="s">
         <v>38</v>
@@ -7408,16 +7433,16 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E253" s="1" t="s">
         <v>70</v>
@@ -7428,16 +7453,16 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E254" s="1" t="s">
         <v>135</v>
@@ -7448,36 +7473,36 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E255" s="1" t="s">
         <v>144</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E256" s="1" t="s">
         <v>155</v>
@@ -7488,16 +7513,16 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>169</v>
@@ -7508,16 +7533,16 @@
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E258" s="1" t="s">
         <v>188</v>
@@ -7528,16 +7553,16 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E259" s="1" t="s">
         <v>208</v>
@@ -7548,16 +7573,16 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E260" s="1" t="s">
         <v>217</v>
@@ -7568,16 +7593,16 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E261" s="1" t="s">
         <v>226</v>
@@ -7588,16 +7613,16 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E262" s="1" t="s">
         <v>4</v>
@@ -7608,16 +7633,16 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D263" s="1" t="s">
         <v>572</v>
-      </c>
-      <c r="B263" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="C263" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D263" s="1" t="s">
-        <v>571</v>
       </c>
       <c r="E263" s="1" t="s">
         <v>8</v>
@@ -7628,16 +7653,16 @@
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E264" s="1" t="s">
         <v>11</v>
@@ -7648,16 +7673,16 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E265" s="1" t="s">
         <v>14</v>
@@ -7668,16 +7693,16 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E266" s="1" t="s">
         <v>18</v>
@@ -7688,16 +7713,16 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E267" s="1" t="s">
         <v>32</v>
@@ -7708,16 +7733,16 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E268" s="1" t="s">
         <v>35</v>
@@ -7728,16 +7753,16 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E269" s="1" t="s">
         <v>38</v>
@@ -7748,16 +7773,16 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E270" s="1" t="s">
         <v>70</v>
@@ -7768,16 +7793,16 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E271" s="1" t="s">
         <v>135</v>
@@ -7788,16 +7813,16 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E272" s="1" t="s">
         <v>144</v>
@@ -7808,16 +7833,16 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E273" s="1" t="s">
         <v>155</v>
@@ -7828,16 +7853,16 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E274" s="1" t="s">
         <v>169</v>
@@ -7848,16 +7873,16 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E275" s="1" t="s">
         <v>4</v>
@@ -7868,16 +7893,16 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B276" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D276" s="1" t="s">
         <v>599</v>
-      </c>
-      <c r="B276" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="C276" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D276" s="1" t="s">
-        <v>598</v>
       </c>
       <c r="E276" s="1" t="s">
         <v>8</v>
@@ -7888,16 +7913,16 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E277" s="1" t="s">
         <v>11</v>
@@ -7908,36 +7933,36 @@
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E278" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E279" s="1" t="s">
         <v>18</v>
@@ -7948,16 +7973,16 @@
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E280" s="1" t="s">
         <v>32</v>
@@ -7968,16 +7993,16 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E281" s="1" t="s">
         <v>35</v>
@@ -7988,16 +8013,16 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E282" s="1" t="s">
         <v>38</v>
@@ -8008,16 +8033,16 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E283" s="1" t="s">
         <v>70</v>
@@ -8028,16 +8053,16 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E284" s="1" t="s">
         <v>135</v>
@@ -8048,16 +8073,16 @@
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>144</v>
@@ -8068,16 +8093,16 @@
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E286" s="1" t="s">
         <v>155</v>
@@ -8088,16 +8113,16 @@
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E287" s="1" t="s">
         <v>169</v>
@@ -8108,16 +8133,16 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E288" s="1" t="s">
         <v>4</v>
@@ -8128,36 +8153,36 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B289" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C289" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D289" s="1" t="s">
         <v>627</v>
-      </c>
-      <c r="B289" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="C289" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D289" s="1" t="s">
-        <v>626</v>
       </c>
       <c r="E289" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E290" s="1" t="s">
         <v>11</v>
@@ -8168,16 +8193,16 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>14</v>
@@ -8188,16 +8213,16 @@
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>18</v>
@@ -8208,16 +8233,16 @@
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>32</v>
@@ -8228,16 +8253,16 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>35</v>
@@ -8248,16 +8273,16 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>38</v>
@@ -8268,16 +8293,16 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E296" s="1" t="s">
         <v>70</v>
@@ -8288,16 +8313,16 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>135</v>
@@ -8308,16 +8333,16 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>144</v>
@@ -8328,16 +8353,16 @@
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E299" s="1" t="s">
         <v>155</v>
@@ -8348,22 +8373,82 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E300" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A301" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="B301" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="C301" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D301" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="E301" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F301" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A302" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B302" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="C302" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D302" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="E302" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F302" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A303" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="B303" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="C303" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D303" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="E303" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F303" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/DND05S.xlsx
+++ b/DND05S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="651">
   <si>
     <t/>
   </si>
@@ -1105,25 +1105,25 @@
     <t>10012548</t>
   </si>
   <si>
-    <t>SOKLIN RLX/LAV RF770</t>
+    <t>SOKLIN RLX/LAV RF760</t>
   </si>
   <si>
     <t>10003646</t>
   </si>
   <si>
-    <t>SO KLIN P/L APPLE770</t>
+    <t>SO KLIN P/L APPLE760</t>
   </si>
   <si>
     <t>10003645</t>
   </si>
   <si>
-    <t>SO KLIN P/L LMN 780</t>
+    <t>SO KLIN P/L LMN 760</t>
   </si>
   <si>
     <t>20101095</t>
   </si>
   <si>
-    <t>SO KLN LNT SEREH 770</t>
+    <t>SO KLN LNT SEREH 760</t>
   </si>
   <si>
     <t>20131223</t>
@@ -1255,9 +1255,6 @@
     <t>LFBY CC PRG LME2X610</t>
   </si>
   <si>
-    <t>TG,(E-1B)</t>
-  </si>
-  <si>
     <t>20134576</t>
   </si>
   <si>
@@ -1967,27 +1964,6 @@
   </si>
   <si>
     <t>VAPE MILK TEA 600ML</t>
-  </si>
-  <si>
-    <t>20128374</t>
-  </si>
-  <si>
-    <t>LFEBUOY REF LIME 650</t>
-  </si>
-  <si>
-    <t>999</t>
-  </si>
-  <si>
-    <t>20104950</t>
-  </si>
-  <si>
-    <t>RINSO MLTO JP/PCH510</t>
-  </si>
-  <si>
-    <t>20132664</t>
-  </si>
-  <si>
-    <t>VIXAL KUAT SEGAR 600</t>
   </si>
 </sst>
 </file>
@@ -2380,14 +2356,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F303"/>
+  <dimension ref="A1:F300"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="5" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
+    <col min="4" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6128,15 +6103,15 @@
         <v>14</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>414</v>
+        <v>15</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>415</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>416</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
@@ -6153,10 +6128,10 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>417</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>418</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
@@ -6173,10 +6148,10 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>420</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
@@ -6193,10 +6168,10 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>422</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
@@ -6213,16 +6188,16 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B192" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="B192" s="1" t="s">
+      <c r="C192" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D192" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>425</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>4</v>
@@ -6233,16 +6208,16 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>8</v>
@@ -6253,16 +6228,16 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="B194" s="1" t="s">
-        <v>429</v>
-      </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>11</v>
@@ -6273,16 +6248,16 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="B195" s="1" t="s">
-        <v>431</v>
-      </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E195" s="1" t="s">
         <v>14</v>
@@ -6293,16 +6268,16 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="B196" s="1" t="s">
-        <v>433</v>
-      </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>18</v>
@@ -6313,16 +6288,16 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="B197" s="1" t="s">
+      <c r="C197" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D197" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="C197" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D197" s="1" t="s">
-        <v>436</v>
       </c>
       <c r="E197" s="1" t="s">
         <v>4</v>
@@ -6333,16 +6308,16 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="B198" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>8</v>
@@ -6353,16 +6328,16 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B199" s="1" t="s">
-        <v>440</v>
-      </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>11</v>
@@ -6373,16 +6348,16 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="B200" s="1" t="s">
-        <v>442</v>
-      </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>14</v>
@@ -6393,16 +6368,16 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="B201" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>18</v>
@@ -6413,16 +6388,16 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="B202" s="1" t="s">
-        <v>446</v>
-      </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>32</v>
@@ -6433,16 +6408,16 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="B203" s="1" t="s">
-        <v>448</v>
-      </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>35</v>
@@ -6453,16 +6428,16 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="B204" s="1" t="s">
-        <v>450</v>
-      </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>70</v>
@@ -6473,16 +6448,16 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B205" s="1" t="s">
-        <v>452</v>
-      </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E205" s="1" t="s">
         <v>135</v>
@@ -6493,16 +6468,16 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B206" s="1" t="s">
+      <c r="C206" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D206" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="C206" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>455</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>4</v>
@@ -6513,16 +6488,16 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>457</v>
-      </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>8</v>
@@ -6533,16 +6508,16 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="B208" s="1" t="s">
-        <v>459</v>
-      </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>11</v>
@@ -6553,16 +6528,16 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="B209" s="1" t="s">
-        <v>461</v>
-      </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>14</v>
@@ -6573,16 +6548,16 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B210" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="B210" s="1" t="s">
-        <v>463</v>
-      </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>18</v>
@@ -6593,16 +6568,16 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B211" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="B211" s="1" t="s">
-        <v>465</v>
-      </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>32</v>
@@ -6613,16 +6588,16 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B212" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="B212" s="1" t="s">
-        <v>467</v>
-      </c>
       <c r="C212" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>35</v>
@@ -6633,36 +6608,36 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="B213" s="1" t="s">
-        <v>469</v>
-      </c>
       <c r="C213" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>472</v>
-      </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>70</v>
@@ -6673,36 +6648,36 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="B215" s="1" t="s">
-        <v>474</v>
-      </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E215" s="1" t="s">
         <v>135</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="B216" s="1" t="s">
+      <c r="C216" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D216" s="1" t="s">
         <v>476</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D216" s="1" t="s">
-        <v>477</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>4</v>
@@ -6713,16 +6688,16 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="B217" s="1" t="s">
-        <v>479</v>
-      </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>8</v>
@@ -6733,16 +6708,16 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="B218" s="1" t="s">
-        <v>481</v>
-      </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E218" s="1" t="s">
         <v>11</v>
@@ -6753,16 +6728,16 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B219" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="B219" s="1" t="s">
-        <v>483</v>
-      </c>
       <c r="C219" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>14</v>
@@ -6773,16 +6748,16 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B220" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="B220" s="1" t="s">
-        <v>485</v>
-      </c>
       <c r="C220" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>18</v>
@@ -6793,16 +6768,16 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B221" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="B221" s="1" t="s">
-        <v>487</v>
-      </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>32</v>
@@ -6813,16 +6788,16 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="B222" s="1" t="s">
-        <v>489</v>
-      </c>
       <c r="C222" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>35</v>
@@ -6833,16 +6808,16 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B223" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="B223" s="1" t="s">
-        <v>491</v>
-      </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>38</v>
@@ -6853,16 +6828,16 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B224" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="B224" s="1" t="s">
-        <v>493</v>
-      </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>70</v>
@@ -6873,16 +6848,16 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="B225" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="B225" s="1" t="s">
-        <v>495</v>
-      </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>135</v>
@@ -6893,16 +6868,16 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B226" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="B226" s="1" t="s">
-        <v>497</v>
-      </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>144</v>
@@ -6913,16 +6888,16 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="B227" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="B227" s="1" t="s">
-        <v>499</v>
-      </c>
       <c r="C227" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>155</v>
@@ -6933,16 +6908,16 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B228" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="B228" s="1" t="s">
-        <v>501</v>
-      </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>169</v>
@@ -6953,16 +6928,16 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="B229" s="1" t="s">
-        <v>503</v>
-      </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>169</v>
@@ -6973,16 +6948,16 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="B230" s="1" t="s">
-        <v>505</v>
-      </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>169</v>
@@ -6993,16 +6968,16 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B231" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="B231" s="1" t="s">
-        <v>507</v>
-      </c>
       <c r="C231" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>169</v>
@@ -7013,16 +6988,16 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B232" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="B232" s="1" t="s">
-        <v>509</v>
-      </c>
       <c r="C232" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>169</v>
@@ -7033,16 +7008,16 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B233" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="B233" s="1" t="s">
+      <c r="C233" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D233" s="1" t="s">
         <v>511</v>
-      </c>
-      <c r="C233" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D233" s="1" t="s">
-        <v>512</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>4</v>
@@ -7053,16 +7028,16 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B234" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="B234" s="1" t="s">
-        <v>514</v>
-      </c>
       <c r="C234" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>8</v>
@@ -7073,16 +7048,16 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="B235" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B235" s="1" t="s">
-        <v>516</v>
-      </c>
       <c r="C235" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>11</v>
@@ -7093,16 +7068,16 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="B236" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="B236" s="1" t="s">
-        <v>518</v>
-      </c>
       <c r="C236" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>14</v>
@@ -7113,16 +7088,16 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="B237" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="B237" s="1" t="s">
-        <v>520</v>
-      </c>
       <c r="C237" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>18</v>
@@ -7133,16 +7108,16 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="B238" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="B238" s="1" t="s">
-        <v>522</v>
-      </c>
       <c r="C238" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>32</v>
@@ -7153,16 +7128,16 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="B239" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="B239" s="1" t="s">
-        <v>524</v>
-      </c>
       <c r="C239" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>35</v>
@@ -7173,16 +7148,16 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="B240" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="B240" s="1" t="s">
-        <v>526</v>
-      </c>
       <c r="C240" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E240" s="1" t="s">
         <v>38</v>
@@ -7193,16 +7168,16 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="B241" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="B241" s="1" t="s">
-        <v>528</v>
-      </c>
       <c r="C241" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E241" s="1" t="s">
         <v>70</v>
@@ -7213,16 +7188,16 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="B242" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="B242" s="1" t="s">
-        <v>530</v>
-      </c>
       <c r="C242" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E242" s="1" t="s">
         <v>135</v>
@@ -7233,16 +7208,16 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="B243" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="B243" s="1" t="s">
-        <v>532</v>
-      </c>
       <c r="C243" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E243" s="1" t="s">
         <v>144</v>
@@ -7253,16 +7228,16 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="B244" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="B244" s="1" t="s">
-        <v>534</v>
-      </c>
       <c r="C244" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E244" s="1" t="s">
         <v>155</v>
@@ -7273,16 +7248,16 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="B245" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="B245" s="1" t="s">
+      <c r="C245" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D245" s="1" t="s">
         <v>536</v>
-      </c>
-      <c r="C245" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D245" s="1" t="s">
-        <v>537</v>
       </c>
       <c r="E245" s="1" t="s">
         <v>4</v>
@@ -7293,16 +7268,16 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="B246" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="B246" s="1" t="s">
-        <v>539</v>
-      </c>
       <c r="C246" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E246" s="1" t="s">
         <v>8</v>
@@ -7313,16 +7288,16 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="B247" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="B247" s="1" t="s">
-        <v>541</v>
-      </c>
       <c r="C247" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E247" s="1" t="s">
         <v>11</v>
@@ -7333,16 +7308,16 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B248" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="B248" s="1" t="s">
-        <v>543</v>
-      </c>
       <c r="C248" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E248" s="1" t="s">
         <v>14</v>
@@ -7353,16 +7328,16 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B249" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="B249" s="1" t="s">
-        <v>545</v>
-      </c>
       <c r="C249" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E249" s="1" t="s">
         <v>18</v>
@@ -7373,16 +7348,16 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B250" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="B250" s="1" t="s">
-        <v>547</v>
-      </c>
       <c r="C250" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>32</v>
@@ -7393,16 +7368,16 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B251" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="B251" s="1" t="s">
-        <v>549</v>
-      </c>
       <c r="C251" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E251" s="1" t="s">
         <v>35</v>
@@ -7413,16 +7388,16 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B252" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="B252" s="1" t="s">
-        <v>551</v>
-      </c>
       <c r="C252" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E252" s="1" t="s">
         <v>38</v>
@@ -7433,16 +7408,16 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="B253" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="B253" s="1" t="s">
-        <v>553</v>
-      </c>
       <c r="C253" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E253" s="1" t="s">
         <v>70</v>
@@ -7453,16 +7428,16 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B254" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="B254" s="1" t="s">
-        <v>555</v>
-      </c>
       <c r="C254" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E254" s="1" t="s">
         <v>135</v>
@@ -7473,16 +7448,16 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="B255" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="B255" s="1" t="s">
-        <v>557</v>
-      </c>
       <c r="C255" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E255" s="1" t="s">
         <v>144</v>
@@ -7493,16 +7468,16 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="B256" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="B256" s="1" t="s">
-        <v>559</v>
-      </c>
       <c r="C256" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E256" s="1" t="s">
         <v>155</v>
@@ -7513,16 +7488,16 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="B257" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="B257" s="1" t="s">
-        <v>561</v>
-      </c>
       <c r="C257" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>169</v>
@@ -7533,16 +7508,16 @@
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="B258" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="B258" s="1" t="s">
-        <v>563</v>
-      </c>
       <c r="C258" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E258" s="1" t="s">
         <v>188</v>
@@ -7553,16 +7528,16 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B259" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="B259" s="1" t="s">
-        <v>565</v>
-      </c>
       <c r="C259" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E259" s="1" t="s">
         <v>208</v>
@@ -7573,16 +7548,16 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="B260" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="B260" s="1" t="s">
-        <v>567</v>
-      </c>
       <c r="C260" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E260" s="1" t="s">
         <v>217</v>
@@ -7593,16 +7568,16 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B261" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="B261" s="1" t="s">
-        <v>569</v>
-      </c>
       <c r="C261" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E261" s="1" t="s">
         <v>226</v>
@@ -7613,16 +7588,16 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="B262" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="B262" s="1" t="s">
+      <c r="C262" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D262" s="1" t="s">
         <v>571</v>
-      </c>
-      <c r="C262" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D262" s="1" t="s">
-        <v>572</v>
       </c>
       <c r="E262" s="1" t="s">
         <v>4</v>
@@ -7633,16 +7608,16 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="B263" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="B263" s="1" t="s">
-        <v>574</v>
-      </c>
       <c r="C263" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E263" s="1" t="s">
         <v>8</v>
@@ -7653,16 +7628,16 @@
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B264" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="B264" s="1" t="s">
-        <v>576</v>
-      </c>
       <c r="C264" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E264" s="1" t="s">
         <v>11</v>
@@ -7673,16 +7648,16 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B265" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="B265" s="1" t="s">
-        <v>578</v>
-      </c>
       <c r="C265" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E265" s="1" t="s">
         <v>14</v>
@@ -7693,16 +7668,16 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B266" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="B266" s="1" t="s">
-        <v>580</v>
-      </c>
       <c r="C266" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E266" s="1" t="s">
         <v>18</v>
@@ -7713,16 +7688,16 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="B267" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="B267" s="1" t="s">
-        <v>582</v>
-      </c>
       <c r="C267" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E267" s="1" t="s">
         <v>32</v>
@@ -7733,16 +7708,16 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B268" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="B268" s="1" t="s">
-        <v>584</v>
-      </c>
       <c r="C268" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E268" s="1" t="s">
         <v>35</v>
@@ -7753,16 +7728,16 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="B269" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="B269" s="1" t="s">
-        <v>586</v>
-      </c>
       <c r="C269" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E269" s="1" t="s">
         <v>38</v>
@@ -7773,16 +7748,16 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="B270" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="B270" s="1" t="s">
-        <v>588</v>
-      </c>
       <c r="C270" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E270" s="1" t="s">
         <v>70</v>
@@ -7793,16 +7768,16 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="B271" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="B271" s="1" t="s">
-        <v>590</v>
-      </c>
       <c r="C271" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E271" s="1" t="s">
         <v>135</v>
@@ -7813,16 +7788,16 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="B272" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="B272" s="1" t="s">
-        <v>592</v>
-      </c>
       <c r="C272" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E272" s="1" t="s">
         <v>144</v>
@@ -7833,16 +7808,16 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="B273" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="B273" s="1" t="s">
-        <v>594</v>
-      </c>
       <c r="C273" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E273" s="1" t="s">
         <v>155</v>
@@ -7853,16 +7828,16 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="B274" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="B274" s="1" t="s">
-        <v>596</v>
-      </c>
       <c r="C274" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E274" s="1" t="s">
         <v>169</v>
@@ -7873,16 +7848,16 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="B275" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="B275" s="1" t="s">
+      <c r="C275" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D275" s="1" t="s">
         <v>598</v>
-      </c>
-      <c r="C275" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D275" s="1" t="s">
-        <v>599</v>
       </c>
       <c r="E275" s="1" t="s">
         <v>4</v>
@@ -7893,16 +7868,16 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B276" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="B276" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="C276" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E276" s="1" t="s">
         <v>8</v>
@@ -7913,16 +7888,16 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B277" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="B277" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="C277" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E277" s="1" t="s">
         <v>11</v>
@@ -7933,36 +7908,36 @@
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="B278" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="B278" s="1" t="s">
-        <v>605</v>
-      </c>
       <c r="C278" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E278" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B279" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="B279" s="1" t="s">
-        <v>608</v>
-      </c>
       <c r="C279" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E279" s="1" t="s">
         <v>18</v>
@@ -7973,16 +7948,16 @@
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="B280" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="B280" s="1" t="s">
-        <v>610</v>
-      </c>
       <c r="C280" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E280" s="1" t="s">
         <v>32</v>
@@ -7993,16 +7968,16 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="B281" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="B281" s="1" t="s">
-        <v>612</v>
-      </c>
       <c r="C281" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E281" s="1" t="s">
         <v>35</v>
@@ -8013,16 +7988,16 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="B282" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="B282" s="1" t="s">
-        <v>614</v>
-      </c>
       <c r="C282" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E282" s="1" t="s">
         <v>38</v>
@@ -8033,16 +8008,16 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B283" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="B283" s="1" t="s">
-        <v>616</v>
-      </c>
       <c r="C283" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E283" s="1" t="s">
         <v>70</v>
@@ -8053,16 +8028,16 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="B284" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="B284" s="1" t="s">
-        <v>618</v>
-      </c>
       <c r="C284" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E284" s="1" t="s">
         <v>135</v>
@@ -8073,16 +8048,16 @@
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B285" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="B285" s="1" t="s">
-        <v>620</v>
-      </c>
       <c r="C285" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>144</v>
@@ -8093,16 +8068,16 @@
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="B286" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="B286" s="1" t="s">
-        <v>622</v>
-      </c>
       <c r="C286" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E286" s="1" t="s">
         <v>155</v>
@@ -8113,16 +8088,16 @@
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="B287" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="B287" s="1" t="s">
-        <v>624</v>
-      </c>
       <c r="C287" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E287" s="1" t="s">
         <v>169</v>
@@ -8133,16 +8108,16 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="B288" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="B288" s="1" t="s">
+      <c r="C288" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D288" s="1" t="s">
         <v>626</v>
-      </c>
-      <c r="C288" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D288" s="1" t="s">
-        <v>627</v>
       </c>
       <c r="E288" s="1" t="s">
         <v>4</v>
@@ -8153,16 +8128,16 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="B289" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="B289" s="1" t="s">
-        <v>629</v>
-      </c>
       <c r="C289" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E289" s="1" t="s">
         <v>8</v>
@@ -8173,16 +8148,16 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="B290" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="B290" s="1" t="s">
-        <v>631</v>
-      </c>
       <c r="C290" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E290" s="1" t="s">
         <v>11</v>
@@ -8193,16 +8168,16 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="B291" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="B291" s="1" t="s">
-        <v>633</v>
-      </c>
       <c r="C291" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>14</v>
@@ -8213,16 +8188,16 @@
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="B292" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="B292" s="1" t="s">
-        <v>635</v>
-      </c>
       <c r="C292" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>18</v>
@@ -8233,16 +8208,16 @@
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="B293" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="B293" s="1" t="s">
-        <v>637</v>
-      </c>
       <c r="C293" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>32</v>
@@ -8253,16 +8228,16 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="B294" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="B294" s="1" t="s">
-        <v>639</v>
-      </c>
       <c r="C294" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>35</v>
@@ -8273,16 +8248,16 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="B295" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="B295" s="1" t="s">
-        <v>641</v>
-      </c>
       <c r="C295" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>38</v>
@@ -8293,16 +8268,16 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="B296" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="B296" s="1" t="s">
-        <v>643</v>
-      </c>
       <c r="C296" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E296" s="1" t="s">
         <v>70</v>
@@ -8313,16 +8288,16 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="B297" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="B297" s="1" t="s">
-        <v>645</v>
-      </c>
       <c r="C297" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>135</v>
@@ -8333,16 +8308,16 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="B298" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="B298" s="1" t="s">
-        <v>647</v>
-      </c>
       <c r="C298" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>144</v>
@@ -8353,16 +8328,16 @@
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="B299" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="B299" s="1" t="s">
-        <v>649</v>
-      </c>
       <c r="C299" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E299" s="1" t="s">
         <v>155</v>
@@ -8373,82 +8348,22 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="B300" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="B300" s="1" t="s">
-        <v>651</v>
-      </c>
       <c r="C300" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E300" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A301" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="B301" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="C301" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D301" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="E301" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F301" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A302" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="B302" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="C302" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D302" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="E302" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F302" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A303" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="B303" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="C303" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D303" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="E303" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F303" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/DND05S.xlsx
+++ b/DND05S.xlsx
@@ -1180,7 +1180,7 @@
     <t>20131788</t>
   </si>
   <si>
-    <t>MAMA LMN JR.NPS 950</t>
+    <t>MAMA LMN JR.NPS 920</t>
   </si>
   <si>
     <t>27</t>
@@ -1189,7 +1189,7 @@
     <t>20142275</t>
   </si>
   <si>
-    <t>MAMA LIME CHARCO 950</t>
+    <t>MAMA LIME CHARCO 920</t>
   </si>
   <si>
     <t>20034450</t>

--- a/DND05S.xlsx
+++ b/DND05S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="654">
   <si>
     <t/>
   </si>
@@ -100,13 +100,13 @@
     <t>20067585</t>
   </si>
   <si>
-    <t>SKLN LQD SC/BLOSM675</t>
+    <t>SKLN LQD SC/BLOSM700</t>
   </si>
   <si>
     <t>20054747</t>
   </si>
   <si>
-    <t>SKLIN LQD V/BLSOM675</t>
+    <t>SKLIN LQD V/BLSOM700</t>
   </si>
   <si>
     <t>6</t>
@@ -115,7 +115,7 @@
     <t>20046548</t>
   </si>
   <si>
-    <t>SKLIN LQD SFTRGN 675</t>
+    <t>SKLIN LQD SFTRGN 700</t>
   </si>
   <si>
     <t>7</t>
@@ -202,25 +202,25 @@
     <t>20093627</t>
   </si>
   <si>
-    <t>SKLN LQD SKR STRW500</t>
+    <t>SKLN LQD SKR STRW510</t>
   </si>
   <si>
     <t>20123818</t>
   </si>
   <si>
-    <t>SKLN LQD PROV LVD500</t>
+    <t>SKLN LQD PROV LVD510</t>
   </si>
   <si>
     <t>20091870</t>
   </si>
   <si>
-    <t>SKLN LQ WHT&amp;BRGHT500</t>
+    <t>SKLN LQ WHT&amp;BRGHT510</t>
   </si>
   <si>
     <t>20114428</t>
   </si>
   <si>
-    <t>SKLN LQD KOR CMLA500</t>
+    <t>SKLN LQD KOR CMLA510</t>
   </si>
   <si>
     <t>9</t>
@@ -259,6 +259,12 @@
     <t>LARIST SMR.BRZ 700ML</t>
   </si>
   <si>
+    <t>20143785</t>
+  </si>
+  <si>
+    <t>IDM D/C AUTUM SNT700</t>
+  </si>
+  <si>
     <t>20139955</t>
   </si>
   <si>
@@ -976,6 +982,12 @@
     <t>IDM PURPOSE CLN 400</t>
   </si>
   <si>
+    <t>10003498</t>
+  </si>
+  <si>
+    <t>CLEAR PUMP ORIGNL500</t>
+  </si>
+  <si>
     <t>10014263</t>
   </si>
   <si>
@@ -1312,21 +1324,15 @@
     <t>SNLGHT BIO NATURE600</t>
   </si>
   <si>
-    <t>10003498</t>
-  </si>
-  <si>
-    <t>CLEAR PUMP ORIGNL500</t>
+    <t>10013205</t>
+  </si>
+  <si>
+    <t>SUNLIGHT J/NIPIS.750</t>
   </si>
   <si>
     <t>30</t>
   </si>
   <si>
-    <t>10013205</t>
-  </si>
-  <si>
-    <t>SUNLIGHT J/NIPIS.750</t>
-  </si>
-  <si>
     <t>20139947</t>
   </si>
   <si>
@@ -1369,6 +1375,12 @@
     <t>STELA A/F RJ AMPT350</t>
   </si>
   <si>
+    <t>10034652</t>
+  </si>
+  <si>
+    <t>GLADE OCEAN ESCP 350</t>
+  </si>
+  <si>
     <t>10004032</t>
   </si>
   <si>
@@ -1405,7 +1417,7 @@
     <t>10005246</t>
   </si>
   <si>
-    <t>WING PRCLN CLN BR750</t>
+    <t>WING PRCLN CLN BR700</t>
   </si>
   <si>
     <t>20040315</t>
@@ -1684,286 +1696,283 @@
     <t>SOFEL LOT.KRN/SMR 60</t>
   </si>
   <si>
+    <t>10040202</t>
+  </si>
+  <si>
+    <t>SOFFELL A.NYMK K/J60</t>
+  </si>
+  <si>
+    <t>10037280</t>
+  </si>
+  <si>
+    <t>BAGUS KAPUR AJAIB</t>
+  </si>
+  <si>
+    <t>20109069</t>
+  </si>
+  <si>
+    <t>BAGUS LEM TIKUS PCS</t>
+  </si>
+  <si>
+    <t>10003479</t>
+  </si>
+  <si>
+    <t>GAJAH LEM TIKUS KT70</t>
+  </si>
+  <si>
+    <t>20139525</t>
+  </si>
+  <si>
+    <t>VAPE DORA LEM TIKUS</t>
+  </si>
+  <si>
+    <t>20124418</t>
+  </si>
+  <si>
+    <t>VAPE SWEET PWDR 200</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>20039183</t>
+  </si>
+  <si>
+    <t>HIT ALAT+REF EXP APL</t>
+  </si>
+  <si>
+    <t>20139144</t>
+  </si>
+  <si>
+    <t>HIT XPRES PINK BL.35</t>
+  </si>
+  <si>
+    <t>20131161</t>
+  </si>
+  <si>
+    <t>HIT REF XPRES APLE35</t>
+  </si>
+  <si>
+    <t>20095744</t>
+  </si>
+  <si>
+    <t>HIT REF EXPRT FRS 35</t>
+  </si>
+  <si>
+    <t>20023870</t>
+  </si>
+  <si>
+    <t>VAPE LIQUID ELEKTRIK</t>
+  </si>
+  <si>
+    <t>20084568</t>
+  </si>
+  <si>
+    <t>VAPE LIQ.SKR BLOSM45</t>
+  </si>
+  <si>
+    <t>20008748</t>
+  </si>
+  <si>
+    <t>VAPE LIQUID REF 45ML</t>
+  </si>
+  <si>
+    <t>10027329</t>
+  </si>
+  <si>
+    <t>HIT ALT NYAMUK ELC 5</t>
+  </si>
+  <si>
+    <t>10034732</t>
+  </si>
+  <si>
+    <t>HIT MAT ELECTRK 48'S</t>
+  </si>
+  <si>
+    <t>20030445</t>
+  </si>
+  <si>
+    <t>VAPE SPRAY 1XSMP ORG</t>
+  </si>
+  <si>
+    <t>20073974</t>
+  </si>
+  <si>
+    <t>VAPE SPRAY 1XSMP SKR</t>
+  </si>
+  <si>
+    <t>20076987</t>
+  </si>
+  <si>
+    <t>BAYGON FLOW.GRDN 200</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>20022902</t>
+  </si>
+  <si>
+    <t>HIT SPRAY ORG 180</t>
+  </si>
+  <si>
+    <t>20064216</t>
+  </si>
+  <si>
+    <t>HIT INS.SPRY LILY180</t>
+  </si>
+  <si>
+    <t>10015526</t>
+  </si>
+  <si>
+    <t>BAYGON SPRY LVND 750</t>
+  </si>
+  <si>
+    <t>20124346</t>
+  </si>
+  <si>
+    <t>BAYGON JPNSE&amp;PCH 600</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>20098605</t>
+  </si>
+  <si>
+    <t>BYGON SPRY CHR.BL600</t>
+  </si>
+  <si>
+    <t>20071775</t>
+  </si>
+  <si>
+    <t>BAYGON FLO.GRDN 675</t>
+  </si>
+  <si>
+    <t>20139154</t>
+  </si>
+  <si>
+    <t>HIT COTTON PWD 600ML</t>
+  </si>
+  <si>
+    <t>20054151</t>
+  </si>
+  <si>
+    <t>HIT INS.SPRY LILY600</t>
+  </si>
+  <si>
+    <t>10005198</t>
+  </si>
+  <si>
+    <t>HIT INS.SPRAY ORG600</t>
+  </si>
+  <si>
+    <t>20109613</t>
+  </si>
+  <si>
+    <t>HIT SPRY.P/BLOSM 600</t>
+  </si>
+  <si>
+    <t>20080868</t>
+  </si>
+  <si>
+    <t>HIT FRESH CITRUS 600</t>
+  </si>
+  <si>
+    <t>20131365</t>
+  </si>
+  <si>
+    <t>HIT SPRY JPN.SKR 600</t>
+  </si>
+  <si>
+    <t>10003272</t>
+  </si>
+  <si>
+    <t>BAYGON SPRY CITRS675</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>20139446</t>
+  </si>
+  <si>
+    <t>BAYGON CTRS FRSH 400</t>
+  </si>
+  <si>
+    <t>20128132</t>
+  </si>
+  <si>
+    <t>BAYGON FLO.GRDN 400</t>
+  </si>
+  <si>
+    <t>20135247</t>
+  </si>
+  <si>
+    <t>BAYGON FLRL.FNTSY500</t>
+  </si>
+  <si>
+    <t>20135248</t>
+  </si>
+  <si>
+    <t>BAYGON CHRRY BRRY500</t>
+  </si>
+  <si>
+    <t>20088715</t>
+  </si>
+  <si>
+    <t>HIT SPRAY LILY 400ML</t>
+  </si>
+  <si>
+    <t>20022498</t>
+  </si>
+  <si>
+    <t>HIT SPRAY ORG 400ML</t>
+  </si>
+  <si>
+    <t>20134237</t>
+  </si>
+  <si>
+    <t>HIT SPRY.P/BLOSM 400</t>
+  </si>
+  <si>
+    <t>20136130</t>
+  </si>
+  <si>
+    <t>VAPE FLO.BUBBLE 600</t>
+  </si>
+  <si>
+    <t>20124850</t>
+  </si>
+  <si>
+    <t>VAPE SPRY SWET PD600</t>
+  </si>
+  <si>
+    <t>20136134</t>
+  </si>
+  <si>
+    <t>VAPE CANDY FLO 600</t>
+  </si>
+  <si>
+    <t>10006651</t>
+  </si>
+  <si>
+    <t>VAPE FMK ORANGE 600</t>
+  </si>
+  <si>
+    <t>20142133</t>
+  </si>
+  <si>
+    <t>VAPE MILK TEA 600ML</t>
+  </si>
+  <si>
     <t>20078241</t>
   </si>
   <si>
     <t>SOFFELL LOT.APEL 60G</t>
   </si>
   <si>
-    <t>10040202</t>
-  </si>
-  <si>
-    <t>SOFFELL A.NYMK K/J60</t>
-  </si>
-  <si>
-    <t>10037280</t>
-  </si>
-  <si>
-    <t>BAGUS KAPUR AJAIB</t>
-  </si>
-  <si>
-    <t>20109069</t>
-  </si>
-  <si>
-    <t>BAGUS LEM TIKUS PCS</t>
-  </si>
-  <si>
-    <t>10003479</t>
-  </si>
-  <si>
-    <t>GAJAH LEM TIKUS KT70</t>
-  </si>
-  <si>
-    <t>20139525</t>
-  </si>
-  <si>
-    <t>VAPE DORA LEM TIKUS</t>
-  </si>
-  <si>
-    <t>20022902</t>
-  </si>
-  <si>
-    <t>HIT SPRAY ORG 180</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>20064216</t>
-  </si>
-  <si>
-    <t>HIT INS.SPRY LILY180</t>
-  </si>
-  <si>
-    <t>20139144</t>
-  </si>
-  <si>
-    <t>HIT XPRES PINK BL.35</t>
-  </si>
-  <si>
-    <t>20131161</t>
-  </si>
-  <si>
-    <t>HIT REF XPRES APLE35</t>
-  </si>
-  <si>
-    <t>20095744</t>
-  </si>
-  <si>
-    <t>HIT REF EXPRT FRS 35</t>
-  </si>
-  <si>
-    <t>20039183</t>
-  </si>
-  <si>
-    <t>HIT ALAT+REF EXP APL</t>
-  </si>
-  <si>
-    <t>10034732</t>
-  </si>
-  <si>
-    <t>HIT MAT ELECTRK 48'S</t>
-  </si>
-  <si>
-    <t>10027329</t>
-  </si>
-  <si>
-    <t>HIT ALT NYAMUK ELC 5</t>
-  </si>
-  <si>
-    <t>20084568</t>
-  </si>
-  <si>
-    <t>VAPE LIQ.SKR BLOSM45</t>
-  </si>
-  <si>
-    <t>20008748</t>
-  </si>
-  <si>
-    <t>VAPE LIQUID REF 45ML</t>
-  </si>
-  <si>
-    <t>20023870</t>
-  </si>
-  <si>
-    <t>VAPE LIQUID ELEKTRIK</t>
-  </si>
-  <si>
-    <t>20030445</t>
-  </si>
-  <si>
-    <t>VAPE SPRAY 1XSMP ORG</t>
-  </si>
-  <si>
-    <t>20073974</t>
-  </si>
-  <si>
-    <t>VAPE SPRAY 1XSMP SKR</t>
-  </si>
-  <si>
-    <t>20124418</t>
-  </si>
-  <si>
-    <t>VAPE SWEET PWDR 200</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>20076987</t>
-  </si>
-  <si>
-    <t>BAYGON FLOW.GRDN 200</t>
-  </si>
-  <si>
-    <t>10015526</t>
-  </si>
-  <si>
-    <t>BAYGON SPRY LVND 750</t>
-  </si>
-  <si>
-    <t>20124346</t>
-  </si>
-  <si>
-    <t>BAYGON JPNSE&amp;PCH 600</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20098605</t>
-  </si>
-  <si>
-    <t>BYGON SPRY CHR.BL600</t>
-  </si>
-  <si>
-    <t>10003272</t>
-  </si>
-  <si>
-    <t>BAYGON SPRY CITRS675</t>
-  </si>
-  <si>
-    <t>20071775</t>
-  </si>
-  <si>
-    <t>BAYGON FLO.GRDN 675</t>
-  </si>
-  <si>
-    <t>20139154</t>
-  </si>
-  <si>
-    <t>HIT COTTON PWD 600ML</t>
-  </si>
-  <si>
-    <t>20054151</t>
-  </si>
-  <si>
-    <t>HIT INS.SPRY LILY600</t>
-  </si>
-  <si>
-    <t>10005198</t>
-  </si>
-  <si>
-    <t>HIT INS.SPRAY ORG600</t>
-  </si>
-  <si>
-    <t>20109613</t>
-  </si>
-  <si>
-    <t>HIT SPRY.P/BLOSM 600</t>
-  </si>
-  <si>
-    <t>20080868</t>
-  </si>
-  <si>
-    <t>HIT FRESH CITRUS 600</t>
-  </si>
-  <si>
-    <t>20131365</t>
-  </si>
-  <si>
-    <t>HIT SPRY JPN.SKR 600</t>
-  </si>
-  <si>
-    <t>10034652</t>
-  </si>
-  <si>
-    <t>GLADE OCEAN ESCP 350</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>20139446</t>
-  </si>
-  <si>
-    <t>BAYGON CTRS FRSH 400</t>
-  </si>
-  <si>
-    <t>20128132</t>
-  </si>
-  <si>
-    <t>BAYGON FLO.GRDN 400</t>
-  </si>
-  <si>
-    <t>20135247</t>
-  </si>
-  <si>
-    <t>BAYGON FLRL.FNTSY500</t>
-  </si>
-  <si>
-    <t>20135248</t>
-  </si>
-  <si>
-    <t>BAYGON CHRRY BRRY500</t>
-  </si>
-  <si>
-    <t>20088715</t>
-  </si>
-  <si>
-    <t>HIT SPRAY LILY 400ML</t>
-  </si>
-  <si>
-    <t>20022498</t>
-  </si>
-  <si>
-    <t>HIT SPRAY ORG 400ML</t>
-  </si>
-  <si>
-    <t>20134237</t>
-  </si>
-  <si>
-    <t>HIT SPRY.P/BLOSM 400</t>
-  </si>
-  <si>
-    <t>20136130</t>
-  </si>
-  <si>
-    <t>VAPE FLO.BUBBLE 600</t>
-  </si>
-  <si>
-    <t>20124850</t>
-  </si>
-  <si>
-    <t>VAPE SPRY SWET PD600</t>
-  </si>
-  <si>
-    <t>20136134</t>
-  </si>
-  <si>
-    <t>VAPE CANDY FLO 600</t>
-  </si>
-  <si>
-    <t>10006651</t>
-  </si>
-  <si>
-    <t>VAPE FMK ORANGE 600</t>
-  </si>
-  <si>
-    <t>20142133</t>
-  </si>
-  <si>
-    <t>VAPE MILK TEA 600ML</t>
+    <t>999</t>
   </si>
 </sst>
 </file>
@@ -2356,13 +2365,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F300"/>
+  <dimension ref="A1:F301"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="5" width="4" customWidth="1"/>
+    <col min="4" max="4" width="5" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3063,7 +3073,7 @@
         <v>32</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -3077,10 +3087,10 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -3100,7 +3110,7 @@
         <v>32</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -3120,7 +3130,7 @@
         <v>32</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -3140,7 +3150,7 @@
         <v>32</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -3160,18 +3170,18 @@
         <v>32</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -3180,10 +3190,10 @@
         <v>32</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -3200,7 +3210,7 @@
         <v>32</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -3220,7 +3230,7 @@
         <v>32</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -3237,10 +3247,10 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -3260,7 +3270,7 @@
         <v>35</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -3280,10 +3290,10 @@
         <v>35</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -3300,10 +3310,10 @@
         <v>35</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -3320,7 +3330,7 @@
         <v>35</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -3340,7 +3350,7 @@
         <v>35</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -3360,7 +3370,7 @@
         <v>35</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -3380,7 +3390,7 @@
         <v>35</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -3397,10 +3407,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -3420,7 +3430,7 @@
         <v>38</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -3440,10 +3450,10 @@
         <v>38</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -3460,10 +3470,10 @@
         <v>38</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3477,13 +3487,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3500,7 +3510,7 @@
         <v>70</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -3520,7 +3530,7 @@
         <v>70</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -3540,7 +3550,7 @@
         <v>70</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -3557,10 +3567,10 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -3568,22 +3578,22 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="C61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="E61" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -3597,13 +3607,13 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -3617,10 +3627,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -3637,10 +3647,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3648,19 +3658,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="C65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="E65" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -3677,10 +3687,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3697,10 +3707,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -3717,10 +3727,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -3737,10 +3747,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -3748,22 +3758,22 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="C70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="E70" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3777,33 +3787,33 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="C72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F72" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3817,13 +3827,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -3837,13 +3847,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3857,30 +3867,30 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="E76" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -3897,10 +3907,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3917,10 +3927,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3937,10 +3947,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3957,10 +3967,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3977,10 +3987,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3997,10 +4007,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -4017,13 +4027,13 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -4037,33 +4047,33 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>189</v>
+        <v>21</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="E85" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -4077,10 +4087,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>15</v>
@@ -4097,10 +4107,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>15</v>
@@ -4117,10 +4127,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>15</v>
@@ -4137,13 +4147,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>189</v>
+        <v>15</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -4157,13 +4167,13 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -4177,13 +4187,13 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -4197,13 +4207,13 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>15</v>
+        <v>191</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -4217,30 +4227,30 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="C94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="E94" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>21</v>
@@ -4257,10 +4267,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>21</v>
@@ -4277,10 +4287,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>21</v>
@@ -4297,33 +4307,33 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="C98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -4337,13 +4347,13 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -4357,13 +4367,13 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -4377,30 +4387,30 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="C102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="E102" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>21</v>
@@ -4417,10 +4427,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>21</v>
@@ -4437,13 +4447,13 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -4457,13 +4467,13 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -4477,33 +4487,33 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>15</v>
+        <v>96</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="C107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>237</v>
-      </c>
       <c r="E107" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -4517,10 +4527,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>21</v>
@@ -4537,13 +4547,13 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4557,10 +4567,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -4577,33 +4587,33 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>249</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="E112" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F112" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -4617,13 +4627,13 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -4637,10 +4647,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -4657,10 +4667,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -4677,13 +4687,13 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -4697,13 +4707,13 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4717,13 +4727,13 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4737,13 +4747,13 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4757,13 +4767,13 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4777,30 +4787,30 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="C122" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="C122" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="E122" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -4817,10 +4827,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -4837,10 +4847,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -4857,10 +4867,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -4877,10 +4887,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -4897,10 +4907,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4917,10 +4927,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4937,30 +4947,30 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="C130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="E130" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>21</v>
@@ -4977,13 +4987,13 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>160</v>
+        <v>21</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4997,33 +5007,33 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>294</v>
+        <v>162</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="C133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F133" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -5037,13 +5047,13 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>21</v>
+        <v>296</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -5057,10 +5067,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>21</v>
@@ -5077,10 +5087,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>21</v>
@@ -5097,13 +5107,13 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -5117,30 +5127,30 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="E139" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -5157,33 +5167,33 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>312</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B141" s="1" t="s">
+      <c r="C141" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F141" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F141" s="1" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -5197,13 +5207,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -5217,13 +5227,13 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>5</v>
+        <v>314</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -5237,13 +5247,13 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>160</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -5257,50 +5267,50 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>21</v>
+        <v>162</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B147" s="1" t="s">
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="E147" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>21</v>
@@ -5317,10 +5327,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>21</v>
@@ -5337,13 +5347,13 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -5357,13 +5367,13 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -5377,13 +5387,13 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -5397,53 +5407,53 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>339</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>294</v>
+        <v>96</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B154" s="1" t="s">
+      <c r="E154" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F154" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="E154" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F154" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -5457,13 +5467,13 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>21</v>
+        <v>296</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -5477,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -5497,13 +5507,13 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>160</v>
+        <v>21</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -5517,13 +5527,13 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -5537,13 +5547,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -5557,13 +5567,13 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -5577,53 +5587,53 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>360</v>
-      </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B163" s="1" t="s">
+      <c r="C163" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="C163" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>358</v>
-      </c>
       <c r="E163" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>94</v>
+        <v>162</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -5637,13 +5647,13 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>5</v>
+        <v>162</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -5657,13 +5667,13 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -5677,10 +5687,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5697,10 +5707,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5717,10 +5727,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5737,10 +5747,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5748,39 +5758,39 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>377</v>
-      </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B171" s="1" t="s">
+      <c r="C171" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="C171" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>375</v>
-      </c>
       <c r="E171" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5797,13 +5807,13 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5817,10 +5827,10 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5837,10 +5847,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5857,13 +5867,13 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5877,10 +5887,10 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5888,39 +5898,39 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>392</v>
-      </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>390</v>
-      </c>
       <c r="E178" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5937,10 +5947,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5957,10 +5967,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5977,10 +5987,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5997,10 +6007,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -6017,13 +6027,13 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6037,50 +6047,50 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>409</v>
-      </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>249</v>
+        <v>77</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B186" s="1" t="s">
+      <c r="C186" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C186" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>407</v>
-      </c>
       <c r="E186" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>21</v>
@@ -6097,13 +6107,13 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>15</v>
+        <v>251</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -6117,10 +6127,10 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>21</v>
@@ -6137,13 +6147,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -6157,13 +6167,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>160</v>
+        <v>21</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -6177,13 +6187,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -6197,50 +6207,50 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>21</v>
+        <v>162</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>426</v>
-      </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>21</v>
+        <v>162</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B194" s="1" t="s">
+      <c r="C194" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D194" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C194" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D194" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="E194" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>21</v>
@@ -6257,13 +6267,13 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -6277,10 +6287,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>21</v>
@@ -6297,30 +6307,30 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>94</v>
+        <v>15</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="B198" s="1" t="s">
-        <v>437</v>
-      </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>21</v>
@@ -6328,19 +6338,19 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="B199" s="1" t="s">
+      <c r="C199" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D199" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="C199" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D199" s="1" t="s">
-        <v>435</v>
-      </c>
       <c r="E199" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>21</v>
@@ -6357,10 +6367,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>21</v>
@@ -6377,13 +6387,13 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -6397,13 +6407,13 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -6417,13 +6427,13 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>312</v>
+        <v>77</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -6437,13 +6447,13 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>339</v>
+        <v>314</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -6457,13 +6467,13 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>135</v>
+        <v>38</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -6477,50 +6487,50 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>21</v>
+        <v>343</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>456</v>
-      </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>8</v>
+        <v>137</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="B208" s="1" t="s">
+      <c r="C208" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="C208" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>454</v>
-      </c>
       <c r="E208" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>21</v>
@@ -6537,13 +6547,13 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -6557,13 +6567,13 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>294</v>
+        <v>21</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -6577,13 +6587,13 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -6597,13 +6607,13 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>160</v>
+        <v>296</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -6617,53 +6627,53 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>469</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>471</v>
-      </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>312</v>
+        <v>162</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="B215" s="1" t="s">
+      <c r="C215" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F215" s="1" t="s">
         <v>473</v>
-      </c>
-      <c r="C215" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D215" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="E215" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="F215" s="1" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -6677,53 +6687,53 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>77</v>
+        <v>314</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="B217" s="1" t="s">
-        <v>478</v>
-      </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>8</v>
+        <v>137</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>294</v>
+        <v>473</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="B218" s="1" t="s">
+      <c r="C218" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D218" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="C218" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D218" s="1" t="s">
-        <v>476</v>
-      </c>
       <c r="E218" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>294</v>
+        <v>77</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -6737,13 +6747,13 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -6757,13 +6767,13 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -6777,13 +6787,13 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -6797,13 +6807,13 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>77</v>
+        <v>296</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -6817,13 +6827,13 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>77</v>
+        <v>296</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -6837,10 +6847,10 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="F224" s="1" t="s">
         <v>77</v>
@@ -6857,13 +6867,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>135</v>
+        <v>38</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -6877,13 +6887,13 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>144</v>
+        <v>70</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -6897,10 +6907,10 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="F227" s="1" t="s">
         <v>5</v>
@@ -6917,13 +6927,13 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>294</v>
+        <v>5</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -6937,13 +6947,13 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>294</v>
+        <v>5</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -6957,13 +6967,13 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -6977,13 +6987,13 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>77</v>
+        <v>296</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -6997,13 +7007,13 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>77</v>
+        <v>296</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -7017,53 +7027,53 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>511</v>
+        <v>480</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>4</v>
+        <v>171</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>339</v>
+        <v>77</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B234" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="B234" s="1" t="s">
-        <v>513</v>
-      </c>
       <c r="C234" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>511</v>
+        <v>480</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>8</v>
+        <v>171</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>312</v>
+        <v>77</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B235" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="B235" s="1" t="s">
+      <c r="C235" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D235" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="C235" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D235" s="1" t="s">
-        <v>511</v>
-      </c>
       <c r="E235" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>312</v>
+        <v>343</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -7077,13 +7087,13 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -7097,13 +7107,13 @@
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>5</v>
+        <v>314</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -7117,13 +7127,13 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>94</v>
+        <v>314</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -7137,13 +7147,13 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -7157,13 +7167,13 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -7177,13 +7187,13 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>249</v>
+        <v>96</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -7197,13 +7207,13 @@
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>135</v>
+        <v>38</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>249</v>
+        <v>96</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -7217,13 +7227,13 @@
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>144</v>
+        <v>70</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>312</v>
+        <v>251</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -7237,13 +7247,13 @@
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>312</v>
+        <v>251</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -7257,53 +7267,53 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>536</v>
+        <v>515</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>4</v>
+        <v>146</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>5</v>
+        <v>314</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="B246" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="B246" s="1" t="s">
-        <v>538</v>
-      </c>
       <c r="C246" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>536</v>
+        <v>515</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>8</v>
+        <v>157</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>5</v>
+        <v>314</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="B247" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="B247" s="1" t="s">
+      <c r="C247" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D247" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="C247" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D247" s="1" t="s">
-        <v>536</v>
-      </c>
       <c r="E247" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>312</v>
+        <v>5</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -7317,13 +7327,13 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>312</v>
+        <v>5</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -7337,13 +7347,13 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -7357,13 +7367,13 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>339</v>
+        <v>314</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -7377,13 +7387,13 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>77</v>
+        <v>314</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -7397,13 +7407,13 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>294</v>
+        <v>343</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7417,13 +7427,13 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>312</v>
+        <v>77</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -7437,13 +7447,13 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>135</v>
+        <v>38</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -7457,13 +7467,13 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>144</v>
+        <v>70</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>339</v>
+        <v>314</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -7477,13 +7487,13 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>312</v>
+        <v>296</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -7497,13 +7507,13 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>312</v>
+        <v>343</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -7517,13 +7527,13 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>77</v>
+        <v>314</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -7537,13 +7547,13 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>208</v>
+        <v>171</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -7557,13 +7567,13 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>312</v>
+        <v>96</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -7577,13 +7587,13 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>94</v>
+        <v>314</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -7597,33 +7607,33 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>571</v>
+        <v>540</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>4</v>
+        <v>219</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>312</v>
+        <v>96</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B263" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="B263" s="1" t="s">
+      <c r="C263" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D263" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="C263" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D263" s="1" t="s">
-        <v>571</v>
-      </c>
       <c r="E263" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>312</v>
+        <v>5</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -7637,13 +7647,13 @@
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -7657,13 +7667,13 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -7677,13 +7687,13 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -7697,13 +7707,13 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -7717,13 +7727,13 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>312</v>
+        <v>5</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -7737,13 +7747,13 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>312</v>
+        <v>5</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -7757,10 +7767,10 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>5</v>
@@ -7777,13 +7787,13 @@
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>5</v>
+        <v>314</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -7797,13 +7807,13 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>5</v>
+        <v>314</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -7817,10 +7827,10 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>77</v>
@@ -7837,10 +7847,10 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>77</v>
@@ -7863,7 +7873,7 @@
         <v>4</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>5</v>
+        <v>314</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -7883,7 +7893,7 @@
         <v>8</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -7903,7 +7913,7 @@
         <v>11</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -7923,15 +7933,15 @@
         <v>14</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>605</v>
+        <v>314</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="B279" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="B279" s="1" t="s">
-        <v>607</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>3</v>
@@ -7943,7 +7953,7 @@
         <v>18</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>312</v>
+        <v>607</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -7963,7 +7973,7 @@
         <v>32</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -7983,7 +7993,7 @@
         <v>35</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -8023,7 +8033,7 @@
         <v>70</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -8040,10 +8050,10 @@
         <v>598</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -8060,7 +8070,7 @@
         <v>598</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>5</v>
@@ -8080,7 +8090,7 @@
         <v>598</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>5</v>
@@ -8100,10 +8110,10 @@
         <v>598</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -8123,7 +8133,7 @@
         <v>4</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>94</v>
+        <v>314</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -8143,7 +8153,7 @@
         <v>8</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -8163,7 +8173,7 @@
         <v>11</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -8183,7 +8193,7 @@
         <v>14</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -8203,7 +8213,7 @@
         <v>18</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8223,7 +8233,7 @@
         <v>32</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8243,7 +8253,7 @@
         <v>35</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8300,7 +8310,7 @@
         <v>626</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F297" s="1" t="s">
         <v>5</v>
@@ -8320,7 +8330,7 @@
         <v>626</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F298" s="1" t="s">
         <v>5</v>
@@ -8340,10 +8350,10 @@
         <v>626</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8360,10 +8370,30 @@
         <v>626</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A301" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="B301" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="C301" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D301" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="E301" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F301" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
   </sheetData>

--- a/DND05S.xlsx
+++ b/DND05S.xlsx
@@ -667,7 +667,7 @@
     <t>20064413</t>
   </si>
   <si>
-    <t>ATCK JAZ1 S/CNTA 1.4</t>
+    <t>ATCK JAZ1 S/CNTA 1.3</t>
   </si>
   <si>
     <t>16</t>
@@ -676,19 +676,19 @@
     <t>20064414</t>
   </si>
   <si>
-    <t>ATTACK JAZ1 P/SGR1.4</t>
+    <t>ATTACK JAZ1 P/SGR1.3</t>
   </si>
   <si>
     <t>20130527</t>
   </si>
   <si>
-    <t>ATTACK DET+SF RB 1.4</t>
+    <t>ATTACK DET+SF RB 1.2</t>
   </si>
   <si>
     <t>20138108</t>
   </si>
   <si>
-    <t>JAZ 1 PRPL BLS 1.4KG</t>
+    <t>JAZ 1 PRPL BLS 1.2KG</t>
   </si>
   <si>
     <t>20071827</t>
@@ -715,7 +715,7 @@
     <t>20074992</t>
   </si>
   <si>
-    <t>BUKRIM OXY/K VIOL700</t>
+    <t>BUKRIM OXY/K VIOL650</t>
   </si>
   <si>
     <t>20119238</t>
@@ -7830,7 +7830,7 @@
         <v>573</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>77</v>
@@ -7850,7 +7850,7 @@
         <v>573</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>77</v>

--- a/DND05S.xlsx
+++ b/DND05S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="651">
   <si>
     <t/>
   </si>
@@ -154,7 +154,7 @@
     <t>20140001</t>
   </si>
   <si>
-    <t>RINSO PURE LIQ 510G</t>
+    <t>RNSO PURE LIQ 510 G</t>
   </si>
   <si>
     <t>20133212</t>
@@ -178,25 +178,25 @@
     <t>20137793</t>
   </si>
   <si>
-    <t>RINSO ROSE FRESH 510</t>
+    <t>RNSO ROSE FRS 510 G</t>
   </si>
   <si>
     <t>20054750</t>
   </si>
   <si>
-    <t>RNSO+ML LIQ PRFM 510</t>
+    <t>RNSO LIQ PRFM 510 G</t>
   </si>
   <si>
     <t>20093188</t>
   </si>
   <si>
-    <t>RINSO MLTO GLD LQ510</t>
+    <t>RNSO MLT G.LQ 510 G</t>
   </si>
   <si>
     <t>20122879</t>
   </si>
   <si>
-    <t>RNSO MLTO KRN STR510</t>
+    <t>RNSO MLT K STR 510 G</t>
   </si>
   <si>
     <t>20093627</t>
@@ -247,12 +247,6 @@
     <t>RT,(E-1.5B)</t>
   </si>
   <si>
-    <t>20132442</t>
-  </si>
-  <si>
-    <t>SYANG LIQ ORIGNAL700</t>
-  </si>
-  <si>
     <t>20135849</t>
   </si>
   <si>
@@ -1243,7 +1237,7 @@
     <t>20090067</t>
   </si>
   <si>
-    <t>SNLGHT MINT A.BAU600</t>
+    <t>SNLGHT M A.BAU 600 G</t>
   </si>
   <si>
     <t>28</t>
@@ -1252,7 +1246,7 @@
     <t>20086172</t>
   </si>
   <si>
-    <t>SNLIGHT MND.ORGE 600</t>
+    <t>SNLGHT M.ORGE 600 G</t>
   </si>
   <si>
     <t>20112492</t>
@@ -1309,7 +1303,7 @@
     <t>10005482</t>
   </si>
   <si>
-    <t>SNLIGHT LIME PCH 660</t>
+    <t>SNLGHT LME PCH 660 G</t>
   </si>
   <si>
     <t>20143091</t>
@@ -1321,13 +1315,13 @@
     <t>20135144</t>
   </si>
   <si>
-    <t>SNLGHT BIO NATURE600</t>
+    <t>SNLGHT B.NTURE 600 G</t>
   </si>
   <si>
     <t>10013205</t>
   </si>
   <si>
-    <t>SUNLIGHT J/NIPIS.750</t>
+    <t>SNLGHT J/NIPIS 675 G</t>
   </si>
   <si>
     <t>30</t>
@@ -1336,13 +1330,13 @@
     <t>20139947</t>
   </si>
   <si>
-    <t>SNLGHT BIO BLBR 675G</t>
+    <t>SNLGHT B.BLBR 675 G</t>
   </si>
   <si>
     <t>20139948</t>
   </si>
   <si>
-    <t>SNLGHT BERY&amp;LIME 675</t>
+    <t>SNLGHT BRY&amp;LME 675 G</t>
   </si>
   <si>
     <t>20142277</t>
@@ -1744,19 +1738,19 @@
     <t>20139144</t>
   </si>
   <si>
-    <t>HIT XPRES PINK BL.35</t>
+    <t>HIT XPRS P.BLO 35 ML</t>
   </si>
   <si>
     <t>20131161</t>
   </si>
   <si>
-    <t>HIT REF XPRES APLE35</t>
+    <t>HIT RF XPRS A 35 ML</t>
   </si>
   <si>
     <t>20095744</t>
   </si>
   <si>
-    <t>HIT REF EXPRT FRS 35</t>
+    <t>HIT RF EXT FRS 35 ML</t>
   </si>
   <si>
     <t>20023870</t>
@@ -1789,6 +1783,12 @@
     <t>HIT MAT ELECTRK 48'S</t>
   </si>
   <si>
+    <t>20008742</t>
+  </si>
+  <si>
+    <t>VAPE MAT BUBBLE 60'S</t>
+  </si>
+  <si>
     <t>20030445</t>
   </si>
   <si>
@@ -1846,7 +1846,7 @@
     <t>20071775</t>
   </si>
   <si>
-    <t>BAYGON FLO.GRDN 675</t>
+    <t>BAYGON FLO.GN 675 ML</t>
   </si>
   <si>
     <t>20139154</t>
@@ -1888,7 +1888,7 @@
     <t>10003272</t>
   </si>
   <si>
-    <t>BAYGON SPRY CITRS675</t>
+    <t>BAYGON SPR CT 675 ML</t>
   </si>
   <si>
     <t>37</t>
@@ -1964,15 +1964,6 @@
   </si>
   <si>
     <t>VAPE MILK TEA 600ML</t>
-  </si>
-  <si>
-    <t>20078241</t>
-  </si>
-  <si>
-    <t>SOFFELL LOT.APEL 60G</t>
-  </si>
-  <si>
-    <t>999</t>
   </si>
 </sst>
 </file>
@@ -2365,14 +2356,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F301"/>
+  <dimension ref="A1:F300"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="5" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
+    <col min="4" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3030,10 +3020,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>77</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -3050,7 +3040,7 @@
         <v>18</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>15</v>
@@ -3070,10 +3060,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -3087,10 +3077,10 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -3110,7 +3100,7 @@
         <v>32</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -3130,7 +3120,7 @@
         <v>32</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -3150,7 +3140,7 @@
         <v>32</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -3170,18 +3160,18 @@
         <v>32</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>5</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -3190,10 +3180,10 @@
         <v>32</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -3210,7 +3200,7 @@
         <v>32</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -3230,7 +3220,7 @@
         <v>32</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -3247,10 +3237,10 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -3270,7 +3260,7 @@
         <v>35</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -3290,10 +3280,10 @@
         <v>35</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>5</v>
+        <v>94</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -3310,10 +3300,10 @@
         <v>35</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -3330,7 +3320,7 @@
         <v>35</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -3350,7 +3340,7 @@
         <v>35</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -3370,7 +3360,7 @@
         <v>35</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -3390,7 +3380,7 @@
         <v>35</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -3407,10 +3397,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -3430,7 +3420,7 @@
         <v>38</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -3450,10 +3440,10 @@
         <v>38</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>5</v>
+        <v>94</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -3470,10 +3460,10 @@
         <v>38</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3487,13 +3477,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3510,7 +3500,7 @@
         <v>70</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -3530,7 +3520,7 @@
         <v>70</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -3550,7 +3540,7 @@
         <v>70</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -3567,10 +3557,10 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -3578,22 +3568,22 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="E61" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>5</v>
+        <v>94</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -3607,13 +3597,13 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -3627,10 +3617,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -3647,10 +3637,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3658,19 +3648,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="E65" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -3687,10 +3677,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3707,10 +3697,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -3727,10 +3717,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -3747,10 +3737,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -3758,22 +3748,22 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="E70" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3787,33 +3777,33 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>15</v>
+        <v>160</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>162</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3827,13 +3817,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -3847,13 +3837,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3867,30 +3857,30 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="E76" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -3907,10 +3897,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3927,10 +3917,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3947,10 +3937,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3967,10 +3957,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3987,10 +3977,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -4007,10 +3997,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -4027,13 +4017,13 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -4047,33 +4037,33 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>21</v>
+        <v>189</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="E85" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -4087,10 +4077,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>15</v>
@@ -4107,10 +4097,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>15</v>
@@ -4127,10 +4117,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>15</v>
@@ -4147,13 +4137,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>15</v>
+        <v>189</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -4167,13 +4157,13 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -4187,13 +4177,13 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -4207,13 +4197,13 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -4227,30 +4217,30 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="E94" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>21</v>
@@ -4267,10 +4257,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>21</v>
@@ -4287,10 +4277,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>21</v>
@@ -4307,33 +4297,33 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="E98" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -4347,13 +4337,13 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -4367,13 +4357,13 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -4387,30 +4377,30 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>96</v>
+        <v>21</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="E102" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>21</v>
@@ -4427,10 +4417,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>21</v>
@@ -4447,13 +4437,13 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -4467,13 +4457,13 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>5</v>
+        <v>94</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -4487,33 +4477,33 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>96</v>
+        <v>15</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="E107" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -4527,10 +4517,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>21</v>
@@ -4547,13 +4537,13 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4567,10 +4557,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -4587,33 +4577,33 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>5</v>
+        <v>249</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="E112" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>251</v>
+        <v>21</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -4627,13 +4617,13 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -4647,10 +4637,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -4667,10 +4657,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -4687,13 +4677,13 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>5</v>
+        <v>94</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -4707,13 +4697,13 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4727,13 +4717,13 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4747,13 +4737,13 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4767,13 +4757,13 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4787,30 +4777,30 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>137</v>
+        <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>272</v>
-      </c>
       <c r="E122" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -4827,10 +4817,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -4847,10 +4837,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -4867,10 +4857,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -4887,10 +4877,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -4907,10 +4897,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4927,10 +4917,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4947,30 +4937,30 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="E130" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>21</v>
@@ -4987,13 +4977,13 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>21</v>
+        <v>160</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -5007,33 +4997,33 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>162</v>
+        <v>294</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F133" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -5047,13 +5037,13 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>296</v>
+        <v>21</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -5067,10 +5057,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>21</v>
@@ -5087,10 +5077,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>21</v>
@@ -5107,13 +5097,13 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -5127,30 +5117,30 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="E139" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -5167,33 +5157,33 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>5</v>
+        <v>312</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F141" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F141" s="1" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -5207,13 +5197,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -5227,13 +5217,13 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>314</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -5247,13 +5237,13 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>5</v>
+        <v>160</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -5267,13 +5257,13 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>162</v>
+        <v>94</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -5287,30 +5277,30 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>96</v>
+        <v>21</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>327</v>
-      </c>
       <c r="E147" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>21</v>
@@ -5327,10 +5317,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>21</v>
@@ -5347,10 +5337,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>21</v>
@@ -5367,13 +5357,13 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -5387,10 +5377,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -5407,13 +5397,13 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>5</v>
+        <v>94</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -5427,33 +5417,33 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>96</v>
+        <v>341</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>342</v>
-      </c>
       <c r="E154" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>343</v>
+        <v>294</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -5467,13 +5457,13 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>296</v>
+        <v>21</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -5487,10 +5477,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>21</v>
@@ -5507,13 +5497,13 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -5527,13 +5517,13 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>15</v>
+        <v>160</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -5547,13 +5537,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -5567,13 +5557,13 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -5587,13 +5577,13 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -5607,33 +5597,33 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="E163" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -5647,13 +5637,13 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>162</v>
+        <v>94</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -5667,13 +5657,13 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -5687,10 +5677,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5707,10 +5697,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5727,10 +5717,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5747,10 +5737,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5767,10 +5757,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5778,22 +5768,22 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>379</v>
-      </c>
       <c r="E171" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5807,13 +5797,13 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5827,10 +5817,10 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5847,10 +5837,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5867,10 +5857,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5887,13 +5877,13 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5907,30 +5897,30 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="E178" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5947,10 +5937,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5967,10 +5957,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5987,10 +5977,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -6007,10 +5997,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -6027,10 +6017,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -6047,13 +6037,13 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -6067,33 +6057,33 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>411</v>
-      </c>
       <c r="E186" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>21</v>
+        <v>249</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -6107,13 +6097,13 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>251</v>
+        <v>21</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -6127,13 +6117,13 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6147,13 +6137,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -6167,13 +6157,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>21</v>
+        <v>160</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -6187,13 +6177,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -6207,13 +6197,13 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -6227,30 +6217,30 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>411</v>
+        <v>426</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>162</v>
+        <v>21</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D194" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B194" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D194" s="1" t="s">
-        <v>428</v>
-      </c>
       <c r="E194" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>21</v>
@@ -6267,10 +6257,10 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>21</v>
@@ -6287,13 +6277,13 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -6307,13 +6297,13 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -6327,10 +6317,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>21</v>
@@ -6338,19 +6328,19 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D199" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="B199" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="C199" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D199" s="1" t="s">
-        <v>439</v>
-      </c>
       <c r="E199" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>21</v>
@@ -6367,10 +6357,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>21</v>
@@ -6387,13 +6377,13 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -6407,13 +6397,13 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -6427,13 +6417,13 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>77</v>
+        <v>312</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -6447,13 +6437,13 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>314</v>
+        <v>341</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -6467,13 +6457,13 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -6487,13 +6477,13 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>343</v>
+        <v>94</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -6507,30 +6497,30 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>439</v>
+        <v>456</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>137</v>
+        <v>4</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>96</v>
+        <v>21</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="B208" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>458</v>
-      </c>
       <c r="E208" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>21</v>
@@ -6547,10 +6537,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>21</v>
@@ -6567,13 +6557,13 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -6587,13 +6577,13 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>77</v>
+        <v>294</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -6607,13 +6597,13 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>296</v>
+        <v>5</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -6627,13 +6617,13 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>5</v>
+        <v>160</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -6647,33 +6637,33 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>162</v>
+        <v>471</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>473</v>
+        <v>312</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -6687,13 +6677,13 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>314</v>
+        <v>471</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -6707,33 +6697,33 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>458</v>
+        <v>478</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>137</v>
+        <v>4</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>473</v>
+        <v>77</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D218" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="B218" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="C218" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D218" s="1" t="s">
-        <v>480</v>
-      </c>
       <c r="E218" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>77</v>
+        <v>294</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -6747,13 +6737,13 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -6767,13 +6757,13 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -6787,13 +6777,13 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -6807,13 +6797,13 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -6827,13 +6817,13 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>296</v>
+        <v>77</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -6847,10 +6837,10 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F224" s="1" t="s">
         <v>77</v>
@@ -6867,10 +6857,10 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F225" s="1" t="s">
         <v>77</v>
@@ -6887,13 +6877,13 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -6907,10 +6897,10 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F227" s="1" t="s">
         <v>5</v>
@@ -6927,10 +6917,10 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="F228" s="1" t="s">
         <v>5</v>
@@ -6947,13 +6937,13 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>5</v>
+        <v>294</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -6967,13 +6957,13 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -6987,13 +6977,13 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -7007,13 +6997,13 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>296</v>
+        <v>77</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -7027,10 +7017,10 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>77</v>
@@ -7047,33 +7037,33 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>480</v>
+        <v>513</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>171</v>
+        <v>4</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>77</v>
+        <v>341</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D235" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="B235" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="C235" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D235" s="1" t="s">
-        <v>515</v>
-      </c>
       <c r="E235" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>343</v>
+        <v>312</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -7087,13 +7077,13 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -7107,13 +7097,13 @@
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -7127,13 +7117,13 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>314</v>
+        <v>5</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -7147,13 +7137,13 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>5</v>
+        <v>94</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -7167,13 +7157,13 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -7187,13 +7177,13 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -7207,13 +7197,13 @@
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>96</v>
+        <v>249</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -7227,13 +7217,13 @@
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -7247,13 +7237,13 @@
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>251</v>
+        <v>312</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -7267,13 +7257,13 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -7287,30 +7277,30 @@
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>515</v>
+        <v>538</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>157</v>
+        <v>4</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>314</v>
+        <v>5</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D247" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="B247" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="C247" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D247" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="E247" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>5</v>
@@ -7327,13 +7317,13 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>5</v>
+        <v>312</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -7347,13 +7337,13 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -7367,13 +7357,13 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -7387,13 +7377,13 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>314</v>
+        <v>341</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -7407,13 +7397,13 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>343</v>
+        <v>77</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7427,13 +7417,13 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>77</v>
+        <v>294</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -7447,13 +7437,13 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -7467,13 +7457,13 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -7487,13 +7477,13 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>296</v>
+        <v>341</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -7507,13 +7497,13 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>343</v>
+        <v>312</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -7527,13 +7517,13 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>314</v>
+        <v>77</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -7547,13 +7537,13 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -7567,13 +7557,13 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>96</v>
+        <v>312</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -7587,13 +7577,13 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>314</v>
+        <v>94</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -7607,33 +7597,33 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>540</v>
+        <v>571</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>219</v>
+        <v>4</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D263" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="B263" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="C263" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D263" s="1" t="s">
-        <v>573</v>
-      </c>
       <c r="E263" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>5</v>
+        <v>312</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -7647,13 +7637,13 @@
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -7667,13 +7657,13 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -7687,13 +7677,13 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -7707,13 +7697,13 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>314</v>
+        <v>5</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -7727,10 +7717,10 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>5</v>
@@ -7747,10 +7737,10 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>5</v>
@@ -7767,13 +7757,13 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>5</v>
+        <v>312</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -7787,13 +7777,13 @@
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -7807,13 +7797,13 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -7827,10 +7817,10 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>77</v>
@@ -7847,10 +7837,10 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>77</v>
@@ -7873,7 +7863,7 @@
         <v>4</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -7893,7 +7883,7 @@
         <v>8</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -7913,7 +7903,7 @@
         <v>11</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -7933,7 +7923,7 @@
         <v>14</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -7973,7 +7963,7 @@
         <v>32</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -7993,7 +7983,7 @@
         <v>35</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -8033,7 +8023,7 @@
         <v>70</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -8050,10 +8040,10 @@
         <v>598</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -8070,7 +8060,7 @@
         <v>598</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>5</v>
@@ -8090,7 +8080,7 @@
         <v>598</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>5</v>
@@ -8110,10 +8100,10 @@
         <v>598</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -8133,7 +8123,7 @@
         <v>4</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -8153,7 +8143,7 @@
         <v>8</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -8173,7 +8163,7 @@
         <v>11</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -8193,7 +8183,7 @@
         <v>14</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -8213,7 +8203,7 @@
         <v>18</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8233,7 +8223,7 @@
         <v>32</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8253,7 +8243,7 @@
         <v>35</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8310,7 +8300,7 @@
         <v>626</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F297" s="1" t="s">
         <v>5</v>
@@ -8330,7 +8320,7 @@
         <v>626</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F298" s="1" t="s">
         <v>5</v>
@@ -8350,10 +8340,10 @@
         <v>626</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8370,30 +8360,10 @@
         <v>626</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A301" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="B301" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="C301" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D301" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="E301" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F301" s="1" t="s">
-        <v>314</v>
       </c>
     </row>
   </sheetData>
